--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -728,7 +728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -805,13 +805,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1931,16 +1934,32 @@
           <t>系明文'保证为录取学生提供资助';20 hr/wk=$14,625/yr+100% 学费;10 hr=$7,325+75% 学费;医保补贴</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(推断):terminal MA按项目整体录取,官网未见套磁要求;可先邮件 jmthoma4@olemiss.edu 了解方向</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>⚠️ 未明确;联系 jmthoma4@olemiss.edu</t>
         </is>
       </c>
       <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>不需要(研究生院页面将 Sociology MA 列为不要求 GRE/GMAT 的项目,页面表述略含糊)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院称所有国际生硕博申请须提交 TOEFL(最低79,2年内有效),未见美国学位豁免条款,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>jmthoma4@olemiss.edu(社会学研究生项目联系人);gschool@olemiss.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>https://olemiss.edu/socanth/academics/ma-sociology/</t>
@@ -2291,7 +2310,11 @@
 所有获得助理职位录用通知的申请者面试后将收到正式录用通知书。</t>
         </is>
       </c>
-      <c r="F21" s="12" t="n"/>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>必须:需与HES内有导师的实验室联系并获得临时录取(provisional acceptance)才能被录取</t>
+        </is>
+      </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
           <t>与HES内有导师的具体实验室联系并临时录取
@@ -2311,8 +2334,16 @@
 8月31日春季入学。</t>
         </is>
       </c>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 系官网未提及GRE,疑似不需要,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J21" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院对近期获得美国大学学位者豁免TOEFL/IELTS);否则 TOEFL ≥80,IELTS ≥6.5</t>
+        </is>
+      </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
           <t>heather.leach@colostate.edu
@@ -2379,7 +2410,11 @@
           <t>可选的</t>
         </is>
       </c>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="27" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院对5年内获美国学位者豁免);但当TA需TOEFL口语≥24(2026/1/21后新版口语≥5.0)或通过校内口语评估(EPI)</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2419,15 +2454,31 @@
           <t>我们是一个以导师为驱动的项目，申请我们的研究生项目前，与潜在的导师建立联系非常重要。与导师的联系至关重要，因为他们会支持你的申请并在申请过程中为你争取权益。通常被录取的学生已经与他们希望共事的教师进行了交流并建立了一定的关系。</t>
         </is>
       </c>
-      <c r="G23" s="12" t="n"/>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>可以申请(多数学生获TA/RA,全额助教含学费减免+津贴)。研究生院最低GPA 3.0(低于3.0不审);需500字内个人陈述、研究陈述(thesis)、3封推荐信</t>
+        </is>
+      </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
           <t>硕士的秋季申请截止日期是12月1日。</t>
         </is>
       </c>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
+      <c r="I23" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ 系官网未见GRE要求,疑似不需要,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J23" s="27" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:2年内获美国区域认证大学学士及以上学位可豁免,需申请后提交豁免表);否则 TOEFL ≥80,IELTS ≥6.5,Duolingo ≥110</t>
+        </is>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>hkgradprogram@utah.edu(H&amp;K研究生项目办公室,项目经理 Andrea Moss)</t>
+        </is>
+      </c>
       <c r="L23" s="15" t="inlineStr">
         <is>
           <t>https://health.utah.edu/health-kinesiology/graduate-programs/faq</t>
@@ -2460,13 +2511,29 @@
           <t>运动机能与健康部门为研究生提供多项机会（~7个） 每年为校内硕士生提供助教职位，传统两年制 程序。在线教育或快速入门项目的硕士生通常都是 未被考虑申请研究生助理职位。大多数助教项目覆盖所有学费 以及学年内支付学费和津贴 （9月至5月）。如需申请研究生助理职位，请填写 K&amp;H补充申请表，一旦你开始申请，将会发送给你 怀俄明大学申请。</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="26" t="n">
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>必须:须先找到研究生导师,建议9月至次年1月联系潜在导师,否则不太可能被录取或获GA推荐</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>可以申请(校内两年制硕士每年约7个TA名额,需填K&amp;H补充申请表)。本科最好为健康/运动科学/运动机能学/体育;其他专业可临时录取并补修人体解剖、人体系统生理学、运动生理学等;GPA≥3.0,3封推荐信</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
         <v>46054</v>
       </c>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="I24" s="27" t="inlineStr">
+        <is>
+          <t>可选(不要求,可提交以增强申请)</t>
+        </is>
+      </c>
+      <c r="J24" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:非英语母语者需 TOEFL ≥76(iBT)/IELTS ≥6.5;研究生院未明示美国学位豁免(各系页面说法不一),建议邮件确认;当TA另需通过 OPIc 口语考试(可由导师申请豁免)</t>
+        </is>
+      </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
           <t>Division of Kinesiology and Health
@@ -2508,16 +2575,36 @@
           <t>merit 50–100%学费+REAL带薪工作+APE award;优先截止前自动考虑</t>
         </is>
       </c>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(SOPHAS申请),个人陈述可写感兴趣方向</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr">
+        <is>
+          <t>可以申请(优先截止前完成申请自动考虑merit奖学金)。MPH无特定本科专业要求;Biostatistics等方向可能有数学先修,建议查看具体系要求</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>奖学金优先 2027/1/5;国际生建议 2027/5/1 前;最终 2027/7/15</t>
+        </is>
+      </c>
+      <c r="I25" s="29" t="inlineStr">
+        <is>
+          <t>不需要(多数项目不考虑GRE;Biostatistics 方向为可选)</t>
+        </is>
+      </c>
+      <c r="J25" s="29" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:在美国院校完成学位可豁免);否则 TOEFL iBT ≥79-80,IELTS ≥6</t>
+        </is>
+      </c>
+      <c r="K25" s="29" t="inlineStr">
+        <is>
+          <t>sphadmissions@emory.edu(Rollins 招生办公室,404-727-3956)</t>
+        </is>
+      </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
           <t>https://sph.emory.edu/admissions/tuition-funding/scholarships</t>
@@ -2666,32 +2753,32 @@
           <t>25% GRA 为主:月薪+学费+医保;~70% MHA 生获系资助</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取(每年20–25人),滚动审核,有线上/线下面试</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>可以申请(⚠️ 原备注:国际生能否获资助未明确)。先修:各专业均可,无指定先修课;最低GPA 3.0;3封推荐信(建议≥1学术+≥1职业);医疗相关经历非必需但加分</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>奖学金/助研优先 2026/12/1;最终 2027/3/1(⚠️ 另一官网页写5/1,之后视名额滚动)(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>不需要</t>
         </is>
       </c>
-      <c r="J28" s="28" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>否(美国认证院校学位豁免);否则 TOEFL iBT 建议 ≥100</t>
         </is>
       </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="K28" s="26" t="inlineStr">
         <is>
           <t>karen-hammar@uiowa.edu(MHA项目主任 Karen Hammar)</t>
         </is>
@@ -2728,7 +2815,7 @@
           <t>'多数 MS 生获 2 年支持';50% TA/RA + 硕士 fellowship</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>⚠️ 建议:资助为TA/RA,建议提前联系方向匹配的教师(官网未明确要求)</t>
         </is>
@@ -2738,22 +2825,22 @@
           <t>✅ 国际生可持(教学需英语)</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>2027/2/1(仅秋季入学)</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="I29" s="26" t="inlineStr">
         <is>
           <t>可选(推荐但不要求)</t>
         </is>
       </c>
-      <c r="J29" s="28" t="inlineStr">
+      <c r="J29" s="26" t="inlineStr">
         <is>
           <t>是:SIU仅豁免美国硕士学位,美本不豁免;TOEFL iBT ≥80 / IELTS ≥6.5;当TA需通过ITA Interview</t>
         </is>
       </c>
-      <c r="K29" s="28" t="inlineStr">
+      <c r="K29" s="26" t="inlineStr">
         <is>
           <t>geog@siu.edu(地理系);gradschl@siu.edu(研究生院)</t>
         </is>
@@ -2790,7 +2877,7 @@
           <t>TA/RA:学费奖学金+津贴(15-20 hr);Graduate Recruitment Scholarship(5 hr)覆盖大部分学费;1-15 截止</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>⚠️ 建议:可先联系研究生主任 Dr. Tom Smucker 了解方向匹配;官网未要求套磁</t>
         </is>
@@ -2800,17 +2887,17 @@
           <t>✅ 明文'国内外申请者按 merit 同等考虑'</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr">
         <is>
           <t>资助考虑截止 2027/1/15(⚠️ 官网为资助全面考虑日,非明确录取截止,建议1/15前提交)</t>
         </is>
       </c>
-      <c r="I30" s="28" t="inlineStr">
+      <c r="I30" s="26" t="inlineStr">
         <is>
           <t>不需要</t>
         </is>
       </c>
-      <c r="J30" s="28" t="inlineStr">
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>⚠️ 不明确:官网要求非英语母语者提交 TOEFL/IELTS,未见美国学位豁免说明(⚠️ 第三方:TOEFL 80 / IELTS 6.5 / Duolingo 115),建议邮件确认</t>
         </is>
@@ -2848,7 +2935,7 @@
           <t>'All applicants, domestic and international, are considered for multi-year guaranteed funding packages…typically 2 years for MS';TA含stipend+医保+学费减免</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>不需要:国内外申请者统一考虑多年资助包;⚠️ 个人陈述写明方向/教授,建议提前联系潜在导师</t>
         </is>
@@ -2858,22 +2945,22 @@
           <t>可</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>2026/12/15(仅秋季入学;⚠️ 日期见于Cartography/GIS thesis页,MS Geography同期但未单独核实)</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I31" s="26" t="inlineStr">
         <is>
           <t>不接受:系里自2020秋起不要求也不考虑GRE</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>⚠️ 大概率否:要求母语非英语或本科非英语授课者提交 TOEFL/IELTS,美本英语授课通常可豁免,建议确认</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr">
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>gradschool@geography.wisc.edu(研究生项目主任/招生)</t>
         </is>
@@ -2910,7 +2997,7 @@
           <t>'strives to provide support for all students who require it'(TA/RA),MA资助2年,TA学费减免</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="26" t="inlineStr">
         <is>
           <t>强烈建议:官网称联系潜在导师是关键步骤,录取看 merit 与教师研究匹配</t>
         </is>
@@ -2920,12 +3007,12 @@
           <t>未说明</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H32" s="26" t="inlineStr">
         <is>
           <t>研究生院资助/fellowship 2026/12/12;系资助 2027/1/10(按往年周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I32" s="26" t="inlineStr">
         <is>
           <t>不需要(研究生院页面;⚠️ Peterson's 仍列GRE,可能过时)</t>
         </is>
@@ -2964,22 +3051,22 @@
           <t>'Our small, tightly-knit cohorts are mostly fully funded and receive stipend and tuition remission'</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="26" t="inlineStr">
         <is>
           <t>必须:最终录取需一名教师同意指导;官网强烈建议申请前联系教师,资助多来自导师科研经费(GRA)</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="26" t="inlineStr">
         <is>
           <t>可以申请(原备注:未说明)。先修:欢迎非地理专业背景;MA需外语能力,MS不需;需2–3页陈述(写明意向导师及是否已联系)、3封推荐信</t>
         </is>
       </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>资助优先 2027/1/15;秋季最终 2027/5/1(⚠️ Peterson's 称国际生1/15)</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="I33" s="26" t="inlineStr">
         <is>
           <t>⚠️ 不需要(官网未列GRE;Peterson's 称需GRE≥297,可能过时)</t>
         </is>
@@ -3018,16 +3105,36 @@
           <t>'Assistantships include a tuition waiver and a monthly stipend';'TA for M.S. students are typically funded for two years'</t>
         </is>
       </c>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 建议:官网未明确要求套磁;可先联系研究生事务教师 Walker Ashley 了解导师/助教情况</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(助教含学费减免+月津贴,硕士通常资助两年)。优先 Atmospheric Science/Earth Science/Geography/Geology 或相关专业,其他专业有大量相关课程也可;需2封推荐信+CV</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>秋季资助考虑 2027/2/1(春季 10/1);⚠️ 研究生院通用截止 秋季 8/1(国际生 5/1),以系为准</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院认可在美国认证院校获得的学士及以上学位为英语能力证明);否则 TOEFL ≥80,IELTS ≥6.5,PTE ≥53</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>washley@niu.edu(研究生事务/指导 Walker Ashley);askeae@niu.edu(系通用邮箱)</t>
+        </is>
+      </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
           <t>https://www.niu.edu/earth-atmosphere-environment/graduate/index.shtml</t>
@@ -3060,16 +3167,36 @@
           <t>年 &gt;$40 万 merit 支持;~60% 入学生获 offer;1/4 时 GA=$5,710/学期+全额学费减免;12-15 优先</t>
         </is>
       </c>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>✅ 明文'国内外申请者自动考虑'</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,无需提前联系导师</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(明文国内外申请者自动考虑merit资助;约60%入学生获offer)。⚠️ 官网未见特定本科专业/先修课要求;需满足研究生院GPA要求(通常最后60学分≥3.0)</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>资助优先 2026/12/15;最终 2027/1/15(申请窗口 2026/9/15 开放;2月底出结果)</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>不接受(系明确不要求也不审阅GRE成绩)</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院对5年内获美国学位者豁免);当TA需TOEFL口语达标(新版≥5.0)或通过校内口语评估</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>agreen4@illinois.edu(Andrew Greenlee 教授,MUP申请咨询);jakowal@illinois.edu(Jennifer Kowalski)</t>
+        </is>
+      </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
           <t>https://urban.illinois.edu/programs-applying/financial-aid/</t>
@@ -3102,16 +3229,36 @@
           <t>'所有 assistant 工作 20 hr/wk 换津贴+9 学分学费减免';项目主任任命;'非常成功'安置学生</t>
         </is>
       </c>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>必须:申请时需在系内选择1-2名教师作为潜在导师;建议提前联系</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(助教20小时/周换津贴+学费减免)。先修:需修过部分本科心理学课程,至少1门统计和1门研究方法;需CV、个人陈述(研究兴趣)、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H36" s="26" t="inlineStr">
+        <is>
+          <t>全面考虑 2027/1/10(含推荐信);最终 2027/3/1;2月下旬面试(按2026周期日期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>可选(Applied Research/Experimental/Quantitative 方向可选;Behavior Analysis 方向不需要)</t>
+        </is>
+      </c>
+      <c r="J36" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院目录明文美国认证院校学士及以上学位成绩单可满足英语要求);否则 TOEFL iBT ≥80(2026/1/21后新版≥4),IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>leventbc@jmu.edu(⚠️ 2026秋目录所列项目主任 Brian Leventhal,来源不一致);研究生心理学系电话 540-568-6439</t>
+        </is>
+      </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
           <t>https://www.jmu.edu/chbs/gradpsyc/psycsciences/assistantships.shtml</t>
@@ -3144,16 +3291,36 @@
           <t>'系向一年级学生授予 GA':月薪+秋春夏学费减免;Berk 发展心理 fellowship(2 年级)</t>
         </is>
       </c>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>✅ 明文'符合美国移民法就业资格即可'</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(推断):官网未提及需提前联系导师,按项目整体录取;可联系发展心理方向协调员了解</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(明文符合美国移民法就业资格即可获GA;TA另需TOEFL口语≥26)。先修:心理学或相关专业(如HDFS、教育心理);建议统计+研究方法合计≥6学分及1门人类发展课程</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>秋季 2026/12/1(仅秋季入学)</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>不需要(不用于评估;可提交以证明数学能力)</t>
+        </is>
+      </c>
+      <c r="J37" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:学校国际招生页仅列英语国家豁免,未见美国学位豁免明文;TOEFL iBT ≥79-81,IELTS ≥6.5;当TA需TOEFL口语≥26(州法要求,即使录取豁免也需满足)。建议邮件 InternationalAdmissions@IllinoisState.edu 确认</t>
+        </is>
+      </c>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>ljfinan@IllinoisState.edu(发展心理学研究生协调员 Laura Finan);hdeland@IllinoisState.edu(研究生项目办公室经理)</t>
+        </is>
+      </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
           <t>https://psychology.illinoisstate.edu/academics/scholarships/</t>
@@ -3480,29 +3647,29 @@
           <t>'Approximately eighty percent of our master's students receive financial assistance';奖学金仅覆盖学费,无stipend</t>
         </is>
       </c>
-      <c r="F45" s="28" t="inlineStr">
+      <c r="F45" s="26" t="inlineStr">
         <is>
           <t>MEM: 不需要:按项目整体录取,陈述中可写感兴趣的教授
 MESc: 必须:研究型学位,申请前需联系导师并列出意向教师(⚠️目录称需导师出具同意信)</t>
         </is>
       </c>
-      <c r="G45" s="28" t="inlineStr">
+      <c r="G45" s="26" t="inlineStr">
         <is>
           <t>可以申请(国际生可获YSE奖学金,约80%硕士生获资助,仅抵学费)。无硬性先修课和最低GPA;强烈建议修过生态学/生态系统、自然科学、社会科学、微观经济学和统计学;MEM入学时需具备上述基础(统计可修学院提供的非学分预备课)。</t>
         </is>
       </c>
       <c r="H45" s="12" t="n"/>
-      <c r="I45" s="28" t="inlineStr">
+      <c r="I45" s="26" t="inlineStr">
         <is>
           <t>可选(GRE/GMAT/LSAT 均可选)</t>
         </is>
       </c>
-      <c r="J45" s="28" t="inlineStr">
+      <c r="J45" s="26" t="inlineStr">
         <is>
           <t>否(美国学位豁免:本科全程在英语授课院校可申请豁免);否则需 TOEFL iBT ≥100 / IELTS ≥7.0(单项≥6.5),不接受 Duolingo</t>
         </is>
       </c>
-      <c r="K45" s="28" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>admissions.yse@yale.edu(YSE招生与资助办公室);⚠️ quetcy.maldonado@yale.edu(硕士项目协调员,需确认是否在任)</t>
         </is>
@@ -3539,28 +3706,28 @@
           <t>'tries very hard to make sure all graduate students have financial support in the form of Graduate Assistantships';GRA/GTA享州内学费,GTA另有学费减免;GTA考虑截止3/1</t>
         </is>
       </c>
-      <c r="F46" s="28" t="inlineStr">
+      <c r="F46" s="26" t="inlineStr">
         <is>
           <t>必须:论文型MS须有教师同意担任导师才会被录取,资助多由导师的GRA经费提供</t>
         </is>
       </c>
-      <c r="G46" s="28" t="inlineStr">
+      <c r="G46" s="26" t="inlineStr">
         <is>
           <t>可以申请(⚠️ 国际生能否获GRA/GTA未见明文限制)。⚠️ 需理科相关本科背景(在线PSM明确要求);最近两年GPA≥3.0;3封推荐信(不得来自意向导师或委员会成员);个人陈述写研究兴趣与职业目标;录取前须有导师同意。</t>
         </is>
       </c>
-      <c r="H46" s="28" t="inlineStr">
+      <c r="H46" s="26" t="inlineStr">
         <is>
           <t>⚠️ LRES申请页:秋季 6/15、春季 11/1(可能针对在线Professional MS);论文型MS视导师经费录取,GTA考虑截止 3/1;建议 2027/3/1 前提交(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I46" s="28" t="inlineStr">
+      <c r="I46" s="26" t="inlineStr">
         <is>
           <t>⚠️ 不需要:系页面未列GRE(在线PSM明确不需要),论文型建议邮件确认</t>
         </is>
       </c>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="28" t="inlineStr">
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>lresinfo@montana.edu(LRES系研究生项目);gradschool@montana.edu(MSU研究生院)</t>
         </is>
@@ -3597,32 +3764,32 @@
           <t>系 FAQ:'多数生统学生被任命为 TA 和/或 RA';≥25% 任命含学费奖学金+50% 费用+津贴;12-01 优先</t>
         </is>
       </c>
-      <c r="F47" s="28" t="inlineStr">
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,TA/RA由系里统一分配;个人陈述可写感兴趣的教授</t>
         </is>
       </c>
-      <c r="G47" s="28" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>可以申请(国际生可获TA/RA)。需学士学位、GPA≥3.0;先修:三门微积分(单变量、积分、多元,对应MATH:1850/1860/2850)+线性代数(MATH:2700);至少会一门编程语言;建议理科/数学/健康科学背景,有统计或数据分析经验者优先。</t>
         </is>
       </c>
-      <c r="H47" s="28" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>资助优先 2026/12/1;最终 2027/1/10;仅秋季入学,通过SOPHAS申请(⚠️ 依据官网现行页面,2027周期请再确认)</t>
         </is>
       </c>
-      <c r="I47" s="28" t="inlineStr">
+      <c r="I47" s="26" t="inlineStr">
         <is>
           <t>不需要</t>
         </is>
       </c>
-      <c r="J47" s="28" t="inlineStr">
+      <c r="J47" s="26" t="inlineStr">
         <is>
           <t>否(美国学位豁免:美国认证大学学士自动豁免);否则 TOEFL iBT ≥100 / IELTS ≥7.0 / Duolingo ≥120;⚠️ 当TA可能需参加校内英语口语评估</t>
         </is>
       </c>
-      <c r="K47" s="28" t="inlineStr">
+      <c r="K47" s="26" t="inlineStr">
         <is>
           <t>biostatistics@uiowa.edu(生统系研究生项目管理员);admissions@uiowa.edu(UIowa招生办)</t>
         </is>
@@ -4331,7 +4498,7 @@
           <t>'Students admitted to all graduate programs in SPHHS are eligible to receive on-campus assistantships';'Each assistantship includes a stipend, tuition waiver, and health-fee waiver'</t>
         </is>
       </c>
-      <c r="F64" s="29" t="inlineStr">
+      <c r="F64" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取(SOPHAS),个人陈述可写感兴趣的HPM教授;MS偏研究,可选择性提前联系项目主任了解匹配度</t>
         </is>
@@ -4341,22 +4508,22 @@
           <t>未说明</t>
         </is>
       </c>
-      <c r="H64" s="29" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>SOPHAS 截止 2/1(MS/MPH/PhD;仅秋季入学,8月中开放,建议尽早),即 2027/2/1(⚠️ 第三方显示2027周期同为2/1,官网2027年份待确认)</t>
         </is>
       </c>
-      <c r="I64" s="29" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>不需要(SPHHS官网:所有学位及证书项目不要求GRE/GMAT;⚠️ Peterson's仍列GRE,已过时)</t>
         </is>
       </c>
-      <c r="J64" s="29" t="inlineStr">
+      <c r="J64" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:研究生院对非美国公民/永居的非母语者要求成绩,另有豁免条件(旧版研究生简章及经济系页面含'在美国获得学位'豁免,大概率可豁免,需邮件 gradadm@grad.umass.edu 确认);若需提交:TOEFL ≥80(2026年1月后新制≥4),IELTS ≥6.5,Duolingo ≥115</t>
         </is>
       </c>
-      <c r="K64" s="29" t="inlineStr">
+      <c r="K64" s="30" t="inlineStr">
         <is>
           <t>sphhsgradapply@umass.edu(SPHHS 校园项目研究生招生);abartnik@umass.edu(HPM系办公室协调员)</t>
         </is>
@@ -4393,7 +4560,7 @@
           <t>TA/RA $6,413–12,827/学期+州外学费减免+50–100%州内学费;'Priority…given to doctoral students, then master's'</t>
         </is>
       </c>
-      <c r="F65" s="29" t="inlineStr">
+      <c r="F65" s="30" t="inlineStr">
         <is>
           <t>不需要:MPH按项目整体录取,无需套磁;TA/RA优先给博士生,可在录取后联系系里/教授询问岗位</t>
         </is>
@@ -4404,17 +4571,17 @@
         </is>
       </c>
       <c r="H65" s="21" t="n"/>
-      <c r="I65" s="29" t="inlineStr">
+      <c r="I65" s="30" t="inlineStr">
         <is>
           <t>不需要(官网:GRE仅PhD Epidemiology、MS/PhD Biostatistics需要;MPH已取消GRE/MCAT要求)</t>
         </is>
       </c>
-      <c r="J65" s="29" t="inlineStr">
+      <c r="J65" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免:研究生院规定在美国区域认证院校获学士/研究生学位者免交;⚠️ 信息学院页面提及学位距入学不超过2年,建议确认)。若需:TOEFL ≥79(2026/1/21后新制≥4)</t>
         </is>
       </c>
-      <c r="K65" s="29" t="inlineStr">
+      <c r="K65" s="30" t="inlineStr">
         <is>
           <t>coph-admit@arizona.edu(公共卫生学院招生办)</t>
         </is>
@@ -4451,7 +4618,7 @@
           <t>GTA:$15,000/9 个月+外州学费豁免+大部分学费减免+医保;20 hr 教活动课</t>
         </is>
       </c>
-      <c r="F66" s="29" t="inlineStr">
+      <c r="F66" s="30" t="inlineStr">
         <is>
           <t>不需要:系里整体审核(holistic review)录取;个人陈述可提感兴趣的教授/研究方向</t>
         </is>
@@ -4462,7 +4629,7 @@
         </is>
       </c>
       <c r="H66" s="21" t="n"/>
-      <c r="I66" s="29" t="inlineStr">
+      <c r="I66" s="30" t="inlineStr">
         <is>
           <t>⚠️ 官网未提及;第三方(IDP)称最后60学分GPA&lt;3.5时需GRE,建议邮件确认</t>
         </is>
@@ -4837,16 +5004,28 @@
           <t>系有多个GTA'carry a stipend and tuition reduction'(部分学费减免)</t>
         </is>
       </c>
-      <c r="F75" s="21" t="n"/>
-      <c r="G75" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;如想申GTA或做生物力学实验室研究,可提前联系系里了解岗位</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可申GTA,带stipend+部分学费减免)。先修:Exercise Science方向需≥18学分运动/体育/健身相关课程;3封推荐信(≥1封来自教授);⚠️ 最低GPA各来源不一(2.7/2.75/3.0),未达标可有条件录取</t>
         </is>
       </c>
       <c r="H75" s="21" t="n"/>
       <c r="I75" s="21" t="n"/>
-      <c r="J75" s="21" t="n"/>
-      <c r="K75" s="21" t="n"/>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国区域认证大学学位者无需提交英语成绩);否则TOEFL ≥79,IELTS ≥6.0</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>ksm@usd.edu(Kinesiology &amp; Sport Management 系);gradadmissions@usd.edu(研究生招生办)</t>
+        </is>
+      </c>
       <c r="L75" s="21" t="inlineStr">
         <is>
           <t>https://www.usd.edu/Academics/Graduate-Programs/Kinesiology-and-Sport-Management</t>
@@ -4879,16 +5058,28 @@
           <t>GA竞争性;'General tuition and the non-resident fees are waived for graduate assistants';≤20h/周</t>
         </is>
       </c>
-      <c r="F76" s="21" t="n"/>
-      <c r="G76" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可联系学院主任 Dr. Stephanie McCoy Smith 咨询GA岗位</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA免学费及外州费)。先修:运动科学或相关本科;化学或生物1门+生理学、营养学本科课;最低GPA 2.75(最后60学分);需SOP、简历、3封推荐信。⚠️ 该方向目录标注100%在线,需确认是否有校园版/能否持F-1</t>
         </is>
       </c>
       <c r="H76" s="21" t="n"/>
       <c r="I76" s="21" t="n"/>
-      <c r="J76" s="21" t="n"/>
-      <c r="K76" s="21" t="n"/>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国认证大学学位可免);否则TOEFL ≥71,IELTS ≥6.0</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>stephanie.mccoy@usm.edu(学院主任/项目顾问 Dr. Stephanie Smith);电话 601-266-5358(School of Kinesiology and Nutrition)</t>
+        </is>
+      </c>
       <c r="L76" s="21" t="inlineStr">
         <is>
           <t>https://www.usm.edu/graduate-programs/kinesiology-sport-coaching-education.php</t>
@@ -4921,16 +5112,36 @@
           <t>'Most SHPK GTAs are awarded to PhD students; however, master's students are also eligible';全年接受GTA申请</t>
         </is>
       </c>
-      <c r="F77" s="21" t="n"/>
-      <c r="G77" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H77" s="21" t="n"/>
-      <c r="I77" s="21" t="n"/>
-      <c r="J77" s="21" t="n"/>
-      <c r="K77" s="21" t="n"/>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GTA多给博士,硕士可申,建议联系方向教授表达兴趣</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(硕士也可申GTA,全年接受申请)。先修:解剖与生理学、运动生理学、3学分高年级运动科学课(可入学后补修,不计学分);最后60学分GPA ≥3.0</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>滚动录取;优先截止 秋季 2027/3/1(春季7/1)。国际生建议提前6–8个月准备</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 必需(研究生手册写Exercise Physiology方向需提交GRE;项目页未写,可能过时,建议确认)</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院有英语豁免表,美国本科学位应可豁免,需确认;否则TOEFL ≥79,IELTS ≥6.5,Duolingo ≥100</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>SHPK@twu.edu(School of Health Promotion &amp; Kinesiology)</t>
+        </is>
+      </c>
       <c r="L77" s="21" t="inlineStr">
         <is>
           <t>https://twu.edu/kinesiology/graduate-programs/</t>
@@ -4963,16 +5174,32 @@
           <t>'All qualifying applicants are considered for assistantships. You do not need to apply';1/15前申请优先考虑资助</t>
         </is>
       </c>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H78" s="21" t="n"/>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>不需要:硕士按项目整体录取(MS/PhD衔接轨道需导师背书);可在文书中写感兴趣教授</t>
+        </is>
+      </c>
+      <c r="G78" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(合格申请人自动考虑资助,无需单独申请)。⚠️ 项目页未列具体先修/最低GPA(同系MSAT要求GPA ≥3.0),建议运动科学相关背景</t>
+        </is>
+      </c>
+      <c r="H78" s="30" t="inlineStr">
+        <is>
+          <t>资助/优先 2027/1/15;最终 2027/7/1(视名额)</t>
+        </is>
+      </c>
       <c r="I78" s="21" t="n"/>
-      <c r="J78" s="21" t="n"/>
-      <c r="K78" s="21" t="n"/>
+      <c r="J78" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,材料齐后招生专员手动豁免);入学后所有国际生需参加UNCG英语测评</t>
+        </is>
+      </c>
+      <c r="K78" s="30" t="inlineStr">
+        <is>
+          <t>plkocher@uncg.edu(研究生项目主任 Pam Brown);clbooth@uncg.edu(研究生协调员 Carol Booth)</t>
+        </is>
+      </c>
       <c r="L78" s="21" t="inlineStr">
         <is>
           <t>https://kin.uncg.edu/graduate-degrees/faqs/</t>
@@ -5005,16 +5232,36 @@
           <t>'Associateships provide professional experience and financial support';12/1为资助截止;无MS比例</t>
         </is>
       </c>
-      <c r="F79" s="21" t="n"/>
-      <c r="G79" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H79" s="21" t="n"/>
-      <c r="I79" s="21" t="n"/>
-      <c r="J79" s="21" t="n"/>
-      <c r="K79" s="21" t="n"/>
+      <c r="F79" s="30" t="inlineStr">
+        <is>
+          <t>建议:Associateship多与教授项目/实验室挂钩,建议联系方向匹配教授(如 kackley.19@osu.edu)</t>
+        </is>
+      </c>
+      <c r="G79" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获GTA/GRA associateship;担任GTA需通过口语测试)。先修:4年制本科学位;⚠️ 第三方称GPA ≥3.0,官网未注明具体先修课</t>
+        </is>
+      </c>
+      <c r="H79" s="30" t="inlineStr">
+        <is>
+          <t>资助截止 2026/12/1;之后滚动录取至名额满(申请9/1开放)</t>
+        </is>
+      </c>
+      <c r="I79" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(研究生院不要求,项目页未提及),建议确认</t>
+        </is>
+      </c>
+      <c r="J79" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:须在入学前24个月内获美国学士学位);入学后需英语写作测评;当GTA需口语能力认证(OPA)</t>
+        </is>
+      </c>
+      <c r="K79" s="30" t="inlineStr">
+        <is>
+          <t>kinesiology@osu.edu(Kinesiology 研究生项目)</t>
+        </is>
+      </c>
       <c r="L79" s="21" t="inlineStr">
         <is>
           <t>https://ehe.osu.edu/graduate/kinesiology/health-and-exercise-science/ms-kinesiology</t>
@@ -5047,15 +5294,31 @@
           <t>校级GA:30学分学费减免/年+非居民学费全免+系定stipend;岗位在Workday发布</t>
         </is>
       </c>
-      <c r="F80" s="21" t="n"/>
-      <c r="G80" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H80" s="21" t="n"/>
-      <c r="I80" s="21" t="n"/>
-      <c r="J80" s="21" t="n"/>
+      <c r="F80" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:研究型论文硕士,依托Human Performance Lab,建议先联系研究生项目主任 Scott Trappe 或方向导师</t>
+        </is>
+      </c>
+      <c r="G80" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA含学费减免+非居民费全免+stipend)。先修:必须修过有机化学I+II(含实验);GPA&lt;2.75可凭其他成就有条件考虑;需CV、3封推荐信、补充表+写作样本</t>
+        </is>
+      </c>
+      <c r="H80" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2027/2/1(⚠️ Peterson's 称1/15);国际生截止以研究生招生办为准</t>
+        </is>
+      </c>
+      <c r="I80" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 可能必需:第三方(Mastersportal/Peterson's)列为必需,官网页未提及,建议确认</t>
+        </is>
+      </c>
+      <c r="J80" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:美国认证大学学位或≥24学分美国学习可免);否则TOEFL ≥79,IELTS ≥6.5;成绩2年有效</t>
+        </is>
+      </c>
       <c r="K80" s="21" t="n"/>
       <c r="L80" s="21" t="inlineStr">
         <is>
@@ -5089,16 +5352,36 @@
           <t>硕士GA stipend $10,000–12,500/年+fee remission;'Master student assistantships are for only one year'</t>
         </is>
       </c>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="21" t="inlineStr">
-        <is>
-          <t>可(AI需过TEPAIC)</t>
-        </is>
-      </c>
-      <c r="H81" s="21" t="n"/>
-      <c r="I81" s="21" t="n"/>
-      <c r="J81" s="21" t="n"/>
-      <c r="K81" s="21" t="n"/>
+      <c r="F81" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G81" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获GA;担任AI需通过TEPAIC口语测试)。先修:学士学位,无统一必修课(各方向可能另有要求);SOP ≤600字;经SOPHAS申请+IU研究生院补充申请</t>
+        </is>
+      </c>
+      <c r="H81" s="30" t="inlineStr">
+        <is>
+          <t>优先 2027/1/15;最终 2027/4/1(按SOPHAS中具体项目为准)</t>
+        </is>
+      </c>
+      <c r="I81" s="30" t="inlineStr">
+        <is>
+          <t>可选(SPH-B所有研究生项目GRE可选)</t>
+        </is>
+      </c>
+      <c r="J81" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免);⚠️ 部分资助机会仍可能要求英语成绩;担任AI需TEPAIC</t>
+        </is>
+      </c>
+      <c r="K81" s="30" t="inlineStr">
+        <is>
+          <t>sphgrad@iu.edu(SPH-Bloomington研究生招生)</t>
+        </is>
+      </c>
       <c r="L81" s="21" t="inlineStr">
         <is>
           <t>https://bulletins.iu.edu/iub/phb/2020-2021/graduate/financial-aid.shtml</t>
@@ -5131,16 +5414,36 @@
           <t>'Each applicant is evaluated for an assistantship. No separate application';按学期任命、无续聘保证</t>
         </is>
       </c>
-      <c r="F82" s="21" t="n"/>
-      <c r="G82" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H82" s="21" t="n"/>
-      <c r="I82" s="21" t="n"/>
-      <c r="J82" s="21" t="n"/>
-      <c r="K82" s="21" t="n"/>
+      <c r="F82" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,所有申请人自动评估assistantship</t>
+        </is>
+      </c>
+      <c r="G82" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生担任TA需通过SPEAK或TOEFL口语≥26)。无专业/先修要求,所有专业可申;本科高年级GPA ≥3.0;2封推荐信;申请费$30</t>
+        </is>
+      </c>
+      <c r="H82" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/2/1;早申(建议国际生)2027/4/1;最终 2027/7/1(⚠️ 国际生页另写秋季1/15,冲突,建议确认)</t>
+        </is>
+      </c>
+      <c r="I82" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 可能不需要:研究生院已对多数硕士豁免GRE(Spring 2026起无全校要求),但MPH目录仍提及GRE 50%分位,建议确认</t>
+        </is>
+      </c>
+      <c r="J82" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学士学位可豁免校级英语要求,但系可另有要求);当TA需SPEAK或TOEFL口语≥26</t>
+        </is>
+      </c>
+      <c r="K82" s="30" t="inlineStr">
+        <is>
+          <t>cosspp-publichealthinfo@fsu.edu(MPH招生);hmahony@fsu.edu(MPH项目主任 Helen Mahony)</t>
+        </is>
+      </c>
       <c r="L82" s="21" t="inlineStr">
         <is>
           <t>https://cosspp.fsu.edu/publichealth/funding-and-scholarships/</t>
@@ -5173,16 +5476,36 @@
           <t>约30%(MPH)/40%(SM)获school grants,多覆盖1/4–1/2学费;Presidential Scholars约10人全额学费</t>
         </is>
       </c>
-      <c r="F83" s="21" t="n"/>
-      <c r="G83" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H83" s="21" t="n"/>
-      <c r="I83" s="21" t="n"/>
-      <c r="J83" s="21" t="n"/>
-      <c r="K83" s="21" t="n"/>
+      <c r="F83" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G83" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获school grants)。MPH-65学分版需学士学位+≥2年连续全职公卫相关工作经验;SM需展示定量能力(⚠️ 各SM方向先修不同,见项目页)</t>
+        </is>
+      </c>
+      <c r="H83" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/1(SOPHAS,多数项目);决定2–3月邮件通知</t>
+        </is>
+      </c>
+      <c r="I83" s="30" t="inlineStr">
+        <is>
+          <t>可选(MPH全部方向、SM-HPM为test-optional;⚠️ 其他SM方向需查项目页)</t>
+        </is>
+      </c>
+      <c r="J83" s="30" t="inlineStr">
+        <is>
+          <t>否(获得英语授课院校学位者免考)</t>
+        </is>
+      </c>
+      <c r="K83" s="30" t="inlineStr">
+        <is>
+          <t>admissions@hsph.harvard.edu(Harvard Chan 招生办)</t>
+        </is>
+      </c>
       <c r="L83" s="21" t="inlineStr">
         <is>
           <t>https://hsph.harvard.edu/tuition-and-financial-aid/types-of-financial-aid/</t>
@@ -5215,28 +5538,28 @@
           <t>'All students admitted…reviewed for institutional academic merit scholarships';$7,500–30,000/年</t>
         </is>
       </c>
-      <c r="F84" s="29" t="inlineStr">
+      <c r="F84" s="30" t="inlineStr">
         <is>
           <t>不需要:MPH/MS 经 SOPHAS 按项目整体录取,个人陈述可写感兴趣的教授/研究方向</t>
         </is>
       </c>
-      <c r="G84" s="29" t="inlineStr">
+      <c r="G84" s="30" t="inlineStr">
         <is>
           <t>可以申请(国际生仅可获 merit 奖学金;need-based 资助限美籍)。先修:MPH 接受任何本科专业,无硬性先修课;MS(如生物统计)需微积分等数理基础;⚠️ 官网未列最低 GPA</t>
         </is>
       </c>
-      <c r="H84" s="29" t="inlineStr">
+      <c r="H84" s="30" t="inlineStr">
         <is>
           <t>优先(含奖学金考虑)2026/12/1;MPH 一般截止约 2027/1/15(2026 周期曾延至 2 月)(按2026周期,2027待公布);⚠️ 第三方显示 Accelerated MPH 2027/1/15</t>
         </is>
       </c>
-      <c r="I84" s="29" t="inlineStr">
+      <c r="I84" s="30" t="inlineStr">
         <is>
           <t>可选:2026 秋季起所有硕士项目标化成绩均为可选</t>
         </is>
       </c>
       <c r="J84" s="21" t="n"/>
-      <c r="K84" s="29" t="inlineStr">
+      <c r="K84" s="30" t="inlineStr">
         <is>
           <t>ph-admit@columbia.edu(Mailman 招生办)</t>
         </is>
@@ -5273,28 +5596,28 @@
           <t>'$34M in scholarships and tuition assistance';GSI/GSRA可申;无比例</t>
         </is>
       </c>
-      <c r="F85" s="29" t="inlineStr">
+      <c r="F85" s="30" t="inlineStr">
         <is>
           <t>不需要:按系整体录取(SOPHAS),个人陈述可写感兴趣的教授;GSRA 多需录取后自行联系教授</t>
         </is>
       </c>
-      <c r="G85" s="29" t="inlineStr">
+      <c r="G85" s="30" t="inlineStr">
         <is>
           <t>可以申请(国际生可申 GSI/GSRA 及系奖学金)。先修:一般接受任何专业;Biostatistics 需微积分/线代,EHS 等需理科基础(⚠️ 按系不同);⚠️ 官网未列最低 GPA</t>
         </is>
       </c>
-      <c r="H85" s="29" t="inlineStr">
+      <c r="H85" s="30" t="inlineStr">
         <is>
           <t>资助/奖学金优先 2026/12/1;国际生最终 2027/1/15;美籍最终 2027/5/15(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I85" s="29" t="inlineStr">
+      <c r="I85" s="30" t="inlineStr">
         <is>
           <t>⚠️ 多数项目不需要/可选(第三方 Peterson's 仍列 GRE,官网未核实,建议按具体系确认)</t>
         </is>
       </c>
       <c r="J85" s="21" t="n"/>
-      <c r="K85" s="29" t="inlineStr">
+      <c r="K85" s="30" t="inlineStr">
         <is>
           <t>⚠️ sph.inquiries@umich.edu(SPH 招生办,未经本次检索核实)</t>
         </is>
@@ -5331,16 +5654,36 @@
           <t>GTA/GRA:学费减免+医保+津贴;CHS 硕士 $1,900/月(0.5 FTE);外州学费全免</t>
         </is>
       </c>
-      <c r="F86" s="21" t="n"/>
-      <c r="G86" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H86" s="21" t="n"/>
-      <c r="I86" s="21" t="n"/>
-      <c r="J86" s="21" t="n"/>
-      <c r="K86" s="21" t="n"/>
+      <c r="F86" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GTA/GRA可联系项目协调员咨询</t>
+        </is>
+      </c>
+      <c r="G86" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获GTA/GRA,外州学费全免)。先修:本科GPA ≥3.0;需简历/CV、2封推荐信;⚠️ 未列具体先修课</t>
+        </is>
+      </c>
+      <c r="H86" s="30" t="inlineStr">
+        <is>
+          <t>滚动录取,建议开学前≥6周提交;⚠️ 为争取GTA/GRA建议2027/3前提交</t>
+        </is>
+      </c>
+      <c r="I86" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 项目页未列要求,应为不需要,建议确认</t>
+        </is>
+      </c>
+      <c r="J86" s="30" t="inlineStr">
+        <is>
+          <t>否(英语国家英语授课学位豁免,美国学位适用);否则TOEFL ≥79,IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K86" s="30" t="inlineStr">
+        <is>
+          <t>darcy.mcmaughan@okstate.edu(项目协调员 Dr. DJ McMaughan)</t>
+        </is>
+      </c>
       <c r="L86" s="21" t="inlineStr">
         <is>
           <t>https://go.okstate.edu/graduate-academics/programs/masters/health-promotion-ms.html</t>
@@ -5667,28 +6010,28 @@
           <t>所有 MPH 申请者自动考虑系学费奖学金(12-01 优先);GSI/GSRA 含学费+津贴+医保</t>
         </is>
       </c>
-      <c r="F94" s="29" t="inlineStr">
+      <c r="F94" s="30" t="inlineStr">
         <is>
           <t>不需要:按系整体录取(SOPHAS),个人陈述可写感兴趣的教授;GSRA 多需录取后自行联系教授</t>
         </is>
       </c>
-      <c r="G94" s="29" t="inlineStr">
+      <c r="G94" s="30" t="inlineStr">
         <is>
           <t>可以申请(✅ 官网明文国内外申请者同等考虑系学费奖学金)。先修:一般接受任何专业;部分系(Biostat 等)需数理先修;⚠️ 未列最低 GPA</t>
         </is>
       </c>
-      <c r="H94" s="29" t="inlineStr">
+      <c r="H94" s="30" t="inlineStr">
         <is>
           <t>资助/奖学金优先 2026/12/1;国际生最终 2027/1/15;美籍最终 2027/5/15(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I94" s="29" t="inlineStr">
+      <c r="I94" s="30" t="inlineStr">
         <is>
           <t>⚠️ 多数项目不需要/可选(第三方 Peterson's 仍列 GRE,官网未核实,建议按具体系确认)</t>
         </is>
       </c>
       <c r="J94" s="21" t="n"/>
-      <c r="K94" s="29" t="inlineStr">
+      <c r="K94" s="30" t="inlineStr">
         <is>
           <t>⚠️ sph.inquiries@umich.edu(SPH 招生办,未经本次检索核实)</t>
         </is>
@@ -6061,7 +6404,7 @@
           <t>各校有限 GRA/部分奖学金;NW 最高 $20,000 奖学金无 assistantship</t>
         </is>
       </c>
-      <c r="F103" s="29" t="inlineStr">
+      <c r="F103" s="30" t="inlineStr">
         <is>
           <t>KUMC: 不需要:MHSA 按项目整体录取(⚠️ 推断)
 Georgia State: 不需要:职业型项目(⚠️ 推断)
@@ -6230,32 +6573,32 @@
           <t>MA 生'通常获 1-4 学期支持';TA/RA 10-20 hr 含津贴+学费减免</t>
         </is>
       </c>
-      <c r="F107" s="29" t="inlineStr">
+      <c r="F107" s="30" t="inlineStr">
         <is>
           <t>⚠️ 官网未明确要求;建议:可先邮件联系研究方向匹配的教授,个人陈述中写明感兴趣的教授</t>
         </is>
       </c>
-      <c r="G107" s="29" t="inlineStr">
+      <c r="G107" s="30" t="inlineStr">
         <is>
           <t>可以申请(国际生可获TA/RA,但当TA需另证口语:TOEFL口语≥22/IELTS口语≥7.0/PTE口语≥75)。先修:区域认证学士学位,官网未列必修先修课;⚠️ 第三方称GPA 3.0为常见门槛。材料:CV、个人陈述(750–1000词)、3封推荐信</t>
         </is>
       </c>
-      <c r="H107" s="29" t="inlineStr">
+      <c r="H107" s="30" t="inlineStr">
         <is>
           <t>大学fellowship 2026/12/15;系assistantship 2027/1/31;1/31后仍审但资助优先级降低;不需资助者可申请周期外审核(⚠️ 按往年周期,2027待确认)</t>
         </is>
       </c>
-      <c r="I107" s="29" t="inlineStr">
+      <c r="I107" s="30" t="inlineStr">
         <is>
           <t>不需要(系官网:GRE no longer required)</t>
         </is>
       </c>
-      <c r="J107" s="29" t="inlineStr">
+      <c r="J107" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):在美国院校完成≥30本科学分且GPA≥3.0即免TOEFL/IELTS(⚠️ 政策文件为2019–2020版);但当TA仍需证明口语(TOEFL口语≥22/IELTS口语≥7.0/PTE口语≥75或校内口语测试)</t>
         </is>
       </c>
-      <c r="K107" s="29" t="inlineStr">
+      <c r="K107" s="30" t="inlineStr">
         <is>
           <t>nathaniel.trumbull@uconn.edu(研究生项目协调员,⚠️ 系目录另列 debarchana.ghosh@uconn.edu 为协调员);gscu@uconn.edu(系办公室)</t>
         </is>
@@ -6292,32 +6635,32 @@
           <t>'硕士与博士级有限 assistantship';硕士最多 2 年</t>
         </is>
       </c>
-      <c r="F108" s="29" t="inlineStr">
+      <c r="F108" s="30" t="inlineStr">
         <is>
           <t>建议:系官网设有"Which Faculty Members are Accepting New Students?"页面,建议先确认在招导师并联系</t>
         </is>
       </c>
-      <c r="G108" s="29" t="inlineStr">
+      <c r="G108" s="30" t="inlineStr">
         <is>
           <t>可以申请(有限assistantship,⚠️ 官网未明确国际生限制)。注意:官方目录为 Geography M.S.(非MA)。先修:区域认证学士,GPA≥2.75;材料:成绩单、简历、goal statement、3封推荐信;⚠️ Peterson's称需相当于地理辅修(24学分)、建议GPA≥3.3</t>
         </is>
       </c>
-      <c r="H108" s="29" t="inlineStr">
+      <c r="H108" s="30" t="inlineStr">
         <is>
           <t>秋季优先截止 2027/2/1(材料齐全者最受优先考虑;按2025-26目录,2027待确认)</t>
         </is>
       </c>
-      <c r="I108" s="29" t="inlineStr">
+      <c r="I108" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:官方目录招生要求未列GRE(大概率不需要);Peterson's 信息互相矛盾,建议邮件确认</t>
         </is>
       </c>
-      <c r="J108" s="29" t="inlineStr">
+      <c r="J108" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确(大概率否):Kent 要求"教育主要在美国以外"者提供英语证明,美本应可豁免,但未明文列出美国学位豁免,豁免需书面向国际招生办申请。不豁免时:TOEFL≥79,IELTS≥6.5,PTE≥58,DET≥110</t>
         </is>
       </c>
-      <c r="K108" s="29" t="inlineStr">
+      <c r="K108" s="30" t="inlineStr">
         <is>
           <t>ssmiley8@kent.edu(⚠️ 目录所列项目联系人 Sarah Smiley);geography@kent.edu(地理系办公室)</t>
         </is>
@@ -6354,32 +6697,32 @@
           <t>有限 assistantship;获资助者保证 4 学期(学费+津贴+医保补贴)</t>
         </is>
       </c>
-      <c r="F109" s="29" t="inlineStr">
+      <c r="F109" s="30" t="inlineStr">
         <is>
           <t>强烈建议:官网称录取很看重导师匹配,申请前联系潜在导师(建议8–9月),网申需填写意向教授</t>
         </is>
       </c>
-      <c r="G109" s="29" t="inlineStr">
+      <c r="G109" s="30" t="inlineStr">
         <is>
           <t>可以申请(有限assistantship,获资助者保证4学期;⚠️ 官网未明确限制国际生)。先修:学士学位,官网未列必修先修课;材料:CV、成绩单、letter of intent(约1500–2000词,≤3页单倍行距)、2封推荐信(第3封及≤15页写作样本可选)、申请费$50</t>
         </is>
       </c>
-      <c r="H109" s="29" t="inlineStr">
+      <c r="H109" s="30" t="inlineStr">
         <is>
           <t>最终 2026/12/1(2027秋季,Graduate School官网);春季入学仅特殊情况,需先联系研究生主任</t>
         </is>
       </c>
-      <c r="I109" s="29" t="inlineStr">
+      <c r="I109" s="30" t="inlineStr">
         <is>
           <t>不接受(官网:请勿提交GRE,委员会不审阅)</t>
         </is>
       </c>
-      <c r="J109" s="29" t="inlineStr">
+      <c r="J109" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确(大概率否):Graduate School 要求在非英语官方国家获英文授课学位者提交成绩,美国学位不在此列;但系有权自行要求。不豁免时:TOEFL≥80(2026/1/21后新版≥4.0)、IELTS≥6.5、PTE≥53、DET≥120</t>
         </is>
       </c>
-      <c r="K109" s="29" t="inlineStr">
+      <c r="K109" s="30" t="inlineStr">
         <is>
           <t>cnagel@mailbox.sc.edu(研究生主任 Caroline Nagel);nickless@mailbox.sc.edu(学生服务协调员 Sena Nickles)</t>
         </is>
@@ -7028,16 +7371,32 @@
           <t>全职GA 30学分学费减免+州外减免+stipend</t>
         </is>
       </c>
-      <c r="F126" s="21" t="n"/>
-      <c r="G126" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H126" s="21" t="n"/>
-      <c r="I126" s="21" t="n"/>
+      <c r="F126" s="30" t="inlineStr">
+        <is>
+          <t>不需要:无单独系内申请,经研究生院申请后选Urban Planning;GA职位建议主动联系项目主任</t>
+        </is>
+      </c>
+      <c r="G126" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。先修:无指定本科专业;系要求本科GPA≥3.0,2.75–3.0可试读录取(前9学分需≥3.0);材料:成绩单、简历、300–500字目的陈述。另有PAB认证本科生36学分快轨</t>
+        </is>
+      </c>
+      <c r="H126" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未列明确截止:材料须在开学前至少两周送达研究生院;资助/assistantship 3/1(第三方及手册提及,建议2027/3/1前提交);建议邮件确认</t>
+        </is>
+      </c>
+      <c r="I126" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未提及GRE要求(手册录取标准未列考试),大概率不需要,建议确认</t>
+        </is>
+      </c>
       <c r="J126" s="21" t="n"/>
-      <c r="K126" s="21" t="n"/>
+      <c r="K126" s="30" t="inlineStr">
+        <is>
+          <t>planning@bsu.edu(城市规划系);admissions@bsu.edu(学校招生办)</t>
+        </is>
+      </c>
       <c r="L126" s="21" t="inlineStr">
         <is>
           <t>https://www.bsu.edu/academics/collegesanddepartments/urban-planning/applications-financial-aid/graduate-assistantships</t>
@@ -7070,32 +7429,32 @@
           <t>GA 10h/周含学费减免+医保补贴;二年级Public Service Assistantship</t>
         </is>
       </c>
-      <c r="F127" s="29" t="inlineStr">
+      <c r="F127" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,GA由系里分配;SOP可写感兴趣的教授/方向</t>
         </is>
       </c>
-      <c r="G127" s="29" t="inlineStr">
+      <c r="G127" s="30" t="inlineStr">
         <is>
           <t>可以申请(⚠️ 国际生GA资格官网未明文,建议确认)。需四年制学士学位、学术记录良好,不限本科专业;材料:非官方成绩单、3封推荐信(≥1封教授)、简历、≤1000字SOP。⚠️ 第三方称最低GPA 3.0</t>
         </is>
       </c>
-      <c r="H127" s="29" t="inlineStr">
+      <c r="H127" s="30" t="inlineStr">
         <is>
           <t>滚动录取,2027/1/15起开始审理(按2026-27手册);建议 2027/3/1 前提交以优先考虑系里assistantship</t>
         </is>
       </c>
-      <c r="I127" s="29" t="inlineStr">
+      <c r="I127" s="30" t="inlineStr">
         <is>
           <t>不需要(官网标注 GRE Waived)</t>
         </is>
       </c>
-      <c r="J127" s="29" t="inlineStr">
+      <c r="J127" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):Clemson研究生院对美国区域认证院校学位豁免ELP,在读学位可先获豁免、入学前补交学位成绩单。否则 TOEFL ≥80(项目偏好100)/IELTS ≥6.5/Duolingo ≥115</t>
         </is>
       </c>
-      <c r="K127" s="29" t="inlineStr">
+      <c r="K127" s="30" t="inlineStr">
         <is>
           <t>mcrp@clemson.edu(MCRP项目邮箱);grdapp@clemson.edu(研究生院招生)</t>
         </is>
@@ -7132,27 +7491,27 @@
           <t>'TAships and GRships include a stipend and a full waiver of base tuition';'All graduate applicants (domestic and international) are automatically considered'</t>
         </is>
       </c>
-      <c r="F128" s="29" t="inlineStr">
+      <c r="F128" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,所有申请者(含国际生)自动考虑TA/GR</t>
         </is>
       </c>
-      <c r="G128" s="29" t="inlineStr">
+      <c r="G128" s="30" t="inlineStr">
         <is>
           <t>可以申请(国际生同样自动考虑TA/GR,含stipend+基础学费全免)。不限本科专业;⚠️ 第三方称最低GPA 3.0;TOEFL ≥80/IELTS ≥6.5(如需)</t>
         </is>
       </c>
-      <c r="H128" s="29" t="inlineStr">
+      <c r="H128" s="30" t="inlineStr">
         <is>
           <t>录取+资助优先 2027/1/10;⚠️ 系页面称晚申请可至 2/1;最终:国际生 6/1、国内 7/1(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I128" s="29" t="inlineStr">
+      <c r="I128" s="30" t="inlineStr">
         <is>
           <t>不需要(可选提交,须截止前送达;校代码4853/系代码4402)</t>
         </is>
       </c>
-      <c r="J128" s="29" t="inlineStr">
+      <c r="J128" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免,有条件):美国区域认证学士学位须在提交申请并缴费前2年内获得;否则 TOEFL ≥80/IELTS ≥6.5/Duolingo ≥110</t>
         </is>
@@ -7190,23 +7549,23 @@
           <t>merit aid(assistantships/fellowships/tuition remission)需1/15前申请;'Funds will only cover a portion of all applicants'</t>
         </is>
       </c>
-      <c r="F129" s="29" t="inlineStr">
+      <c r="F129" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,奖学金/assistantship由学院综合评审分配</t>
         </is>
       </c>
       <c r="G129" s="21" t="n"/>
-      <c r="H129" s="29" t="inlineStr">
+      <c r="H129" s="30" t="inlineStr">
         <is>
           <t>资助优先 2027/1/15(按2026周期,2027待公布);⚠️ 最终(2026周期program explorer):国际生 4/1、美国申请者 7/1;春季 11/1</t>
         </is>
       </c>
-      <c r="I129" s="29" t="inlineStr">
+      <c r="I129" s="30" t="inlineStr">
         <is>
           <t>不需要(近几个周期均对所有申请者 waive)</t>
         </is>
       </c>
-      <c r="J129" s="29" t="inlineStr">
+      <c r="J129" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:Bloustein项目列表写 Non-U.S. applicants 需 TOEFL/IELTS/Duolingo,未写美国学位豁免;研究生院部分项目对≥3年英语授课本科豁免,建议邮件确认</t>
         </is>
@@ -7244,27 +7603,27 @@
           <t>'limited number of graduate assistantships on a competitive basis';考虑截止3/1</t>
         </is>
       </c>
-      <c r="F130" s="29" t="inlineStr">
+      <c r="F130" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,GA有限且竞争性分配</t>
         </is>
       </c>
-      <c r="G130" s="29" t="inlineStr">
+      <c r="G130" s="30" t="inlineStr">
         <is>
           <t>可以申请(GA名额有限、竞争性)。研究生院最低GPA 3.0(低于者可凭工作经历等综合考虑);不限本科专业;材料:成绩单、个人陈述、简历、3封推荐信</t>
         </is>
       </c>
-      <c r="H130" s="29" t="inlineStr">
+      <c r="H130" s="30" t="inlineStr">
         <is>
           <t>GA/资助优先 2027/3/1(春季入学 10/1);最终滚动截止:秋季 8/1、春季 1/1</t>
         </is>
       </c>
-      <c r="I130" s="29" t="inlineStr">
+      <c r="I130" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不需要:现行FAQ未提GRE;旧版FAQ仅要求非美国本科者提交GRE(美本不受影响)</t>
         </is>
       </c>
-      <c r="J130" s="29" t="inlineStr">
+      <c r="J130" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):已获英语授课认可院校学位者豁免;否则 TOEFL iBT ≥90(各部分≥20)/IELTS ≥6.5。⚠️ 豁免措辞为'已获得'学位,在读者建议确认</t>
         </is>
@@ -7302,12 +7661,36 @@
           <t>Wilder Graduate Scholars Fellowship:州内学费杂费+stipend(2024-25共$32,752),1年,24个名额跨4项目;国际生资格未明</t>
         </is>
       </c>
-      <c r="F131" s="21" t="n"/>
-      <c r="G131" s="21" t="n"/>
-      <c r="H131" s="21" t="n"/>
-      <c r="I131" s="21" t="n"/>
-      <c r="J131" s="21" t="n"/>
-      <c r="K131" s="21" t="n"/>
+      <c r="F131" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述可写感兴趣方向</t>
+        </is>
+      </c>
+      <c r="G131" s="30" t="inlineStr">
+        <is>
+          <t>可以申请,但Wilder Graduate Scholars Fellowship国际生资格未明。先修:无指定专业;本科GPA≥2.7(4.0制),低于可试读录取;3封推荐信,至少2封来自教师</t>
+        </is>
+      </c>
+      <c r="H131" s="30" t="inlineStr">
+        <is>
+          <t>早申/优先 2027/2/1;目录另列秋季优先 4/1;最终 2027/5/1(按Wilder官网周期推算,2027待确认);逾期可交但不保证审理</t>
+        </is>
+      </c>
+      <c r="I131" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:官方目录测试要求栏未能读取,第三方称需GRE但可能过时,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J131" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:VCU研究生豁免列表所列国家未能确认含美国;否则需 TOEFL iBT ≥80(2026/1/21后新制≥4.5)/ IELTS ≥6.5,2年有效,建议确认</t>
+        </is>
+      </c>
+      <c r="K131" s="30" t="inlineStr">
+        <is>
+          <t>wsrecruit@vcu.edu(Wilder School招生/招募)</t>
+        </is>
+      </c>
       <c r="L131" s="21" t="inlineStr">
         <is>
           <t>https://wilder.vcu.edu/student-support-resources/internships-and-experiential-learning-/wilder-graduate-scholars-fellowship/</t>
@@ -7340,12 +7723,36 @@
           <t>TA/RA'cover tuition, plus a stipend'</t>
         </is>
       </c>
-      <c r="F132" s="21" t="n"/>
-      <c r="G132" s="21" t="n"/>
-      <c r="H132" s="21" t="n"/>
-      <c r="I132" s="21" t="n"/>
-      <c r="J132" s="21" t="n"/>
-      <c r="K132" s="21" t="n"/>
+      <c r="F132" s="30" t="inlineStr">
+        <is>
+          <t>建议:研究型MS(可写论文),官网要求申请人先阅读研究生手册并联系Graduate Chair Dr. Harold Perkins</t>
+        </is>
+      </c>
+      <c r="G132" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(TA/RA可覆盖学费+stipend;资助仅限秋季入学)。先修:接受非地理专业,但需在个人陈述说明本科如何为地理研究生学习做准备;资助/无条件录取一般需GPA≥3.0;1–2页陈述、简历、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H132" s="30" t="inlineStr">
+        <is>
+          <t>资助截止 2027/1/15(申请窗口 2026/10/15–2027/1/15);一般2月审理,3/15前通知</t>
+        </is>
+      </c>
+      <c r="I132" s="30" t="inlineStr">
+        <is>
+          <t>不需要(系官网明确GRE not required)</t>
+        </is>
+      </c>
+      <c r="J132" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):OU规定来自非英语国家者须在入学前2年内获得美国区域认证院校学士学位才可豁免;否则 ⚠️ TOEFL 80 / IELTS 6.5(第三方)。当TA可能另有口语要求,建议确认</t>
+        </is>
+      </c>
+      <c r="K132" s="30" t="inlineStr">
+        <is>
+          <t>perkinsh@ohio.edu(Graduate Chair Dr. Harold Perkins)</t>
+        </is>
+      </c>
       <c r="L132" s="21" t="inlineStr">
         <is>
           <t>https://www.ohio.edu/cas/geography/graduate/financial-aid</t>
@@ -7378,12 +7785,36 @@
           <t>'eligible for GRA and TA positions after their first semester';$300k+奖学金/年</t>
         </is>
       </c>
-      <c r="F133" s="21" t="n"/>
-      <c r="G133" s="21" t="n"/>
-      <c r="H133" s="21" t="n"/>
-      <c r="I133" s="21" t="n"/>
-      <c r="J133" s="21" t="n"/>
-      <c r="K133" s="21" t="n"/>
+      <c r="F133" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述可写感兴趣教授/方向</t>
+        </is>
+      </c>
+      <c r="G133" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(第一学期后可申GRA/TA)。先修:无指定本科专业;1000–1500字目的陈述,另可提交可选写作样本</t>
+        </is>
+      </c>
+      <c r="H133" s="30" t="inlineStr">
+        <is>
+          <t>2027/1/3 10:59PM CST(官网,仅秋季入学);⚠️ 第三方列2026/12/15,以官网为准</t>
+        </is>
+      </c>
+      <c r="I133" s="30" t="inlineStr">
+        <is>
+          <t>不需要(MSCRP已永久免GRE)</t>
+        </is>
+      </c>
+      <c r="J133" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):UT研究生院豁免持美国院校学士学位者;否则 TOEFL ≥79 / IELTS ≥6.5 / DET ≥115</t>
+        </is>
+      </c>
+      <c r="K133" s="30" t="inlineStr">
+        <is>
+          <t>soa_grad@austin.utexas.edu(建筑学院研究生招生办);CRP-advisor@austin.utexas.edu(MSCRP研究生顾问)</t>
+        </is>
+      </c>
       <c r="L133" s="21" t="inlineStr">
         <is>
           <t>https://soa.utexas.edu/apply/financial-support</t>
@@ -7416,16 +7847,36 @@
           <t>'Both US and non-US citizens are eligible for merit-based scholarships';委员会审核时分配</t>
         </is>
       </c>
-      <c r="F134" s="21" t="n"/>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,委员会审核时分配奖学金</t>
+        </is>
+      </c>
       <c r="G134" s="21" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="H134" s="21" t="n"/>
-      <c r="I134" s="21" t="n"/>
-      <c r="J134" s="21" t="n"/>
-      <c r="K134" s="21" t="n"/>
+      <c r="H134" s="30" t="inlineStr">
+        <is>
+          <t>2027/1/13 11:59PM ET(Weitzman官网,2027秋季MCP)</t>
+        </is>
+      </c>
+      <c r="I134" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:How to Apply页仍将MCP列入标准化考试要求(5年有效),旧页面曾称Fall 2023免GRE;建议按需提交或邮件确认</t>
+        </is>
+      </c>
+      <c r="J134" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):Weitzman规定本科≥4年非英语授课者才需提交;美国本科英语授课无需提交。如需提交仅接受 TOEFL/IELTS/Duolingo</t>
+        </is>
+      </c>
+      <c r="K134" s="30" t="inlineStr">
+        <is>
+          <t>admissions@design.upenn.edu(Weitzman招生办);cityplan@design.upenn.edu(城市与区域规划系)</t>
+        </is>
+      </c>
       <c r="L134" s="21" t="inlineStr">
         <is>
           <t>https://www.design.upenn.edu/graduate-admissions/tuition-and-financial-aid</t>
@@ -7458,16 +7909,32 @@
           <t>'GE awards include a full tuition waiver, health insurance, and a competitive monthly stipend';'approximately 30 terms of GE positions per year'(≈10个全年,跨MCRP/MPA/MNM);优先2/1</t>
         </is>
       </c>
-      <c r="F135" s="21" t="n"/>
-      <c r="G135" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H135" s="21" t="n"/>
-      <c r="I135" s="21" t="n"/>
+      <c r="F135" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可参加线上信息会(2026/11/13、2027/1/15)</t>
+        </is>
+      </c>
+      <c r="G135" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GE含全额学费减免+医保+月薪)。先修:无指定专业;需修过高年级本科或研究生入门统计(可作PPPM 613前置/同修,相当课程或工作经验可豁免);3封推荐信</t>
+        </is>
+      </c>
+      <c r="H135" s="30" t="inlineStr">
+        <is>
+          <t>优先 2027/2/1;最终 2027/8/15(太平洋时间23:59);逾期视名额接收</t>
+        </is>
+      </c>
+      <c r="I135" s="30" t="inlineStr">
+        <is>
+          <t>可选(提交则综合考虑,也接受GMAT)</t>
+        </is>
+      </c>
       <c r="J135" s="21" t="n"/>
-      <c r="K135" s="21" t="n"/>
+      <c r="K135" s="30" t="inlineStr">
+        <is>
+          <t>choquett@uoregon.edu(研究生协调员Bob Choquette);abrown33@uoregon.edu(MCRP主任Anne Brown)</t>
+        </is>
+      </c>
       <c r="L135" s="21" t="inlineStr">
         <is>
           <t>https://pppm.uoregon.edu/grad/funding</t>
@@ -7500,12 +7967,32 @@
           <t>GA:≥9学分学费减免+部分fee+月stipend;PPDA两年承诺(学费≤36学分/年+时薪)每届约2人</t>
         </is>
       </c>
-      <c r="F136" s="21" t="n"/>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可预约与MURP主任一对一交流</t>
+        </is>
+      </c>
       <c r="G136" s="21" t="n"/>
-      <c r="H136" s="21" t="n"/>
-      <c r="I136" s="21" t="n"/>
-      <c r="J136" s="21" t="n"/>
-      <c r="K136" s="21" t="n"/>
+      <c r="H136" s="30" t="inlineStr">
+        <is>
+          <t>优先 2026/1/9;第二轮 3/27;第三轮 5/29(补充材料各轮后一周)(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I136" s="30" t="inlineStr">
+        <is>
+          <t>不接受(自Fall 2021起GRE不再纳入审核)</t>
+        </is>
+      </c>
+      <c r="J136" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 否(美国学位豁免):PSU研究生英语要求页(ondeck子域)列美国学士学位为有效证明;否则 TOEFL ≥80(2年内)</t>
+        </is>
+      </c>
+      <c r="K136" s="30" t="inlineStr">
+        <is>
+          <t>murpadm@pdx.edu(MURP招生);⚠️ askusp@pdx.edu(第三方列出)</t>
+        </is>
+      </c>
       <c r="L136" s="21" t="inlineStr">
         <is>
           <t>https://www.pdx.edu/urban-studies-planning/financial-resources</t>
@@ -7538,16 +8025,36 @@
           <t>Full line=20h/周+9学分学费+stipend;资助截止3/15;研究生院明文国际生可获系管奖学金与assistantship</t>
         </is>
       </c>
-      <c r="F137" s="21" t="n"/>
+      <c r="F137" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
       <c r="G137" s="21" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="H137" s="21" t="n"/>
-      <c r="I137" s="21" t="n"/>
-      <c r="J137" s="21" t="n"/>
-      <c r="K137" s="21" t="n"/>
+      <c r="H137" s="30" t="inlineStr">
+        <is>
+          <t>资助截止 2027/3/15(仅秋季);⚠️ 非资助申请可能为滚动录取(据MRP/JD页,建议3/15前提交)</t>
+        </is>
+      </c>
+      <c r="I137" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 可能不需要:第三方称独立MRP无GRE要求,官网未确认</t>
+        </is>
+      </c>
+      <c r="J137" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):在美国院校完成≥4个全日制学期且平均≥B可申请豁免(研究生院评估);否则 ⚠️ TOEFL 79 / IELTS 6.5 / Duolingo 110 / PTE 53</t>
+        </is>
+      </c>
+      <c r="K137" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ lawsonc@albany.edu(Regional Planning研究生主任Catherine Lawson,邮箱来自旧页面,建议核实)</t>
+        </is>
+      </c>
       <c r="L137" s="21" t="inlineStr">
         <is>
           <t>https://www.albany.edu/geographyplanning/programs/mrp-urban-and-regional-planning</t>
@@ -7580,12 +8087,28 @@
           <t>两年RA(stipend+24学分学费)限BIPOC/Hispanic GPA≥3.5;FDOT Transit Fellow一年stipend+全额学费;系资助申请2/15</t>
         </is>
       </c>
-      <c r="F138" s="21" t="n"/>
+      <c r="F138" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,滚动审理</t>
+        </is>
+      </c>
       <c r="G138" s="21" t="n"/>
-      <c r="H138" s="21" t="n"/>
-      <c r="I138" s="21" t="n"/>
+      <c r="H138" s="30" t="inlineStr">
+        <is>
+          <t>系资助 2027/2/15;国际生秋季 2027/1/15(⚠️ 页面正文另写6/1,冲突);美国申请者 7/1;滚动录取</t>
+        </is>
+      </c>
+      <c r="I138" s="30" t="inlineStr">
+        <is>
+          <t>不需要(MSP暂免GRE)</t>
+        </is>
+      </c>
       <c r="J138" s="21" t="n"/>
-      <c r="K138" s="21" t="n"/>
+      <c r="K138" s="30" t="inlineStr">
+        <is>
+          <t>durp@coss.fsu.edu(DURP招生协调员)</t>
+        </is>
+      </c>
       <c r="L138" s="21" t="inlineStr">
         <is>
           <t>https://cosspp.fsu.edu/durp/Admissions/</t>
@@ -7618,12 +8141,32 @@
           <t>Irving Harris MCH Scholars:每年 3 个新生获学费减免+月津贴(一年级秋春);MCH MPH Scholars 2/yr $2,000-5,000</t>
         </is>
       </c>
-      <c r="F139" s="21" t="n"/>
+      <c r="F139" s="30" t="inlineStr">
+        <is>
+          <t>不需要:SOPHAS统一申请,按项目整体录取</t>
+        </is>
+      </c>
       <c r="G139" s="21" t="n"/>
-      <c r="H139" s="21" t="n"/>
-      <c r="I139" s="21" t="n"/>
-      <c r="J139" s="21" t="n"/>
-      <c r="K139" s="21" t="n"/>
+      <c r="H139" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网冲突:MCH页写国际生 2026/12/15、国内 2027/2/1;SPH总页写资助优先 12/1、国际生 2/1、最终 4/15;建议12/1前提交</t>
+        </is>
+      </c>
+      <c r="I139" s="30" t="inlineStr">
+        <is>
+          <t>可选(提交会被考虑,代码7931)</t>
+        </is>
+      </c>
+      <c r="J139" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):UIC豁免近5年内在美国认证院校全日制学习≥2年者;否则 TOEFL iBT 80(新制4.5)/ IELTS 6.5 / PTE 54</t>
+        </is>
+      </c>
+      <c r="K139" s="30" t="inlineStr">
+        <is>
+          <t>sph-admissions@uic.edu(公卫学院招生);jacobw@uic.edu(招生助理主任Jacob Wilson)</t>
+        </is>
+      </c>
       <c r="L139" s="21" t="inlineStr">
         <is>
           <t>https://maternalchild.uic.edu/admissions/financial-aid-and-scholarships</t>
@@ -7930,28 +8473,28 @@
           <t>TA/RA/work-study多渠道;无学费减免说明</t>
         </is>
       </c>
-      <c r="F147" s="29" t="inlineStr">
+      <c r="F147" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取;个人陈述中写明研究兴趣与感兴趣的教师即可</t>
         </is>
       </c>
-      <c r="G147" s="29" t="inlineStr">
+      <c r="G147" s="30" t="inlineStr">
         <is>
           <t>可以申请(资助为TA/RA/work-study,未见学费减免说明)。需学士学位,总GPA≥3.0;心理学专业或具足够心理学背景(大学数学、统计、实验心理学及生物/物理/社会科学基础);非心理专业建议补统计、研究方法、认知、生理心理、社会心理等;未完全达标的优秀者也可被考虑</t>
         </is>
       </c>
-      <c r="H147" s="29" t="inlineStr">
+      <c r="H147" s="30" t="inlineStr">
         <is>
           <t>2026/12/15(系FAQ:全部材料截止,次年秋季入学);⚠️ 校目录(2025/6)写1/1,以系网站为准</t>
         </is>
       </c>
-      <c r="I147" s="29" t="inlineStr">
+      <c r="I147" s="30" t="inlineStr">
         <is>
           <t>不需要(系FAQ明确不要求;旧手册写可选)</t>
         </is>
       </c>
       <c r="J147" s="21" t="n"/>
-      <c r="K147" s="29" t="inlineStr">
+      <c r="K147" s="30" t="inlineStr">
         <is>
           <t>alac@uccs.edu(Andrew Lac,Psychological Science培养主任);intladms@uccs.edu(国际生招生)</t>
         </is>
@@ -7988,32 +8531,32 @@
           <t>校级GA:tuition remission+月薪+医保;硕士≤4学期</t>
         </is>
       </c>
-      <c r="F148" s="29" t="inlineStr">
+      <c r="F148" s="30" t="inlineStr">
         <is>
           <t>建议:研究型MA(Plan A论文),个人陈述写明匹配教师;官网未要求申请前联系</t>
         </is>
       </c>
-      <c r="G148" s="29" t="inlineStr">
+      <c r="G148" s="30" t="inlineStr">
         <is>
           <t>可以申请(校级GA含学费减免+月薪+医保)。学士学位GPA≥3.0;≥15学分心理学课程,须含基础统计、高年级实验课,以及以实验方法为主的独立研究(数据收集、统计分析、报告写作);方向:Cognitive/Developmental/Neuroscience &amp; Behavior</t>
         </is>
       </c>
-      <c r="H148" s="29" t="inlineStr">
+      <c r="H148" s="30" t="inlineStr">
         <is>
           <t>1/10(按2026周期为2026/1/10,2027待公布)</t>
         </is>
       </c>
-      <c r="I148" s="29" t="inlineStr">
+      <c r="I148" s="30" t="inlineStr">
         <is>
           <t>可选:提交与否均审核</t>
         </is>
       </c>
-      <c r="J148" s="29" t="inlineStr">
+      <c r="J148" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免);否则 TOEFL iBT ≥80,IELTS ≥6.5,PTE ≥53,Duolingo ≥110</t>
         </is>
       </c>
-      <c r="K148" s="29" t="inlineStr">
+      <c r="K148" s="30" t="inlineStr">
         <is>
           <t>unopsycgrad@unomaha.edu(心理系研究生项目)</t>
         </is>
@@ -8050,27 +8593,27 @@
           <t>GIA岗位需按优先截止申请;GTA限二年级;GRA看导师经费</t>
         </is>
       </c>
-      <c r="F149" s="29" t="inlineStr">
+      <c r="F149" s="30" t="inlineStr">
         <is>
           <t>建议:申请材料须按偏好列出3位匹配教师(研究兴趣声明);GRA看导师经费,可提前邮件联系</t>
         </is>
       </c>
-      <c r="G149" s="29" t="inlineStr">
+      <c r="G149" s="30" t="inlineStr">
         <is>
           <t>可以申请(GIA岗位需按优先截止申请;GTA限二年级)。GPA≥3.0;心理学导论、统计、实验/研究方法(或相关学科)须B及以上;需研究兴趣声明、简历/CV、1-2页个人陈述;国际学历申请费$90</t>
         </is>
       </c>
-      <c r="H149" s="29" t="inlineStr">
+      <c r="H149" s="30" t="inlineStr">
         <is>
           <t>资助优先 2026/2/1;最终 2026/4/30(按2026周期,2027待公布);仅秋季入学</t>
         </is>
       </c>
-      <c r="I149" s="29" t="inlineStr">
+      <c r="I149" s="30" t="inlineStr">
         <is>
           <t>不需要(明确不纳入录取考虑)</t>
         </is>
       </c>
-      <c r="J149" s="29" t="inlineStr">
+      <c r="J149" s="30" t="inlineStr">
         <is>
           <t>否(美国区域认证学士学位豁免);否则 TOEFL iBT ≥78(2026/1/21前考试的标准,新分制下要求待确认)</t>
         </is>
@@ -8732,27 +9275,27 @@
           <t>GA薪资表:MS $18,348–27,800/yr,Tuition Waiver: YES;由导师发布岗位</t>
         </is>
       </c>
-      <c r="F166" s="29" t="inlineStr">
+      <c r="F166" s="30" t="inlineStr">
         <is>
           <t>强烈建议:官网要求先匹配兴趣相符的教师并获其支持作为major professor;GA岗位多由导师发布</t>
         </is>
       </c>
-      <c r="G166" s="29" t="inlineStr">
+      <c r="G166" s="30" t="inlineStr">
         <is>
           <t>可以申请。先修:欢迎林业、渔业、野生动物及其他背景,背景不符可能需补课;硕士最低本科GPA 3.0。TA另需符合UGA TA英语政策</t>
         </is>
       </c>
-      <c r="H166" s="29" t="inlineStr">
+      <c r="H166" s="30" t="inlineStr">
         <is>
           <t>Graduate School助教金截止 12/1(建议 2026/12/1 前完成申请以竞争资助);最终截止:国际生 4/15、国内 7/1(按官网常规日期,2027待核实)</t>
         </is>
       </c>
-      <c r="I166" s="29" t="inlineStr">
+      <c r="I166" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:Warnell助研岗位注明不需要GRE;Peterson's(第三方)仍列GRE,建议邮件确认</t>
         </is>
       </c>
-      <c r="J166" s="29" t="inlineStr">
+      <c r="J166" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):UGA研究生院规定美国认证大学学位一般免交TOEFL/IELTS(个别项目可另要求);如需:TOEFL 80(各项≥20)/IELTS 6.5;当TA另有英语要求</t>
         </is>
@@ -8790,32 +9333,32 @@
           <t>'limited number of assistantships on a competitive basis';MS stipend $16,500/yr+全额学费减免(自付fees)</t>
         </is>
       </c>
-      <c r="F167" s="29" t="inlineStr">
+      <c r="F167" s="30" t="inlineStr">
         <is>
           <t>必须:SRNR录取要求申请时已确定major professor,建议先联系导师确认岗位</t>
         </is>
       </c>
-      <c r="G167" s="29" t="inlineStr">
+      <c r="G167" s="30" t="inlineStr">
         <is>
           <t>可以申请(资助为竞争性少量assistantship)。先修:认证大学学士学位,需获项目51%研究生教师认可并有确定导师;成功申请者一般GPA≥3.25、GRE V+Q≥300</t>
         </is>
       </c>
-      <c r="H167" s="29" t="inlineStr">
+      <c r="H167" s="30" t="inlineStr">
         <is>
           <t>⚠️ 研究生院历史资助优先日 1/25;国际生最终截止 5/1 或 5/15(LSU不同页面冲突),国内约 6/30–7/1;项目可能更早(按往年,2027待公布)</t>
         </is>
       </c>
-      <c r="I167" s="29" t="inlineStr">
+      <c r="I167" s="30" t="inlineStr">
         <is>
           <t>⚠️ 必需/参考:官网称成功申请者GRE V+Q一般≥300;Gilbert资助要求≥310,建议确认是否仍强制</t>
         </is>
       </c>
-      <c r="J167" s="29" t="inlineStr">
+      <c r="J167" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):LSU规定持美国院校学士学位可免;如需:TOEFL 79,IELTS 6.5</t>
         </is>
       </c>
-      <c r="K167" s="29" t="inlineStr">
+      <c r="K167" s="30" t="inlineStr">
         <is>
           <t>⚠️ staylor@lsu.edu(研究生协调员 Dr. Sabrina Taylor,官网不同版本另列 wkelso@lsu.edu);gradadmission@lsu.edu(研究生院招生)</t>
         </is>
@@ -8852,28 +9395,28 @@
           <t>'application will not be reviewed until you and your future advisor have arrangements for funding';GRA经导师</t>
         </is>
       </c>
-      <c r="F168" s="29" t="inlineStr">
+      <c r="F168" s="30" t="inlineStr">
         <is>
           <t>必须:须有教师同意担任导师才会审理申请;thesis MS须与导师落实资助方案后才审</t>
         </is>
       </c>
-      <c r="G168" s="29" t="inlineStr">
+      <c r="G168" s="30" t="inlineStr">
         <is>
           <t>可以申请,但须先落实导师和资助(GRA经导师)。先修:⚠️ 官网未列具体先修课,建议咨询研究生顾问</t>
         </is>
       </c>
-      <c r="H168" s="29" t="inlineStr">
+      <c r="H168" s="30" t="inlineStr">
         <is>
           <t>奖学金提名 2026/12/31(需完成申请);国际生最终 2027/2/1;国内 2027/5/1</t>
         </is>
       </c>
       <c r="I168" s="21" t="n"/>
-      <c r="J168" s="29" t="inlineStr">
+      <c r="J168" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):TAMU规定持美国认证院校学士学位免交成绩(项目可另设更高要求);当TA需通过ELPE口语(≥80)或申请替代认证</t>
         </is>
       </c>
-      <c r="K168" s="29" t="inlineStr">
+      <c r="K168" s="30" t="inlineStr">
         <is>
           <t>⚠️ 官网邮箱未能读取:研究生学术顾问 Wenwen Zhou,电话979-314-5715,建议通过rwfm.tamu.edu/contact-advisor联系</t>
         </is>
@@ -8910,24 +9453,24 @@
           <t>入学时部分学费merit奖;GSI/GSRA含全额学费+医保+stipend但竞争性、多入学后申请</t>
         </is>
       </c>
-      <c r="F169" s="29" t="inlineStr">
+      <c r="F169" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取;GSRA多入学后申请,可在申请材料中提及感兴趣教授</t>
         </is>
       </c>
       <c r="G169" s="21" t="n"/>
-      <c r="H169" s="29" t="inlineStr">
+      <c r="H169" s="30" t="inlineStr">
         <is>
           <t>资助优先 2026/12/15;资助最终 2027/1/14;最终:国际生 2027/4/1,国内 2027/4/30</t>
         </is>
       </c>
-      <c r="I169" s="29" t="inlineStr">
+      <c r="I169" s="30" t="inlineStr">
         <is>
           <t>不接受(已不再要求也不接受GRE)</t>
         </is>
       </c>
       <c r="J169" s="21" t="n"/>
-      <c r="K169" s="29" t="inlineStr">
+      <c r="K169" s="30" t="inlineStr">
         <is>
           <t>⚠️ seas-admissions@umich.edu(SEAS招生,据记忆需核实);电话 (734) 764-6453</t>
         </is>
@@ -9666,28 +10209,28 @@
           <t>'Assistantships provide a tuition waiver and a stipend';硕士最多2年半时;non-thesis低优先</t>
         </is>
       </c>
-      <c r="F187" s="29" t="inlineStr">
+      <c r="F187" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不需要(官网未要求):按项目整体录取;可在个人陈述中写方向匹配的教授,或先联系方向负责人(如犯罪学 Katie Constantin)</t>
         </is>
       </c>
-      <c r="G187" s="29" t="inlineStr">
+      <c r="G187" s="30" t="inlineStr">
         <is>
           <t>可以申请(助教/助研含学费减免+津贴,国际生可申)。先修:官网未列明最低GPA与必修先修课;项目核心为理论、方法、统计。材料:CV、3位推荐人、2-3页个人陈述、非正式成绩单,写作样本可选</t>
         </is>
       </c>
-      <c r="H187" s="29" t="inlineStr">
+      <c r="H187" s="30" t="inlineStr">
         <is>
           <t>资助优先 2027/2/1;秋季最终 2027/4/1(据系研究生手册2025年12月版;旧页面曾写4/15,2027待确认)</t>
         </is>
       </c>
-      <c r="I187" s="29" t="inlineStr">
+      <c r="I187" s="30" t="inlineStr">
         <is>
           <t>不需要(系申请页明确不再要求GRE)</t>
         </is>
       </c>
       <c r="J187" s="21" t="n"/>
-      <c r="K187" s="29" t="inlineStr">
+      <c r="K187" s="30" t="inlineStr">
         <is>
           <t>jonathan.s.coley@okstate.edu(研究生项目主任 Jonathan Coley);grad-i@okstate.edu(研究生院国际招生)</t>
         </is>
@@ -9724,7 +10267,7 @@
           <t>'All applicants are considered for funding';GA stipend $18,540/9月</t>
         </is>
       </c>
-      <c r="F188" s="29" t="inlineStr">
+      <c r="F188" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,所有申请者自动参与资助评审;目标陈述中写研究兴趣及与教师的匹配即可</t>
         </is>
@@ -9735,13 +10278,13 @@
         </is>
       </c>
       <c r="H188" s="21" t="n"/>
-      <c r="I188" s="29" t="inlineStr">
+      <c r="I188" s="30" t="inlineStr">
         <is>
           <t>不需要(自2026秋季入学起取消GRE;旧版2025-26目录仍写需要)</t>
         </is>
       </c>
       <c r="J188" s="21" t="n"/>
-      <c r="K188" s="29" t="inlineStr">
+      <c r="K188" s="30" t="inlineStr">
         <is>
           <t>sroxburg@kent.edu(研究生项目协调员 Susan Roxburgh);soc_crim@kent.edu(系办公室)</t>
         </is>
@@ -9778,7 +10321,7 @@
           <t>GA+学费杂费减免'including out-of-state or international tuition';通常2年</t>
         </is>
       </c>
-      <c r="F189" s="29" t="inlineStr">
+      <c r="F189" s="30" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取;个人陈述说明攻读社会学的原因与兴趣方向即可</t>
         </is>
@@ -9788,18 +10331,18 @@
           <t>可</t>
         </is>
       </c>
-      <c r="H189" s="29" t="inlineStr">
+      <c r="H189" s="30" t="inlineStr">
         <is>
           <t>GA资助优先 2027/3/1;最终:国际生 2027/5/1(秋季),国内 2027/7/1(按系官网现行日期,2027待确认)</t>
         </is>
       </c>
-      <c r="I189" s="29" t="inlineStr">
+      <c r="I189" s="30" t="inlineStr">
         <is>
           <t>不需要(系官网明确不要求GRE;Peterson's称需要,已过时)</t>
         </is>
       </c>
       <c r="J189" s="21" t="n"/>
-      <c r="K189" s="29" t="inlineStr">
+      <c r="K189" s="30" t="inlineStr">
         <is>
           <t>socgradcoord@memphis.edu(研究生项目邮箱);tmccuddy@memphis.edu(研究生主任 Timothy McCuddy)</t>
         </is>
@@ -10464,22 +11007,22 @@
           <t>'limited number of graduate assistantships…we cannot make any guarantees';'primarily awarded to doctoral students'</t>
         </is>
       </c>
-      <c r="F206" s="30" t="inlineStr">
+      <c r="F206" s="31" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,每年仅秋季入学一次;个人陈述可写感兴趣的教授</t>
         </is>
       </c>
-      <c r="G206" s="30" t="inlineStr">
+      <c r="G206" s="31" t="inlineStr">
         <is>
           <t>可以申请,但资助极少(系招生页称目前不为硕士生提供assistantship,GA主要给博士)。先修:美国认证大学学士学位;无指定专业先修课;需700–1200词个人陈述、3封推荐信、全部成绩单;⚠️ 最低GPA系页未写明(研究生院通常要求约2.75,建议确认)</t>
         </is>
       </c>
-      <c r="H206" s="30" t="inlineStr">
+      <c r="H206" s="31" t="inlineStr">
         <is>
           <t>2027/1/15(按系研究生手册2024–25所列每年1/15截止,2027待公布);每年仅秋季入学一次</t>
         </is>
       </c>
-      <c r="I206" s="30" t="inlineStr">
+      <c r="I206" s="31" t="inlineStr">
         <is>
           <t>不需要(系招生页明确不要求GRE)</t>
         </is>
@@ -10518,32 +11061,32 @@
           <t>'Applicants may be considered for graduate assistantships from the Department'</t>
         </is>
       </c>
-      <c r="F207" s="30" t="inlineStr">
+      <c r="F207" s="31" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,GA随申请自动考虑无需另申;个人陈述可写感兴趣的方向/教授</t>
         </is>
       </c>
-      <c r="G207" s="30" t="inlineStr">
+      <c r="G207" s="31" t="inlineStr">
         <is>
           <t>可以申请(系里可考虑授予GA,无需单独申请;当TA需满足伊州非母语TA英语要求)。先修:区域认证大学四年制学士;最后60学时GPA≥3.0;目的陈述+3位推荐人;无指定专业先修课</t>
         </is>
       </c>
-      <c r="H207" s="30" t="inlineStr">
+      <c r="H207" s="31" t="inlineStr">
         <is>
           <t>2027/2/1(按官网秋季截止2/1,2027待公布);GA随申请一并考虑,建议尽早提交</t>
         </is>
       </c>
-      <c r="I207" s="30" t="inlineStr">
+      <c r="I207" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要(官网未列GRE;Peterson's仍列GRE,疑已过时)</t>
         </is>
       </c>
-      <c r="J207" s="30" t="inlineStr">
+      <c r="J207" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:ISU英语豁免指南列有美国区域认证学士学位这一豁免途径,但表格显示可能仅对应部分pathway,需向 InternationalAdmissions@IllinoisState.edu 确认;不豁免则 TOEFL ≥81,IELTS ≥6.5,Duolingo ≥110。当TA另需伊州非母语TA英语证明(如IELTS 8.0)</t>
         </is>
       </c>
-      <c r="K207" s="30" t="inlineStr">
+      <c r="K207" s="31" t="inlineStr">
         <is>
           <t>fcs@ilstu.edu(系办公室;研究生顾问 Dr. Jen Barnes,电话309-438-3558)</t>
         </is>
@@ -10580,27 +11123,27 @@
           <t>仅校级GA池:最低stipend $3,200/学期,部分至全额学费减免</t>
         </is>
       </c>
-      <c r="F208" s="30" t="inlineStr">
+      <c r="F208" s="31" t="inlineStr">
         <is>
           <t>不需要:经HAMPCAS统一申请,按项目整体录取,入围者需面试</t>
         </is>
       </c>
-      <c r="G208" s="30" t="inlineStr">
+      <c r="G208" s="31" t="inlineStr">
         <is>
           <t>可以申请(国际生可申请校级GA池)。先修:认证院校学士学位;累计GPA≥3.0(不足可用最近40学分的替代GPA);无指定专业先修课;经HAMPCAS申请,需面试</t>
         </is>
       </c>
-      <c r="H208" s="30" t="inlineStr">
+      <c r="H208" s="31" t="inlineStr">
         <is>
           <t>优先 3/1;需F-1签证的国际生 4/15;之后滚动审核至招满(按2025周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I208" s="30" t="inlineStr">
+      <c r="I208" s="31" t="inlineStr">
         <is>
           <t>不需要(官网明确不要求GRE/GMAT)</t>
         </is>
       </c>
-      <c r="J208" s="30" t="inlineStr">
+      <c r="J208" s="31" t="inlineStr">
         <is>
           <t>⚠️ 很可能否:ODU英语要求页列'在英语为官方语言国家的认证院校获学士/硕士学位'可满足要求(未点名美国,措辞有版本差异);否则 TOEFL iBT ≥79(2026/1/21后新制≥4.5),IELTS ≥6.5,Duolingo ≥120</t>
         </is>
@@ -10638,32 +11181,32 @@
           <t>'GRA positions advertised within the department when faculty have funded research'</t>
         </is>
       </c>
-      <c r="F209" s="30" t="inlineStr">
+      <c r="F209" s="31" t="inlineStr">
         <is>
           <t>不需要:项目整体综合录取,符合条件者需与教师进行简短面试</t>
         </is>
       </c>
-      <c r="G209" s="30" t="inlineStr">
+      <c r="G209" s="31" t="inlineStr">
         <is>
           <t>可以申请(GRA仅在教师有经费项目时系内招聘,不保证)。先修:区域认证大学学士;GPA≥3.0;医疗行业工作经验优先但非必需;需目标陈述、简历、成绩单(⚠️推荐信要求各页面说法不一);⚠️ F-1需确认就读校园面授班</t>
         </is>
       </c>
-      <c r="H209" s="30" t="inlineStr">
+      <c r="H209" s="31" t="inlineStr">
         <is>
           <t>优先截止:秋季 4/1(春季 11/1),之后视名额继续审核(按现行官网,2027待公布)</t>
         </is>
       </c>
-      <c r="I209" s="30" t="inlineStr">
+      <c r="I209" s="31" t="inlineStr">
         <is>
           <t>不需要(官网称GRE/GMAT已不再要求)</t>
         </is>
       </c>
-      <c r="J209" s="30" t="inlineStr">
+      <c r="J209" s="31" t="inlineStr">
         <is>
           <t>否(美国区域认证大学学位豁免,GMU全校政策)</t>
         </is>
       </c>
-      <c r="K209" s="30" t="inlineStr">
+      <c r="K209" s="31" t="inlineStr">
         <is>
           <t>muriyo@gmu.edu(MHA项目协调员 Dr. Maria Uriyo);masongrad@gmu.edu(研究生招生)</t>
         </is>
@@ -11306,7 +11849,7 @@
           <t>'A number of graduate assistantships awarded each year';GA含stipend+学费减免+医保;无硕士比例</t>
         </is>
       </c>
-      <c r="F225" s="30" t="inlineStr">
+      <c r="F225" s="31" t="inlineStr">
         <is>
           <t>不需要:MPH经SOPHAS按项目整体录取;GA多由教师科研经费资助,无正式申请流程,录取后可主动联系有经费的教师</t>
         </is>
@@ -11316,22 +11859,22 @@
           <t>未说明</t>
         </is>
       </c>
-      <c r="H225" s="30" t="inlineStr">
+      <c r="H225" s="31" t="inlineStr">
         <is>
           <t>⚠️ 资助/GA考虑截止 2027/1/5;最终截止 2027/5/1(据UGA Bulletin HPM方向页面,未标年份,按往年惯例推定,2027待公布)</t>
         </is>
       </c>
-      <c r="I225" s="30" t="inlineStr">
+      <c r="I225" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要(第三方称MPH已不要求GRE,UGA DrPH官网亦已取消;MPH页未直接确认)</t>
         </is>
       </c>
-      <c r="J225" s="30" t="inlineStr">
+      <c r="J225" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免):UGA研究生院2025/3/12新政,美国认证院校学位免TOEFL/IELTS(个别院系可另行要求);否则TOEFL ≥80(口语/写作≥20)或IELTS ≥6.5(单项≥6.0),不接受Duolingo;如任TA另需满足TA英语政策</t>
         </is>
       </c>
-      <c r="K225" s="30" t="inlineStr">
+      <c r="K225" s="31" t="inlineStr">
         <is>
           <t>mph@uga.edu(校园MPH招生办);gradadm@uga.edu(研究生院招生)</t>
         </is>
@@ -11368,28 +11911,28 @@
           <t>校级:'Most assistantships are awarded to doctoral students';学院GA页未抓到</t>
         </is>
       </c>
-      <c r="F226" s="30" t="inlineStr">
+      <c r="F226" s="31" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,个人陈述可写感兴趣方向/教授;校级GA多给博士生</t>
         </is>
       </c>
-      <c r="G226" s="30" t="inlineStr">
+      <c r="G226" s="31" t="inlineStr">
         <is>
           <t>可以申请(国际生可申请;校级称GA多授予博士生,硕士资助有限)。先修:认证院校学士学位,本科GPA ≥3.0;需个人陈述、简历、成绩单、推荐信(官网说法2–3封不一);国际生另需财力证明等签证材料</t>
         </is>
       </c>
-      <c r="H226" s="30" t="inlineStr">
+      <c r="H226" s="31" t="inlineStr">
         <is>
           <t>⚠️ 官网说法不一:catalog称国际生秋季优先截止 3/15;国际招生页称秋季 6/15,截止后仍可能受理;建议 2027/3/15 前提交(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I226" s="30" t="inlineStr">
+      <c r="I226" s="31" t="inlineStr">
         <is>
           <t>不需要(学院明确MPH/MS不要求GRE,仅PhD需要)</t>
         </is>
       </c>
       <c r="J226" s="22" t="n"/>
-      <c r="K226" s="30" t="inlineStr">
+      <c r="K226" s="31" t="inlineStr">
         <is>
           <t>publichealth@kent.edu(公共卫生学院总邮箱);⚠️ kbaker80@kent.edu(研究生项目助理协调员,目录信息待核实)</t>
         </is>
@@ -12182,32 +12725,32 @@
           <t>'limited number of tuition waivers to first-year';assistantships'rarely awarded in the first semester'</t>
         </is>
       </c>
-      <c r="F245" s="30" t="inlineStr">
+      <c r="F245" s="31" t="inlineStr">
         <is>
           <t>不需要:专业型硕士按项目整体录取,个人陈述可写感兴趣的教授</t>
         </is>
       </c>
-      <c r="G245" s="30" t="inlineStr">
+      <c r="G245" s="31" t="inlineStr">
         <is>
           <t>可以申请(国际生可获有限的首年学费减免;assistantship首学期很少发放)。先修:区域认证学士学位,研究生院最低GPA 3.0;无指定本科专业</t>
         </is>
       </c>
-      <c r="H245" s="30" t="inlineStr">
+      <c r="H245" s="31" t="inlineStr">
         <is>
           <t>资助优先 1/19;其后 2/22、3/22 两轮,3/22后滚动审核至开学前一个月;国际生最晚 5/25(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I245" s="30" t="inlineStr">
+      <c r="I245" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要(第三方显示不要求GRE,官网未明确写出)</t>
         </is>
       </c>
-      <c r="J245" s="30" t="inlineStr">
+      <c r="J245" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免):研究生院规定在美国区域认证院校获学士及以上学位者免交;否则 TOEFL ≥79(口语≥26)/IELTS ≥7</t>
         </is>
       </c>
-      <c r="K245" s="30" t="inlineStr">
+      <c r="K245" s="31" t="inlineStr">
         <is>
           <t>capla-grad@arizona.edu(CAPLA研究生项目协调员)</t>
         </is>
@@ -12244,32 +12787,32 @@
           <t>系有若干GTA(MS 1年,可续);GA按居民学费+stipend+≤9学分fee waiver</t>
         </is>
       </c>
-      <c r="F246" s="30" t="inlineStr">
+      <c r="F246" s="31" t="inlineStr">
         <is>
           <t>建议:小型项目,GTA由系分配,可先邮件项目主任 Thomas Albright 了解研究方向与助教机会</t>
         </is>
       </c>
-      <c r="G246" s="30" t="inlineStr">
+      <c r="G246" s="31" t="inlineStr">
         <is>
           <t>可以申请(系有少量GTA,国际生可申)。先修:学士学位,GPA ≥3.0;需修过入门统计课(可在第一学期补修);需目的陈述+3封推荐信</t>
         </is>
       </c>
-      <c r="H246" s="30" t="inlineStr">
+      <c r="H246" s="31" t="inlineStr">
         <is>
           <t>秋季 2/1(2/1前完成申请保证被考虑;按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I246" s="30" t="inlineStr">
+      <c r="I246" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:2022-23目录写需提交GRE成绩;研究生院称由项目自定,建议邮件确认</t>
         </is>
       </c>
-      <c r="J246" s="30" t="inlineStr">
+      <c r="J246" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免):在美国认证英语授课院校在校(非网课)获学士及以上学位者免交;否则 TOEFL ≥79/IELTS ≥6.5</t>
         </is>
       </c>
-      <c r="K246" s="30" t="inlineStr">
+      <c r="K246" s="31" t="inlineStr">
         <is>
           <t>talbright@unr.edu(LUPP项目主任 Thomas Albright,⚠️来源较旧,需确认仍在任)</t>
         </is>
@@ -12306,18 +12849,18 @@
           <t>校级TA/RA/fellowship含stipend+tuition award;'in-state, out-of-state, or international student, you may be eligible'</t>
         </is>
       </c>
-      <c r="F247" s="30" t="inlineStr">
+      <c r="F247" s="31" t="inlineStr">
         <is>
           <t>不需要:专业型硕士按项目整体录取</t>
         </is>
       </c>
-      <c r="G247" s="30" t="inlineStr">
+      <c r="G247" s="31" t="inlineStr">
         <is>
           <t>可以申请(校级TA/RA/fellowship明确对国际生开放)。先修:区域认证学士学位;GPA ≥3.0正式录取,2.5–2.9可条件录取;需叙述性个人陈述+3封推荐信</t>
         </is>
       </c>
       <c r="H247" s="22" t="n"/>
-      <c r="I247" s="30" t="inlineStr">
+      <c r="I247" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:Peterson's列GRE为部分申请者需提交,另有第三方称不需要,建议邮件确认</t>
         </is>
@@ -12356,32 +12899,32 @@
           <t>仅$1,000–8,000奖学金;无assistantship说明</t>
         </is>
       </c>
-      <c r="F248" s="30" t="inlineStr">
+      <c r="F248" s="31" t="inlineStr">
         <is>
           <t>不需要:专业型硕士按项目整体录取</t>
         </is>
       </c>
-      <c r="G248" s="30" t="inlineStr">
+      <c r="G248" s="31" t="inlineStr">
         <is>
           <t>可以申请,但资助仅$1,000–8,000奖学金,无assistantship说明。先修:须获学士学位,最低GPA 3.0;无指定本科专业</t>
         </is>
       </c>
-      <c r="H248" s="30" t="inlineStr">
+      <c r="H248" s="31" t="inlineStr">
         <is>
           <t>秋季:国际生 12/15,本国生 1/15(须按时才有奖学金资格);迟交至 5/1按名额审核且不可获奖学金(官网当前页日期,2027周期待确认)</t>
         </is>
       </c>
-      <c r="I248" s="30" t="inlineStr">
+      <c r="I248" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要(官网录取页未提GRE;第三方称GPA&lt;3.0时需提交)</t>
         </is>
       </c>
-      <c r="J248" s="30" t="inlineStr">
+      <c r="J248" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免):在美国获学士及以上学位即满足英语要求;否则 TOEFL ≥79/IELTS ≥6.5</t>
         </is>
       </c>
-      <c r="K248" s="30" t="inlineStr">
+      <c r="K248" s="31" t="inlineStr">
         <is>
           <t>⚠️ 邮箱未在检索结果中显示:研究生招生经理 Jodi Stock(见学院staff页),学院电话 303-315-1000;jennifer.steffeljohnson@ucdenver.edu(MURP教师,⚠️来源可能过时)</t>
         </is>
@@ -13090,23 +13633,23 @@
           <t>'limited number of GTAs';州外学费减免仅第一年、只降到州内</t>
         </is>
       </c>
-      <c r="F265" s="30" t="inlineStr">
+      <c r="F265" s="31" t="inlineStr">
         <is>
           <t>⚠️ 官网未明确要求:按项目整体录取,可能面试;PSYS为读博/科研导向方向,建议陈述中写明匹配教授,可提前邮件联系</t>
         </is>
       </c>
-      <c r="G265" s="30" t="inlineStr">
+      <c r="G265" s="31" t="inlineStr">
         <is>
           <t>可以申请(GTA名额有限,州外学费减免仅第一年且只降到州内)。先修:期望心理学专业且心理学GPA≥3.0;非心理专业需≥21学分心理学课(含研究方法与统计,研究方法须为心理学课);总GPA≥3.0;3封推荐信(至少1封来自教授)、陈述、CV;只能申请一个方向</t>
         </is>
       </c>
       <c r="H265" s="22" t="n"/>
-      <c r="I265" s="30" t="inlineStr">
+      <c r="I265" s="31" t="inlineStr">
         <is>
           <t>不需要(官网FAQ:目前不考虑GRE)</t>
         </is>
       </c>
-      <c r="J265" s="30" t="inlineStr">
+      <c r="J265" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免:UNCW研究生院认可美国认证院校学士学位免语言成绩;否则 TOEFL ≥79)</t>
         </is>
@@ -13144,28 +13687,28 @@
           <t>系分配TA/RA;校外GA'discounted tuition rates'</t>
         </is>
       </c>
-      <c r="F266" s="30" t="inlineStr">
+      <c r="F266" s="31" t="inlineStr">
         <is>
           <t>⚠️ 官网未明确:HF方向规模小、偏实验室制,建议提前联系HF方向教师(目录联系人 Michael Granaas)</t>
         </is>
       </c>
-      <c r="G266" s="30" t="inlineStr">
+      <c r="G266" s="31" t="inlineStr">
         <is>
           <t>可以申请。先修:认证院校学士学位;最低GPA 3.0;推荐信2封(新版目录,旧版3封)、statement of purpose、成绩单;申请费$35;MA含必修实习;分论文/非论文(30–36学分)</t>
         </is>
       </c>
-      <c r="H266" s="30" t="inlineStr">
+      <c r="H266" s="31" t="inlineStr">
         <is>
           <t>⚠️ HFES目录:优先 12/31;最终按名额滚动(开学前约4周);官网目录另列秋季 8/1;Peterson's 列 2/1;第三方称国际生 7/20。建议 2026/12/31 前提交并邮件确认</t>
         </is>
       </c>
-      <c r="I266" s="30" t="inlineStr">
+      <c r="I266" s="31" t="inlineStr">
         <is>
           <t>⚠️ 可能不需要:HFES目录称 Fall 2023 起免GRE,官网目录未见GRE要求,建议确认</t>
         </is>
       </c>
       <c r="J266" s="22" t="n"/>
-      <c r="K266" s="30" t="inlineStr">
+      <c r="K266" s="31" t="inlineStr">
         <is>
           <t>⚠️ Michael.Granaas@usd.edu(HFES目录所列项目联系人,可能过时);心理系电话 605-658-6140</t>
         </is>
@@ -13202,32 +13745,32 @@
           <t>校级GA'stipend and possible tuition remission';国际生页明列assistantship为资助途径</t>
         </is>
       </c>
-      <c r="F267" s="30" t="inlineStr">
+      <c r="F267" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要:按项目整体录取(MA要求论文),陈述中可写感兴趣的教授</t>
         </is>
       </c>
-      <c r="G267" s="30" t="inlineStr">
+      <c r="G267" s="31" t="inlineStr">
         <is>
           <t>可以申请(国际生页明列assistantship为资助途径)。⚠️ 先修(Peterson's):心理学≥15学分(含心理统计、研究方法);最低GPA 2.7(General)/3.2(Clinical方向);需推荐信、个人陈述</t>
         </is>
       </c>
-      <c r="H267" s="30" t="inlineStr">
+      <c r="H267" s="31" t="inlineStr">
         <is>
           <t>⚠️ 第三方:General Psychology 3/1(国际生同,资助申请同为3/1);Clinical方向 2/15 优先;另有来源称统一 2/15。建议 2027/2/15 前提交(按旧周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I267" s="30" t="inlineStr">
+      <c r="I267" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:Peterson's 列必需(Clinical要求V+Q≥300、单项≥148);另一来源称可选,建议确认</t>
         </is>
       </c>
-      <c r="J267" s="30" t="inlineStr">
+      <c r="J267" s="31" t="inlineStr">
         <is>
           <t>⚠️ 大概率否:第三方(Studee)称在美国区域认证院校获学士可豁免;官网写 TOEFL iBT ≥80(部分项目更高),未直接查到豁免条款,建议向 goglobalgraduate@udayton.edu 确认</t>
         </is>
       </c>
-      <c r="K267" s="30" t="inlineStr">
+      <c r="K267" s="31" t="inlineStr">
         <is>
           <t>gradadmission@udayton.edu(研究生招生办,通用);goglobalgraduate@udayton.edu(国际研究生招生)</t>
         </is>
@@ -13264,18 +13807,18 @@
           <t>仅校级GA(≤20h/周);奖学金$1–2k</t>
         </is>
       </c>
-      <c r="F268" s="30" t="inlineStr">
+      <c r="F268" s="31" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取;须完成6学分论文,陈述中可写感兴趣的教授</t>
         </is>
       </c>
-      <c r="G268" s="30" t="inlineStr">
+      <c r="G268" s="31" t="inlineStr">
         <is>
           <t>可以申请(仅校级GA,每周≤20小时)。先修(2025–26目录):本科最后60学分GPA≥3.0;统计和/或研究方法本科课成绩B以上;3封推荐信;500词目标陈述;CV。论文型项目,共36学分,为读博做准备</t>
         </is>
       </c>
       <c r="H268" s="22" t="n"/>
-      <c r="I268" s="30" t="inlineStr">
+      <c r="I268" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要:2025–26目录未列GRE(旧目录曾要求 V153/Q144),建议确认</t>
         </is>
@@ -13944,28 +14487,28 @@
           <t>'try our best to fund our terminal master's degree students when resources are available';TA/RA=stipend+9学分学费</t>
         </is>
       </c>
-      <c r="F284" s="30" t="inlineStr">
+      <c r="F284" s="31" t="inlineStr">
         <is>
           <t>不需要:按项目整体录取,SOP需写研究兴趣及希望合作的系内教师</t>
         </is>
       </c>
-      <c r="G284" s="30" t="inlineStr">
+      <c r="G284" s="31" t="inlineStr">
         <is>
           <t>可以申请,但系里资助(TA等)主要给MS-to-PhD和PhD-only申请者,terminal MS只在有资源时尽量资助。先修:官网未列最低GPA或具体先修学分;MS必修社会学理论、研究方法、社会统计(SOCI 5050/5200/5210或同等课程)。材料:CV、SOP、2封推荐信、$75申请费(GradCAS)</t>
         </is>
       </c>
-      <c r="H284" s="30" t="inlineStr">
+      <c r="H284" s="31" t="inlineStr">
         <is>
           <t>资助优先 2027/2/1(秋季);之后每月滚动审核至 2027/7/31;MS-only也可春季入学,春季截止 11/30(⚠️ 官网未注明年份,建议核实)</t>
         </is>
       </c>
-      <c r="I284" s="30" t="inlineStr">
+      <c r="I284" s="31" t="inlineStr">
         <is>
           <t>不需要(系官网:GRE不要求)</t>
         </is>
       </c>
       <c r="J284" s="22" t="n"/>
-      <c r="K284" s="30" t="inlineStr">
+      <c r="K284" s="31" t="inlineStr">
         <is>
           <t>William.Scarborough@unt.edu(研究生项目主任);sociology@unt.edu(系办公室)</t>
         </is>
@@ -14044,27 +14587,27 @@
           <t>'Assistantships are available to a few select graduate students';GA按州内学费计,州外差额靠另一奖学金;截止2/15</t>
         </is>
       </c>
-      <c r="F286" s="30" t="inlineStr">
+      <c r="F286" s="31" t="inlineStr">
         <is>
           <t>不适用:该项目已停止招生</t>
         </is>
       </c>
-      <c r="G286" s="30" t="inlineStr">
+      <c r="G286" s="31" t="inlineStr">
         <is>
           <t>❌ 该项目已停止招收新生(ODU官网:this program is no longer accepting new students,学位须于2025年8月前完成;目录写已建议关闭)。原要求:GPA≥3.0,本科社会学或刑事司法≥12学分,含理论、研究方法、统计。系里目前只开设犯罪学与刑事司法PhD</t>
         </is>
       </c>
-      <c r="H286" s="30" t="inlineStr">
+      <c r="H286" s="31" t="inlineStr">
         <is>
           <t>❌ 已停招;原截止:GA 2/15,最终 3/1(仅秋季入学)</t>
         </is>
       </c>
-      <c r="I286" s="30" t="inlineStr">
+      <c r="I286" s="31" t="inlineStr">
         <is>
           <t>必需(原要求;项目已停招)</t>
         </is>
       </c>
-      <c r="J286" s="30" t="inlineStr">
+      <c r="J286" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:原要求非母语国际生 TOEFL 550(纸考)等,未写美国学位豁免;项目已停招</t>
         </is>
@@ -14144,28 +14687,28 @@
           <t>硕士'仅部分资助';merit 奖学金 ≤50% 州内学费;International Chancellor's Scholarship</t>
         </is>
       </c>
-      <c r="F288" s="30" t="inlineStr">
+      <c r="F288" s="31" t="inlineStr">
         <is>
           <t>不需要:硕士按项目整体录取(只有PhD申请者需在个人陈述中写希望合作的教师)</t>
         </is>
       </c>
-      <c r="G288" s="30" t="inlineStr">
+      <c r="G288" s="31" t="inlineStr">
         <is>
           <t>可以申请(有国际生专项奖 International Chancellor's Scholarship)。⚠️ 先修(按2023-2025目录):社会科学或相关专业本科,GPA≥3.3(录取者通常≥3.5);统计和研究方法课程成绩优秀;材料:成绩单、CV、3封推荐信</t>
         </is>
       </c>
       <c r="H288" s="22" t="n"/>
-      <c r="I288" s="30" t="inlineStr">
+      <c r="I288" s="31" t="inlineStr">
         <is>
           <t>⚠️ 目录未提GRE,可能不需要,建议确认</t>
         </is>
       </c>
-      <c r="J288" s="30" t="inlineStr">
+      <c r="J288" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:目录写英语为第二语言的外国学生都需TOEFL,未写美国学位豁免,建议邮件确认</t>
         </is>
       </c>
-      <c r="K288" s="30" t="inlineStr">
+      <c r="K288" s="31" t="inlineStr">
         <is>
           <t>kristin.august@rutgers.edu(项目主任 Kristin August)</t>
         </is>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -3353,16 +3353,28 @@
           <t>'Students in the thesis track typically receive a teaching assistantship in their first year and sometimes in part of their second year';non-thesis无资助</t>
         </is>
       </c>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F38" s="26" t="inlineStr">
+        <is>
+          <t>强烈建议:thesis轨为导师学徒制,学生跟随一位教师做实证研究;申请时需注明thesis/non-thesis轨,建议提前联系方向匹配的教授</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(thesis轨通常首年获TA,non-thesis无资助)。本科学士学位(区域认证);研究生院常规录取GPA≥3.0(限制性录取2.75);个人陈述300–400字,说明对行为生物学基础的兴趣;⚠️ 官网未列具体先修课</t>
         </is>
       </c>
       <c r="H38" s="12" t="n"/>
       <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):两年内从美国院校毕业可自动豁免;否则需TOEFL≥79;⚠️ 部分系保留要求EAP考试的权利</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
+        <is>
+          <t>jalene.lamontagne@umsl.edu(⚠️ 心理系研究生项目主任,待确认是否负责MA);gradadm@umsl.edu(研究生院招生)</t>
+        </is>
+      </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
           <t>https://bulletin.umsl.edu/programs/psychology-ma-psychological-and-brain-sciences-emphasis/index.html</t>
@@ -3395,16 +3407,32 @@
           <t>'provides funding for most of its graduate students through research assistantships';校级0.5FTE最低$6,400/学期+学费+医保</t>
         </is>
       </c>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>必须:官网建议先联系有意向的教师,教师同意接收后再申请</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(多数学生通过RA获资助)。接受多元本科背景,视研究方向可能需补先修课;最后60学分GPA≥3.2;申请费$55</t>
         </is>
       </c>
       <c r="H39" s="12" t="n"/>
-      <c r="I39" s="12" t="n"/>
-      <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
+      <c r="I39" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:官网项目页未提GRE,Petersons称需GRE,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院对就读于英语授课院校者豁免英语考试,美本应符合,但未明文写'美国学位';否则TOEFL≥79/IELTS≥6.5/Duolingo≥105</t>
+        </is>
+      </c>
+      <c r="K39" s="26" t="inlineStr">
+        <is>
+          <t>becky.hirst@usu.edu(Environment and Society研究生项目协调员);claudia.radel@usu.edu(系主任)</t>
+        </is>
+      </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
           <t>https://www.usu.edu/degrees-majors/environment-and-society_ms_phd</t>
@@ -3437,16 +3465,36 @@
           <t>'more than 70% of on-campus students receive funding';≥$20k GA进GSSP覆盖全部学费+医保,但州外学费只保第一年</t>
         </is>
       </c>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>必须:录取以有导师接收为前提(admission contingent upon acceptance by an advisor),需先联系教授</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(&gt;70%在校生获资助;GSSP州外学费只保首年)。本科GPA≥3.0;MS Natural Resources期望自然资源相关本科或相关经验;缺科学/数学/专业背景课可入学前或入学后补</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>滚动审理;⚠️ 研究生院优先截止:国际生秋季 2027/3/1,美国公民 6/25;项目截止可能更早,资助建议12月–1月前联系导师并提交</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>不需要(FER官网称已不要求GRE)</t>
+        </is>
+      </c>
+      <c r="J40" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 大概率否:研究生院规定在美国四年制院校完成≥1年全日制学位学习可免TOEFL(未在FER页面明文);否则TOEFL≥80,2年内有效</t>
+        </is>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
+        <is>
+          <t>fer-gradpgm@ncsu.edu(FER研究生项目);forestry-web@ncsu.edu(系办公室)</t>
+        </is>
+      </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
           <t>https://cnr.ncsu.edu/fer/graduate/support/</t>
@@ -3479,16 +3527,36 @@
           <t>'Nearly all of our M.S. and Ph.D. graduate students are financially supported with graduate assistantships and paid tuition'</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
-      <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>强烈建议:学院'highly encourages'申请前联系研究方向匹配的SFR教师;资助多随导师经费</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(几乎所有MS/PhD学生获助教/研究助理+学费)。MS为论文型;需研究生院申请表、成绩单、3封推荐信;⚠️ MS未列具体先修课(MF先修:微积分预备、统计、生物、化学)</t>
+        </is>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>滚动录取,秋/春均可入学;奖学金考虑截止 2027/1/15,建议此前提交</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:MF页称考虑GRE(可豁免),研究生院项目页显示'Test Required: None',建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 可能豁免:研究生院规定在英语授课院校获学位者可免TOEFL,在美国院校读满四年'在某些情况下'可豁免,非自动;否则TOEFL≥80;当TA需TOEFL≥90–92</t>
+        </is>
+      </c>
+      <c r="K41" s="26" t="inlineStr">
+        <is>
+          <t>parinaz.rahimzadeh@maine.edu(SFR研究生项目协调员);sfr@maine.edu(学院办公室)</t>
+        </is>
+      </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
           <t>https://forest.umaine.edu/graduate-programs/</t>
@@ -3521,16 +3589,36 @@
           <t>'most graduate students are supported'(RA/TA含stipend、学费、医保);'Very rarely does a student enroll in the M.S. program without support'</t>
         </is>
       </c>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>可(明文鼓励国际生)</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n"/>
-      <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>强烈建议:RA/TA多由导师提供,首学期需导师审批学习计划,建议申请前联系系内教授确认是否招生</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(明文鼓励国际生;RA/TA含stipend+学费+医保)。⚠️ 官网未列具体先修课或最低GPA</t>
+        </is>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>秋季 2027/2/15;春季 12/1(按2026周期,2027待公布);⚠️ Petersons称国际生秋季4/1,以系官网为准</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>可选(系FAQ明确GRE optional)</t>
+        </is>
+      </c>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位可申请豁免):需提交美国本科学位证明并填English Proficiency Test Score Waiver Form,经系和研究生院批准;否则TOEFL≥80</t>
+        </is>
+      </c>
+      <c r="K42" s="26" t="inlineStr">
+        <is>
+          <t>Michael.Givens@unh.edu(系项目经理,负责研究生档案);Rebecca.Rowe@unh.edu(系主任)</t>
+        </is>
+      </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
           <t>https://colsa.unh.edu/natural-resources-environment/academics/graduate-program-information</t>
@@ -3563,16 +3651,36 @@
           <t>'Most MS students are supported by Research and Teaching Assistantships, which include a stipend, health insurance, and scholarship funds for graduate courses'</t>
         </is>
       </c>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>强烈建议:官网要求开始申请时即联系研究生主任(DGS);求职信需写明希望合作的教师;资助需联系DGS/教师</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(多数MS获RA/TA含stipend、医保、学费奖学金)。本科GPA≥3.0;建议林学或相关自然资源本科背景;需个人陈述、3封推荐信、写作样本可选</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>资助(RA/TA)截止约 2027/2/1;国际生秋季最终 2027/3/15;国内为开学前1个月(按2025-26文件,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>可选(2025年文件:不要求但推荐)</t>
+        </is>
+      </c>
+      <c r="J43" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院认可美国认证院校学士学位作为英语能力证明;⚠️ 项目可设更严要求</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>jian.yang@uky.edu(林学系研究生主任DGS)</t>
+        </is>
+      </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
           <t>https://forestry.mgcafe.uky.edu/graduate-funding</t>
@@ -3605,16 +3713,32 @@
           <t>'most of our graduate students are supported through research grants obtained by individual faculty';示例$21,000/yr×2年+学费减免</t>
         </is>
       </c>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>必须:需教师同意担任Major Advisor才录取;官网称未获导师支持'highly unlikely'被录取</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(多数学生由导师课题经费资助,如$21,000/年+学费减免)。Forest Resources:林学/林产品或相关理学士优先但非必须;WFB:野生动物/生态/生物或相关学士;需2封推荐信</t>
         </is>
       </c>
       <c r="H44" s="12" t="n"/>
-      <c r="I44" s="12" t="n"/>
-      <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
+      <c r="I44" s="26" t="inlineStr">
+        <is>
+          <t>不需要(申请不要求,但个别导师可能要求)</t>
+        </is>
+      </c>
+      <c r="J44" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院明文美国区域认证院校学位满足英语要求;否则TOEFL≥80</t>
+        </is>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
+        <is>
+          <t>pjodice@clemson.edu(FEC研究生项目协调员);tbecker@clemson.edu(研究生服务经理)</t>
+        </is>
+      </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
           <t>https://www.clemson.edu/cafls/forestry-environmental-conservation/students/graduate.html</t>
@@ -3826,16 +3950,36 @@
           <t>每年 ~10-15 个 GA 给新生(RA/TA 含薪水+全额学费+医保);所有录取自动考虑;12-01 优先</t>
         </is>
       </c>
-      <c r="F48" s="12" t="n"/>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确;GA 无国籍限制</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="n"/>
-      <c r="I48" s="12" t="n"/>
-      <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>不需要:项目整体录取(SOPHAS),所有录取者自动考虑GA;项目不预审申请</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(GA无国籍限制,每年~10–15个新生GA)。先修:三学期微积分(含多元微积分)+一学期线性代数;建议一年概率与数理统计;编程/应用统计有帮助非必需;未修完需在SOP中说明</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>优先/奖学金 2026/12/1;最终 2027/4/1(按当前周期,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>不需要(SPH硕博均不要求)</t>
+        </is>
+      </c>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:SPH豁免条件为开学前24个月内在美国/加拿大院校修满16学期学分(美本应届生通常满足);未明文美国学位单独豁免;否则SPH要求TOEFL≥100</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t>brown198@umn.edu(Major Coordinator Sally Olander);bstdgs@umn.edu(研究生主任)</t>
+        </is>
+      </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
           <t>https://www.sph.umn.edu/academics/graduate/ms/biostatistics/cost/</t>
@@ -3868,15 +4012,31 @@
           <t>'Almost all master's students who want an assistantship are able to find one within their first year';GA享州内学费率+stipend(非全免)</t>
         </is>
       </c>
-      <c r="F49" s="12" t="n"/>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(SOPHAS),GA多在入学后第一年内自行找到</t>
+        </is>
+      </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
           <t>未说明</t>
         </is>
       </c>
-      <c r="H49" s="12" t="n"/>
-      <c r="I49" s="12" t="n"/>
-      <c r="J49" s="12" t="n"/>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>MS Epidemiology:秋季 2027/1/15;MS Biostatistics:秋季 2027/2/1(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>不需要(Arnold School明确两项目不要求/不审阅GRE)</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,⚠️ 依据MPH页面):有美国院校学位可豁免;否则TOEFL≥90/IELTS≥7.0</t>
+        </is>
+      </c>
       <c r="K49" s="12" t="n"/>
       <c r="L49" s="12" t="inlineStr">
         <is>
@@ -3910,16 +4070,36 @@
           <t>'90% of the admitted students receive an assistantship, which pays a stipend ($12,600/9 months) and tuition';'100% Tuition Waiver';60%医保折扣;最多4学期</t>
         </is>
       </c>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="n"/>
-      <c r="I50" s="12" t="n"/>
-      <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,资助由系里统一分配;个人陈述写教育目标即可</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(90%录取者获助教金$12,600/9月+100%学费减免)。需本科学位;需先修社会理论、研究方法、统计、写作(缺则补SOCI 33004/33103/34203);犯罪学方向需犯罪学/刑事司法入门课;需写作样本、2–3封推荐信</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>早录取/资助全额考虑 2027/2/1;常规截止 5/15(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr">
+        <is>
+          <t>必需(系页面及目录均要求GRE)</t>
+        </is>
+      </c>
+      <c r="J50" s="26" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生目录允许美国认证院校学士学位豁免英语考试;⚠️ 但研究生院称申请GA者无论是否豁免都须满足英语要求,建议确认是否需另交TOEFL</t>
+        </is>
+      </c>
+      <c r="K50" s="26" t="inlineStr">
+        <is>
+          <t>mwbradl@uark.edu(社会学与犯罪学系研究生主任Mindy Bradley)</t>
+        </is>
+      </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
           <t>https://sociology.uark.edu/graduate-masters-program/</t>
@@ -3952,16 +4132,32 @@
           <t>硕士 GA:19.6 hr=$17,150/yr 或 16 hr=$15,000/yr+学费减免;'不保证但近年多数硕士生获得'</t>
         </is>
       </c>
-      <c r="F51" s="21" t="n"/>
+      <c r="F51" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未明确要求;建议申请前联系研究方向匹配的教师及 Graduate Chair(GA 多与教师项目相关)</t>
+        </is>
+      </c>
       <c r="G51" s="21" t="inlineStr">
         <is>
           <t>✅ 国际 TA 需参加 ITA Institute(隐含可持)</t>
         </is>
       </c>
       <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
-      <c r="J51" s="21" t="n"/>
-      <c r="K51" s="21" t="n"/>
+      <c r="I51" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系官网未提 GRE;Peterson's(第三方,可能过时)列为必需,建议确认</t>
+        </is>
+      </c>
+      <c r="J51" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:UNL 研究生院对美国认证院校学士及以上学位者豁免;⚠️ 系页称母语非英语需验证英语能力,建议确认)。国际TA需参加 ITA Institute</t>
+        </is>
+      </c>
+      <c r="K51" s="30" t="inlineStr">
+        <is>
+          <t>rdalla1@unl.edu(Rochelle Dalla,CYAF 系 Graduate Chair)</t>
+        </is>
+      </c>
       <c r="L51" s="21" t="inlineStr">
         <is>
           <t>https://cehs.unl.edu/cyaf/cyaf-funding-and-assistantship-opportunities</t>
@@ -3994,15 +4190,31 @@
           <t>竞争性系 assistantship;全含学费减免(含暑期);33/40/50% 任命;硕士最多 2 年</t>
         </is>
       </c>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H52" s="21" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未明确;如可申请,建议提前联系研究方向匹配的教师</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>❌ 很可能无法申请:系官网称 MS HDFS 仅接收 UGA Double Dawgs 本硕连读学生(外校美本需邮件确认)。若可申:认证院校学士,行为/家庭科学背景优先,GPA≥3.3;简历、3封推荐信、≤1500字目的陈述;⚠️ 国际生资助未明确</t>
+        </is>
+      </c>
+      <c r="H52" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/1(仅秋季入学)</t>
+        </is>
+      </c>
+      <c r="I52" s="30" t="inlineStr">
+        <is>
+          <t>不需要(官网列 M.S. HDFS (Double Dawg Pathway) 不需要 GRE;Peterson's 旧信息称必需)</t>
+        </is>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免;UGA 研究生院2025年3月修订后仍保留)。担任TA需另证英语能力</t>
+        </is>
+      </c>
       <c r="K52" s="21" t="n"/>
       <c r="L52" s="21" t="inlineStr">
         <is>
@@ -4036,16 +4248,36 @@
           <t>25-67% assistantship:$8,720(25%)或 $17,439(50%)+学费减免;JBT Fellowship $20,000×2 年</t>
         </is>
       </c>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H53" s="21" t="n"/>
-      <c r="I53" s="21" t="n"/>
-      <c r="J53" s="21" t="n"/>
-      <c r="K53" s="21" t="n"/>
+      <c r="F53" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:录取看与教师研究的匹配度(至少3位教师审材料),建议申请前联系方向匹配的教师</t>
+        </is>
+      </c>
+      <c r="G53" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确;TA需另证英语口语能力)。先修:需有社会或行为科学相关课程;最低GPA 3.0/4.0。材料:GPA、推荐信、写作样本、个人陈述;仅秋季入学</t>
+        </is>
+      </c>
+      <c r="H53" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/15(仅秋季入学,官网每年12/15)</t>
+        </is>
+      </c>
+      <c r="I53" s="30" t="inlineStr">
+        <is>
+          <t>可选(成绩需为申请前2年内)</t>
+        </is>
+      </c>
+      <c r="J53" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:入学前5年内获美国学位即可;非豁免者 TOEFL iBT ≥103)。担任TA需另证英语口语能力,美国学位不豁免</t>
+        </is>
+      </c>
+      <c r="K53" s="30" t="inlineStr">
+        <is>
+          <t>bogolsky@illinois.edu(Brian Ogolsky,研究生项目主任);hdfs@illinois.edu(系办)</t>
+        </is>
+      </c>
       <c r="L53" s="21" t="inlineStr">
         <is>
           <t>https://hdfs.illinois.edu/admissions/financial-support/graduate-financial-support</t>
@@ -4078,16 +4310,36 @@
           <t>'尽可能也为 MA 生提供资助'(PhD 优先);TA/RA 10-20 hr 含全额学费+津贴+医保</t>
         </is>
       </c>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="21" t="n"/>
-      <c r="K54" s="21" t="n"/>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>建议:系里建议对项目有强烈兴趣者直接联系所选专业方向的教师;MA名额很少,主要面向计划读博者</t>
+        </is>
+      </c>
+      <c r="G54" s="30" t="inlineStr">
+        <is>
+          <t>可以申请,但 MA 名额很少,通常只考虑明确打算继续读博的学生(⚠️ 国际生资助未明确,PhD优先;TA需另证英语能力)。先修:⚠️ 官网未列具体先修课;需满足研究生院要求。材料:3封推荐信、成绩单、个人陈述(说明与项目匹配度)</t>
+        </is>
+      </c>
+      <c r="H54" s="30" t="inlineStr">
+        <is>
+          <t>2027/3/1(仅秋季入学;申请费减免请求需在 12/12 前提交)</t>
+        </is>
+      </c>
+      <c r="I54" s="30" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J54" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院明确豁免美国公民/永久居民;按学历豁免需在英语授课院校完成规定学分且GPA≥3.0,美本很可能符合但需向 gradadmissions@uconn.edu 申请豁免。TA仍需另证英语能力</t>
+        </is>
+      </c>
+      <c r="K54" s="30" t="inlineStr">
+        <is>
+          <t>HDFSgradprogram@uconn.edu(HDFS 研究生项目);gradadmissions@uconn.edu(研究生院招生)</t>
+        </is>
+      </c>
       <c r="L54" s="21" t="inlineStr">
         <is>
           <t>https://hdfs.uconn.edu/grad/financial-support</t>
@@ -4120,16 +4372,32 @@
           <t>'优先 PhD;有余则给硕士';仅秋春;需全时</t>
         </is>
       </c>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H55" s="21" t="n"/>
-      <c r="I55" s="21" t="n"/>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:系官网称申请前应联系感兴趣的教师,申请表需列出希望合作的教师名单</t>
+        </is>
+      </c>
+      <c r="G55" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(资助优先PhD,有余给硕士,⚠️ 国际生资格未明确)。先修:美国区域认证学士或同等学历;系里不设最低GPA/GRE。材料:目标陈述、意向教师名单、3位推荐人</t>
+        </is>
+      </c>
+      <c r="H55" s="30" t="inlineStr">
+        <is>
+          <t>优先 2026/12/1;之后滚动审理至开学前(⚠️ 官网另列秋季 4/15,存在矛盾,建议12/1前提交)</t>
+        </is>
+      </c>
+      <c r="I55" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系FAQ称不设最低GRE,但同页称校内MS申请包含GRE,建议向协调员确认</t>
+        </is>
+      </c>
       <c r="J55" s="21" t="n"/>
-      <c r="K55" s="21" t="n"/>
+      <c r="K55" s="30" t="inlineStr">
+        <is>
+          <t>jeremiah.ramirez@ttu.edu(Jeremiah Ramirez,HDFS 研究生项目协调员);Ali.J.Luempert@ttu.edu(研究生项目副主任)</t>
+        </is>
+      </c>
       <c r="L55" s="21" t="inlineStr">
         <is>
           <t>https://www.depts.ttu.edu/hs/hdfs/graduate/masters_details.php</t>
@@ -4163,15 +4431,27 @@
         </is>
       </c>
       <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H56" s="21" t="n"/>
+      <c r="G56" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确;2/1优先截止者获 assistantship 考虑)。先修:⚠️ 本科后60学分GPA≥3.0(第三方);材料:3封推荐信、目的陈述、简历</t>
+        </is>
+      </c>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/2/1;最终 2027/3/15(按往年周期,2027待公布)</t>
+        </is>
+      </c>
       <c r="I56" s="21" t="n"/>
-      <c r="J56" s="21" t="n"/>
-      <c r="K56" s="21" t="n"/>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:UF称美国学位可由院系酌情豁免;否则 IELTS ≥6,TOEFL ≥77/80(来源不一),建议向协调员确认</t>
+        </is>
+      </c>
+      <c r="K56" s="30" t="inlineStr">
+        <is>
+          <t>hliss@ufl.edu(Heidi Radunovich,FYCS 研究生协调员;⚠️ 邮箱与姓名不一致,建议核实)</t>
+        </is>
+      </c>
       <c r="L56" s="21" t="inlineStr">
         <is>
           <t>https://fycs.ifas.ufl.edu/graduate-programs/master-of-science-on-campus</t>
@@ -4204,16 +4484,36 @@
           <t>任何 HDFS 生可通过春季问卷申 TA/RA;'视资源而定';参考包 ≥$21,523+学费+医保</t>
         </is>
       </c>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H57" s="21" t="n"/>
-      <c r="I57" s="21" t="n"/>
-      <c r="J57" s="21" t="n"/>
-      <c r="K57" s="21" t="n"/>
+      <c r="F57" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议(Plan A):申请时需注明希望的研究导师;Plan B(专业型)不需要</t>
+        </is>
+      </c>
+      <c r="G57" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确,TA/RA视资源)。先修:认证院校学士;本科最后两年GPA≥3.0;3封推荐信;简历、学术与个人陈述、系申请表;Plan A 30学分含6学分论文</t>
+        </is>
+      </c>
+      <c r="H57" s="30" t="inlineStr">
+        <is>
+          <t>Plan A(研究型)2026/12/1;Plan B 2027/2/1(⚠️ 官网表格列含义不清,需确认)</t>
+        </is>
+      </c>
+      <c r="I57" s="30" t="inlineStr">
+        <is>
+          <t>可选(系不要求;Plan A与国际申请人鼓励提交5年内成绩)</t>
+        </is>
+      </c>
+      <c r="J57" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:MSU豁免需本科院校在其认可名单上(美国院校多在列),需确认;否则 TOEFL iBT ≥80</t>
+        </is>
+      </c>
+      <c r="K57" s="30" t="inlineStr">
+        <is>
+          <t>vallotto@msu.edu(Claire Vallotton,硕博项目实质问题);reidphil@msu.edu(Phil Reid,研究生事务行政助理)</t>
+        </is>
+      </c>
       <c r="L57" s="21" t="inlineStr">
         <is>
           <t>https://hdfs.msu.edu/academics/graduate/ta-info</t>
@@ -4246,16 +4546,36 @@
           <t>GTA 作为'支付研究生学费的方式';GRA 视资金;每年 2 个 fellowship</t>
         </is>
       </c>
-      <c r="F58" s="21" t="n"/>
-      <c r="G58" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H58" s="21" t="n"/>
-      <c r="I58" s="21" t="n"/>
-      <c r="J58" s="21" t="n"/>
-      <c r="K58" s="21" t="n"/>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未明确;Plan A论文型建议提前联系教师,可向研究生项目主任咨询导师匹配</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确)。先修:HDFS或相关专业学士,累计GPA≥3.0;相关专业需至少2门人类发展、1门家庭研究、1门统计课,各≥3.0。推荐信2–3封(建议3封)、CV</t>
+        </is>
+      </c>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>2027/1/5(按官网现行,⚠️ 页面约10个月前更新,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I58" s="30" t="inlineStr">
+        <is>
+          <t>可选(系已免除 GRE 要求)</t>
+        </is>
+      </c>
+      <c r="J58" s="30" t="inlineStr">
+        <is>
+          <t>否(近期获得美国学位豁免;"近期"定义需确认)。否则 TOEFL iBT ≥80</t>
+        </is>
+      </c>
+      <c r="K58" s="30" t="inlineStr">
+        <is>
+          <t>gloria.luong@colostate.edu(Gloria Luong,研究生项目主任);hdfsinfo@colostate.edu(系办)</t>
+        </is>
+      </c>
       <c r="L58" s="21" t="inlineStr">
         <is>
           <t>https://www.chhs.colostate.edu/hdfs/programs-and-degrees/advising-and-support/graduate-advising/frequently-asked-questions/</t>
@@ -4288,16 +4608,36 @@
           <t>'可能获学费减免或 GA'</t>
         </is>
       </c>
-      <c r="F59" s="21" t="n"/>
-      <c r="G59" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H59" s="21" t="n"/>
-      <c r="I59" s="21" t="n"/>
-      <c r="J59" s="21" t="n"/>
-      <c r="K59" s="21" t="n"/>
+      <c r="F59" s="30" t="inlineStr">
+        <is>
+          <t>不需要:入学后与导师及委员会制定培养计划;可联系项目协调员咨询</t>
+        </is>
+      </c>
+      <c r="G59" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确)。先修:人类发展、家庭科学、儿童与家庭服务、幼教或相关领域学士;正式录取需本科总GPA≥3.0。材料:推荐信、2–3页职业目标陈述、简历</t>
+        </is>
+      </c>
+      <c r="H59" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2027/4/1(项目截止,早于研究生院国际生 5/1);春季 10/15</t>
+        </is>
+      </c>
+      <c r="I59" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:项目页未提GRE;手册称仅DFS与MFT方向需GRE(且已豁免),AHS很可能不需要</t>
+        </is>
+      </c>
+      <c r="J59" s="30" t="inlineStr">
+        <is>
+          <t>否(在英语为主要语言国家认证院校获学士及以上可豁免;⚠️ 需向研究生院确认)。否则 TOEFL ≥79,IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K59" s="30" t="inlineStr">
+        <is>
+          <t>brandt.gardner@okstate.edu(Brandt Gardner,HDFS 项目协调员)</t>
+        </is>
+      </c>
       <c r="L59" s="21" t="inlineStr">
         <is>
           <t>https://go.okstate.edu/graduate-academics/programs/masters/applied-human-services-ms</t>
@@ -4330,16 +4670,36 @@
           <t>1-15 前提交 GA 申请表+CV</t>
         </is>
       </c>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H60" s="21" t="n"/>
-      <c r="I60" s="21" t="n"/>
-      <c r="J60" s="21" t="n"/>
-      <c r="K60" s="21" t="n"/>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>建议:目录要求联系HDFS研究生协调员安排面试;GA需1/15前将申请表+CV交给协调员</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA需1/15前提交申请表+CV,⚠️ 国际生资格未明确)。先修:HDFS或相关领域学士,GPA≥3.0;3封推荐信(至少2封学术)、独立写作样本、500–1000字个人陈述</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>GA申请 2027/1/15;研究生院国际生 2027/5/1(建议1/1前提交)</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系官网称硕博均不需要GRE,但研究生目录仍要求有竞争力的GRE;倾向不需要,建议确认</t>
+        </is>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,研究生院目录明文)</t>
+        </is>
+      </c>
+      <c r="K60" s="30" t="inlineStr">
+        <is>
+          <t>tom.phillips@msstate.edu(Tommy Phillips,HDFS 研究生协调员;⚠️ 目录另列 Lori Elmore-Staton)</t>
+        </is>
+      </c>
       <c r="L60" s="21" t="inlineStr">
         <is>
           <t>https://www.humansci.msstate.edu/students/grad/hdfs.php</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -6076,16 +6076,28 @@
           <t>系 GA:$15,915-19,096 津贴+州内或外州学费减免;1-15 优先</t>
         </is>
       </c>
-      <c r="F87" s="21" t="n"/>
+      <c r="F87" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:硕士按项目整体录取(官网未明确);如争取系GA可提前邮件系里询问</t>
+        </is>
+      </c>
       <c r="G87" s="21" t="inlineStr">
         <is>
           <t>⚠️ 未明确</t>
         </is>
       </c>
-      <c r="H87" s="21" t="n"/>
+      <c r="H87" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 研究生院最终截止:秋季 2027/8/1(系里可能更早);第三方(Petersons)显示国际生秋季 4/1;系GA优先 1/15(见E列)</t>
+        </is>
+      </c>
       <c r="I87" s="21" t="n"/>
       <c r="J87" s="21" t="n"/>
-      <c r="K87" s="21" t="n"/>
+      <c r="K87" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ alsulliv@uark.edu(Amanda Sullivan,公共卫生系研究生协调员,信息可能过时);elindly@uark.edu(MPH协调员)</t>
+        </is>
+      </c>
       <c r="L87" s="21" t="inlineStr">
         <is>
           <t>https://hhpr.uark.edu/financial-aid.php</t>
@@ -6118,16 +6130,32 @@
           <t>'任何全录取修 ≥9 学分者可申'assistantship(10-20 hr);外州自动州内费率;逐学期</t>
         </is>
       </c>
-      <c r="F88" s="21" t="n"/>
-      <c r="G88" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H88" s="21" t="n"/>
-      <c r="I88" s="21" t="n"/>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G88" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确;handbook称全录取修≥9学分者均可申assistantship)。先修:四年制学士学位,GPA≥3.0;⚠️ 官网列有≥2年本科后健康相关工作经验要求,建议确认是否硬性</t>
+        </is>
+      </c>
+      <c r="H88" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2027/2/15(研究生院MPH页,按2026周期,2027待公布);经SOPHAS提交,⚠️ SOPHAS截止日请核实</t>
+        </is>
+      </c>
+      <c r="I88" s="30" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
       <c r="J88" s="21" t="n"/>
-      <c r="K88" s="21" t="n"/>
+      <c r="K88" s="30" t="inlineStr">
+        <is>
+          <t>CEBLAKE@mailbox.sc.edu(HPEB研究生项目主任 Christine Blake);EDENAG@mailbox.sc.edu(MPH项目主任 Edena Guimaraes)</t>
+        </is>
+      </c>
       <c r="L88" s="21" t="inlineStr">
         <is>
           <t>https://sc.edu/study/colleges_schools/public_health/documents/hpeb-masters-handbook.pdf</t>
@@ -6202,15 +6230,31 @@
           <t>'a limited number of graduate assistantships'(13–20h/周),学费减免(自付fees);录取后联系系主任,无正式申请流程</t>
         </is>
       </c>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="21" t="n"/>
+      <c r="F90" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GA无正式申请流程,录取后联系系主任</t>
+        </is>
+      </c>
+      <c r="G90" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可申少量GA,名额有限)。先修:学士学位,建议GPA≥3.0;经SOPHAS申请并向UGA研究生院缴补充申请费;3封推荐信、CV、个人陈述</t>
+        </is>
+      </c>
+      <c r="H90" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/1/5;最终 2027/5/1(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I90" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J90" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院政策,美国认证院校学位通常无需TOEFL/IELTS;⚠️ 个别项目可能仍要求,建议确认)</t>
+        </is>
+      </c>
       <c r="K90" s="21" t="n"/>
       <c r="L90" s="21" t="inlineStr">
         <is>
@@ -6244,16 +6288,32 @@
           <t>硕士stipend $10,000–12,500,仅1年;'financial support is not guaranteed with admission'</t>
         </is>
       </c>
-      <c r="F91" s="21" t="n"/>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
       <c r="G91" s="21" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="H91" s="21" t="n"/>
+      <c r="H91" s="30" t="inlineStr">
+        <is>
+          <t>优先 2027/1/15;最终 2027/4/1(学院通用日期,各项目可能不同);Hoosier Public Health Scholars奖学金预申请 2027/1/15</t>
+        </is>
+      </c>
       <c r="I91" s="21" t="n"/>
-      <c r="J91" s="21" t="n"/>
-      <c r="K91" s="21" t="n"/>
+      <c r="J91" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:官网明确持有美国大学学位可免;否则 IELTS ≥6.5/Duolingo ≥105)</t>
+        </is>
+      </c>
+      <c r="K91" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ sphgrad@indiana.edu(SPH研究生招生,来自2022-23 bulletin,建议核实)</t>
+        </is>
+      </c>
       <c r="L91" s="21" t="inlineStr">
         <is>
           <t>https://bulletin.iu.edu/iub/phb/2020-2021/graduate/financial-aid.shtml</t>
@@ -6286,16 +6346,32 @@
           <t>校级GA=月薪+学费减免+医保;资助截止12/1;项目页无比例</t>
         </is>
       </c>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
+      <c r="F92" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G92" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生GA资格未明确)。先修:入学前获学士学位,GPA≥3.0(累计或最后90学分);经SOPHAS申请,3封推荐信、个人陈述、CV</t>
+        </is>
+      </c>
+      <c r="H92" s="30" t="inlineStr">
+        <is>
+          <t>优先 2026/12/1(资助同日);最终 2027/6/1(SOPHAS,太平洋时间20:59);1–6月每月底发结果</t>
+        </is>
+      </c>
+      <c r="I92" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J92" s="21" t="n"/>
-      <c r="K92" s="21" t="n"/>
+      <c r="K92" s="30" t="inlineStr">
+        <is>
+          <t>amanda.armington@oregonstate.edu(MPH项目经理)</t>
+        </is>
+      </c>
       <c r="L92" s="21" t="inlineStr">
         <is>
           <t>https://health.oregonstate.edu/hphb/mph</t>
@@ -6428,16 +6504,36 @@
           <t>TA/RA:10 hr=$6,413/学期+50% 州内学费+外州豁免;20 hr=$12,827/学期+全额州内学费+外州豁免+医保</t>
         </is>
       </c>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="inlineStr">
-        <is>
-          <t>✅ 国际生同等考虑但无经济保证</t>
-        </is>
-      </c>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-      <c r="J95" s="21" t="n"/>
-      <c r="K95" s="21" t="n"/>
+      <c r="F95" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G95" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生同等考虑TA/RA但无经济保证)。先修:学士学位,GPA≥3.0(最后60学分);大学代数/预备微积分/微积分一门(C以上),部分方向需生物课;2封推荐信、CV、个人陈述(⚠️ 先修课来自在线MPH页)</t>
+        </is>
+      </c>
+      <c r="H95" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/1/15;最终 2027/4/1(校园MPH;SOPHAS处理需3–4周,建议提前提交)</t>
+        </is>
+      </c>
+      <c r="I95" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:截止页称需在截止前提交GRE成绩,但在线MPH已取消GRE;建议邮件确认校园MPH/MS政策</t>
+        </is>
+      </c>
+      <c r="J95" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院与公卫学院均豁免美国区域认证学士/研究生学位;⚠️ 个别系页称学位须在2年内);否则TOEFL iBT ≥90</t>
+        </is>
+      </c>
+      <c r="K95" s="30" t="inlineStr">
+        <is>
+          <t>coph-admit@arizona.edu(公卫学院招生主任)</t>
+        </is>
+      </c>
       <c r="L95" s="21" t="inlineStr">
         <is>
           <t>https://publichealth.arizona.edu/graduate-students/tuition-financial-assistance</t>
@@ -6470,16 +6566,36 @@
           <t>Holger Hansen Fellowship:学费减免+年津贴;每学期 ≤10 个 Course Assistant $5,000/门</t>
         </is>
       </c>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 联系 publichealth@uchc.edu</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
-      <c r="K96" s="21" t="n"/>
+      <c r="F96" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G96" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格建议联系 publichealth@uchc.edu)。先修:无具体先修课,综合评估公卫兴趣、GPA、相关经历;GPA&lt;3.0也可考虑</t>
+        </is>
+      </c>
+      <c r="H96" s="30" t="inlineStr">
+        <is>
+          <t>优先:国际生 2027/2/1;美国公民/PR 2027/4/1;7月第二周后不再受理秋季申请(按2026周期,2027待公布);非滚动</t>
+        </is>
+      </c>
+      <c r="I96" s="30" t="inlineStr">
+        <is>
+          <t>不需要(可提交,但不用于奖学金评定)</t>
+        </is>
+      </c>
+      <c r="J96" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 大概率否:研究生院政策豁免在美国完成≥1年全日制课程的国际生(美本应满足,需与 gradadmissions@uconn.edu 确认);否则TOEFL ≥79/IELTS ≥6.5;当TA另需英语能力证明</t>
+        </is>
+      </c>
+      <c r="K96" s="30" t="inlineStr">
+        <is>
+          <t>publichealth@uchc.edu(公共卫生项目);gradadmissions@uconn.edu(研究生院招生)</t>
+        </is>
+      </c>
       <c r="L96" s="21" t="inlineStr">
         <is>
           <t>https://mph.uconn.edu/tuition-and-financial-information/</t>
@@ -6512,16 +6628,36 @@
           <t>TA/PA/RA 为主要资助:全额学费减免(含外州)+月津贴+保险;'许多学生获得'但非保证</t>
         </is>
       </c>
-      <c r="F97" s="21" t="n"/>
-      <c r="G97" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 校园 TA/PA/RA 通常 F-1 可</t>
-        </is>
-      </c>
-      <c r="H97" s="21" t="n"/>
-      <c r="I97" s="21" t="n"/>
-      <c r="J97" s="21" t="n"/>
-      <c r="K97" s="21" t="n"/>
+      <c r="F97" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G97" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 校园TA/PA/RA通常F-1可)。先修:美国区域认证学士学位,GPA≥3.0;≥1学期大学数学或统计(MATH 112/STATS 201同等)+≥1学期生物/化学/物理;录取后夏季需完成线上Foundational Knowledge课程</t>
+        </is>
+      </c>
+      <c r="H97" s="30" t="inlineStr">
+        <is>
+          <t>2027/1/15(唯一截止,仅秋季入学;申请约10月初开放)</t>
+        </is>
+      </c>
+      <c r="I97" s="30" t="inlineStr">
+        <is>
+          <t>不接受(不要求,提交也不予考虑)</t>
+        </is>
+      </c>
+      <c r="J97" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院政策,美国区域认证学士学位即满足英语要求)</t>
+        </is>
+      </c>
+      <c r="K97" s="30" t="inlineStr">
+        <is>
+          <t>mph@mailplus.wisc.edu(MPH项目)</t>
+        </is>
+      </c>
       <c r="L97" s="21" t="inlineStr">
         <is>
           <t>https://www.med.wisc.edu/education/master-of-public-health-mph/tuition-and-aid</t>
@@ -6554,16 +6690,32 @@
           <t>学院 GA 按 SOPHAS merit 授予(无需另申);学费+9 个月津贴</t>
         </is>
       </c>
-      <c r="F98" s="21" t="n"/>
+      <c r="F98" s="30" t="inlineStr">
+        <is>
+          <t>不需要:GA按SOPHAS申请材料merit授予,无需另申或套磁</t>
+        </is>
+      </c>
       <c r="G98" s="21" t="inlineStr">
         <is>
           <t>✅ F-1 可;需 OPI 口语</t>
         </is>
       </c>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
+      <c r="H98" s="30" t="inlineStr">
+        <is>
+          <t>秋季:国际生 2027/4/1;国内 2027/7/1(官网);⚠️ 旧目录显示GA优先 2/1,建议2/1前提交以争取GA</t>
+        </is>
+      </c>
+      <c r="I98" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J98" s="21" t="n"/>
-      <c r="K98" s="21" t="n"/>
+      <c r="K98" s="30" t="inlineStr">
+        <is>
+          <t>huntjr1@etsu.edu(研究生项目顾问 Jennifer Hunt);publichealth@etsu.edu(公卫学院)</t>
+        </is>
+      </c>
       <c r="L98" s="21" t="inlineStr">
         <is>
           <t>https://www.etsu.edu/cph/academics/pubhealth_ga.php</t>
@@ -6638,16 +6790,36 @@
           <t>所有录取自动考虑 HPM 奖学金+Dean's Scholarship+外州学费奖;RA/TA'非常竞争'</t>
         </is>
       </c>
-      <c r="F100" s="21" t="n"/>
+      <c r="F100" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,录取者自动考虑奖学金;RA竞争激烈,可选择性联系研究方向匹配的教授</t>
+        </is>
+      </c>
       <c r="G100" s="21" t="inlineStr">
         <is>
           <t>⚠️ 未限制</t>
         </is>
       </c>
-      <c r="H100" s="21" t="n"/>
-      <c r="I100" s="21" t="n"/>
-      <c r="J100" s="21" t="n"/>
-      <c r="K100" s="21" t="n"/>
+      <c r="H100" s="30" t="inlineStr">
+        <is>
+          <t>优先 2026/12/1;最终 2027/7/15(仅秋季入学,美东时间23:59,材料须齐全)</t>
+        </is>
+      </c>
+      <c r="I100" s="30" t="inlineStr">
+        <is>
+          <t>不需要(SPH所有项目均不要求GRE)</t>
+        </is>
+      </c>
+      <c r="J100" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 大概率否:SPH国际生页规定过去24个月内在美国认证院校完成≥16学期学分可豁免(美本应届通常满足,需经WES ICAP/SOPHAS核实);否则TOEFL 偏好≥100</t>
+        </is>
+      </c>
+      <c r="K100" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ loas0001@umn.edu(研究生项目协调员 Katie Keyser);sph-ask@umn.edu(SPH通用咨询;协调员信息有冲突,建议核实)</t>
+        </is>
+      </c>
       <c r="L100" s="21" t="inlineStr">
         <is>
           <t>https://www.sph.umn.edu/academics/degrees-programs/ms/health-services-research-policy-administration/funding/</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -1514,15 +1514,31 @@
           <t>所有录取 MA 生保证 2 年:学费(≤14 学分/学期)+津贴+部分医保+暑期资助;通过 TA/RA/fellowship 发放</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>✅ 明文:'domestic and international students receive guaranteed funding'</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>强烈建议:系官网明确要求申请前联系潜在导师,才能获得完整考虑(full consideration)</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 明文:'domestic and international students receive guaranteed funding',MA保证2年)。先修:区域认证大学四年制学士即可,不限地理专业;非地理背景可能被要求补修不计研究生学分的课程;需个人陈述(≤2页)+多元化陈述。⚠️ 官网未列最低GPA</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>2026/12/15 所有材料截止(官网规则:入学前一年12/15,如 Fall 26 为 2025/12/15);仅秋季入学,1月集中审核,2月底-3月初出结果</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要/未提及:系官网申请清单未列GRE,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>否(大概率豁免):UMN研究生院规定近2年内在美国完成≥16学期学分(非ESL)即满足英语要求,美本应届/近两年毕业符合;⚠️ 系内未见更严规定,建议确认。需提交时为 TOEFL 79/IELTS 6.5(⚠️第三方)</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1556,16 +1572,36 @@
           <t>系政策:'不录取无法通过 assistantship/fellowship 资助的学生';TA/RA 20 hr/wk 覆盖学费+月津贴;MS 全 2 年;12-01 截止</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>✅ 无国籍限制</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>建议:系看重研究兴趣与教师学术方向的契合,陈述需具体描述拟开展的研究;官网未强制套磁,但提前联系潜在导师有利</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 无国籍限制;系政策不录取无法提供assistantship/fellowship的学生)。先修:需学士学位;本科大三大四GPA≥3.0,并修过地理或相关学科课程</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>资助/录取截止 2026/12/1 17:00 ET;推荐信 12/15(按2026周期为 2025/12/1,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生 Bulletin 写需GRE,但系申请页未提及;同校地球科学等系已不要求,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):PSU研究生院对持美国认证院校学士/硕士者免TOEFL/IELTS(⚠️来源为PSU分校页面,建议确认);⚠️ 担任TA可能需另过英语口语评估</t>
+        </is>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>grad@geog.psu.edu(地理系研究生项目);mng5361@psu.edu(研究生项目协调员 MacKenzie Goss,⚠️页面可能过时)</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>https://www.geog.psu.edu/graduate/graduate-admissions-and-aid/graduate-funding</t>
@@ -1598,15 +1634,31 @@
           <t>系政策:'只向已确认 GTA/GRA/fellowship 资助的学生发录取';GTA 含学费+津贴</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>✅ 需另过 GTA 口语英语测试</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>建议:官网未强制套磁,但只向已确认GTA/GRA/fellowship资助者发录取,陈述需写明具体研究兴趣,提前联系潜在导师有利</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 需另过GTA口语英语测试:学位豁免不适用于GTA,须符合Kansas Board of Regents要求)。先修:认证院校学士学位及正式成绩单、简历、研究兴趣与目标陈述;⚠️ 官网未列最低GPA及先修课</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>秋季入学并考虑fellowship/TA:1/6 前提交全部材料(⚠️ 系页未标年份,推测 2027/1/6);春季 10/1;研究生院2027秋申请已于2026/9/8开放</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>不需要(可选提交,不提交不影响录取)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):在美国认证院校在校完成(非网课)的学士学位可满足KU英语要求;但不适用于GTA,担任GTA须另符合Kansas Board of Regents口语英语要求</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1640,16 +1692,36 @@
           <t>RA(10-20 hr/wk)含'全额学费减免+津贴+GatorCare';优先截止 ~1-31</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确;部分命名 RA 面向美籍弱势群体</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>不需要:整体评审、滚动录取;RA分配至教授研究项目,个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>可以申请,但⚠️ 国际生资助资格官网未明确;部分命名RA面向美籍弱势群体。先修:⚠️ 系官网未列专业/先修课/最低GPA要求;材料须全部经UF研究生招生系统提交,勿直接寄系里</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>滚动录取(秋/春均可),完整申请约3周出结果;RA优先截止约 1/31,建议 2027/1/31 前提交;⚠️ 秋季最终截止有 mid-June/early-July 两种说法</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>不需要(自2020秋季起取消)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系页称国际生仍需TOEFL/IELTS(UF最低 TOEFL 80/IELTS 6.5);UF研究生目录称在美国获得学位者可由系酌情豁免,需向系确认</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>alakshendra@dcp.ufl.edu(研究生协调员 Dr. Abhinav Alakshendra);vniblett@dcp.ufl.edu(学术项目专员 Vanessa Niblett)</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>https://dcp.ufl.edu/urp/scholarship-and-assistantship-opportunities/</t>
@@ -1682,16 +1754,32 @@
           <t>GA 获'全额学费减免+按工时津贴';分配至 faculty 研究(气候韧性、海平面、可步行性)</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>不需要:按项目录取;GA分配至教师研究项目,需另交GA申请表,陈述可写感兴趣的研究方向/教授</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>⚠️ 未明确</t>
         </is>
       </c>
       <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>可选(仅在能证明学术准备时提交)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:FAU研究生最低 TOEFL iBT 79/IELTS 6.0;FAU英语豁免页列美国区域认证院校学位可豁免,但主要面向本科,研究生是否适用需向Graduate College确认</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>lmerlin@fau.edu(MURP项目协调员 Dr. Louis A. Merlin);durp@fau.edu(城市与区域规划系)</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>https://www.fau.edu/science/departments/urban-regional-planning/murp/assistantships/</t>
@@ -1724,16 +1812,32 @@
           <t>半时 TA(20 hr)=全额学费减免+免费医保+津贴;最多 2 年;1-15 前自动考虑</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>✅ campus 申请者可</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>不需要:按项目录取;1/15前申请即自动考虑TA</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(✅ campus申请者可获TA)。先修:任意专业、区域认证学士学位;最后60学分GPA≥3.0(2.5-3.0可酌情考虑);需个人陈述(≤600词)、简历、成绩单、英语能力证明;⚠️ 推荐信要求官网与第三方有出入</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>秋季(校内)优先截止 2027/1/15(含TA自动考虑);⚠️ 最终截止未明确</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>可选(GPA 2.5-3.0或非相关专业者可提交加分)</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>SGSUP.gradprograms@asu.edu(SGSUP研究生项目办公室);mfquiroz@asu.edu(研究生顾问 Fernanda Quiroz)</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>https://sgsup.asu.edu/degree-programs/graduate-degrees/financial-support</t>
@@ -1766,16 +1870,36 @@
           <t>GA 含学费减免+小额月津贴;Housing &amp; Community Dev Fellowship=全额学费+小额津贴;3-1 截止</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>✅ 明文向国际申请者开放;F-1 另有 merit 奖学金</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>不需要:按项目录取;GA申请材料直接发系研究生协调员</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 明文向国际申请者开放;F-1另有merit奖学金)。先修:学士学位,GPA一般≥2.75(系可例外);需500词个人陈述、简历、本科成绩单</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>GA/资助优先 2027/3/1;秋季最终 2027/7/1(春季 12/1);⚠️ 国际生截止可能更早,建议确认</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生招生页将美国认证院校学士/硕士学位列为英语能力证明方式之一;⚠️ 系可设更严要求,建议确认</t>
+        </is>
+      </c>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>cityplanning@memphis.edu(系/研究生协调员);⚠️ casanto@memphis.edu(系主任 Charles Santo,第三方来源)</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>https://www.memphis.edu/planning/financial-aid.php</t>
@@ -1808,16 +1932,36 @@
           <t>'每个学生都获 TA 或 RA':全额学费减免+医保+9 个月津贴+暑期津贴;~20 hr/wk</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确;on-campus GA 通常 F-1 可持</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>强烈建议:申请时须指名1位以上希望合作的教师并说明契合度,官网强烈鼓励申请前联系确认其是否招生(部分教师2027-28不招)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确;on-campus GA通常F-1可持)。先修:须修过实验/研究方法和心理统计;非心理专业修过这两门(或有充足量化研究经验)也可;需研究陈述+3封推荐信</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>2027/2/1(所有材料);申请费/TOEFL豁免申请须在 2027/1/25 前提交</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>不接受(系明确不接受GRE)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生需TOEFL/IELTS(代码5115),可在1/25前提交TOEFL豁免申请,美本大概率可获批,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>psychology@wm.edu(心理系研究生项目/Lynnette Bolden)</t>
+        </is>
+      </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
           <t>https://www.wm.edu/as/psych-sciences/gradprogram/financial-support/</t>
@@ -1850,16 +1994,36 @@
           <t>'多数学生同时获 assistantship(津贴)和 scholarship(学费)';merit-based 无需单独申请</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>不需要:官网未要求套磁,按项目整体录取;研究导向项目,个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生资助资格未明确)。先修:心理学导论、研究方法、统计;非心理专业具备上述基础也可;每年录10-16人,近3年平均GPA 3.76、GRE 315</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>2027/1/15(研究生院截止表;⚠️ 有第三方称 2/1)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>可选(系鼓励提交GRE General)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>否(大概率豁免):研究生院英语要求仅针对'未从美国院校毕业且母语非英语'的国际生;⚠️ 未见明文豁免,建议向 graduate@wfu.edu 确认</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>furrrm@wfu.edu(研究生项目主任 R. Michael Furr);graduate@wfu.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
           <t>https://psychology.wfu.edu/graduate-financial-aid/</t>
@@ -1892,15 +2056,31 @@
           <t>FAQ:'All M.S. (thesis) and Ph.D. students are guaranteed assistantships (which come with tuition waivers) for at least 2 and 5 years'</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>必须:申请前须联系并获得一位教师同意担任导师,否则不予考虑;个人陈述末尾需列潜在导师</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>未说明</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>2026/12/1(每年唯一截止,仅秋季入学;按时申请并获导师提名者可受邀参加1月招生周末)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>不接受(官网称不再要求也不予考虑GRE)</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):UGA研究生院规定美国认证院校学位持有者通常无需TOEFL/IELTS(个别系可另要求);担任TA须按UGA TA政策另证英语能力</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -7481,12 +7661,32 @@
           <t>'MS students are eligible to receive TA/RA…competitive…include a tuition waiver and subsidized health insurance'</t>
         </is>
       </c>
-      <c r="F115" s="21" t="n"/>
-      <c r="G115" s="21" t="n"/>
-      <c r="H115" s="21" t="n"/>
-      <c r="I115" s="21" t="n"/>
+      <c r="F115" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:研究型论文硕士,官网建议申请前联系潜在导师,确认先修能力与研究匹配</t>
+        </is>
+      </c>
+      <c r="G115" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(MS生可竞争TA/RA,含学费减免和医保补贴)。需美国区域认证学士学位,本科GPA≥3.0;导师可能要求统计、GIS、制图、写作、数学基础(补修课不计学位学分)。系里称不单凭GRE/GPA决定录取,综合评估。</t>
+        </is>
+      </c>
+      <c r="H115" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网信息冲突:ESS新页面为 12/12(仅秋季入学),旧系页为 1/10(按2026周期,2027待公布);国际生建议截止前≥90天提交</t>
+        </is>
+      </c>
+      <c r="I115" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院将GRE列为学术型项目要求,但系新页面称不以GRE/GPA单独录取或拒绝,建议邮件确认</t>
+        </is>
+      </c>
       <c r="J115" s="21" t="n"/>
-      <c r="K115" s="21" t="n"/>
+      <c r="K115" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ pam.mitchell@geog.utah.edu(地理研究生协调员 Pam Mitchell,旧页面);summer.rupper@ess.utah.edu(ESS研究生事务副主任)</t>
+        </is>
+      </c>
       <c r="L115" s="21" t="inlineStr">
         <is>
           <t>https://ess.utah.edu/graduate/geography-ms.php</t>
@@ -7519,12 +7719,32 @@
           <t>'Between 5 and 10 half-time assistantships each year on a competitive basis';≥25% TA/RA全额学费减免</t>
         </is>
       </c>
-      <c r="F116" s="21" t="n"/>
-      <c r="G116" s="21" t="n"/>
-      <c r="H116" s="21" t="n"/>
-      <c r="I116" s="21" t="n"/>
+      <c r="F116" s="30" t="inlineStr">
+        <is>
+          <t>建议:按项目整体录取,无导师匹配流程;个人陈述写明1-2位感兴趣教授,可提前邮件联系</t>
+        </is>
+      </c>
+      <c r="G116" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(每年5-10个半职TA/RA,竞争性,含学费减免;截止前申请自动进入资助池)。需地理或相关学科扎实本科背景,本科专业GPA≥3.0;3封推荐信。论文型MS共32学分,需至少一门GIS课程。</t>
+        </is>
+      </c>
+      <c r="H116" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/15(2027秋季,含资助考虑;无春季入学)</t>
+        </is>
+      </c>
+      <c r="I116" s="30" t="inlineStr">
+        <is>
+          <t>不需要(不要求也不考虑GRE)</t>
+        </is>
+      </c>
       <c r="J116" s="21" t="n"/>
-      <c r="K116" s="21" t="n"/>
+      <c r="K116" s="30" t="inlineStr">
+        <is>
+          <t>mcohn@illinois.edu(研究生项目管理员 Matt Cohn)</t>
+        </is>
+      </c>
       <c r="L116" s="21" t="inlineStr">
         <is>
           <t>https://ggis.illinois.edu/academics/graduate-programs/assistantships-fellowships</t>
@@ -7557,12 +7777,32 @@
           <t>GTA/GRA;MS stipend $1,501/月+州外减免+30学分学费减免</t>
         </is>
       </c>
-      <c r="F117" s="21" t="n"/>
+      <c r="F117" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:申请信需写明潜在导师,建议申请前联系教师</t>
+        </is>
+      </c>
       <c r="G117" s="21" t="n"/>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-      <c r="J117" s="21" t="n"/>
-      <c r="K117" s="21" t="n"/>
+      <c r="H117" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/2/1;最终秋季 2027/7/1(春季11/1、夏季4/1)(按官网常规周期,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I117" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系页面未提及GRE,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J117" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):在英语为主要语言国家的英语授课认证院校获学士学位可豁免;否则TOEFL ≥79(新制4.0),IELTS ≥6.5,DET ≥115</t>
+        </is>
+      </c>
+      <c r="K117" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ thomas.lavanchy@okstate.edu(研究生事务协调员 Thomas LaVanchy,搜索结果中邮箱被截断,待核实)</t>
+        </is>
+      </c>
       <c r="L117" s="21" t="inlineStr">
         <is>
           <t>https://cas.okstate.edu/geography/graduate_studies/assistantships</t>
@@ -7595,12 +7835,32 @@
           <t>'typically offer teaching assistantships to our top applicants';部分TA仅给in-state待遇;MS通常2年</t>
         </is>
       </c>
-      <c r="F118" s="21" t="n"/>
-      <c r="G118" s="21" t="n"/>
-      <c r="H118" s="21" t="n"/>
-      <c r="I118" s="21" t="n"/>
+      <c r="F118" s="30" t="inlineStr">
+        <is>
+          <t>建议:可联系研究生主任咨询申请、录取与资助;个人陈述写明与教师研究的匹配</t>
+        </is>
+      </c>
+      <c r="G118" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(TA优先给顶尖申请者;部分TA仅州内学费待遇)。需学士学位,地理或多种相关专业均可;无最低GPA,录取者多数远高于3.0;3封推荐信。论文型32学分/非论文36学分。</t>
+        </is>
+      </c>
+      <c r="H118" s="30" t="inlineStr">
+        <is>
+          <t>无硬性截止;资助优先 2027/1/1(2月初出结果),之后按收件先后考虑资助</t>
+        </is>
+      </c>
+      <c r="I118" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J118" s="21" t="n"/>
-      <c r="K118" s="21" t="n"/>
+      <c r="K118" s="30" t="inlineStr">
+        <is>
+          <t>omb-grad-advising@tamu.edu(研究生项目协调员 Heather Albrecht);⚠️ filippi@tamu.edu(研究生项目主任 Anthony Filippi,来源有冲突)</t>
+        </is>
+      </c>
       <c r="L118" s="21" t="inlineStr">
         <is>
           <t>https://artsci.tamu.edu/geography/academics/graduate/funding.html</t>
@@ -7633,11 +7893,31 @@
           <t>约6–10 GA+2–3 TA/年;第一年'likely cover most basic tuition fees';国际生非居民学费减免2年(校级竞争)</t>
         </is>
       </c>
-      <c r="F119" s="21" t="n"/>
-      <c r="G119" s="21" t="n"/>
-      <c r="H119" s="21" t="n"/>
-      <c r="I119" s="21" t="n"/>
-      <c r="J119" s="21" t="n"/>
+      <c r="F119" s="30" t="inlineStr">
+        <is>
+          <t>必须:需有教师同意担任导师(faculty sponsor)才会被录取,建议截止前联系</t>
+        </is>
+      </c>
+      <c r="G119" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA/TA名额有限;国际生非居民学费减免为校级竞争)。本科全部课程GPA≥3.0;相关专业学士、3封推荐信;约500字研究兴趣陈述需体现与教师研究的关联;准备不足需额外补修课程。</t>
+        </is>
+      </c>
+      <c r="H119" s="30" t="inlineStr">
+        <is>
+          <t>Cal State Apply 2026/12/1;材料及系内申请 2026/12/15(2027秋季;不招春季)</t>
+        </is>
+      </c>
+      <c r="I119" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(2026秋季不要求,可自愿提交);2027政策未确认</t>
+        </is>
+      </c>
+      <c r="J119" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):有美国区域认证学士学位无需提交;否则TOEFL ≥79(新制4),IELTS ≥6.5,DET ≥105</t>
+        </is>
+      </c>
       <c r="K119" s="21" t="n"/>
       <c r="L119" s="21" t="inlineStr">
         <is>
@@ -7671,12 +7951,32 @@
           <t>GA $9,000/年;仅竞争性免州外差额</t>
         </is>
       </c>
-      <c r="F120" s="21" t="n"/>
-      <c r="G120" s="21" t="n"/>
+      <c r="F120" s="30" t="inlineStr">
+        <is>
+          <t>建议:非必须;需提交说明申请动机的cover letter,可先联系项目主任/潜在导师</t>
+        </is>
+      </c>
+      <c r="G120" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA $9,000/年,州外差额仅竞争性减免)。需认证学士学位;非地理本科需在研究生委员会指导下补修自然地理、人文地理、地理技术;优先GPA≥3.0。另需≤2页cover letter。</t>
+        </is>
+      </c>
       <c r="H120" s="21" t="n"/>
-      <c r="I120" s="21" t="n"/>
-      <c r="J120" s="21" t="n"/>
-      <c r="K120" s="21" t="n"/>
+      <c r="I120" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:旧目录要求GRE(优先任一部分≥50百分位);当前项目页称GPA≥3.0+两页职业目标陈述可免GRE;研究生院整体不强制</t>
+        </is>
+      </c>
+      <c r="J120" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):在美国院校就读可豁免;否则TOEFL ≥79(单项≥11),IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K120" s="30" t="inlineStr">
+        <is>
+          <t>martindj1@appstate.edu(项目主任 Dr. Derek Martin)</t>
+        </is>
+      </c>
       <c r="L120" s="21" t="inlineStr">
         <is>
           <t>https://geo.appstate.edu/graduate-students/academics</t>
@@ -7709,12 +8009,32 @@
           <t>'competitively offers assistantships to MS in Geography students'(证书不资助)</t>
         </is>
       </c>
-      <c r="F121" s="21" t="n"/>
+      <c r="F121" s="30" t="inlineStr">
+        <is>
+          <t>不需要:两步录取(研究生院+学院),无需提前联系;可向研究生顾问 Dr. Hallett 咨询</t>
+        </is>
+      </c>
       <c r="G121" s="21" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
-      <c r="J121" s="21" t="n"/>
-      <c r="K121" s="21" t="n"/>
+      <c r="H121" s="30" t="inlineStr">
+        <is>
+          <t>滚动录取(每学期可入学);助教资助考虑截止 2027/2/15</t>
+        </is>
+      </c>
+      <c r="I121" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J121" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:校方豁免"在英语国家完成学业"者,但未确认美国学士学位是否自动豁免,需问International Admissions;非豁免需TOEFL ≥80,IELTS ≥6.5,DET ≥105</t>
+        </is>
+      </c>
+      <c r="K121" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ lucius.hallett@wmich.edu(研究生顾问 Lucius Hallett,来自旧文件);egs-info@wmich.edu(学院总邮箱)</t>
+        </is>
+      </c>
       <c r="L121" s="21" t="inlineStr">
         <is>
           <t>https://wmich.edu/environment/academics/masters</t>
@@ -7747,12 +8067,32 @@
           <t>GTA/GRA 硕士 $1,225-1,668/月;'减免部分学费'+大部分医保</t>
         </is>
       </c>
-      <c r="F122" s="21" t="n"/>
+      <c r="F122" s="30" t="inlineStr">
+        <is>
+          <t>不需要:专业型规划硕士,按项目整体录取</t>
+        </is>
+      </c>
       <c r="G122" s="21" t="n"/>
-      <c r="H122" s="21" t="n"/>
-      <c r="I122" s="21" t="n"/>
-      <c r="J122" s="21" t="n"/>
-      <c r="K122" s="21" t="n"/>
+      <c r="H122" s="30" t="inlineStr">
+        <is>
+          <t>奖学金优先 2027/1/15;最终 2027/2/15(按目录常规周期,仅秋季入学;⚠️ 学院博士已提前至12/15,MCRP 2027待公布)</t>
+        </is>
+      </c>
+      <c r="I122" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:第三方称可选但鼓励提交;双学位项目必需;建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J122" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 大概率否:学院博士手册称美国学士学位者无需TOEFL,未确认适用MCRP;GT 2027秋起公民身份不再单独满足英语要求</t>
+        </is>
+      </c>
+      <c r="K122" s="30" t="inlineStr">
+        <is>
+          <t>crp@design.gatech.edu(规划学院研究生招生顾问)</t>
+        </is>
+      </c>
       <c r="L122" s="21" t="inlineStr">
         <is>
           <t>https://planning.gatech.edu/financial-aid</t>
@@ -7827,12 +8167,32 @@
           <t>GA含9学分学费(州内率)+硕士stipend $4,200/学期;GPA≥3.0</t>
         </is>
       </c>
-      <c r="F124" s="21" t="n"/>
+      <c r="F124" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GA需在申请时勾选意向</t>
+        </is>
+      </c>
       <c r="G124" s="21" t="n"/>
-      <c r="H124" s="21" t="n"/>
-      <c r="I124" s="21" t="n"/>
-      <c r="J124" s="21" t="n"/>
-      <c r="K124" s="21" t="n"/>
+      <c r="H124" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 国际生秋季约 2027/7/20(国际招生指南,约2年前);第三方Peterson's:秋季国内7/1、国际5/15;⚠️ 资助截止(第三方)3/1,建议尽早</t>
+        </is>
+      </c>
+      <c r="I124" s="30" t="inlineStr">
+        <is>
+          <t>必需:目录要求V+Q平均50百分位、写作≥4.0;仅有美国研究生学位者豁免;2025秋起不再自动豁免,仅项目主任可批准</t>
+        </is>
+      </c>
+      <c r="J124" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):从美国大学毕业可豁免;否则TOEFL ≥78(单项≥17),IELTS ≥6.0</t>
+        </is>
+      </c>
+      <c r="K124" s="30" t="inlineStr">
+        <is>
+          <t>d.arrighi@csuohio.edu(研究生项目协调员 Dave Arrighi);urbanprograms@csuohio.edu(MUPD项目办公室)</t>
+        </is>
+      </c>
       <c r="L124" s="21" t="inlineStr">
         <is>
           <t>https://levin.csuohio.edu/lssc/graduate-assistantships</t>
@@ -7865,12 +8225,36 @@
           <t>'merit-based and extremely competitive';GA 10–20h/周×9月;奖学金10–100%学费</t>
         </is>
       </c>
-      <c r="F125" s="21" t="n"/>
-      <c r="G125" s="21" t="n"/>
-      <c r="H125" s="21" t="n"/>
-      <c r="I125" s="21" t="n"/>
-      <c r="J125" s="21" t="n"/>
-      <c r="K125" s="21" t="n"/>
+      <c r="F125" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,文书写规划目标及为何选MCP</t>
+        </is>
+      </c>
+      <c r="G125" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(奖学金/GA基于成绩,竞争激烈)。不要求规划本科,背景不限;正式录取需专业课B平均;缺先修可有条件录取并补修不计学分课。材料:2-3封推荐信、简历、2页目标陈述;作品集可选。STEM认证学位。</t>
+        </is>
+      </c>
+      <c r="H125" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/1/10;不需资助可至 2027/6/30(⚠️ 按往年周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I125" s="30" t="inlineStr">
+        <is>
+          <t>不需要(官网现页面)</t>
+        </is>
+      </c>
+      <c r="J125" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院对"全英语授课院校学士"可申请豁免,须提交申请后邮件 grad.admissions@uc.edu 申请;否则TOEFL ≥87,IELTS ≥6.5,DET ≥110</t>
+        </is>
+      </c>
+      <c r="K125" s="30" t="inlineStr">
+        <is>
+          <t>hollstlh@ucmail.uc.edu(MCP项目主任 Leah Hollstein);heinka@ucmail.uc.edu(规划学院项目协调员 Kendra Hein)</t>
+        </is>
+      </c>
       <c r="L125" s="21" t="inlineStr">
         <is>
           <t>https://www.daap.uc.edu/academic-programs/school-of-planning/master-of-community-planning/master-of-community-planning-curr.html</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -4912,15 +4912,31 @@
           <t>竞争性 TA/RA/fellowship</t>
         </is>
       </c>
-      <c r="F61" s="21" t="n"/>
-      <c r="G61" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H61" s="21" t="n"/>
-      <c r="I61" s="21" t="n"/>
-      <c r="J61" s="21" t="n"/>
+      <c r="F61" s="30" t="inlineStr">
+        <is>
+          <t>建议:按项目录取,但个人陈述须说明目标与系里可用导师的匹配;录取看名额与教师专长匹配,所有候选人需面试</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 官网未明确国际生资助资格,TA/RA/fellowship 为竞争性)。先修:无指定课程;本科累计GPA≥3.0、专业GPA≥3.25(研究生GPA≥3.5);3封推荐信+个人陈述;全职/非全职均可申请</t>
+        </is>
+      </c>
+      <c r="H61" s="30" t="inlineStr">
+        <is>
+          <t>最终 2026/12/15(系官网;⚠️ Peterson's 另列 2/1,以系官网为准)</t>
+        </is>
+      </c>
+      <c r="I61" s="30" t="inlineStr">
+        <is>
+          <t>不需要(HDFS 官网明确 MS 不要求 GRE)</t>
+        </is>
+      </c>
+      <c r="J61" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:HDFS 要求非母语者 TOEFL iBT ≥100 或 IELTS ≥7.0;研究生院仅对英语为主要语言国家的学位授权豁免,须由项目负责人正式申请,美国学位能否豁免需邮件确认</t>
+        </is>
+      </c>
       <c r="K61" s="21" t="n"/>
       <c r="L61" s="21" t="inlineStr">
         <is>
@@ -4954,16 +4970,36 @@
           <t>'The programs offer graduate research and teaching assistantships, supplementary awards and scholarships';录取后告知资助包</t>
         </is>
       </c>
-      <c r="F62" s="21" t="n"/>
-      <c r="G62" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H62" s="21" t="n"/>
-      <c r="I62" s="21" t="n"/>
-      <c r="J62" s="21" t="n"/>
-      <c r="K62" s="21" t="n"/>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>不需要:录取时由项目分配委员会主席(chair);意向书应具体写明1-2个想研究的方向</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>可以申请,但须签署 BYU Honor Code 并完成宗教背书面试(非LDS申请人需当地宗教领袖+BYU Chaplain);须住在可开车到校距离。先修:无指定课程;美国同等学士学位、GPA≥3.0;3封推荐信(不接受亲友/宗教领袖)、≥2页写作样本(禁用AI)、CV、意向书;每年仅录6-10人</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>最终 2027/1/10 23:59(美东时间);每年仅秋季入学,通常3月出结果</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>可选(鼓励但不要求;5年以上成绩不接受,不可用GMAT替代)</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:项目称国际生需 TOEFL(2年内有效);研究生院称可由项目发放英语豁免,但未公布标准;⚠️ 第三方称 TOEFL ≥85/IELTS ≥7。美本能否豁免需邮件确认</t>
+        </is>
+      </c>
+      <c r="K62" s="30" t="inlineStr">
+        <is>
+          <t>mfhdgrad@byu.edu(MFHD 研究生项目,电话 801-422-2060)</t>
+        </is>
+      </c>
       <c r="L62" s="21" t="inlineStr">
         <is>
           <t>https://gradstudies.byu.edu/departments/family-life-department</t>
@@ -4996,16 +5032,28 @@
           <t>'Students may be eligible for tuition waivers or graduate assistantships from the department'</t>
         </is>
       </c>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H63" s="21" t="n"/>
+      <c r="F63" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不适用:该MS为PhD内的 in-flight 硕士;申请PhD时导师在项目内分配,可联系项目协调员确认</t>
+        </is>
+      </c>
+      <c r="G63" s="30" t="inlineStr">
+        <is>
+          <t>❌ 该 Developmental &amp; Family Science MS 不单独招生:官网称仅对已录取 HDFS PhD 的学生开放(研究生手册同);如需此方向须申请 PhD。PhD录取看GPA≥3.0、3封推荐信、目标陈述、CV;非母语者 TOEFL ≥79</t>
+        </is>
+      </c>
+      <c r="H63" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季优先 2026/12/1;秋季最终 2026/12/15(系页面较旧,2027待确认)</t>
+        </is>
+      </c>
       <c r="I63" s="21" t="n"/>
       <c r="J63" s="21" t="n"/>
-      <c r="K63" s="21" t="n"/>
+      <c r="K63" s="30" t="inlineStr">
+        <is>
+          <t>brandt.gardner@okstate.edu(HDFS 项目协调员 Dr. Brandt Gardner,⚠️ 需核实是否仍在任)</t>
+        </is>
+      </c>
       <c r="L63" s="21" t="inlineStr">
         <is>
           <t>https://go.okstate.edu/graduate-academics/programs/masters/developmental-and-family-science-ms.html</t>
@@ -5208,16 +5256,36 @@
           <t>GTA .50 FTE 覆盖学费(≤15 hr)+费用+津贴;2-1 截止</t>
         </is>
       </c>
-      <c r="F67" s="21" t="n"/>
-      <c r="G67" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H67" s="21" t="n"/>
-      <c r="I67" s="21" t="n"/>
-      <c r="J67" s="21" t="n"/>
-      <c r="K67" s="21" t="n"/>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>必须:录取前须有一名 Kinesiology 教师同意担任 mentor,学院建议申请前就联系好</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GTA 2/1 截止)。先修:任何学士学位即可,本科GPA≥2.75;非运动学背景强烈建议修过运动生理、生物力学、运动学习及基础科学课;3封推荐信+意向书+简历;国际生另需财力证明和医保</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>资助(GTA)2027/2/1;秋季最终 2027/5/1(国际生 2027/4/1)</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:学院官网与 Bulletin 均未列 GRE;Peterson's 称必需,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>否(研究生院 FAQ:在美国区域认证院校取得学位的国际生收到正式成绩单后可免考,逐案审核);如需考:TOEFL iBT ≥79 且各项≥16,IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>rudisme@auburn.edu(School of Kinesiology 主任 Dr. Mary Rudisill);gradadm@auburn.edu(研究生院招生)</t>
+        </is>
+      </c>
       <c r="L67" s="21" t="inlineStr">
         <is>
           <t>https://education.auburn.edu/kinesiology/kines-grad-admissions-reqs.php</t>
@@ -5250,16 +5318,36 @@
           <t>每年 15-20 个 GA;3-1 截止</t>
         </is>
       </c>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H68" s="21" t="n"/>
-      <c r="I68" s="21" t="n"/>
-      <c r="J68" s="21" t="n"/>
-      <c r="K68" s="21" t="n"/>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>不需要:导师在入学后组建委员会时自选;申请前有问题可联系项目主任</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA 3/1 截止)。先修:优先运动学背景,否则可能需补 Human Anatomy &amp; Physiology、Exercise Physiology、Biomechanics、Anatomical Kinesiology;最后60学分GPA≥3.0;3封推荐信(≥2封来自教师)+目的陈述</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/3/1;最终(无资助)2027/7/1</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系官网未列;第三方(Peterson's/Mastersportal)称需 GRE 或 MAT(≥40百分位),建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>否(研究生院政策:在美国等英语授课国家完成两年大学学习即视为英语达标;⚠️ 建议确认)</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>melissa.johnson@usu.edu(研究生项目协调员 Melissa Johnson);brennan.thompson@usu.edu(项目主任 Brennan Thompson)</t>
+        </is>
+      </c>
       <c r="L68" s="21" t="inlineStr">
         <is>
           <t>https://www.usu.edu/degrees-majors/kinesiology_ms</t>
@@ -5292,16 +5380,32 @@
           <t>TA ~$16,500/yr+学费减免+医保;通常 1-2 年</t>
         </is>
       </c>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>建议:研究型项目按研究兴趣匹配教师,个人陈述须点名最匹配的运动生理教师;顶尖候选人有面试</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(TA 含学费减免)。先修:优先 EXSS/体育/运动学专业;须在截止前完成5门先修(人体解剖、人体生理、含实验的运动生理+2门健康体能类如运动测试/营养/生物力学),建议各门 B- 以上;另需≥3学分统计课(B-以上,AP不算);3封推荐信</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>最终 2027/1/12(仅秋季入学)</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>不需要(系官网:不再要求 GRE)</t>
+        </is>
+      </c>
       <c r="J69" s="21" t="n"/>
-      <c r="K69" s="21" t="n"/>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>nelspopp@email.unc.edu(EXSS 研究生招生主任 Dr. Nels Popp)</t>
+        </is>
+      </c>
       <c r="L69" s="21" t="inlineStr">
         <is>
           <t>https://exss.unc.edu/exercise-physiology/assistantships/</t>
@@ -5376,15 +5480,31 @@
           <t>'All applicants who are admitted are considered for graduate assistantships';年支持$9,595–22,176+学费减免;TA由学院出、RA看导师经费</t>
         </is>
       </c>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-      <c r="J71" s="21" t="n"/>
+      <c r="F71" s="30" t="inlineStr">
+        <is>
+          <t>必须:录取由教师个人决定是否接收研究方向匹配的学生,申请前应联系潜在导师</t>
+        </is>
+      </c>
+      <c r="G71" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(所有录取者均被考虑 GA;国际生需提交财力证明表)。先修:无统一先修课,优先运动学/运动科学相关学士,其他背景可能需补课;本科GPA≥3.0;目的陈述+3封推荐信</t>
+        </is>
+      </c>
+      <c r="H71" s="30" t="inlineStr">
+        <is>
+          <t>全面考虑截止 2026/12/15;之后视名额审核(⚠️ Peterson's 列 12/1)</t>
+        </is>
+      </c>
+      <c r="I71" s="30" t="inlineStr">
+        <is>
+          <t>不需要(健康学院研究生页称不要求 GRE;⚠️ 第三方仍列必需)</t>
+        </is>
+      </c>
+      <c r="J71" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院对特定国家学位豁免,名单未确认含美国;⚠️ 第三方称美国学位可免;否则 TOEFL ≥80/IELTS ≥6.5/Duolingo ≥110</t>
+        </is>
+      </c>
       <c r="K71" s="21" t="n"/>
       <c r="L71" s="21" t="inlineStr">
         <is>
@@ -5418,16 +5538,36 @@
           <t>'Graduate research and teaching assistantships are available and are renewable for two years';学院GRA/GTA含学费+月stipend+医保;3/1前发offer</t>
         </is>
       </c>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
-      <c r="J72" s="21" t="n"/>
-      <c r="K72" s="21" t="n"/>
+      <c r="F72" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 建议:申请材料需写明专业目标和兴趣方向,宜先联系感兴趣实验室的教师</t>
+        </is>
+      </c>
+      <c r="G72" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(学院 GRA/GTA 含学费+津贴+医保)。先修:需具备运动学本科核心能力,非运动学背景可能需补本科课;⚠️ GPA≥3.0(Peterson's);3封推荐信+目标陈述;方向为运动生理或运动行为科学</t>
+        </is>
+      </c>
+      <c r="H72" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 国际生秋季 2027/1/8(Mastersportal);Peterson's 列优先 2/1;资助 offer 3/1 前发出,建议1月前提交</t>
+        </is>
+      </c>
+      <c r="I72" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系官网未列;Peterson's 称需 GRE,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J72" s="30" t="inlineStr">
+        <is>
+          <t>否(K-State 研究生院:美国认证大学学位豁免英语考试;⚠️ 部分系限两年内学位,需确认)</t>
+        </is>
+      </c>
+      <c r="K72" s="30" t="inlineStr">
+        <is>
+          <t>scopp@k-state.edu(Kinesiology Program Chair Steven Copp,⚠️ 页面较旧);gradapply@k-state.edu(研究生院招生)</t>
+        </is>
+      </c>
       <c r="L72" s="21" t="inlineStr">
         <is>
           <t>https://www.hhs.k-state.edu/health-sciences/academics/graduate/kinesiology/masters.html</t>
@@ -5460,16 +5600,36 @@
           <t>GA=stipend+学费减免+医保,9个月可续1年;'chances depend on the pool';另有GEM奖学金免非居民学费(GPA≥3.3,含国际生)</t>
         </is>
       </c>
-      <c r="F73" s="21" t="n"/>
-      <c r="G73" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H73" s="21" t="n"/>
-      <c r="I73" s="21" t="n"/>
-      <c r="J73" s="21" t="n"/>
-      <c r="K73" s="21" t="n"/>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>必须:申请信须写明潜在 faculty mentor,建议申请前邮件联系匹配教师</t>
+        </is>
+      </c>
+      <c r="G73" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA 与 GEM 奖学金均含国际生)。先修:美国区域认证学士学位,最近学士GPA≥3.0;课程背景需能支撑所选方向(如运动生理);申请信+简历+3封推荐信</t>
+        </is>
+      </c>
+      <c r="H73" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/2/1(GA 之后滚动审核);最终 2027/8/1(⚠️ 页面较旧)</t>
+        </is>
+      </c>
+      <c r="I73" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:官网申请清单未列 GRE,可能不需要;第三方称需5年内 GRE</t>
+        </is>
+      </c>
+      <c r="J73" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际招生称在名单国家英语授课院校取得学位可免,名单未确认含美国;否则 ⚠️ TOEFL ≥80/IELTS ≥6.5(第三方)</t>
+        </is>
+      </c>
+      <c r="K73" s="30" t="inlineStr">
+        <is>
+          <t>KinesiologyGrad@boisestate.edu(研究生项目协调员 Eric Martin);tinafreeman@boisestate.edu(研究生招生协调员)</t>
+        </is>
+      </c>
       <c r="L73" s="21" t="inlineStr">
         <is>
           <t>https://www.boisestate.edu/kinesiology-masters/student-funding-opportunities/</t>
@@ -5502,16 +5662,36 @@
           <t>项目页:优先截止前申请可考虑TA;校级:半时GA全额学费减免+stipend+医保;国际生随GA获州外学费减免</t>
         </is>
       </c>
-      <c r="F74" s="21" t="n"/>
-      <c r="G74" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H74" s="21" t="n"/>
-      <c r="I74" s="21" t="n"/>
-      <c r="J74" s="21" t="n"/>
-      <c r="K74" s="21" t="n"/>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>建议:系里建议先找潜在导师(thesis 方向尤其重要),确认其实验室有名额</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(优先截止前申请可考虑 TA;国际生随 GA 获州外学费减免)。先修:无指定课程,需具备生物、生理、健康等基础,不足需先补本科课;500字陈述+3封推荐信(2封来自教授);通过 GradCAS 申请</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/1/10(项目页;⚠️ 研究生院页写 1/4);之后仍收申请</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>否(WSU 研究生院:美国区域认证院校学士及以上学位豁免英语考试)</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>ceshs.gradstudies@wsu.edu(学院研究生教育办公室 Kjelda Berg);gradschool@wsu.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L74" s="21" t="inlineStr">
         <is>
           <t>https://ceshs.wsu.edu/degrees/kinesiology-grad-program-application-process</t>
@@ -7032,16 +7212,36 @@
           <t>GA:全额学费+费用+月津贴(20 hr,有限);分部奖学金</t>
         </is>
       </c>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 联系 cph@osu.edu</t>
-        </is>
-      </c>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
+      <c r="F101" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(部分申请人需面试),个人陈述可写职业目标</t>
+        </is>
+      </c>
+      <c r="G101" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ GA资助有限,国际生资助细节建议邮件 cph@osu.edu 确认)。先修:≥3学分入门财务会计(可入学前暑期补修);GPA≥3.0;3封推荐信;部分申请人面试;经SOPHAS+OSU补充申请</t>
+        </is>
+      </c>
+      <c r="H101" s="30" t="inlineStr">
+        <is>
+          <t>奖学金优先 2026/11/14;常规 2027/2/2(仅秋季入学;⚠️ 按官网当前页面,未标明2027周期)</t>
+        </is>
+      </c>
+      <c r="I101" s="30" t="inlineStr">
+        <is>
+          <t>可选(公卫学院所有研究生项目GRE可选)</t>
+        </is>
+      </c>
+      <c r="J101" s="30" t="inlineStr">
+        <is>
+          <t>否(仅主要在美国以外受教育的非母语者需提交);若需:TOEFL ≥79,IELTS ≥6.5,DET ≥120</t>
+        </is>
+      </c>
+      <c r="K101" s="30" t="inlineStr">
+        <is>
+          <t>cph@osu.edu(公卫学院招生与学生服务);gpadmissions@osu.edu(OSU研究生招生)</t>
+        </is>
+      </c>
       <c r="L101" s="21" t="inlineStr">
         <is>
           <t>https://cph.osu.edu/mha/scholarships-financial-aid</t>
@@ -7074,16 +7274,32 @@
           <t>'多数 MHA 生'通过本地医疗机构付费 GA 获经验+州内学费</t>
         </is>
       </c>
-      <c r="F102" s="21" t="n"/>
-      <c r="G102" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 医院 GA 可能需工作授权</t>
-        </is>
-      </c>
-      <c r="H102" s="21" t="n"/>
-      <c r="I102" s="21" t="n"/>
+      <c r="F102" s="30" t="inlineStr">
+        <is>
+          <t>必须:所有国际申请人须在申请前联系MHA项目临时主任 Dr. Nabil Natafgi</t>
+        </is>
+      </c>
+      <c r="G102" s="30" t="inlineStr">
+        <is>
+          <t>可以申请,但医院付费GA可能需工作授权(⚠️ F-1校外实习需CPT,建议确认)。先修:四年制学士,本科GPA≥3.00;未见特定先修课;经SOPHAS或HAMPCAS(二选一)申请</t>
+        </is>
+      </c>
+      <c r="H102" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2026/7/15(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I102" s="30" t="inlineStr">
+        <is>
+          <t>不需要(可选提交GRE/GMAT;⚠️ 旧FAQ称必需,以项目页为准)</t>
+        </is>
+      </c>
       <c r="J102" s="21" t="n"/>
-      <c r="K102" s="21" t="n"/>
+      <c r="K102" s="30" t="inlineStr">
+        <is>
+          <t>nnatafgi@mailbox.sc.edu(MHA项目临时主任 Dr. Nabil Natafgi)</t>
+        </is>
+      </c>
       <c r="L102" s="21" t="inlineStr">
         <is>
           <t>https://sc.edu/study/colleges_schools/public_health/study/graduate_degrees/health_services_policy_and_management/mha/</t>
@@ -7167,12 +7383,36 @@
           <t>系 assistantship ~$18,000/yr+学费减免;13-20 hr;硕士可续 2 年</t>
         </is>
       </c>
-      <c r="F104" s="21" t="n"/>
-      <c r="G104" s="21" t="n"/>
-      <c r="H104" s="21" t="n"/>
-      <c r="I104" s="21" t="n"/>
-      <c r="J104" s="21" t="n"/>
-      <c r="K104" s="21" t="n"/>
+      <c r="F104" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:论文型须有教师同意任导师否则基本不录,建议联系3-4位;论文型优先获assistantship</t>
+        </is>
+      </c>
+      <c r="G104" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获系assistantship约$18,900/yr+9学分学费减免;TA需SPEAK≥45)。先修:地理或相关专业,其他专业可能需补课;建议GPA≥3.0;需CV、写作样本、陈述、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H104" s="30" t="inlineStr">
+        <is>
+          <t>优先 1/19(资助自1/15起考虑);滚动至 3/1(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I104" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(硕士GRE豁免明确至2026秋,2027待确认)</t>
+        </is>
+      </c>
+      <c r="J104" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:官网未见美国学位豁免说明;TOEFL iBT 80(bulletin另写100,有冲突);TA需SPEAK ≥45</t>
+        </is>
+      </c>
+      <c r="K104" s="30" t="inlineStr">
+        <is>
+          <t>tmccreary@fsu.edu(研究生项目主任 Tyler McCreary,系官网);⚠️ aryoung@fsu.edu(学术项目协调员,来自bulletin,需确认)</t>
+        </is>
+      </c>
       <c r="L104" s="21" t="inlineStr">
         <is>
           <t>https://registrar.fsu.edu/bulletin/graduate-departments/geography</t>
@@ -7205,12 +7445,36 @@
           <t>~30 个系 assistantship/yr(1/3 时,13 hr);学费降至 $25/学期+津贴;硕士最多 2 年</t>
         </is>
       </c>
-      <c r="F105" s="21" t="n"/>
-      <c r="G105" s="21" t="n"/>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="21" t="n"/>
-      <c r="K105" s="21" t="n"/>
+      <c r="F105" s="30" t="inlineStr">
+        <is>
+          <t>建议:不要求申请前联系,入学后第一学期内确定导师;可提前联系研究方向相符的教授</t>
+        </is>
+      </c>
+      <c r="G105" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获系assistantship;当TA需另满足英语要求)。先修:未列具体先修课;MS偏自然地理/技术方法,MA偏人文地理;需成绩单、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H105" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/1(全额考虑与资助;系强烈偏好秋季入学)</t>
+        </is>
+      </c>
+      <c r="I105" s="30" t="inlineStr">
+        <is>
+          <t>不需要(GIScience方向强烈建议提交)</t>
+        </is>
+      </c>
+      <c r="J105" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,研究生院2025/3新政;个别项目可另要求,TA需另满足英语要求)</t>
+        </is>
+      </c>
+      <c r="K105" s="30" t="inlineStr">
+        <is>
+          <t>geographygradprogram@uga.edu(研究生项目/研究生主任 Jennifer Rice)</t>
+        </is>
+      </c>
       <c r="L105" s="21" t="inlineStr">
         <is>
           <t>https://geography.uga.edu/financial-assistance</t>
@@ -7243,16 +7507,36 @@
           <t>MA 通常 2 年 TA/RA;50% TA=$14,001/学期+9-18 学分学费减免;'录取不承诺资助'</t>
         </is>
       </c>
-      <c r="F106" s="21" t="n"/>
-      <c r="G106" s="21" t="inlineStr">
-        <is>
-          <t>✅ TA/RA 可</t>
-        </is>
-      </c>
-      <c r="H106" s="21" t="n"/>
-      <c r="I106" s="21" t="n"/>
-      <c r="J106" s="21" t="n"/>
-      <c r="K106" s="21" t="n"/>
+      <c r="F106" s="30" t="inlineStr">
+        <is>
+          <t>建议:申请表需填写最多4位潜在导师,录取看与教师兴趣匹配,建议提前联系1-2位</t>
+        </is>
+      </c>
+      <c r="G106" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 国际生可获TA/RA)。先修:不限地理专业,需有本科统计课,建议有数学和计算机基础;系最低GPA 3.0;3封推荐信</t>
+        </is>
+      </c>
+      <c r="H106" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/1(推荐信等材料 12/10 前);无春季入学</t>
+        </is>
+      </c>
+      <c r="I106" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J106" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系页称国际生须提交英语考试成绩,研究生院未见美国学位豁免;录取后须提交合格成绩</t>
+        </is>
+      </c>
+      <c r="K106" s="30" t="inlineStr">
+        <is>
+          <t>Karen.Weingarten@colorado.edu(研究生项目助理,⚠️ 信息较旧需确认);cugeography@colorado.edu(系办)</t>
+        </is>
+      </c>
       <c r="L106" s="21" t="inlineStr">
         <is>
           <t>https://www.colorado.edu/geography/grad-program/funding-fellowships-scholarships-tas-ras</t>
@@ -7472,11 +7756,27 @@
         </is>
       </c>
       <c r="F110" s="21" t="n"/>
-      <c r="G110" s="21" t="n"/>
+      <c r="G110" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。先修:需相关背景课程(具体未列);GPA:M.A.Geo. ≥3.0(或最后60学时≥3.0),M.S. ≥3.2(系FAQ另写MS 3.4/MAGeo 3.2,有冲突);需陈述、CV、3封推荐信</t>
+        </is>
+      </c>
       <c r="H110" s="21" t="n"/>
-      <c r="I110" s="21" t="n"/>
-      <c r="J110" s="21" t="n"/>
-      <c r="K110" s="21" t="n"/>
+      <c r="I110" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J110" s="30" t="inlineStr">
+        <is>
+          <t>否(美国区域认证学士学位豁免)</t>
+        </is>
+      </c>
+      <c r="K110" s="30" t="inlineStr">
+        <is>
+          <t>geograduate@txstate.edu(研究生咨询);ijo@txstate.edu(研究生项目协调员 Dr. Injeong Jo)</t>
+        </is>
+      </c>
       <c r="L110" s="21" t="inlineStr">
         <is>
           <t>https://wesgis.blogs.wesleyan.edu/2019/12/13/graduate-programs-in-giscience-txstate-geography</t>
@@ -7509,12 +7809,32 @@
           <t>GTA 含全额学费减免+医保+津贴;最多 2 年</t>
         </is>
       </c>
-      <c r="F111" s="21" t="n"/>
-      <c r="G111" s="21" t="n"/>
-      <c r="H111" s="21" t="n"/>
-      <c r="I111" s="21" t="n"/>
+      <c r="F111" s="30" t="inlineStr">
+        <is>
+          <t>建议:系FAQ建议申请人直接联系潜在导师</t>
+        </is>
+      </c>
+      <c r="G111" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。先修:学士学位;GPA≥2.5;非地理背景可修GEOG 4000补基础;3封推荐信;系不减免申请费</t>
+        </is>
+      </c>
+      <c r="H111" s="30" t="inlineStr">
+        <is>
+          <t>优先 2027/1/15;最终 2027/4/15(仅秋季入学)</t>
+        </is>
+      </c>
+      <c r="I111" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J111" s="21" t="n"/>
-      <c r="K111" s="21" t="n"/>
+      <c r="K111" s="30" t="inlineStr">
+        <is>
+          <t>geog-info@du.edu(地理系);⚠️ Eric.Boschmann@du.edu(研究生项目主任,第三方来源)</t>
+        </is>
+      </c>
       <c r="L111" s="21" t="inlineStr">
         <is>
           <t>https://wesgis.blogs.wesleyan.edu/2019/12/13/graduate-programs-at-the-university-of-denver</t>
@@ -7547,12 +7867,32 @@
           <t>每年秋季'少量 GTA 给新申请者';学费减免+津贴</t>
         </is>
       </c>
-      <c r="F112" s="21" t="n"/>
-      <c r="G112" s="21" t="n"/>
-      <c r="H112" s="21" t="n"/>
-      <c r="I112" s="21" t="n"/>
+      <c r="F112" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:非必需,但录取取决于有教师愿意任导师,申请RA尤其应先联系</t>
+        </is>
+      </c>
+      <c r="G112" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。先修:GPA≥3.0,3封推荐信,1-2页陈述;欢迎非地理专业申请</t>
+        </is>
+      </c>
+      <c r="H112" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季 2/1(GTA资助优先;国际生 2/1),旧目录为 1/15(国际 12/15),以研究生院为准</t>
+        </is>
+      </c>
+      <c r="I112" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:旧目录要求GRE,新目录未列,建议邮件确认</t>
+        </is>
+      </c>
       <c r="J112" s="21" t="n"/>
-      <c r="K112" s="21" t="n"/>
+      <c r="K112" s="30" t="inlineStr">
+        <is>
+          <t>ajoslin@k-state.edu(研究生项目主任 Dr. Audrey Joslin);pmcra@k-state.edu(系办)</t>
+        </is>
+      </c>
       <c r="L112" s="21" t="inlineStr">
         <is>
           <t>https://www.k-state.edu/geography/academics/graduate/faq.html</t>
@@ -7586,11 +7926,56 @@
         </is>
       </c>
       <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-      <c r="J113" s="21" t="n"/>
-      <c r="K113" s="21" t="n"/>
+      <c r="G113" s="30" t="inlineStr">
+        <is>
+          <t>IU: 可以申请。GPA≥3.0;硕士为MS(GIS方向),未见MA
+VT: 可以申请。成绩单、2页陈述、3封推荐信、写作样本
+WVU: 可以申请。地理或相关专业,GPA≥3.0,非地理专业首年补课;2封推荐信
+OU: 可以申请。GPA≥3.0;MA可论文/非论文;MS分环境系统/地理空间技术
+UW: 可以申请。最后60学期学分GPA≥3.0;3封推荐信
+UIUC: 可以申请。学士,GPA≥3.0(最后60学时);3封推荐信</t>
+        </is>
+      </c>
+      <c r="H113" s="30" t="inlineStr">
+        <is>
+          <t>IU: 2026/12/1(国内外同)
+VT: 资助全额考虑 2027/1/15;之后仍收但无资助优先
+WVU: 优先 2027/1/15(⚠️ 系页另写12/15)
+OU: 含资助 2027/1/15;不需资助 2027/4/1
+UW: 2026/12/15(最近工作日)
+UIUC: 2026/12/15</t>
+        </is>
+      </c>
+      <c r="I113" s="30" t="inlineStr">
+        <is>
+          <t>IU: 可选
+VT: 不需要(提交会参考)
+WVU: 不需要
+OU: ⚠️ 系页未说明,建议邮件确认
+UW: ⚠️ 不明确(Peterson's列必需,系页未说明)
+UIUC: 不需要(不考虑GRE)</t>
+        </is>
+      </c>
+      <c r="J113" s="30" t="inlineStr">
+        <is>
+          <t>IU: ⚠️ 不明确:TOEFL(纸考600),IELTS ≥6.5(资助建议7.0),DET ≥105;豁免需邮件 geoggsc@iu.edu 申请
+VT: 否(美国学位豁免);若需 TOEFL ≥90(各项≥20)
+WVU: ⚠️ 不明确:系页称非母语者均需提交,未见美国学位豁免
+OU: ⚠️ 不明确:按国籍判断需证明英语能力;⚠️ TOEFL ≥79(第三方)
+UW: 否(美国区域认证学位豁免)
+UIUC: 否(5年内美国学位豁免;TA可能另有要求)</t>
+        </is>
+      </c>
+      <c r="K113" s="30" t="inlineStr">
+        <is>
+          <t>IU: geoggsc@iu.edu(研究生教育协调员 Callaghan Maher)
+VT: oliverr@vt.edu(研究生主任 Robert Oliver);lisal22@vt.edu(研究生协调员 Lisa Lane)
+WVU: hope.stewart@mail.wvu.edu(系页地理研究生咨询联系人);graduateadmissions@mail.wvu.edu(研究生院招生)
+OU: dmdrake@ou.edu(研究生主任 Dr. Dawn Drake);dges@ou.edu(系办)
+UW: ⚠️ zhaobo@uw.edu(研究生主任 Bo Zhao,页面可能过时);ngross@uw.edu(学术服务主任)
+UIUC: mcohn@illinois.edu(研究生项目管理员 Matt Cohn);geography@illinois.edu(系办)</t>
+        </is>
+      </c>
       <c r="L113" s="21" t="inlineStr">
         <is>
           <t>https://www.profellow.com/fellowships/fully-funded-masters-programs-in-geography/</t>
@@ -7623,12 +8008,36 @@
           <t>'All applicants are considered for funding…limited and not guaranteed';资助含stipend+学费+100%医保</t>
         </is>
       </c>
-      <c r="F114" s="21" t="n"/>
-      <c r="G114" s="21" t="n"/>
-      <c r="H114" s="21" t="n"/>
-      <c r="I114" s="21" t="n"/>
-      <c r="J114" s="21" t="n"/>
-      <c r="K114" s="21" t="n"/>
+      <c r="F114" s="30" t="inlineStr">
+        <is>
+          <t>必须:申请前须有至少一位教师同意担任导师,强烈鼓励联系教师</t>
+        </is>
+      </c>
+      <c r="G114" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(所有申请者自动考虑资助,有限不保证)。先修:四年制学士,GPA≥3.0(录取者通常远高于);未列具体先修课;重视CV、陈述、推荐信</t>
+        </is>
+      </c>
+      <c r="H114" s="30" t="inlineStr">
+        <is>
+          <t>2026/11/15(国内外同;逾期不考虑资助)</t>
+        </is>
+      </c>
+      <c r="I114" s="30" t="inlineStr">
+        <is>
+          <t>不需要(不用于资助评定;个别教师可能要求)</t>
+        </is>
+      </c>
+      <c r="J114" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院仅要求主要在美国以外受教育者提交,系页未明确豁免;若需:TOEFL ≥79,IELTS ≥7(口语7),DET ≥130(系要求)</t>
+        </is>
+      </c>
+      <c r="K114" s="30" t="inlineStr">
+        <is>
+          <t>geography-gradstudies@osu.edu(研究生事务);⚠️ branham.118@osu.edu(研究生项目协调员 Joslyn Branham,需确认现任)</t>
+        </is>
+      </c>
       <c r="L114" s="21" t="inlineStr">
         <is>
           <t>https://geography.osu.edu/graduate/funding</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -11826,16 +11826,36 @@
           <t>'M.A. Graduate Assistantships carry a stipend for two semesters and a tuition waiver for 9 hours each semester';竞争性;申请时附短文</t>
         </is>
       </c>
-      <c r="F193" s="21" t="n"/>
-      <c r="G193" s="21" t="inlineStr">
-        <is>
-          <t>未说明(州外差额处理未明)</t>
-        </is>
-      </c>
-      <c r="H193" s="21" t="n"/>
-      <c r="I193" s="21" t="n"/>
-      <c r="J193" s="21" t="n"/>
-      <c r="K193" s="21" t="n"/>
+      <c r="F193" s="30" t="inlineStr">
+        <is>
+          <t>不需要:由系研究生委员会整体评审;个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G193" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA含两学期津贴+每学期9学分学费减免,但州外差额如何处理官网未说明)。先修:学士学位,学校最低GPA 3.0,系里录取者通常 ≥3.25;需个人陈述(≤3页)、写作样本、3封推荐信、简历;官网未列具体先修课</t>
+        </is>
+      </c>
+      <c r="H193" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季优先截止 2/15(系MA页,按2026周期,2027待公布);Peterson's 写 1/15,建议 2027/1/15 前提交</t>
+        </is>
+      </c>
+      <c r="I193" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:MA页列为必需(通常 V≥153、Q≥144),但写明2025-26周期豁免;FAQ仍写需提交;PhD已明确2027秋免GRE,MA待公布</t>
+        </is>
+      </c>
+      <c r="J193" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学士学位豁免,USF研究生招生政策);但国际生当TA需另证口语能力</t>
+        </is>
+      </c>
+      <c r="K193" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 研究生项目主任 Dr. Feng Hao(邮箱见系"Contact Graduate Program"页,搜索未显示);系办公室电话 813-974-2893</t>
+        </is>
+      </c>
       <c r="L193" s="21" t="inlineStr">
         <is>
           <t>https://www.usf.edu/arts-sciences/departments/sociology/graduate-programs/master-of-arts-sociology/graduate-assistantships.aspx</t>
@@ -11868,12 +11888,36 @@
           <t>'competitive funding opportunities';校级GA付学费+fees,硕士全职GA $925/月×9月</t>
         </is>
       </c>
-      <c r="F194" s="21" t="n"/>
-      <c r="G194" s="21" t="n"/>
-      <c r="H194" s="21" t="n"/>
-      <c r="I194" s="21" t="n"/>
-      <c r="J194" s="21" t="n"/>
-      <c r="K194" s="21" t="n"/>
+      <c r="F194" s="30" t="inlineStr">
+        <is>
+          <t>不需要:由招生委员会与项目主任滚动评审</t>
+        </is>
+      </c>
+      <c r="G194" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。先修:认证学士学位,GPA一般 ≥2.75;本科社会学 ≥18学分,含研究方法(SOC 3040)、统计(SOC 3050)、社会学理论(SOC 3060)或同等课程,成绩C以上(GPA/GRE高者可由项目主任豁免);需写作样本、动机信、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H194" s="30" t="inlineStr">
+        <is>
+          <t>秋季 3/1(春季 9/15);滚动审核,国际生建议尽早(2027/1-2月前)提交以留出签证时间</t>
+        </is>
+      </c>
+      <c r="I194" s="30" t="inlineStr">
+        <is>
+          <t>必需(需提交官方GRE成绩)</t>
+        </is>
+      </c>
+      <c r="J194" s="30" t="inlineStr">
+        <is>
+          <t>否(美国本科毕业生豁免TOEFL;否则 TOEFL iBT ≥71 / IELTS ≥6.0 / Duolingo ≥95)</t>
+        </is>
+      </c>
+      <c r="K194" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ Vicky.MacLean@mtsu.edu(社会学研究生项目主任,系联系页);Ugur.Orak@mtsu.edu(advising页亦列为研究生项目主任,两页冲突,建议先确认)</t>
+        </is>
+      </c>
       <c r="L194" s="21" t="inlineStr">
         <is>
           <t>https://www.mtsu.edu/program/sociology-m-a/</t>
@@ -11906,16 +11950,36 @@
           <t>系GA申请截止4/1;校级GA自动州外学费减免+月薪;F/J签证明文可任GA</t>
         </is>
       </c>
-      <c r="F195" s="21" t="n"/>
-      <c r="G195" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H195" s="21" t="n"/>
-      <c r="I195" s="21" t="n"/>
-      <c r="J195" s="21" t="n"/>
-      <c r="K195" s="21" t="n"/>
+      <c r="F195" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述写学术兴趣与选择本项目原因即可</t>
+        </is>
+      </c>
+      <c r="G195" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。先修:最后60学分GPA ≥3.0(或总GPA 3.0);需有社会学理论、统计、SPSS、社会研究方法背景,缺则需补修leveling课程;2页双倍行距个人陈述;MS Applied需简历</t>
+        </is>
+      </c>
+      <c r="H195" s="30" t="inlineStr">
+        <is>
+          <t>秋季优先(资助考虑)2027/2/1;常规截止 国际生 6/1(美国学生 7/15);弹性截止,逾期先到先审(按2026周期日期,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I195" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J195" s="30" t="inlineStr">
+        <is>
+          <t>否(美国区域认证大学学士学位豁免);否则 TOEFL iBT ≥78(旧制)/ Duolingo ≥110 / PTE ≥52</t>
+        </is>
+      </c>
+      <c r="K195" s="30" t="inlineStr">
+        <is>
+          <t>dd34@txstate.edu(Dr. David Dietrich,研究生项目主任);sociology@txstate.edu(社会学系)</t>
+        </is>
+      </c>
       <c r="L195" s="21" t="inlineStr">
         <is>
           <t>https://www.soci.txst.edu/graduate-degree.html</t>
@@ -11948,16 +12012,36 @@
           <t>GE(学费减免+津贴+保险)存在但有限;2026-27 博士无 GE 资助——硕士更紧</t>
         </is>
       </c>
-      <c r="F196" s="21" t="n"/>
-      <c r="G196" s="21" t="inlineStr">
-        <is>
-          <t>✅ 奖学金明文向国际生开放</t>
-        </is>
-      </c>
-      <c r="H196" s="21" t="n"/>
-      <c r="I196" s="21" t="n"/>
-      <c r="J196" s="21" t="n"/>
-      <c r="K196" s="21" t="n"/>
+      <c r="F196" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,每年仅收3-6人;入学后再选研究导师</t>
+        </is>
+      </c>
+      <c r="G196" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(奖学金明文向国际生开放)。先修:相关本科(人类发展、心理、教育、生物、营养、预防科学等)或相关经验;先修课/经验强烈建议但非必须;需目的陈述、推荐信、成绩单</t>
+        </is>
+      </c>
+      <c r="H196" s="30" t="inlineStr">
+        <is>
+          <t>2026/9/1 开放,滚动录取至 2027/6/30;1月开始审核与发offer,建议 2027/1 前提交(按2026周期,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I196" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J196" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学士学位通常豁免,研究生院政策);但当GE(TA)需口语达标(TOEFL口语 ≥26 或同等)</t>
+        </is>
+      </c>
+      <c r="K196" s="30" t="inlineStr">
+        <is>
+          <t>prevsci@uoregon.edu(项目协调员 Christina Schneider);⚠️ 项目主任 Heather Leonard(邮箱两处拼写不一 hleonar3/hleonard3,建议用项目邮箱)</t>
+        </is>
+      </c>
       <c r="L196" s="21" t="inlineStr">
         <is>
           <t>https://education.uoregon.edu/prevsci/funding</t>
@@ -11990,12 +12074,32 @@
           <t>'A limited number of merit-based graduate assistantships…All applicants are automatically considered'</t>
         </is>
       </c>
-      <c r="F197" s="22" t="n"/>
-      <c r="G197" s="22" t="n"/>
-      <c r="H197" s="22" t="n"/>
-      <c r="I197" s="22" t="n"/>
+      <c r="F197" s="31" t="inlineStr">
+        <is>
+          <t>不需要:所有申请者自动考虑GA,按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G197" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:⚠️ 官网未列具体先修课;第三方显示 GPA ≥3.0;需目的陈述、成绩单、推荐信</t>
+        </is>
+      </c>
+      <c r="H197" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ Peterson's:秋季 1/7(国内外相同),即 2027/1/7;研究生院fellowship仅秋季入学可申;以研究生院Academic Programs Portal为准</t>
+        </is>
+      </c>
+      <c r="I197" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(系页称不要求GRE,未完全确认为HDFS页)</t>
+        </is>
+      </c>
       <c r="J197" s="22" t="n"/>
-      <c r="K197" s="22" t="n"/>
+      <c r="K197" s="31" t="inlineStr">
+        <is>
+          <t>dcasper@ches.ua.edu(Deborah Casper,研究生项目协调员)</t>
+        </is>
+      </c>
       <c r="L197" s="22" t="inlineStr">
         <is>
           <t>https://catalog.ua.edu/graduate/human-environmental-sciences/human-development/ms/</t>
@@ -12028,12 +12132,36 @@
           <t>'Funding for M.S. students…is subject to the availability of funds'(PhD才保证)</t>
         </is>
       </c>
-      <c r="F198" s="22" t="n"/>
-      <c r="G198" s="22" t="n"/>
-      <c r="H198" s="22" t="n"/>
-      <c r="I198" s="22" t="n"/>
-      <c r="J198" s="22" t="n"/>
-      <c r="K198" s="22" t="n"/>
+      <c r="F198" s="31" t="inlineStr">
+        <is>
+          <t>建议:系里列出2027-28招生的教师(Crosby、Edler、Leerkes、Lobo),可直接发邮件自我介绍</t>
+        </is>
+      </c>
+      <c r="G198" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:研究生院要求本科GPA ≥3.0;论文型39学分;需1-3页专业陈述、学术写作样本、3封推荐信(至少2封来自教授)</t>
+        </is>
+      </c>
+      <c r="H198" s="31" t="inlineStr">
+        <is>
+          <t>2026/12/15(仅秋季入学,每年一次)</t>
+        </is>
+      </c>
+      <c r="I198" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 必需(仅第三方显示;如要求需5年内成绩),建议以研究生院项目页确认</t>
+        </is>
+      </c>
+      <c r="J198" s="31" t="inlineStr">
+        <is>
+          <t>否(美国区域认证大学学位,招生专员会豁免);否则 TOEFL ≥79,IELTS ≥6.5,Duolingo ≥110</t>
+        </is>
+      </c>
+      <c r="K198" s="31" t="inlineStr">
+        <is>
+          <t>heather_helms@uncg.edu(Dr. Heather Helms,研究生项目主任);hdfs@uncg.edu(系招生邮箱)</t>
+        </is>
+      </c>
       <c r="L198" s="22" t="inlineStr">
         <is>
           <t>https://hdf.uncg.edu/graduate/faq/</t>
@@ -12066,12 +12194,36 @@
           <t>仅校级GA池;项目偏在职/在线</t>
         </is>
       </c>
-      <c r="F199" s="22" t="n"/>
-      <c r="G199" s="22" t="n"/>
-      <c r="H199" s="22" t="n"/>
-      <c r="I199" s="22" t="n"/>
-      <c r="J199" s="22" t="n"/>
-      <c r="K199" s="22" t="n"/>
+      <c r="F199" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G199" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:相关学士学位(儿童发展、人类发展等),非相关专业有潜力也会考虑;最后60学分GPA ≥3.0;需CV和1名推荐人</t>
+        </is>
+      </c>
+      <c r="H199" s="31" t="inlineStr">
+        <is>
+          <t>秋季 7/15(春季 11/15,夏季 4/15);国际生建议提前(签证)</t>
+        </is>
+      </c>
+      <c r="I199" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 未明确要求(研究生院:仅系里要求时提交),大概率不需要</t>
+        </is>
+      </c>
+      <c r="J199" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:学校有TOEFL豁免表格,其他项目(社会学)明文美国学位可豁免,Family Studies未明说;否则 TOEFL ≥79</t>
+        </is>
+      </c>
+      <c r="K199" s="31" t="inlineStr">
+        <is>
+          <t>mbrown50@twu.edu(Melissa McInnis Brown,系招生联系人);erice4@twu.edu(Ellion Maggard,招生协调员)</t>
+        </is>
+      </c>
       <c r="L199" s="22" t="inlineStr">
         <is>
           <t>https://twu.edu/human-sciences/graduate-programs/family-studies/</t>
@@ -12104,11 +12256,31 @@
           <t>校级GA全部学费杂费减免(除活动费);系级未明</t>
         </is>
       </c>
-      <c r="F200" s="22" t="n"/>
-      <c r="G200" s="22" t="n"/>
-      <c r="H200" s="22" t="n"/>
-      <c r="I200" s="22" t="n"/>
-      <c r="J200" s="22" t="n"/>
+      <c r="F200" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G200" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:HDFS、心理学或相关专业学士;最低GPA 2.75,期望 ≥3.0;需一页目标陈述、简历;可选论文/非论文(36学分)</t>
+        </is>
+      </c>
+      <c r="H200" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/4/1(春季 10/1);需在项目截止前至少2个月向研究生院提交申请(即约 2027/2/1 前)</t>
+        </is>
+      </c>
+      <c r="I200" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J200" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证大学学士学位豁免);否则 TOEFL ≥71,IELTS ≥6.0,Duolingo ≥100</t>
+        </is>
+      </c>
       <c r="K200" s="22" t="n"/>
       <c r="L200" s="22" t="inlineStr">
         <is>
@@ -12142,12 +12314,32 @@
           <t>校级GA可能含州外减免+stipend;系页无信息</t>
         </is>
       </c>
-      <c r="F201" s="22" t="n"/>
-      <c r="G201" s="22" t="n"/>
+      <c r="F201" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G201" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:儿童发展、家庭研究、心理、社会学、教育或相关本科;GPA ≥2.7;本科至少各修1门儿童发展和家庭研究课程(否则可能需补修);需3封推荐信、目的陈述</t>
+        </is>
+      </c>
       <c r="H201" s="22" t="n"/>
-      <c r="I201" s="22" t="n"/>
-      <c r="J201" s="22" t="n"/>
-      <c r="K201" s="22" t="n"/>
+      <c r="I201" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 项目页未提及GRE,大概率不需要,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J201" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院规则为本科≥24学分且GPA≥3.0可豁免(美本应满足),但未见明文美国学位豁免;否则 TOEFL ≥78(各部分≥18),IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K201" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ warrens@ecu.edu(Sandra Warren,研究生项目主任,未确认是否负责HDFS);ballards@ecu.edu(系主任 Sharon Ballard)</t>
+        </is>
+      </c>
       <c r="L201" s="22" t="inlineStr">
         <is>
           <t>https://chhs.ecu.edu/hdfs/ms-human-development-family-science/</t>
@@ -12180,12 +12372,36 @@
           <t>'Over $100,000 awarded annually from fellowships';无GA比例</t>
         </is>
       </c>
-      <c r="F202" s="22" t="n"/>
-      <c r="G202" s="22" t="n"/>
-      <c r="H202" s="22" t="n"/>
-      <c r="I202" s="22" t="n"/>
-      <c r="J202" s="22" t="n"/>
-      <c r="K202" s="22" t="n"/>
+      <c r="F202" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G202" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:认证学士学位,最后60学分GPA ≥3.0;需推荐信、个人陈述、CV、写作样本、成绩单</t>
+        </is>
+      </c>
+      <c r="H202" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/1/1(校园项目)</t>
+        </is>
+      </c>
+      <c r="I202" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J202" s="31" t="inlineStr">
+        <is>
+          <t>否(研究生院:持英语国家含美国的学位可豁免,但项目保留要求提交的权利);否则 TOEFL ≥80,IELTS ≥6.5</t>
+        </is>
+      </c>
+      <c r="K202" s="31" t="inlineStr">
+        <is>
+          <t>hdfsgrad@missouri.edu(HDFS研究生办公室);⚠️ lestera@missouri.edu(Ashlie Lester,硕士项目研究生主任,另一页列 Melissa Herzog,建议确认)</t>
+        </is>
+      </c>
       <c r="L202" s="22" t="inlineStr">
         <is>
           <t>https://cehd.missouri.edu/degree/human-development-and-family-science-ms/</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -9524,15 +9524,31 @@
           <t>Master's Tuition Scholarship:第 2 年 75% 学费(或 25%+50%);need-based ≤50% 一年级学费;PFRH 系奖学金</t>
         </is>
       </c>
-      <c r="F140" s="21" t="n"/>
-      <c r="G140" s="21" t="inlineStr">
-        <is>
-          <t>✅ 国际生同等</t>
-        </is>
-      </c>
-      <c r="H140" s="21" t="n"/>
-      <c r="I140" s="21" t="n"/>
-      <c r="J140" s="21" t="n"/>
+      <c r="F140" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(SOPHAS),个人陈述可写感兴趣的研究方向/教授</t>
+        </is>
+      </c>
+      <c r="G140" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生同等考虑;系里按学业、经历、个人陈述给优秀MSPH生学费支持)。先修:认可大学学士;需修过普通生物学、高阶数学(建议微积分+统计)、社会科学各1门;最低GPA 3.0;面向公卫工作经验&lt;2年者。</t>
+        </is>
+      </c>
+      <c r="H140" s="30" t="inlineStr">
+        <is>
+          <t>最终及需求型奖学金优先 2027/3/1(需CSS Profile)(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I140" s="30" t="inlineStr">
+        <is>
+          <t>可选(系官网FAQ)</t>
+        </is>
+      </c>
+      <c r="J140" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):Bloomberg 对持有/攻读美国认证大学学士者免语言成绩;否则 TOEFL ≥100/IELTS ≥7/Duolingo ≥130</t>
+        </is>
+      </c>
       <c r="K140" s="21" t="n"/>
       <c r="L140" s="21" t="inlineStr">
         <is>
@@ -9566,11 +9582,31 @@
           <t>2026-27 硕士 assistant $9,500+部分学费减免;通常第 2 年续</t>
         </is>
       </c>
-      <c r="F141" s="21" t="n"/>
-      <c r="G141" s="21" t="n"/>
-      <c r="H141" s="21" t="n"/>
-      <c r="I141" s="21" t="n"/>
-      <c r="J141" s="21" t="n"/>
+      <c r="F141" s="30" t="inlineStr">
+        <is>
+          <t>建议:按项目录取,但重视研究兴趣与教师匹配,陈述中写明匹配教授;非必须事先套磁</t>
+        </is>
+      </c>
+      <c r="G141" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。注:自2026秋起心理科学MA与临床MA合并为 MA Psychology(Psychological Science track),社会心理属"认知与社会过程"方向。研究生院最低GPA 2.75(或后半段3.0);材料:约1000字目的陈述、2封推荐信、简历、成绩单。</t>
+        </is>
+      </c>
+      <c r="H141" s="30" t="inlineStr">
+        <is>
+          <t>系优先截止 2027/2/1(按2026周期,2027待公布);之后研究生院仍收,但系可能不再考虑录取/GA</t>
+        </is>
+      </c>
+      <c r="I141" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J141" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:目录称有美国以外学习经历者可能需提交,美本可能免交但未明文豁免;门槛 TOEFL 79/IELTS 6.5/PTE 53</t>
+        </is>
+      </c>
       <c r="K141" s="21" t="n"/>
       <c r="L141" s="21" t="inlineStr">
         <is>
@@ -9604,12 +9640,36 @@
           <t>'许多入学 MAPR 生获部分资助(10/20 hr GIA)';自动考虑</t>
         </is>
       </c>
-      <c r="F142" s="21" t="n"/>
-      <c r="G142" s="21" t="n"/>
-      <c r="H142" s="21" t="n"/>
-      <c r="I142" s="21" t="n"/>
-      <c r="J142" s="21" t="n"/>
-      <c r="K142" s="21" t="n"/>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>必须列出:研究兴趣陈述需按优先顺序列3位正在招生的系内教师;不强制事先套磁,但建议核对招生教师名单</t>
+        </is>
+      </c>
+      <c r="G142" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(入学即自动考虑GIA资助)。最低GPA 3.0(或最后60学时3.0);需以B及以上修过心理学导论、统计、实验/研究方法(可录取后、入学前补修);不达标者可考虑有条件录取。</t>
+        </is>
+      </c>
+      <c r="H142" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2026/2/1;最终 2026/4/30(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I142" s="30" t="inlineStr">
+        <is>
+          <t>不需要(提交也不考虑)</t>
+        </is>
+      </c>
+      <c r="J142" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):持美国区域认证学士及以上免语言成绩;否则 TOEFL 78/IELTS 6.5/Duolingo 110</t>
+        </is>
+      </c>
+      <c r="K142" s="30" t="inlineStr">
+        <is>
+          <t>psychology-masters@txstate.edu(心理系硕士项目咨询邮箱);项目主任 Dr. Kate Warnell</t>
+        </is>
+      </c>
       <c r="L142" s="21" t="inlineStr">
         <is>
           <t>https://www.psych.txst.edu/graduate/funding-assistantships.html</t>
@@ -9680,11 +9740,31 @@
           <t>GA stipend $9,480/学年+大部分学费减免(自付约$1,500/学期);给排名靠前学生</t>
         </is>
       </c>
-      <c r="F144" s="21" t="n"/>
-      <c r="G144" s="21" t="n"/>
-      <c r="H144" s="21" t="n"/>
-      <c r="I144" s="21" t="n"/>
-      <c r="J144" s="21" t="n"/>
+      <c r="F144" s="30" t="inlineStr">
+        <is>
+          <t>建议:按项目录取,但重视研究兴趣与教师匹配,陈述中写明匹配教授;非必须事先套磁</t>
+        </is>
+      </c>
+      <c r="G144" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。注:自2026秋起并入 MA Psychology(Psychological Science track)。研究生院最低GPA 2.75(或后半段3.0);材料:约1000字目的陈述、2封推荐信、简历、成绩单;GA给排名靠前者。</t>
+        </is>
+      </c>
+      <c r="H144" s="30" t="inlineStr">
+        <is>
+          <t>系优先截止 2027/2/1(按2026周期,2027待公布);之后研究生院仍收,但系可能不再考虑录取/GA</t>
+        </is>
+      </c>
+      <c r="I144" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J144" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:目录称有美国以外学习经历者可能需提交,美本可能免交但未明文豁免;门槛 TOEFL 79/IELTS 6.5/PTE 53</t>
+        </is>
+      </c>
       <c r="K144" s="21" t="n"/>
       <c r="L144" s="21" t="inlineStr">
         <is>
@@ -9718,16 +9798,32 @@
           <t>'Nearly half of students receive assistantship support annually'</t>
         </is>
       </c>
-      <c r="F145" s="21" t="n"/>
-      <c r="G145" s="21" t="inlineStr">
-        <is>
-          <t>可(F-1 STEM)</t>
-        </is>
-      </c>
-      <c r="H145" s="21" t="n"/>
-      <c r="I145" s="21" t="n"/>
+      <c r="F145" s="30" t="inlineStr">
+        <is>
+          <t>不需要:独立MS按项目录取(仅BS/MS加速项目需自找论文导师);陈述可写感兴趣教授</t>
+        </is>
+      </c>
+      <c r="G145" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(F-1 STEM项目)。需学士学位+心理学或相关先修课;⚠️第三方:≥12学分心理课,含统计/研究方法及实验课,先修GPA≥3.0;可书面申请认定等效课程;限额项目,建议早交。</t>
+        </is>
+      </c>
+      <c r="H145" s="30" t="inlineStr">
+        <is>
+          <t>2027/2/15 开始审核(建议此前提交);最终 2027/4/15(按2026-27目录;国际生学校通用建议 6/1)</t>
+        </is>
+      </c>
+      <c r="I145" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J145" s="21" t="n"/>
-      <c r="K145" s="21" t="n"/>
+      <c r="K145" s="30" t="inlineStr">
+        <is>
+          <t>paul.fuglestad@unf.edu(项目主任 Dr. Paul Fuglestad);psychgrad@unf.edu(心理系研究生咨询,可能为旧地址)</t>
+        </is>
+      </c>
       <c r="L145" s="21" t="inlineStr">
         <is>
           <t>https://www.unf.edu/graduateschool/academics/programs/psychological-science.html</t>
@@ -9760,11 +9856,31 @@
           <t>assistantship/tuition grants,一年级优先;'Affordable tuition with remittances available'</t>
         </is>
       </c>
-      <c r="F146" s="21" t="n"/>
-      <c r="G146" s="21" t="n"/>
-      <c r="H146" s="21" t="n"/>
-      <c r="I146" s="21" t="n"/>
-      <c r="J146" s="21" t="n"/>
+      <c r="F146" s="30" t="inlineStr">
+        <is>
+          <t>建议:论文由导师指导,系里建议联系研究方向匹配的教师了解项目;非必须</t>
+        </is>
+      </c>
+      <c r="G146" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。需心理学或相关领域学术准备(无此背景建议先咨询项目主任);⚠️第三方:最低GPA 3.0;材料含2封推荐信、个人陈述、200字多样性陈述、CV,面试仅受邀;36学分含8学分论文。</t>
+        </is>
+      </c>
+      <c r="H146" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2027/2/10(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I146" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:第三方称无GRE要求,系曾有按年度的GRE豁免,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J146" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):国际招生FAQ称毕业于美国大学可免语言证明(系可能另要求英语测试);否则 TOEFL 78/IELTS 6.0</t>
+        </is>
+      </c>
       <c r="K146" s="21" t="n"/>
       <c r="L146" s="21" t="inlineStr">
         <is>
@@ -9976,11 +10092,31 @@
           <t>handbook:GA'tuition scholarships and stipend…highly competitive';≤18学分学费/年+约$9,000 stipend;数量有限</t>
         </is>
       </c>
-      <c r="F150" s="21" t="n"/>
-      <c r="G150" s="21" t="n"/>
-      <c r="H150" s="21" t="n"/>
-      <c r="I150" s="21" t="n"/>
-      <c r="J150" s="21" t="n"/>
+      <c r="F150" s="30" t="inlineStr">
+        <is>
+          <t>必须在申请中写明潜在导师(导师制,录取后分配导师);建议提前联系</t>
+        </is>
+      </c>
+      <c r="G150" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA竞争激烈)。需≥20学时心理学课程,含统计及实验/研究方法实验课;GPA约3.0(研究生院最低2.7或后半段3.0);仅秋季入学;所有材料经PSYCAS提交。</t>
+        </is>
+      </c>
+      <c r="H150" s="30" t="inlineStr">
+        <is>
+          <t>2027/2/1(按目录,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I150" s="30" t="inlineStr">
+        <is>
+          <t>可选(系页面称当前周期不要求;旧目录写必需,以系页面为准)</t>
+        </is>
+      </c>
+      <c r="J150" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院按国家列豁免清单,美国学位未明文列出,可向国际招生申请豁免;⚠️第三方 TOEFL 75/IELTS 6.0</t>
+        </is>
+      </c>
       <c r="K150" s="21" t="n"/>
       <c r="L150" s="21" t="inlineStr">
         <is>
@@ -10014,10 +10150,26 @@
           <t>'10-month contract that provides tuition and fee remission, and a stipend'(20h/周);'a number of GA positions…highly competitive…full tuition remission and a stipend'</t>
         </is>
       </c>
-      <c r="F151" s="21" t="n"/>
-      <c r="G151" s="21" t="n"/>
-      <c r="H151" s="21" t="n"/>
-      <c r="I151" s="21" t="n"/>
+      <c r="F151" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目录取,论文导师入学后确定;陈述可写匹配教授</t>
+        </is>
+      </c>
+      <c r="G151" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA名额有限、竞争激烈)。需心理学学士,或≥12学分心理课(须含统计和实验室实验课,心理导论不计);材料:综合陈述、2封推荐信、成绩单、$60申请费。</t>
+        </is>
+      </c>
+      <c r="H151" s="30" t="inlineStr">
+        <is>
+          <t>优先 2027/4/1(仅秋季,按2026周期,2027待公布);之后滚动审核至额满</t>
+        </is>
+      </c>
+      <c r="I151" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:学校称多数项目不要求GRE,第三方称需要/可豁免,建议确认</t>
+        </is>
+      </c>
       <c r="J151" s="21" t="n"/>
       <c r="K151" s="21" t="n"/>
       <c r="L151" s="21" t="inlineStr">
@@ -10052,14 +10204,26 @@
           <t>GTA/GRA:$20,000/学年(20 hr)+学费奖学金≤10 学分/学期(前 2 学期)+医保;MS 最多 4 学期;Env Studies 系'优先 PhD'</t>
         </is>
       </c>
-      <c r="F152" s="21" t="n"/>
-      <c r="G152" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 仅要求就业资格</t>
-        </is>
-      </c>
-      <c r="H152" s="21" t="n"/>
-      <c r="I152" s="21" t="n"/>
+      <c r="F152" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:申请需填主/副2位导师,官网强烈鼓励先联系导师确认招生计划;资助多来自导师</t>
+        </is>
+      </c>
+      <c r="G152" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 原备注:资助仅要求有就业资格,国际生可获GTA/GRA)。无明确先修课;按GPA、课程、研究经历、学习计划、推荐信综合评估;MS为研究型论文学位。</t>
+        </is>
+      </c>
+      <c r="H152" s="30" t="inlineStr">
+        <is>
+          <t>资助考虑 2027/1/15;最终 2027/4/30(秋季滚动;按往年日期表,2027周期已开放)</t>
+        </is>
+      </c>
+      <c r="I152" s="30" t="inlineStr">
+        <is>
+          <t>可选(用于资助评估,建议提交)</t>
+        </is>
+      </c>
       <c r="J152" s="21" t="n"/>
       <c r="K152" s="21" t="n"/>
       <c r="L152" s="21" t="inlineStr">
@@ -10094,12 +10258,36 @@
           <t>20 hr assistantship 含学费+费用+医保+津贴;'资金来自导师'——需有资金导师;PSM 无资助</t>
         </is>
       </c>
-      <c r="F153" s="21" t="n"/>
-      <c r="G153" s="21" t="n"/>
-      <c r="H153" s="21" t="n"/>
-      <c r="I153" s="21" t="n"/>
-      <c r="J153" s="21" t="n"/>
-      <c r="K153" s="21" t="n"/>
+      <c r="F153" s="30" t="inlineStr">
+        <is>
+          <t>必须:需有带资金空缺的导师支持;申请须指明至少1位研究匹配教师,仅匹配开放职位者被考虑</t>
+        </is>
+      </c>
+      <c r="G153" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(资助来自导师项目)。需学士学位、最低GPA 3.0,且具备与导师开放职位匹配的专业能力;国际申请费 $70。</t>
+        </is>
+      </c>
+      <c r="H153" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2027/2/1(系官网;⚠️第三方另列 2027/1/15)</t>
+        </is>
+      </c>
+      <c r="I153" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J153" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院对近期获美国大学学位者免语言成绩;⚠️否则 TOEFL 80/IELTS 6.5</t>
+        </is>
+      </c>
+      <c r="K153" s="30" t="inlineStr">
+        <is>
+          <t>WCNR_ESS_info@Mail.ColoState.edu(ESS系通用邮箱)</t>
+        </is>
+      </c>
       <c r="L153" s="21" t="inlineStr">
         <is>
           <t>https://warnercnr.colostate.edu/ess/graduate-programs/ess-graduate-student-handbook/</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -5438,19 +5438,96 @@
           <t>各校 GA/TA 含学费减免(部分为半额)+津贴;竞争性;详见各校页</t>
         </is>
       </c>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="inlineStr">
-        <is>
-          <t>部分明确可(ECU 欢迎非母语)</t>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: 不需要:按项目整体录取;GA(GTA/GRA)竞争激烈,可提前邮件 jason.defreitas@okstate.edu 咨询
+ISU: 强烈建议:录取时即为学生匹配导师(faculty mentor),申请前联系意向导师
+App State: 不需要:按项目录取,个人陈述可写研究兴趣;GA 名额有限
+ECU: 建议:MS GA 多为TA,申请TA需把简历发给指定教师;想做实验室RA可联系导师
+Georgia Southern: 不需要:按项目整体录取(个人陈述+简历,可能面试);GA 事宜可咨询研究生项目主任
+MSU: ⚠️ MS 目前暂停招生;有论文/非论文路径,论文型一般需与导师匹配,建议先邮件 kingrad@msu.edu 询问
+Baylor: 不需要:按项目录取;录取与助教问题直接联系项目主任 Dr. Yunsuk Koh
+UMN: 强烈建议:申请时需选定方向及导师,官网建议申请前联系意向教授
+UConn: 必须:官网要求有意者先联系意向教授,须获导师接收(部分导师只收少数),强烈建议拜访导师
+UGA: 建议(论文型):申请材料需写明与具体教师的研究匹配,宜提前联系;非论文型不需要
+PSU: 必须:导师制,须有教员推荐才能录取;申请表填写意向导师,官网建议申请前联系
+MTSU: 不需要:按项目录取;GA需另交HHP研究生助教申请表,可联系 Dr. Sandra Stevens
+SCSU: 不需要:按项目整体录取;项目内容问题可联系研究生协调员
+ETAMU: 不需要:按项目录取;材料可发研究生协调员</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: 可以申请。Applied Exercise Science 方向36学分(论文/非论文);本科GPA≥3.0,需简历、3封推荐信
+ISU: 可以申请。4年制学士学位,GPA≥3.0(项目可调整);需项目信息表、简历、GA申请表
+App State: 可以申请(有少量竞争性外州学费减免)。GPA≥3.0,或GPA 2.5+GRE≥25百分位;需简历、个人陈述、3封推荐信
+ECU: 可以申请(ECU欢迎非母语申请者)。研究生院最低GPA 2.7;需2封推荐信、SOP、简历;共5个方向,按方向名额录取
+Georgia Southern: 可以申请(国际生需交TOEFL;外国成绩单需WES认证)。Exercise Science 方向:认证学士学位,运动科学本科优先但非必需,可能需补先修课;GPA≥3.0;1–2页个人陈述、含3位推荐人的简历;可能面试
+MSU: ❌ 目前不能申请:官网显示 Kinesiology MS 暂停招生(pausing admissions),重开时间未定。原要求:30学分;非运动学本科需补≥6学分运动学课程(覆盖≥2个领域);⚠️ GPA 约3.0(第三方)
+Baylor: 可以申请(需另交 HHPR 研究生助教 GTA 申请)。运动科学/运动学/运动生理或相关本科;非相关背景须补人体解剖生理和化学;GPA&gt;3.0;3封推荐信、个人陈述、简历,写作样本可选
+UMN: 可以申请(录取与助教/资助一并评审)。需个人陈述、研究陈述、写作样本、3封推荐信、成绩单;国际生申请费$95;⚠️有 Plan A 论文/Plan B 非论文两种说法,以协调员为准
+UConn: 可以申请(论文型MS;当TA须另证英语能力/ITA评估)。本科累计GPA≥3.0(或其他GPA条件,⚠️未见全文);需SOP、推荐信
+UGA: 可以申请。各方向要求不同;Strength &amp; Conditioning 方向须运动学相关本科;需成绩单、SOP、简历、3位推荐人;入学后与导师制定课程计划
+PSU: 可以申请。需个人陈述(含研究兴趣)、2封学术推荐信、全部大学成绩单(初审可非正式);简历和写作样本可选;MS 一般2年
+MTSU: 可以申请(GA含学费减免)。认证学士,须修过人体解剖与生理;⚠️GPA 约2.75(第三方);需GRE;非论文36学分/论文30–33学分
+SCSU: 可以申请。⚠️本科GPA≥3.0、个人陈述、2封推荐信、申请费$50(第三方);学位须开学前2周授予;分 Human Performance/Sport Psychology 方向
+ETAMU: 可以申请。认证学士学位;正式成绩单;部分方向需2封推荐信;Exercise Science 方向申请费$75(MS Health, Kinesiology &amp; Sports Studies)</t>
         </is>
       </c>
       <c r="H70" s="21" t="n"/>
       <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: 否(美国学位豁免:英语国家英语授课学士/研究生学位可豁免);否则 TOEFL≥79/IELTS≥6.5/DET≥115
+ISU: ⚠️ 大概率否:在英语为唯一官方语言国家获学士可豁免(美国是否列入需确认);否则 TOEFL≥79/IELTS≥6.5/DET≥115;入学后英语分级考试及当TA口语认证另有要求
+App State: ⚠️ 不明确:官网称在美认证四年制大学全日制学习≥1年且成绩良好可满足英语要求(大概率豁免);否则 TOEFL 78–79/IELTS 6.5
+ECU: ⚠️ 不明确:研究生院称在美修读大学课程达一定学分/GPA可豁免,需 gradschool@ecu.edu 确认;否则 TOEFL≥78/IELTS≥6.5/DET≥105
+Georgia Southern: ⚠️ 不明确:研究生院称国际生须证明英语能力,未见美国学位豁免条款,建议邮件 gradadmissions@georgiasouthern.edu 确认;⚠️旧页面 TOEFL≥75/IELTS≥6.0
+MSU: 否(美国学士学位可自动豁免,⚠️据 MSU 化学系页面转述的研究生院规则);当TA需通过 SPEAK 口语测试;⚠️第三方称 TOEFL≥70/IELTS≥6
+Baylor: 否(美国学位豁免:研究生院规定美国认证院校学士及以上学位可提交豁免申请);否则 ⚠️TOEFL≥80,成绩2年内有效
+UMN: ⚠️ 大概率否:研究生院规定近2年内在美完成≥16学期学分(不含ESL)可豁免;本科毕业超过2年需确认
+UConn: ⚠️ 大概率否:研究生院豁免英语授课学位(⚠️系页面称在美全日制学习≥1年可豁免);否则 TOEFL≥79(新版4.5)/IELTS≥6.5/DET≥110;当TA仍需英语证明及ITA评估
+UGA: 否(美国学位豁免:研究生院规定美国认证院校学位通常无需TOEFL/IELTS,个别系可另行要求);否则 TOEFL≥80(2026/1后新版4.5)
+PSU: 否(美国学位豁免:研究生院对美国认证院校学士/硕士学位的国际生免TOEFL/IELTS;⚠️系内未单独说明)
+MTSU: ⚠️ 不明确:国际生页面称 F-1 学生须提交英语成绩,未见美国学位豁免;TOEFL≥71/IELTS≥6.0/DET≥95
+SCSU: 否(美国学位豁免:官网明确在美获得副学士及以上学位即满足英语要求);否则 TOEFL≥79(新版4.5)
+ETAMU: ⚠️ 大概率否:计算机系FAQ称美国认证大学学位可豁免TOEFL(运动学未单独说明);否则 TOEFL≥79/IELTS≥6.0</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: jason.defreitas@okstate.edu(项目/GA联系人);grad-i@okstate.edu(研究生院国际招生)
+ISU: gillette@iastate.edu(Dr. Jason Gillette,研究生项目联系人);grad_admissions@iastate.edu(研究生招生办)
+App State: fasczewskiks@appstate.edu(Dr. Kym Fasczewski,研究生项目主任)
+ECU: raedeket@ecu.edu(Tom Raedeke,项目协调员);gradschool@ecu.edu(研究生院)
+Georgia Southern: tpritchard@georgiasouthern.edu(Dr. Tony Pritchard,研究生项目主任;⚠️旧页面列 Bridget Melton);gradadmissions@georgiasouthern.edu(研究生招生办)
+MSU: kingrad@msu.edu(Barb Ritenburg,运动学研究生项目协调员;⚠️列于PhD页面,MS需确认)
+Baylor: Yunsuk_Koh@baylor.edu(Dr. Yunsuk Koh,运动生理研究生项目主任,负责录取与助教);chris_wynveen@baylor.edu(HHPR研究生项目主任)
+UMN: scannon@umn.edu(Sara Cannon,研究生项目协调员);jkonczak@umn.edu(Juergen Konczak,研究生主任)
+UConn: kinesiology@uconn.edu(运动学系);gradadmissions@uconn.edu(研究生院招生)
+UGA: kins@uga.edu(运动学系;研究生主任 Ginny M Frederick)
+PSU: kinesgrad@psu.edu(Shari Grassi,研究生项目助理);KINESinfo@psu.edu(系办)
+MTSU: Sandra.Stevens@mtsu.edu(Dr. Sandra Stevens,运动科学项目联系人/导师);研究生院电话 615-898-2840
+SCSU: axtellr1@southernct.edu(Dr. Robert Axtell,运动科学研究生协调员,⚠️目录可能未更新);gradadmissions@southernct.edu(研究生院)
+ETAMU: ⚠️ 官网邮箱被隐藏:研究生项目协调员 Sarah Mitchell, Ph.D.(系电话 903.886.5549);研究生院电话 903.886.5163,建议官网查询邮箱</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: https://go.okstate.edu/graduate-academics/programs/masters/applied-exercise-science-ms
+ISU: https://www.grad-college.iastate.edu/programs/kinesiology
+App State: https://www.appstate.edu/academics/graduate/id/kinesiology-ms
+ECU: https://hhp.ecu.edu/kine/mskine/
+Georgia Southern: https://www.georgiasouthern.edu/degrees/masters-in-kinesiology/exercise-science
+MSU: https://education.msu.edu/kin/Kinesiology-MS/Requirements
+Baylor: https://hhpr.robbins.baylor.edu/masters/master-science-exercise-physiology
+UMN: https://kin.umn.edu/graduate/kinesiology-ms
+UConn: https://kins.uconn.edu/exercise-science/how-to-apply-graduate-program/
+UGA: https://coe.uga.edu/academics/degrees/ms-kinesiology-exercise-physiology/
+PSU: https://hhd.psu.edu/kines/kinesiology-graduate-program
+MTSU: https://w1.mtsu.edu/hhp/graduate-admissions.php ; https://catalog.mtsu.edu/preview_program.php?catoid=33&amp;poid=11462
+SCSU: https://catalog.southernct.edu/graduate/programs-and-degrees/exercise-science-ms-human-performance.html
+ETAMU: https://www.etamu.edu/programs/health-kinesiology-sports-studies-ms-exercise-science/</t>
         </is>
       </c>
     </row>
@@ -10320,16 +10397,36 @@
           <t>Grad School:硕士 RA/TA 最低 $8,651/学期+州内学费+费用+医保 ≤4 学期;国际硕士生学费减免 4 学期</t>
         </is>
       </c>
-      <c r="F154" s="21" t="n"/>
-      <c r="G154" s="21" t="inlineStr">
-        <is>
-          <t>✅ 明文国际硕士生可获学费减免</t>
-        </is>
-      </c>
-      <c r="H154" s="21" t="n"/>
-      <c r="I154" s="21" t="n"/>
-      <c r="J154" s="21" t="n"/>
-      <c r="K154" s="21" t="n"/>
+      <c r="F154" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 建议:研究型MS,资助多来自导师RA/TA,建议申请前联系感兴趣教授(官网未明文要求)</t>
+        </is>
+      </c>
+      <c r="G154" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 明文国际硕士生可获学费减免;RA/TA最低$8,651/学期)。注意:MSPH自2024秋起暂停招生,应申MS。先修:科学/数学/工程类本科学位,官网无指定先修课;需3封推荐信;无面试</t>
+        </is>
+      </c>
+      <c r="H154" s="30" t="inlineStr">
+        <is>
+          <t>MS 2027秋:最终 2027/2/9(Gillings申请页);⚠️优先截止参照PhD为2026/12/15,MS待确认;2027春 2026/10/13</t>
+        </is>
+      </c>
+      <c r="I154" s="30" t="inlineStr">
+        <is>
+          <t>不需要(Gillings已取消多数硕士项目GRE要求)</t>
+        </is>
+      </c>
+      <c r="J154" s="30" t="inlineStr">
+        <is>
+          <t>否(美国认证大学学位豁免,需上传成绩单证明);否则TOEFL/IELTS,2年内有效</t>
+        </is>
+      </c>
+      <c r="K154" s="30" t="inlineStr">
+        <is>
+          <t>esestudentservices@unc.edu(ESE研究生申请协调员);esegraddirector@unc.edu(研究生项目主任)</t>
+        </is>
+      </c>
       <c r="L154" s="21" t="inlineStr">
         <is>
           <t>https://gradschool.unc.edu/funding/stipends/</t>
@@ -10362,12 +10459,36 @@
           <t>GA是'the most common way that our students are funded':学费减免+医保+月stipend;无保证</t>
         </is>
       </c>
-      <c r="F155" s="21" t="n"/>
-      <c r="G155" s="21" t="n"/>
-      <c r="H155" s="21" t="n"/>
-      <c r="I155" s="21" t="n"/>
-      <c r="J155" s="21" t="n"/>
-      <c r="K155" s="21" t="n"/>
+      <c r="F155" s="30" t="inlineStr">
+        <is>
+          <t>必须:须有教授正式同意担任导师,申请才会提交FES录取委员会评审</t>
+        </is>
+      </c>
+      <c r="G155" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA为主要资助方式,无保证)。先修:四年制本科,GPA≥3.0;需提交Certification of Finances(即使获TA/RA);MS需45学分,必修FES 520/525/526</t>
+        </is>
+      </c>
+      <c r="H155" s="30" t="inlineStr">
+        <is>
+          <t>FES全面考虑 2027/1/1–1/15(研究生院优先 1/1);最终 2027/4/15(3/1、4/15仅有限考虑)(按往年周期,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I155" s="30" t="inlineStr">
+        <is>
+          <t>不需要(研究生院项目页称无必需考试)</t>
+        </is>
+      </c>
+      <c r="J155" s="30" t="inlineStr">
+        <is>
+          <t>否(英语国家学位豁免);申请GTA需TOEFL/IELTS口语最低分</t>
+        </is>
+      </c>
+      <c r="K155" s="30" t="inlineStr">
+        <is>
+          <t>juliet.sutton@oregonstate.edu(FES研究生项目协调员 Juliet Sutton)</t>
+        </is>
+      </c>
       <c r="L155" s="21" t="inlineStr">
         <is>
           <t>https://www.forestry.oregonstate.edu/students/scholarships/graduate-funding</t>
@@ -10400,16 +10521,32 @@
           <t>'Approximately one third of the admitted students'获associateship(stipend+学费+85%医保)</t>
         </is>
       </c>
-      <c r="F156" s="21" t="n"/>
-      <c r="G156" s="21" t="inlineStr">
-        <is>
-          <t>可(GTA需SPEAK)</t>
-        </is>
-      </c>
-      <c r="H156" s="21" t="n"/>
+      <c r="F156" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 强烈建议:研究型MS由导师指导论文,建议申请前联系教授(官网未明文强制)</t>
+        </is>
+      </c>
+      <c r="G156" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GTA需口语认证:TOEFL口语≥28/IELTS口语8.5/OSU口语测试)。先修:四年制学士,最近学位GPA≥3.0(低于可条件录取);成绩单需体现先修课;SOP≤2页(双倍行距)</t>
+        </is>
+      </c>
+      <c r="H156" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 资助优先 2026/11/30;最终 2027/4/30(官网未注明年份,按往年周期)</t>
+        </is>
+      </c>
       <c r="I156" s="21" t="n"/>
-      <c r="J156" s="21" t="n"/>
-      <c r="K156" s="21" t="n"/>
+      <c r="J156" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学士学位在研究生院豁免国家列表内);当GTA需口语认证(⚠️美国学士24个月内毕业或可豁免)</t>
+        </is>
+      </c>
+      <c r="K156" s="30" t="inlineStr">
+        <is>
+          <t>enrgrad@osu.edu(SENR研究生项目);white.1917@osu.edu(⚠️研究生项目协调员 Taylor White,待确认)</t>
+        </is>
+      </c>
       <c r="L156" s="21" t="inlineStr">
         <is>
           <t>https://senr.osu.edu/funding_associateship_fellowship</t>
@@ -10442,12 +10579,36 @@
           <t>≥1/3时间TA/PA/RA含全额学费减免+医保+stipend;需自己找岗位,'RA positions are rarely advertised'</t>
         </is>
       </c>
-      <c r="F157" s="21" t="n"/>
-      <c r="G157" s="21" t="n"/>
-      <c r="H157" s="21" t="n"/>
-      <c r="I157" s="21" t="n"/>
-      <c r="J157" s="21" t="n"/>
-      <c r="K157" s="21" t="n"/>
+      <c r="F157" s="30" t="inlineStr">
+        <is>
+          <t>建议:录取时分配导师,无需预先确认;但需自己找RA/TA岗位且RA很少公开招聘,建议提前联系教授</t>
+        </is>
+      </c>
+      <c r="G157" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。任何认证本科学位均可;⚠️第三方称最低GPA 3.0;需SOP(1–2页,写目标与关注议题)、CV、3封推荐信、非正式成绩单</t>
+        </is>
+      </c>
+      <c r="H157" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2026/12/1(夏季同);春季 2026/10/15</t>
+        </is>
+      </c>
+      <c r="I157" s="30" t="inlineStr">
+        <is>
+          <t>不需要(可提交;申请校级fellowship建议提交)</t>
+        </is>
+      </c>
+      <c r="J157" s="30" t="inlineStr">
+        <is>
+          <t>否(美国区域认证学士学位满足UW-1241英语要求)</t>
+        </is>
+      </c>
+      <c r="K157" s="30" t="inlineStr">
+        <is>
+          <t>grad@nelson.wisc.edu(Nelson学术项目办公室);jemiller@wisc.edu(研究生顾问 Jim Miller)</t>
+        </is>
+      </c>
       <c r="L157" s="21" t="inlineStr">
         <is>
           <t>https://nelson.wisc.edu/graduate/funding/graduate-assistantships/</t>
@@ -10480,12 +10641,36 @@
           <t>8个全年TA给一年级;全年TA全额学费减免;自付约$1,000/学期fees</t>
         </is>
       </c>
-      <c r="F158" s="21" t="n"/>
-      <c r="G158" s="21" t="n"/>
-      <c r="H158" s="21" t="n"/>
-      <c r="I158" s="21" t="n"/>
-      <c r="J158" s="21" t="n"/>
-      <c r="K158" s="21" t="n"/>
+      <c r="F158" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:项目统一录取并分配一年级TA,官网未要求预先联系导师</t>
+        </is>
+      </c>
+      <c r="G158" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(8个全年TA给一年级,含学费减免)。任何本科专业均可;需3封推荐信(至少1封学术)、个人陈述、3篇100字短文、简历;申TA或环境写作方向需写作样本(英语系TA另需≤6页样本)</t>
+        </is>
+      </c>
+      <c r="H158" s="30" t="inlineStr">
+        <is>
+          <t>秋季 2027/1/15(同为TA及资助优先);春季 10/15(仅有空位时,2026春曾不开放)</t>
+        </is>
+      </c>
+      <c r="I158" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(项目页未提及GRE)</t>
+        </is>
+      </c>
+      <c r="J158" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 否(研究生院政策:英语国家大学学位豁免,美国学位应适用)</t>
+        </is>
+      </c>
+      <c r="K158" s="30" t="inlineStr">
+        <is>
+          <t>evst@mso.umt.edu(EVST项目办公室);Robin.Saha@mso.umt.edu(研究生项目主任)</t>
+        </is>
+      </c>
       <c r="L158" s="21" t="inlineStr">
         <is>
           <t>https://www.umt.edu/environmental-studies/graduate/funding.php</t>
@@ -10518,12 +10703,36 @@
           <t>'financially supported through RA and TA that cover tuition, health insurance, and a living stipend';TA竞争激烈</t>
         </is>
       </c>
-      <c r="F159" s="21" t="n"/>
-      <c r="G159" s="21" t="n"/>
-      <c r="H159" s="21" t="n"/>
-      <c r="I159" s="21" t="n"/>
-      <c r="J159" s="21" t="n"/>
-      <c r="K159" s="21" t="n"/>
+      <c r="F159" s="30" t="inlineStr">
+        <is>
+          <t>必须:须先联系潜在导师并获其支持才能申请,否则需等找到导师再申请</t>
+        </is>
+      </c>
+      <c r="G159" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(RA/TA含学费、医保、生活费;TA竞争激烈)。最后60学分GPA≥3.0;先修:社会学/文化人类学3、环境科学3、生物3、普化或普物6、微积分或统计3、普通生态4学分,不足可入学后补</t>
+        </is>
+      </c>
+      <c r="H159" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季优先 2027/1/10(依同学院Natural Resource Sciences页,按往年周期,待确认)</t>
+        </is>
+      </c>
+      <c r="I159" s="30" t="inlineStr">
+        <is>
+          <t>不需要(GRE暂免,直至另行通知)</t>
+        </is>
+      </c>
+      <c r="J159" s="30" t="inlineStr">
+        <is>
+          <t>否(美国区域认证学士学位满足,Option A;⚠️旧页面曾要求毕业2年内)</t>
+        </is>
+      </c>
+      <c r="K159" s="30" t="inlineStr">
+        <is>
+          <t>soe.academics@wsu.edu(SOE研究生协调员 Zoeii Freeman);soe@wsu.edu(学院总邮箱)</t>
+        </is>
+      </c>
       <c r="L159" s="21" t="inlineStr">
         <is>
           <t>https://environment.wsu.edu/graduate-studies/financial-support/</t>
@@ -10556,11 +10765,19 @@
           <t>'competitive stipends for M.S. or Ph.D.'含学年学费+医保;校级GA享州外学费减免</t>
         </is>
       </c>
-      <c r="F160" s="21" t="n"/>
+      <c r="F160" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:官网鼓励申请前联系相关教授,申请表需填写研究方向匹配的教授</t>
+        </is>
+      </c>
       <c r="G160" s="21" t="n"/>
       <c r="H160" s="21" t="n"/>
       <c r="I160" s="21" t="n"/>
-      <c r="J160" s="21" t="n"/>
+      <c r="J160" s="30" t="inlineStr">
+        <is>
+          <t>否(英语授课认证大学学士学位豁免,研究生院审核成绩单后标注);否则TOEFL iBT≥90</t>
+        </is>
+      </c>
       <c r="K160" s="21" t="n"/>
       <c r="L160" s="21" t="inlineStr">
         <is>
@@ -10594,11 +10811,31 @@
           <t>半时GA=stipend+学费grant-in-aid;'All available assistantships are controlled by individual faculty members'</t>
         </is>
       </c>
-      <c r="F161" s="21" t="n"/>
-      <c r="G161" s="21" t="n"/>
-      <c r="H161" s="21" t="n"/>
-      <c r="I161" s="21" t="n"/>
-      <c r="J161" s="21" t="n"/>
+      <c r="F161" s="30" t="inlineStr">
+        <is>
+          <t>必须:录取需教师多数票且有愿意接收的导师;GA岗位全部由教师个人控制</t>
+        </is>
+      </c>
+      <c r="G161" s="30" t="inlineStr">
+        <is>
+          <t>可以申请。总GPA≥2.75、大三大四≥3.00(可酌情例外);非理科背景可provisional录取后补先修;需CV、3封推荐信、学术目标陈述</t>
+        </is>
+      </c>
+      <c r="H161" s="30" t="inlineStr">
+        <is>
+          <t>秋/夏季建议 2027/1/1 前提交;春季 8/1 前;国际生至少开学前4个月提交材料</t>
+        </is>
+      </c>
+      <c r="I161" s="30" t="inlineStr">
+        <is>
+          <t>不需要(可选提交)</t>
+        </is>
+      </c>
+      <c r="J161" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位按GCAC-305豁免;⚠️系里列TOEFL为评估项,建议确认);否则TOEFL新制4.5(口语3.5)/旧制80(口语19)、IELTS 6.5</t>
+        </is>
+      </c>
       <c r="K161" s="21" t="n"/>
       <c r="L161" s="21" t="inlineStr">
         <is>
@@ -10632,12 +10869,32 @@
           <t>导师外部经费RA或TA;'No student is admitted without a designated faculty major advisor'</t>
         </is>
       </c>
-      <c r="F162" s="21" t="n"/>
+      <c r="F162" s="30" t="inlineStr">
+        <is>
+          <t>必须:录取完全由教师决定,'No student is admitted without a designated faculty major advisor'</t>
+        </is>
+      </c>
       <c r="G162" s="21" t="n"/>
-      <c r="H162" s="21" t="n"/>
-      <c r="I162" s="21" t="n"/>
-      <c r="J162" s="21" t="n"/>
-      <c r="K162" s="21" t="n"/>
+      <c r="H162" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季 2027/2/1(按2025周期,2027待公布);春季 10/1(第三方)</t>
+        </is>
+      </c>
+      <c r="I162" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:同系MS3不需要;ECo MS官网未明,第三方称需GRE,建议确认</t>
+        </is>
+      </c>
+      <c r="J162" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院有豁免条件(经济系页面列美国学位可豁免),ECo是否适用待确认;否则IELTS 6.5、TOEFL新制4/旧制80、Duolingo 115</t>
+        </is>
+      </c>
+      <c r="K162" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ kstinson@eco.umass.edu(研究生项目主任 Kristina Stinson,据2025-26 bulletin);系联系表单 umass.edu/environmental-conservation/about/contact</t>
+        </is>
+      </c>
       <c r="L162" s="21" t="inlineStr">
         <is>
           <t>https://www.umass.edu/environmental-conservation/academics/graduate-programs/environmental-conservation-m-s-ph-d</t>
@@ -10670,12 +10927,32 @@
           <t>'Funding includes a tuition waiver and stipend';'Only the strongest applications will potentially receive funding';仅秋季</t>
         </is>
       </c>
-      <c r="F163" s="21" t="n"/>
-      <c r="G163" s="21" t="n"/>
+      <c r="F163" s="30" t="inlineStr">
+        <is>
+          <t>必须:申请需OSU教师的Agreement to Advise(由教师发邮件至esgp@okstate.edu);可临时导师有条件录取</t>
+        </is>
+      </c>
+      <c r="G163" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(仅最强申请人可能获学费减免+stipend;RA/TA由导师视经费任命)。先修:大学代数、生物、普通化学,均需B及以上;推荐GPA≥3.0;需CV、1–2页目标陈述、3封推荐信</t>
+        </is>
+      </c>
       <c r="H163" s="21" t="n"/>
-      <c r="I163" s="21" t="n"/>
-      <c r="J163" s="21" t="n"/>
-      <c r="K163" s="21" t="n"/>
+      <c r="I163" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J163" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位可豁免研究生院英语要求);否则TOEFL iBT 79/新制4.0、IELTS 6.5;当TA可能仍需英语成绩</t>
+        </is>
+      </c>
+      <c r="K163" s="30" t="inlineStr">
+        <is>
+          <t>esgp@okstate.edu(项目主任 Karen Hickman)</t>
+        </is>
+      </c>
       <c r="L163" s="21" t="inlineStr">
         <is>
           <t>https://agriculture.okstate.edu/departments-programs/environmental-science/graduate-program/admission-requirements-and-funding</t>
@@ -11344,16 +11621,36 @@
           <t>NIOSH 式 traineeship:每年 5 个名额(MS 或 PhD)全额学费+津贴+差旅;申请该方向自动考虑</t>
         </is>
       </c>
-      <c r="F178" s="21" t="n"/>
-      <c r="G178" s="21" t="inlineStr">
-        <is>
-          <t>❌ NIOSH ERC 通常仅美籍/PR——需向 mturyk1@uic.edu 确认</t>
-        </is>
-      </c>
-      <c r="H178" s="21" t="n"/>
-      <c r="I178" s="21" t="n"/>
-      <c r="J178" s="21" t="n"/>
-      <c r="K178" s="21" t="n"/>
+      <c r="F178" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;该方向申请者自动考虑traineeship,PS可提及Mary Turyk等职业/环境流行病教师</t>
+        </is>
+      </c>
+      <c r="G178" s="30" t="inlineStr">
+        <is>
+          <t>❌ 资助受限:GLC-OHS(NIOSH)traineeship明文要求美国公民/PR,国际生基本无法获得(可向 mturyk1@uic.edu 确认);项目本身可以申请。先修:偏好生物/物理/社会科学专业(traineeship偏好生物或数学),GPA≥3.0,3封推荐信</t>
+        </is>
+      </c>
+      <c r="H178" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2026/12/1;最终 2027/4/15(国际生 2027/2/1)(按官网当前周期)</t>
+        </is>
+      </c>
+      <c r="I178" s="30" t="inlineStr">
+        <is>
+          <t>可选:学院申请页称标化成绩非必需;⚠️ 研究生目录仍列GRE V+Q≥300,建议确认</t>
+        </is>
+      </c>
+      <c r="J178" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:SPH国际生页豁免条件为在英语为唯一官方语言国家全日制学习≥2年(美国通常符合,但未明写美国学位);否则TOEFL iBT≥80(子分19/17/20/21;2026/1/21后新制另有标准),IELTS≥6.5</t>
+        </is>
+      </c>
+      <c r="K178" s="30" t="inlineStr">
+        <is>
+          <t>sph-admissions@uic.edu(SPH招生办);saria@uic.edu(Director of Graduate Studies, Saria Awadalla)</t>
+        </is>
+      </c>
       <c r="L178" s="21" t="inlineStr">
         <is>
           <t>https://publichealth.uic.edu/academics/public-health-degrees/master-science-degrees/ms-occupational-environmental-epidemiology/student-funding</t>
@@ -11428,16 +11725,36 @@
           <t>merit奖学金50%–100%学费;Rollins Institutional Award $10–30k;REAL校内工作≤$3,000/学期;1/5前自动考虑</t>
         </is>
       </c>
-      <c r="F180" s="21" t="n"/>
-      <c r="G180" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H180" s="21" t="n"/>
-      <c r="I180" s="21" t="n"/>
-      <c r="J180" s="21" t="n"/>
-      <c r="K180" s="21" t="n"/>
+      <c r="F180" s="30" t="inlineStr">
+        <is>
+          <t>不需要:SOPHAS按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G180" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获merit奖学金,1/5前自动考虑)。先修:需相当于美国四年制学士;MSPH Biostat需多元微积分(Calc III)和线性代数,均B+及以上,概率/统计优先;Epi需大学数学课或数学能力证明</t>
+        </is>
+      </c>
+      <c r="H180" s="30" t="inlineStr">
+        <is>
+          <t>奖学金优先 2027/1/5;国际生建议 2027/5/1;最终 2027/7/15(SOPHAS)</t>
+        </is>
+      </c>
+      <c r="I180" s="30" t="inlineStr">
+        <is>
+          <t>Epi:不需要(学院不考虑GRE);Biostat:可选(须与申请同时提交)</t>
+        </is>
+      </c>
+      <c r="J180" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免);否则TOEFL iBT≥79–80,IELTS≥6</t>
+        </is>
+      </c>
+      <c r="K180" s="30" t="inlineStr">
+        <is>
+          <t>sphadmissions@emory.edu(RSPH招生办)</t>
+        </is>
+      </c>
       <c r="L180" s="21" t="inlineStr">
         <is>
           <t>https://sph.emory.edu/admissions/tuition-funding/scholarships</t>
@@ -11470,15 +11787,31 @@
           <t>全日制硕士保证Dean's Merit Award(国际生$10,000/年,部分学费);学院每年8–10个GA向新生开放(3月申请)</t>
         </is>
       </c>
-      <c r="F181" s="21" t="n"/>
-      <c r="G181" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H181" s="21" t="n"/>
-      <c r="I181" s="21" t="n"/>
-      <c r="J181" s="21" t="n"/>
+      <c r="F181" s="30" t="inlineStr">
+        <is>
+          <t>不需要:SOPHAS按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G181" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(全日制硕士国际生保证Dean's Merit $10,000/年)。先修:学士学位,GPA≥3.0;Biostat需线性代数、多元微积分、编程各一学期(另一页写Calc I/II+线代,需确认);Epi建议生物和微积分各一学期,欠缺需补课</t>
+        </is>
+      </c>
+      <c r="H181" s="30" t="inlineStr">
+        <is>
+          <t>优先(奖学金)2027/1/15;一般 2027/3/1;最终滚动至 2027/8/1(视名额,按官网当前周期)</t>
+        </is>
+      </c>
+      <c r="I181" s="30" t="inlineStr">
+        <is>
+          <t>不需要(CIHS所有研究生项目不要求GRE)</t>
+        </is>
+      </c>
+      <c r="J181" s="30" t="inlineStr">
+        <is>
+          <t>否(在美国全日制学习≥4学期且平均B以上可豁免,美本符合);否则TOEFL≥98(新制5.0),IELTS≥7.0,Duolingo≥125</t>
+        </is>
+      </c>
       <c r="K181" s="21" t="n"/>
       <c r="L181" s="21" t="inlineStr">
         <is>
@@ -11512,16 +11845,36 @@
           <t>GTA(固定名额)+GRA;津贴+学费减免≤10 学分;MA 2 年</t>
         </is>
       </c>
-      <c r="F182" s="21" t="n"/>
-      <c r="G182" s="21" t="inlineStr">
-        <is>
-          <t>✅ 页面提及国际 GTA/GRA</t>
-        </is>
-      </c>
-      <c r="H182" s="21" t="n"/>
-      <c r="I182" s="21" t="n"/>
-      <c r="J182" s="21" t="n"/>
-      <c r="K182" s="21" t="n"/>
+      <c r="F182" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GTA名额固定竞争,个人陈述写明研究兴趣即可</t>
+        </is>
+      </c>
+      <c r="G182" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(页面提及国际生可获GTA/GRA)。先修:⚠️ GPA≥3.0(Peterson's);材料:SOP、3封推荐信、写作样本、成绩单;国际生需财力证明</t>
+        </is>
+      </c>
+      <c r="H182" s="30" t="inlineStr">
+        <is>
+          <t>资助/秋季 2027/1/15(国际生 2027/1/8);国内无资助申请至5/1(按研究生目录,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I182" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 必需(研究生目录与Peterson's列GRE General;目录可能过时,建议确认)</t>
+        </is>
+      </c>
+      <c r="J182" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免;⚠️研究生院目录写'近2年内'获美国学位,申请页无时限,毕业超2年需确认);否则TOEFL iBT≥79(⚠️第三方数据)</t>
+        </is>
+      </c>
+      <c r="K182" s="30" t="inlineStr">
+        <is>
+          <t>twl@ksu.edu(社会学研究生主任 Travis Linnemann);socansw@k-state.edu(系办公室)</t>
+        </is>
+      </c>
       <c r="L182" s="21" t="inlineStr">
         <is>
           <t>https://www.k-state.edu/sasw/socio/graduate/financial-assistance.html</t>
@@ -11554,16 +11907,36 @@
           <t>TA/RA 含学费减免+津贴;最多 2 年半时;2-1 截止</t>
         </is>
       </c>
-      <c r="F183" s="21" t="n"/>
-      <c r="G183" s="21" t="inlineStr">
-        <is>
-          <t>✅ 无限制</t>
-        </is>
-      </c>
-      <c r="H183" s="21" t="n"/>
-      <c r="I183" s="21" t="n"/>
-      <c r="J183" s="21" t="n"/>
-      <c r="K183" s="21" t="n"/>
+      <c r="F183" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,TA/RA随录取统一考虑</t>
+        </is>
+      </c>
+      <c r="G183" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(无国籍限制,国际生可获TA/RA)。先修:官网未写最低GPA(⚠️第三方称3.0);材料:简历、3位推荐人、2–3页个人陈述、成绩单、写作样本</t>
+        </is>
+      </c>
+      <c r="H183" s="30" t="inlineStr">
+        <is>
+          <t>资助 2027/2/1;无资助 2027/4/1(按系网页,2027待确认;⚠️Peterson's另列3/1)</t>
+        </is>
+      </c>
+      <c r="I183" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:系页面称目前不要求GRE(页面较旧),MS项目页仍列GRE,建议确认</t>
+        </is>
+      </c>
+      <c r="J183" s="30" t="inlineStr">
+        <is>
+          <t>否(研究生院:在英语为主要语言国家的英语授课院校获学士可豁免;⚠️美国未在结果中明列,建议确认);否则TOEFL iBT≥79,IELTS≥6.5,Duolingo≥115</t>
+        </is>
+      </c>
+      <c r="K183" s="30" t="inlineStr">
+        <is>
+          <t>jonathan.s.coley@okstate.edu(研究生主任 Jonathan Coley);grad-i@okstate.edu(研究生院国际招生)</t>
+        </is>
+      </c>
       <c r="L183" s="21" t="inlineStr">
         <is>
           <t>https://go.okstate.edu/graduate-academics/programs/masters/sociology-ms.html</t>
@@ -11596,16 +11969,36 @@
           <t>GTA:$6,000/学期(20 hr)+全额学费减免(3 门/学期);4 学期可续;医保补贴;SOP 中申请即可</t>
         </is>
       </c>
-      <c r="F184" s="21" t="n"/>
-      <c r="G184" s="21" t="inlineStr">
-        <is>
-          <t>✅ 国际生秋季申(3-1)</t>
-        </is>
-      </c>
-      <c r="H184" s="21" t="n"/>
-      <c r="I184" s="21" t="n"/>
-      <c r="J184" s="21" t="n"/>
-      <c r="K184" s="21" t="n"/>
+      <c r="F184" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GTA在SOP中申请即可</t>
+        </is>
+      </c>
+      <c r="G184" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生秋季申请,3/1前可获GTA考虑)。先修:学士学位,社会学专业/辅修优先但非必需;最后60学分GPA≥3.0;经GradCAS提交500–1000字SOP、写作样本、2封推荐信</t>
+        </is>
+      </c>
+      <c r="H184" s="30" t="inlineStr">
+        <is>
+          <t>GTA资助 2027/3/1;之后仍可能录取但可能错过资助(⚠️第三方另称2/1或5/1,建议确认)</t>
+        </is>
+      </c>
+      <c r="I184" s="30" t="inlineStr">
+        <is>
+          <t>不需要(FAU最新招生文件写明不要求GRE)</t>
+        </is>
+      </c>
+      <c r="J184" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院豁免条件为在美国区域认证院校完成≥60学分或副学士及以上学位(美本应符合,未明写学士);否则TOEFL iBT≥79,IELTS≥6.0</t>
+        </is>
+      </c>
+      <c r="K184" s="30" t="inlineStr">
+        <is>
+          <t>lewinp@fau.edu(研究生主任 Philip Lewin;⚠️部分旧页面列其他人)</t>
+        </is>
+      </c>
       <c r="L184" s="21" t="inlineStr">
         <is>
           <t>https://www.fau.edu/artsandletters/sociology/fundingandsupport</t>
@@ -11680,16 +12073,36 @@
           <t>GTA固定名额、竞争;stipend+每学期≤10学分学费减免;'M.A. students are eligible for departmental funding for two years'</t>
         </is>
       </c>
-      <c r="F186" s="21" t="n"/>
-      <c r="G186" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H186" s="21" t="n"/>
-      <c r="I186" s="21" t="n"/>
-      <c r="J186" s="21" t="n"/>
-      <c r="K186" s="21" t="n"/>
+      <c r="F186" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GTA名额固定竞争,个人陈述写明研究兴趣即可</t>
+        </is>
+      </c>
+      <c r="G186" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(MA学生可获两年系资助)。先修:⚠️ GPA≥3.0(Peterson's);材料:SOP、3封推荐信、写作样本、成绩单;国际生需财力证明</t>
+        </is>
+      </c>
+      <c r="H186" s="30" t="inlineStr">
+        <is>
+          <t>资助/秋季 2027/1/15(国际生 2027/1/8);国内无资助申请至5/1(按研究生目录,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I186" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 必需(研究生目录与Peterson's列GRE General;目录可能过时,建议确认)</t>
+        </is>
+      </c>
+      <c r="J186" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免;⚠️研究生院目录写'近2年内'获美国学位,申请页无时限,毕业超2年需确认);否则TOEFL iBT≥79(⚠️第三方数据)</t>
+        </is>
+      </c>
+      <c r="K186" s="30" t="inlineStr">
+        <is>
+          <t>twl@ksu.edu(社会学研究生主任 Travis Linnemann);socansw@k-state.edu(系办公室)</t>
+        </is>
+      </c>
       <c r="L186" s="21" t="inlineStr">
         <is>
           <t>https://www.k-state.edu/sasw/socio/graduate/financial-assistance.html</t>
@@ -11892,16 +12305,36 @@
           <t>TA/RA最低$10,000/学年+每学期≤9学分学费;入学即获系资助者通常续2年;无需单独申请</t>
         </is>
       </c>
-      <c r="F190" s="21" t="n"/>
-      <c r="G190" s="21" t="inlineStr">
-        <is>
-          <t>可(国际生可获非居民学费award 2年)</t>
-        </is>
-      </c>
-      <c r="H190" s="21" t="n"/>
-      <c r="I190" s="21" t="n"/>
-      <c r="J190" s="21" t="n"/>
-      <c r="K190" s="21" t="n"/>
+      <c r="F190" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,入学即考虑系资助,无需单独申请</t>
+        </is>
+      </c>
+      <c r="G190" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获非居民学费award 2年)。先修:社会学本科优先,其他专业需修过社会学方法、理论、统计核心课;最后60学期学分GPA≥3.0;SOP、写作样本、3封推荐信;仅秋季入学</t>
+        </is>
+      </c>
+      <c r="H190" s="30" t="inlineStr">
+        <is>
+          <t>资助截止 2026/12/20(9/1开放);⚠️ 一份FAQ称晚申请可至4/1但资助排末位,另一份称不收晚申请</t>
+        </is>
+      </c>
+      <c r="I190" s="30" t="inlineStr">
+        <is>
+          <t>不需要(已永久取消,可自愿提交)</t>
+        </is>
+      </c>
+      <c r="J190" s="30" t="inlineStr">
+        <is>
+          <t>否(就读英语授课院校可豁免,美本符合;⚠️建议与研究生院确认);否则IELTS≥6.5(各项≥5.0),Duolingo≥105</t>
+        </is>
+      </c>
+      <c r="K190" s="30" t="inlineStr">
+        <is>
+          <t>megan.sills@usu.edu(研究生项目协调员 Megan Sills);graduateschool@usu.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L190" s="21" t="inlineStr">
         <is>
           <t>https://artsci.usu.edu/social-sciences/sociology/resources/graduate/financial-aid.php</t>
@@ -11934,16 +12367,36 @@
           <t>'competitive graduate assistantships to students accepted into the program';GA=学年stipend+学费减免(不含fees);优先2/1</t>
         </is>
       </c>
-      <c r="F191" s="21" t="n"/>
-      <c r="G191" s="21" t="inlineStr">
-        <is>
-          <t>可(TA需SPEAK)</t>
-        </is>
-      </c>
-      <c r="H191" s="21" t="n"/>
-      <c r="I191" s="21" t="n"/>
-      <c r="J191" s="21" t="n"/>
-      <c r="K191" s="21" t="n"/>
+      <c r="F191" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,GA随录取竞争性发放</t>
+        </is>
+      </c>
+      <c r="G191" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(TA需SPEAK口语测试)。先修:社会学或相关专业学士/社会学辅修;须修过社会学理论和研究方法(缺者入学前补);GPA≥3.0;2封推荐信、个人陈述</t>
+        </is>
+      </c>
+      <c r="H191" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/2/1;无需资助:国际生(境外)5/1,在美申请人 7/1(按2024–25目录,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I191" s="30" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J191" s="30" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士学位豁免);否则TOEFL≥80,IELTS≥6.5,PTE≥53;当TA另需SPEAK</t>
+        </is>
+      </c>
+      <c r="K191" s="30" t="inlineStr">
+        <is>
+          <t>drodgers@niu.edu(研究生主任 Diane Rodgers);asksociology@niu.edu(系办公室)</t>
+        </is>
+      </c>
       <c r="L191" s="21" t="inlineStr">
         <is>
           <t>https://www.niu.edu/clas/sociology/academics/graduate/index.shtml</t>
@@ -11976,12 +12429,28 @@
           <t>'assistantship support for up to two years for master's degree students';RA/TA+无服务fellowship;校级GA学费全付</t>
         </is>
       </c>
-      <c r="F192" s="21" t="n"/>
+      <c r="F192" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,2/1前申请自动考虑GA</t>
+        </is>
+      </c>
       <c r="G192" s="21" t="n"/>
-      <c r="H192" s="21" t="n"/>
-      <c r="I192" s="21" t="n"/>
+      <c r="H192" s="30" t="inlineStr">
+        <is>
+          <t>GA资助 2027/2/1;其他申请至 2027/6/30(按系网页,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I192" s="30" t="inlineStr">
+        <is>
+          <t>不需要(系页面;⚠️旧目录列GRE,建议确认)</t>
+        </is>
+      </c>
       <c r="J192" s="21" t="n"/>
-      <c r="K192" s="21" t="n"/>
+      <c r="K192" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 研究生主任 Patrick Cundiff(邮箱未显示,电话 269-387-5293);系办公室 269-387-5270,建议邮件确认</t>
+        </is>
+      </c>
       <c r="L192" s="21" t="inlineStr">
         <is>
           <t>https://wmich.edu/sociology/scholarships/graduate</t>
@@ -14202,15 +14671,31 @@
           <t>merit奖+capstone实地研究全额资助;'not eligible for The Graduate School's scholarships covering tuition and living stipends'</t>
         </is>
       </c>
-      <c r="F239" s="22" t="n"/>
-      <c r="G239" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H239" s="22" t="n"/>
-      <c r="I239" s="22" t="n"/>
-      <c r="J239" s="22" t="n"/>
+      <c r="F239" s="31" t="inlineStr">
+        <is>
+          <t>不需要:项目整体录取(且目前已暂停招生)</t>
+        </is>
+      </c>
+      <c r="G239" s="31" t="inlineStr">
+        <is>
+          <t>❌ 项目官网称已暂停MS Global Health招生,下一学年不录取新生。历史要求:认证大学本科学位,至少2门高年级理科课,建议修过统计;GPA≥3.0;CV、目的陈述、3封推荐信。国际生不能申请研究生院学费+生活费奖学金</t>
+        </is>
+      </c>
+      <c r="H239" s="31" t="inlineStr">
+        <is>
+          <t>❌ 暂停招生,无2027秋季截止日。历史(2026周期):国际生 2026/1/30;美国申请人 2026/3/31</t>
+        </is>
+      </c>
+      <c r="I239" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J239" s="31" t="inlineStr">
+        <is>
+          <t>否(规定:英语授课学习满4年可免;美本四年应可豁免,⚠️未写明最低分)</t>
+        </is>
+      </c>
       <c r="K239" s="22" t="n"/>
       <c r="L239" s="22" t="inlineStr">
         <is>
@@ -14286,16 +14771,32 @@
           <t>'When funding is available…may offer to fund a student';鼓励找外部资助</t>
         </is>
       </c>
-      <c r="F241" s="22" t="n"/>
-      <c r="G241" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="F241" s="31" t="inlineStr">
+        <is>
+          <t>必须:论文型硕士申请人须先联系研究方向匹配的教师并附CV</t>
+        </is>
+      </c>
+      <c r="G241" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(资金有限,有经费时才资助)。先修:官网未列具体课程;需2分钟视频、≤2页目的陈述、3封推荐信直接寄系;不接受有条件录取</t>
         </is>
       </c>
       <c r="H241" s="22" t="n"/>
-      <c r="I241" s="22" t="n"/>
-      <c r="J241" s="22" t="n"/>
-      <c r="K241" s="22" t="n"/>
+      <c r="I241" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J241" s="31" t="inlineStr">
+        <is>
+          <t>否(英语要求针对未获美国四年制学士学位者,美本应豁免;⚠️原文截断,豁免事宜可询 Dr. Elizabeth Mack emack@msu.edu)</t>
+        </is>
+      </c>
+      <c r="K241" s="31" t="inlineStr">
+        <is>
+          <t>geograd@msu.edu(研究生项目协调员);emack@msu.edu(研究生项目主任 Dr. Elizabeth Mack)</t>
+        </is>
+      </c>
       <c r="L241" s="22" t="inlineStr">
         <is>
           <t>https://geo.msu.edu/graduate-programs/app-overview.html</t>
@@ -14328,16 +14829,36 @@
           <t>'may be eligible for Graduate Employment positions';资助与录取同时决定;暑期fellowship优先博士</t>
         </is>
       </c>
-      <c r="F242" s="22" t="n"/>
-      <c r="G242" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H242" s="22" t="n"/>
-      <c r="I242" s="22" t="n"/>
-      <c r="J242" s="22" t="n"/>
-      <c r="K242" s="22" t="n"/>
+      <c r="F242" s="31" t="inlineStr">
+        <is>
+          <t>强烈建议:申请材料需写明想合作的教师,资助(GE)随录取一并决定</t>
+        </is>
+      </c>
+      <c r="G242" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(可获Graduate Employment岗位)。先修:官网未列具体先修课;重点看目的陈述和推荐信;MA与MS内容相同,MA需外语二年级水平;需同时被系和研究生院录取</t>
+        </is>
+      </c>
+      <c r="H242" s="31" t="inlineStr">
+        <is>
+          <t>2026/12/10(仅秋季入学,所有材料需到齐)</t>
+        </is>
+      </c>
+      <c r="I242" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J242" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学士学位可满足英语要求,申请时勾选);否则 TOEFL ≥88,IELTS ≥7.0,Duolingo ≥120</t>
+        </is>
+      </c>
+      <c r="K242" s="31" t="inlineStr">
+        <is>
+          <t>asu5@uoregon.edu(系研究生项目咨询);pwalker@uoregon.edu(研究生主任 Peter Walker,⚠️人选请核实)</t>
+        </is>
+      </c>
       <c r="L242" s="22" t="inlineStr">
         <is>
           <t>https://socialsciences.uoregon.edu/geography/graduate-programs/funding</t>
@@ -14370,16 +14891,36 @@
           <t>'limited number of GA to both international and domestic students';仅1年、部分资助</t>
         </is>
       </c>
-      <c r="F243" s="22" t="n"/>
-      <c r="G243" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H243" s="22" t="n"/>
-      <c r="I243" s="22" t="n"/>
-      <c r="J243" s="22" t="n"/>
-      <c r="K243" s="22" t="n"/>
+      <c r="F243" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,陈述中说明为何选择Auburn社区规划</t>
+        </is>
+      </c>
+      <c r="G243" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生与本国生均可申请有限GA,仅1年部分资助)。先修:认证大学本科学位,无指定专业;需目的陈述、3封推荐信、成绩单</t>
+        </is>
+      </c>
+      <c r="H243" s="31" t="inlineStr">
+        <is>
+          <t>GA优先 2027/3/1;最终 2027/7/15(春季入学:优先10/1,最终12/15)</t>
+        </is>
+      </c>
+      <c r="I243" s="31" t="inlineStr">
+        <is>
+          <t>不需要(可自愿提交)</t>
+        </is>
+      </c>
+      <c r="J243" s="31" t="inlineStr">
+        <is>
+          <t>否(已获美国区域认证院校学位者,研究生院收到学位成绩单后可免);否则 TOEFL ≥79(各项≥16),IELTS ≥6.5;做TA需另交口语成绩</t>
+        </is>
+      </c>
+      <c r="K243" s="31" t="inlineStr">
+        <is>
+          <t>polisci@auburn.edu(政治学系,MCP所属系)</t>
+        </is>
+      </c>
       <c r="L243" s="22" t="inlineStr">
         <is>
           <t>https://cla.auburn.edu/polisci/master-of-community-planning/admissions/</t>
@@ -14412,16 +14953,36 @@
           <t>仅学院通用GRA/GAA说明;非PAB规划学位</t>
         </is>
       </c>
-      <c r="F244" s="22" t="n"/>
-      <c r="G244" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H244" s="22" t="n"/>
-      <c r="I244" s="22" t="n"/>
-      <c r="J244" s="22" t="n"/>
-      <c r="K244" s="22" t="n"/>
+      <c r="F244" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,提交个人与职业目标陈述即可</t>
+        </is>
+      </c>
+      <c r="G244" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅学院通用GRA/GAA)。注意:实为 Urban Studies M.I.S.(30学分,18个月),非PAB认证规划学位。先修:无最低GPA/GRE;需个人陈述、简历、推荐信,录取后才需正式成绩单</t>
+        </is>
+      </c>
+      <c r="H244" s="31" t="inlineStr">
+        <is>
+          <t>秋季:优先 2027/2/15;常规 2027/4/1;后期 2027/6/1(学院页另列延期 7/1)</t>
+        </is>
+      </c>
+      <c r="I244" s="31" t="inlineStr">
+        <is>
+          <t>不需要(学院硕士项目均不要求GRE)</t>
+        </is>
+      </c>
+      <c r="J244" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:豁免按出生国家(英语国家名单)判定,未见美国学位豁免条款;中国出生者可能需提交TOEFL/IELTS,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K244" s="31" t="inlineStr">
+        <is>
+          <t>urban@gsu.edu(Urban Studies Institute);AYSEnroll@gsu.edu(学院招生/学务)</t>
+        </is>
+      </c>
       <c r="L244" s="22" t="inlineStr">
         <is>
           <t>https://ays.gsu.edu/admissions/funding/</t>
@@ -14690,15 +15251,31 @@
           <t>学费奖学金+MUP专属Jammal奖;无GA比例</t>
         </is>
       </c>
-      <c r="F249" s="22" t="n"/>
-      <c r="G249" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H249" s="22" t="n"/>
-      <c r="I249" s="22" t="n"/>
-      <c r="J249" s="22" t="n"/>
+      <c r="F249" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,滚动审核</t>
+        </is>
+      </c>
+      <c r="G249" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(有学费奖学金及MUP专属奖)。先修:本科学位,GPA一般≥3.0;需个人陈述(≤500词)、2封推荐信、简历、成绩单</t>
+        </is>
+      </c>
+      <c r="H249" s="31" t="inlineStr">
+        <is>
+          <t>奖学金优先 约2027/1/15(按2026周期,2027待公布);之后滚动录取至约8月,建议1/15前提交</t>
+        </is>
+      </c>
+      <c r="I249" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J249" s="31" t="inlineStr">
+        <is>
+          <t>否(UB研究生院对在美国获得学位且未中断学业者通常自动豁免;⚠️MUP页未明写,建议确认);否则 ⚠️TOEFL ≥79,IELTS ≥6.5</t>
+        </is>
+      </c>
       <c r="K249" s="22" t="n"/>
       <c r="L249" s="22" t="inlineStr">
         <is>
@@ -14732,16 +15309,32 @@
           <t>仅泛称'loans and graduate assistantships'</t>
         </is>
       </c>
-      <c r="F250" s="22" t="n"/>
-      <c r="G250" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H250" s="22" t="n"/>
-      <c r="I250" s="22" t="n"/>
+      <c r="F250" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G250" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅泛称GA,资助有限)。先修:认证大学本科学位,累计GPA≥3.0;需个人陈述、2封推荐信、全部成绩单</t>
+        </is>
+      </c>
+      <c r="H250" s="31" t="inlineStr">
+        <is>
+          <t>常规 2027/2/1(3月发录取)(按往年周期)</t>
+        </is>
+      </c>
+      <c r="I250" s="31" t="inlineStr">
+        <is>
+          <t>不需要(系FAQ);但 MRP/MPPA 双学位需GRE</t>
+        </is>
+      </c>
       <c r="J250" s="22" t="n"/>
-      <c r="K250" s="22" t="n"/>
+      <c r="K250" s="31" t="inlineStr">
+        <is>
+          <t>teisenman@umass.edu(MRP项目主任 Theodore Eisenman,⚠️由目录"[at]"格式推断);系电话 413-545-2255</t>
+        </is>
+      </c>
       <c r="L250" s="22" t="inlineStr">
         <is>
           <t>https://www.umass.edu/landscape-planning/financial-aid-scholarships</t>
@@ -14774,16 +15367,36 @@
           <t>自动考虑merit fellowship;'only a limited number…for which non-U.S. graduate students are eligible'</t>
         </is>
       </c>
-      <c r="F251" s="22" t="n"/>
-      <c r="G251" s="22" t="inlineStr">
-        <is>
-          <t>可(有限)</t>
-        </is>
-      </c>
-      <c r="H251" s="22" t="n"/>
-      <c r="I251" s="22" t="n"/>
-      <c r="J251" s="22" t="n"/>
-      <c r="K251" s="22" t="n"/>
+      <c r="F251" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,自动考虑merit fellowship</t>
+        </is>
+      </c>
+      <c r="G251" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获的fellowship有限)。先修:需满足定量要求——大学数学课(≥College Algebra)B+以上,或GRE数学≥56百分位,或完成3周Math Camp;需规划相关经历简历</t>
+        </is>
+      </c>
+      <c r="H251" s="31" t="inlineStr">
+        <is>
+          <t>资助+录取 约2026/12/15;仅录取 约2027/1/15(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I251" s="31" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J251" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证大学学士学位豁免)</t>
+        </is>
+      </c>
+      <c r="K251" s="31" t="inlineStr">
+        <is>
+          <t>upinfo@luskin.ucla.edu(城市规划系);sean@luskin.ucla.edu(招生副主任 Sean Campbell)</t>
+        </is>
+      </c>
       <c r="L251" s="22" t="inlineStr">
         <is>
           <t>https://luskin.ucla.edu/urban-planning/admissions</t>
@@ -14816,16 +15429,36 @@
           <t>'limited financial assistance'for research/professional master's;小额奖</t>
         </is>
       </c>
-      <c r="F252" s="22" t="n"/>
-      <c r="G252" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H252" s="22" t="n"/>
-      <c r="I252" s="22" t="n"/>
-      <c r="J252" s="22" t="n"/>
-      <c r="K252" s="22" t="n"/>
+      <c r="F252" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G252" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(研究/专业硕士资助有限,小额奖)。先修:认证院校学士学位即可,无指定专业;需学术目的陈述、2封推荐信、成绩单</t>
+        </is>
+      </c>
+      <c r="H252" s="31" t="inlineStr">
+        <is>
+          <t>第1轮 2026/12/1(国际生优先);第2轮 2027/1/4(常规及merit奖学金优先);第3轮 2027/4/1(最终);无春季入学</t>
+        </is>
+      </c>
+      <c r="I252" s="31" t="inlineStr">
+        <is>
+          <t>不接受(既不要求也不接受GRE)</t>
+        </is>
+      </c>
+      <c r="J252" s="31" t="inlineStr">
+        <is>
+          <t>否(入学前获美国境内认证大学学士学位且在美就读为主即豁免);否则 TOEFL 建议≥100,IELTS ≥7</t>
+        </is>
+      </c>
+      <c r="K252" s="31" t="inlineStr">
+        <is>
+          <t>aap-grad-admissions@cornell.edu(AAP研究生招生办)</t>
+        </is>
+      </c>
       <c r="L252" s="22" t="inlineStr">
         <is>
           <t>https://gradschool.cornell.edu/financial-support/</t>
@@ -14858,16 +15491,36 @@
           <t>'a limited number of learning assistantships each year'</t>
         </is>
       </c>
-      <c r="F253" s="22" t="n"/>
-      <c r="G253" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H253" s="22" t="n"/>
-      <c r="I253" s="22" t="n"/>
-      <c r="J253" s="22" t="n"/>
-      <c r="K253" s="22" t="n"/>
+      <c r="F253" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G253" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(每年少量learning assistantship)。先修:官网未列标准MA的必修先修课(数学先修问题可询 uep@tufts.edu);核心课程含统计</t>
+        </is>
+      </c>
+      <c r="H253" s="31" t="inlineStr">
+        <is>
+          <t>优先 2027/1/15;常规 2027/4/15;滚动至 2027/8/1</t>
+        </is>
+      </c>
+      <c r="I253" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J253" s="31" t="inlineStr">
+        <is>
+          <t>否(在美国获得大学学位即豁免,提交后48小时内自动审核);否则 TOEFL 一般≥90-100</t>
+        </is>
+      </c>
+      <c r="K253" s="31" t="inlineStr">
+        <is>
+          <t>UEP_Admissions@tufts.edu(UEP项目招生);gradadmissions@tufts.edu(文理研究生招生办)</t>
+        </is>
+      </c>
       <c r="L253" s="22" t="inlineStr">
         <is>
           <t>https://as.tufts.edu/uep/resources-community/funding-resources/funding-opportunities</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -13091,12 +13091,36 @@
           <t>仅校级GA('highly competitive');系页无MS资助说明</t>
         </is>
       </c>
-      <c r="F203" s="22" t="n"/>
-      <c r="G203" s="22" t="n"/>
-      <c r="H203" s="22" t="n"/>
-      <c r="I203" s="22" t="n"/>
-      <c r="J203" s="22" t="n"/>
-      <c r="K203" s="22" t="n"/>
+      <c r="F203" s="31" t="inlineStr">
+        <is>
+          <t>强烈建议:MS为论文型,录取看与教师研究方向匹配;可先联系目标教授或HDFS Graduate Program Officer</t>
+        </is>
+      </c>
+      <c r="G203" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(MS资助仅校级GA,竞争激烈)。先修:行为/社会科学背景,至少1门本科统计或研究方法课;要求较强GPA(未设明确下限);3封推荐信;入围者需线上面试。</t>
+        </is>
+      </c>
+      <c r="H203" s="31" t="inlineStr">
+        <is>
+          <t>第一轮 1/5(即2027/1/5);之后视名额滚动审理(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I203" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系官网未提GRE,Peterson's称需GRE;建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J203" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院规定持美国区域认证院校学位者,收到正式成绩单后可免交;⚠️ 研究生院bulletin仍写非母语者需TOEFL ≥79/IELTS ≥6.5,建议确认。当GTA另需口语成绩(TOEFL/IELTS/iTEP口语)</t>
+        </is>
+      </c>
+      <c r="K203" s="31" t="inlineStr">
+        <is>
+          <t>jbh0020@auburn.edu(HDFS Graduate Program Officer Dr. Ben Hinnant);gradadm@auburn.edu(研究生院招生)</t>
+        </is>
+      </c>
       <c r="L203" s="22" t="inlineStr">
         <is>
           <t>https://humsci.auburn.edu/hdfs/grad/admission.php</t>
@@ -13129,12 +13153,36 @@
           <t>仅'competitive scholarships, fellowships and grants';无MS GA保证</t>
         </is>
       </c>
-      <c r="F204" s="22" t="n"/>
-      <c r="G204" s="22" t="n"/>
-      <c r="H204" s="22" t="n"/>
-      <c r="I204" s="22" t="n"/>
-      <c r="J204" s="22" t="n"/>
-      <c r="K204" s="22" t="n"/>
+      <c r="F204" s="31" t="inlineStr">
+        <is>
+          <t>建议:研究型项目需与导师研究方向匹配,申请前联系相关教师;官网未明确要求</t>
+        </is>
+      </c>
+      <c r="G204" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(MS无GA保证,仅竞争性奖学金)。先修:区域认证学士学位;最后90 quarter学分GPA≥3.0;15 quarter学时行为/社会科学课 + 3 quarter学时统计。无硕士者以MS身份进入PhD轨道。</t>
+        </is>
+      </c>
+      <c r="H204" s="31" t="inlineStr">
+        <is>
+          <t>最终 2026/12/1(2027秋季入学,2026年8月开放申请)</t>
+        </is>
+      </c>
+      <c r="I204" s="31" t="inlineStr">
+        <is>
+          <t>不需要(官网材料清单不含GRE)</t>
+        </is>
+      </c>
+      <c r="J204" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院仅要求非美国/英语国家学位者提交英语成绩;另在美全日制≥2学期且GPA&gt;3.0也可豁免</t>
+        </is>
+      </c>
+      <c r="K204" s="31" t="inlineStr">
+        <is>
+          <t>COHAdmissions@oregonstate.edu(健康学院研究生招生);⚠️ megan.ferris@oregonstate.edu(仅见于HDFS研究生Facebook页,未经官网核实)</t>
+        </is>
+      </c>
       <c r="L204" s="22" t="inlineStr">
         <is>
           <t>https://health.oregonstate.edu/hdfs/graduate</t>
@@ -13167,12 +13215,36 @@
           <t>'prioritizes assistantships for Ph.D. students. If additional funding is available, every effort will be made to provide assistantships to Master's students'</t>
         </is>
       </c>
-      <c r="F205" s="22" t="n"/>
-      <c r="G205" s="22" t="n"/>
-      <c r="H205" s="22" t="n"/>
-      <c r="I205" s="22" t="n"/>
-      <c r="J205" s="22" t="n"/>
-      <c r="K205" s="22" t="n"/>
+      <c r="F205" s="31" t="inlineStr">
+        <is>
+          <t>强烈建议:申请材料需列出希望合作的教师名单;资助优先给PhD,建议提前联系目标教授</t>
+        </is>
+      </c>
+      <c r="G205" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(资助优先PhD,有余额才给MS助教)。先修:系里不设最低GPA/GRE分数线;材料:研究生院申请、成绩单、目标陈述、意向教师名单、3名推荐人。</t>
+        </is>
+      </c>
+      <c r="H205" s="31" t="inlineStr">
+        <is>
+          <t>优先(含fellowship考虑)2026/12/1(约12/15通知);之后按月滚动审理至开学;⚠️ 有旧页面提及4/15截止,需确认</t>
+        </is>
+      </c>
+      <c r="I205" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 必需:系页写on-campus MS需提交GRE,但又称不设分数线(2021/22曾豁免),建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J205" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院OP 64.01规定美国大学学位毕业生免英语成绩(收到并审核成绩单后生效)</t>
+        </is>
+      </c>
+      <c r="K205" s="31" t="inlineStr">
+        <is>
+          <t>elizabeth.trejos@ttu.edu(on-campus研究生项目联系人 Dr. Elizabeth Trejos);⚠️ jeremiah.ramirez@ttu.edu(研究生项目协调员,页面较旧)</t>
+        </is>
+      </c>
       <c r="L205" s="22" t="inlineStr">
         <is>
           <t>https://www.depts.ttu.edu/hs/hdfs/graduate-faqs.php</t>
@@ -13441,12 +13513,36 @@
           <t>仅$1–10k一次性奖学金;研究中心/教师可能提供assistantship</t>
         </is>
       </c>
-      <c r="F210" s="22" t="n"/>
-      <c r="G210" s="22" t="n"/>
-      <c r="H210" s="22" t="n"/>
-      <c r="I210" s="22" t="n"/>
-      <c r="J210" s="22" t="n"/>
-      <c r="K210" s="22" t="n"/>
+      <c r="F210" s="31" t="inlineStr">
+        <is>
+          <t>不需要:职业型硕士,按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G210" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅$1–10k一次性奖学金)。先修:本科学位,最低GPA 3.25;无指定先修课;材料:个人陈述、简历、成绩单、推荐信(系页写≥2封,研究生招生页写3封)。</t>
+        </is>
+      </c>
+      <c r="H210" s="31" t="inlineStr">
+        <is>
+          <t>2027秋季:国际生 2027/5/1;美国申请人 2027/7/1(Rutgers研究生招生页);MHA系页仅写秋季7/1、春季11/1</t>
+        </is>
+      </c>
+      <c r="I210" s="31" t="inlineStr">
+        <is>
+          <t>可选(不要求,可提交GRE/GMAT/LSAT作补充)</t>
+        </is>
+      </c>
+      <c r="J210" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生须提交TOEFL/IELTS/Duolingo;Rutgers研究生招生对在以英语为主要教学语言院校完成整个学士学位者可考虑豁免(需成绩单或学校信函证明),美本大概率可申请豁免,需确认</t>
+        </is>
+      </c>
+      <c r="K210" s="31" t="inlineStr">
+        <is>
+          <t>admissions@ejb.rutgers.edu(Bloustein招生助理 Marie O'Brien);courtney.culler@rutgers.edu(研究生学生服务)</t>
+        </is>
+      </c>
       <c r="L210" s="22" t="inlineStr">
         <is>
           <t>https://bloustein.rutgers.edu/graduate/health-administration/mha-scholarships/</t>
@@ -13479,12 +13575,36 @@
           <t>'Limited Teaching and Research Assistantships may be available'</t>
         </is>
       </c>
-      <c r="F211" s="22" t="n"/>
-      <c r="G211" s="22" t="n"/>
-      <c r="H211" s="22" t="n"/>
-      <c r="I211" s="22" t="n"/>
-      <c r="J211" s="22" t="n"/>
-      <c r="K211" s="22" t="n"/>
+      <c r="F211" s="31" t="inlineStr">
+        <is>
+          <t>不需要:SOPHAS统一申请,按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G211" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(有限TA/RA)。先修:认证院校本科学位,累计GPA≥3.0;无必修先修课,数学/统计、社科、写作成绩好者优先;2封教授推荐信;目标陈述≤750字;自动参评绩优奖学金。</t>
+        </is>
+      </c>
+      <c r="H211" s="31" t="inlineStr">
+        <is>
+          <t>Bulletin写秋季 3/1;招生页写国际生 4/15、国内 6/30(按2026周期,2027待公布);经SOPHAS申请</t>
+        </is>
+      </c>
+      <c r="I211" s="31" t="inlineStr">
+        <is>
+          <t>可选(提交则verbal/quant需≥50百分位;SOPHAS code 0151)</t>
+        </is>
+      </c>
+      <c r="J211" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:Bulletin仅要求非英语授课本科者考试(美本应豁免),但招生页写非母语者需TOEFL ≥79/IELTS ≥6.5/Duolingo ≥110;建议向cph@temple.edu书面确认</t>
+        </is>
+      </c>
+      <c r="K211" s="31" t="inlineStr">
+        <is>
+          <t>cph@temple.edu(公共卫生学院招生办,215-204-5200)</t>
+        </is>
+      </c>
       <c r="L211" s="22" t="inlineStr">
         <is>
           <t>https://bulletin.temple.edu/graduate/scd/cph/health-policy-management-mph/</t>
@@ -13517,12 +13637,36 @@
           <t>校级GA=月薪+学费减免+医保;MPH数量未说明</t>
         </is>
       </c>
-      <c r="F212" s="22" t="n"/>
-      <c r="G212" s="22" t="n"/>
-      <c r="H212" s="22" t="n"/>
-      <c r="I212" s="22" t="n"/>
-      <c r="J212" s="22" t="n"/>
-      <c r="K212" s="22" t="n"/>
+      <c r="F212" s="31" t="inlineStr">
+        <is>
+          <t>不需要:SOPHAS统一申请,按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G212" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(校级GA含月薪+学费减免+医保,MPH名额未说明)。先修:学士学位,GPA≥3.0(累计或最后90学分);无指定先修课;个人陈述、简历、3封推荐信;SOPHAS提交后另发OSU补充申请。</t>
+        </is>
+      </c>
+      <c r="H212" s="31" t="inlineStr">
+        <is>
+          <t>优先 2026/12/1;第二轮 2027/3/1;最终 2027/6/1(太平洋时间20:59);仅秋季入学</t>
+        </is>
+      </c>
+      <c r="I212" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J212" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):OSU研究生院仅要求非美国/英语国家学位者提交;⚠️ MPH页写国际申请人需TOEFL 80(各项≥18)/IELTS 6.5/Duolingo 110,建议确认</t>
+        </is>
+      </c>
+      <c r="K212" s="31" t="inlineStr">
+        <is>
+          <t>COHAdmissions@oregonstate.edu(健康学院研究生招生)</t>
+        </is>
+      </c>
       <c r="L212" s="22" t="inlineStr">
         <is>
           <t>https://health.oregonstate.edu/public-health/mph</t>
@@ -13555,16 +13699,36 @@
           <t>仅校级通用政策;'Both US and non-US citizens are eligible'</t>
         </is>
       </c>
-      <c r="F213" s="22" t="n"/>
-      <c r="G213" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H213" s="22" t="n"/>
-      <c r="I213" s="22" t="n"/>
-      <c r="J213" s="22" t="n"/>
-      <c r="K213" s="22" t="n"/>
+      <c r="F213" s="31" t="inlineStr">
+        <is>
+          <t>不需要:职业型硕士,按项目整体录取</t>
+        </is>
+      </c>
+      <c r="G213" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅校级资助政策,美国与非美国公民均可申请)。先修:医疗管理或相关专业学士,或非相关专业+≥1年医疗行业经验;GPA≥3.0优先;2封推荐信;个人陈述500–750字。⚠️ 搜索显示MHA可能为在线项目,F-1需确认有无面授选项。</t>
+        </is>
+      </c>
+      <c r="H213" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ LeBow通用页:优先奖学金 2027/3/1;国际生 2027/5/1;国内/在线 2027/8/1(2027/8/23开学,全校转学期制)</t>
+        </is>
+      </c>
+      <c r="I213" s="31" t="inlineStr">
+        <is>
+          <t>不需要(可选提交,用于额外奖学金评估)</t>
+        </is>
+      </c>
+      <c r="J213" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:LeBow称在英语国家获学士学位者可咨询招生顾问申请豁免,美本大概率可豁免但非自动</t>
+        </is>
+      </c>
+      <c r="K213" s="31" t="inlineStr">
+        <is>
+          <t>lebowgradenroll@drexel.edu(LeBow研究生招生办,215-895-2115)</t>
+        </is>
+      </c>
       <c r="L213" s="22" t="inlineStr">
         <is>
           <t>https://drexel.edu/graduatecollege/research-funding/assistantships/</t>
@@ -13597,9 +13761,17 @@
           <t>'cannot guarantee…Dean's Office award';≤6个Master's Fellowship;MHA为fee-based</t>
         </is>
       </c>
-      <c r="F214" s="22" t="n"/>
+      <c r="F214" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可预约招生咨询(advising appointment)</t>
+        </is>
+      </c>
       <c r="G214" s="22" t="n"/>
-      <c r="H214" s="22" t="n"/>
+      <c r="H214" s="31" t="inlineStr">
+        <is>
+          <t>优先 2026/12/1;常规截止 2027/1/15(2026/9/1开放,滚动审理)</t>
+        </is>
+      </c>
       <c r="I214" s="22" t="n"/>
       <c r="J214" s="22" t="n"/>
       <c r="K214" s="22" t="n"/>
@@ -13635,12 +13807,36 @@
           <t>'a limited number of fellowships, assistantships, and scholarships on a merit basis'(1/1前申请)</t>
         </is>
       </c>
-      <c r="F215" s="22" t="n"/>
-      <c r="G215" s="22" t="n"/>
-      <c r="H215" s="22" t="n"/>
-      <c r="I215" s="22" t="n"/>
-      <c r="J215" s="22" t="n"/>
-      <c r="K215" s="22" t="n"/>
+      <c r="F215" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(holistic review)</t>
+        </is>
+      </c>
+      <c r="G215" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(1/1前申请可参评有限的绩优fellowship/assistantship/奖学金)。先修:建议修过初级微观经济学、高等代数或微积分、美国政府课(未修也可申请,量化能力强可免微观);研究生院要求最后60学分GPA≥3.0。</t>
+        </is>
+      </c>
+      <c r="H215" s="31" t="inlineStr">
+        <is>
+          <t>优先(含资助考虑)2027/1/1;之后滚动审理,不保证名额(⚠️ MIPA页显示国际生 6/1、国内 8/1,MPA待确认);仅秋季入学</t>
+        </is>
+      </c>
+      <c r="I215" s="31" t="inlineStr">
+        <is>
+          <t>可选(提交GRE或一篇量化短文二选一;无硬性分数线)</t>
+        </is>
+      </c>
+      <c r="J215" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院仅要求母语非英语或本科非英语授课者提交TOEFL/IELTS;⚠️ 未找到单独豁免流程说明</t>
+        </is>
+      </c>
+      <c r="K215" s="31" t="inlineStr">
+        <is>
+          <t>admissions@lafollette.wisc.edu(La Follette招生;⚠️ 仅见于加速项目页面,建议确认)</t>
+        </is>
+      </c>
       <c r="L215" s="22" t="inlineStr">
         <is>
           <t>https://guide.wisc.edu/graduate/lafollette-school-public-affairs/public-affairs-mpa/</t>
@@ -13673,12 +13869,32 @@
           <t>'GA to a select number of master's students each year';录取后再申请</t>
         </is>
       </c>
-      <c r="F216" s="22" t="n"/>
-      <c r="G216" s="22" t="n"/>
-      <c r="H216" s="22" t="n"/>
-      <c r="I216" s="22" t="n"/>
+      <c r="F216" s="31" t="inlineStr">
+        <is>
+          <t>建议:论文方向需导师指导,录取由项目协调员结合教师意见决定;PhD必须先找导师,MS未要求</t>
+        </is>
+      </c>
+      <c r="G216" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(每年少数MS有GA,录取后再申请)。先修:学士学位,总GPA≥3.0或最后60学时≥3.25;GradCAS申请+正式成绩单;方向:运动生理、运动与锻炼心理、应用运动科学;共36学分(含6学分论文)。</t>
+        </is>
+      </c>
+      <c r="H216" s="31" t="inlineStr">
+        <is>
+          <t>最终 2027/8/1;强烈建议国际生 2027/3/1 前、国内生 6/1 前提交(滚动录取,每年8月入学)</t>
+        </is>
+      </c>
+      <c r="I216" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J216" s="22" t="n"/>
-      <c r="K216" s="22" t="n"/>
+      <c r="K216" s="31" t="inlineStr">
+        <is>
+          <t>Sabrina.Queen@unt.edu(KHPR研究生协调员);khpr@unt.edu(系办公室)</t>
+        </is>
+      </c>
       <c r="L216" s="22" t="inlineStr">
         <is>
           <t>https://pahs.unt.edu/academics/kinesiology-ms.html</t>
@@ -13711,15 +13927,27 @@
           <t>仅校级GA池:GA自动获非居民学费减免+月薪,50%FTE享医保;F/J签证学生明文可任GA</t>
         </is>
       </c>
-      <c r="F217" s="22" t="n"/>
-      <c r="G217" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="F217" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,研究生院统一审核;如有问题可联系项目研究生导师 Dr. Joni Mettler</t>
+        </is>
+      </c>
+      <c r="G217" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(F/J签证学生明文可任GA)。先修:区域认证学士学位;本科运动科学课程≥6学分(2025秋起,不足需补修leveling课);GPA≥2.75(总GPA或最后60学时)。需简历、约500字个人陈述、3封推荐信</t>
         </is>
       </c>
       <c r="H217" s="22" t="n"/>
-      <c r="I217" s="22" t="n"/>
-      <c r="J217" s="22" t="n"/>
+      <c r="I217" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J217" s="31" t="inlineStr">
+        <is>
+          <t>否(美国区域认证大学学士学位豁免);否则 TOEFL iBT ≥78,PTE ≥52,Duolingo ≥110</t>
+        </is>
+      </c>
       <c r="K217" s="22" t="n"/>
       <c r="L217" s="22" t="inlineStr">
         <is>
@@ -13753,15 +13981,27 @@
           <t>'only about 10 percent of master's students will receive an assistantship'</t>
         </is>
       </c>
-      <c r="F218" s="22" t="n"/>
-      <c r="G218" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H218" s="22" t="n"/>
+      <c r="F218" s="31" t="inlineStr">
+        <is>
+          <t>建议:仅约10%硕士获助教,部门助教需1/1前申请;运动生理方向可提前联系实验室导师了解GA/论文机会</t>
+        </is>
+      </c>
+      <c r="G218" s="31" t="inlineStr">
+        <is>
+          <t>可以申请,但资助稀少(约10%硕士获assistantship)。GPA&lt;3.0一般不予考虑;⚠️ 官网未列具体先修课,建议邮件确认。论文方向(6学分)适合读博者</t>
+        </is>
+      </c>
+      <c r="H218" s="31" t="inlineStr">
+        <is>
+          <t>Exercise Physiology 优先及部门助教截止 1/1(生物力学 2/1);国际生需在 12/31 前完成研究生院申请;之后有名额可补录(⚠️ 按往年系页面,2027待核实)</t>
+        </is>
+      </c>
       <c r="I218" s="22" t="n"/>
-      <c r="J218" s="22" t="n"/>
+      <c r="J218" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院政策对“学位授予院校以英语为主要教学语言”者豁免,美本应可适用但未明文写美国学位;否则 TOEFL iBT ≥80(各项约20)、IELTS ≥6.5、Duolingo ≥120</t>
+        </is>
+      </c>
       <c r="K218" s="22" t="n"/>
       <c r="L218" s="22" t="inlineStr">
         <is>
@@ -13795,16 +14035,36 @@
           <t>校级:½-time GA 100%学费+非居民费减免,2026-27最低stipend $15,000/9月;系级是否常规给MS未明文</t>
         </is>
       </c>
-      <c r="F219" s="22" t="n"/>
-      <c r="G219" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H219" s="22" t="n"/>
-      <c r="I219" s="22" t="n"/>
-      <c r="J219" s="22" t="n"/>
-      <c r="K219" s="22" t="n"/>
+      <c r="F219" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可联系研究生项目协调员了解GA机会</t>
+        </is>
+      </c>
+      <c r="G219" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:相关领域学士学位,GPA≥3.0(研究生院建议最后60学时3.0);未列具体先修课。需1–2页个人陈述、简历、1封推荐信(最好来自教授)</t>
+        </is>
+      </c>
+      <c r="H219" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/4/1(滚动审核);春季 10/1</t>
+        </is>
+      </c>
+      <c r="I219" s="31" t="inlineStr">
+        <is>
+          <t>可选:GPA≥3.0不需要;GPA&lt;3.0可提交5年内GRE作为补充(研究生院建议 V146/Q140/AW3.0)</t>
+        </is>
+      </c>
+      <c r="J219" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:2026研究生院目录要求“母语非英语和/或高等教育主要在美国以外完成”者提交,美本按此应可豁免;但旧版申请指南称所有国际生需 TOEFL ≥79,建议向 gschool@olemiss.edu 确认</t>
+        </is>
+      </c>
+      <c r="K219" s="31" t="inlineStr">
+        <is>
+          <t>tlandre@olemiss.edu(Thomas Andre,研究生项目协调员);mmmisita@olemiss.edu(Micah Misita,运动学学术运营协调员)</t>
+        </is>
+      </c>
       <c r="L219" s="22" t="inlineStr">
         <is>
           <t>https://gradschool.olemiss.edu/funding-and-opportunities/graduate-assistantships/</t>
@@ -13837,16 +14097,32 @@
           <t>校级GA:tuition remission+月薪+医保补贴;硕士≤4学期;系级数量未公布</t>
         </is>
       </c>
-      <c r="F220" s="22" t="n"/>
-      <c r="G220" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F220" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;如需GA可向学院/研究生项目咨询</t>
+        </is>
+      </c>
+      <c r="G220" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。GPA≥3.0无条件录取(2.70–2.99可临时录取);⚠️ 未列具体先修课。需2封推荐信、≤300字目标陈述、成绩单。论文(30+6学分)或非论文36学分+综合考试</t>
         </is>
       </c>
       <c r="H220" s="22" t="n"/>
-      <c r="I220" s="22" t="n"/>
-      <c r="J220" s="22" t="n"/>
-      <c r="K220" s="22" t="n"/>
+      <c r="I220" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:Peterson's 列为需要GRE(可能过时),其他来源称无要求,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J220" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学士学位自动豁免);否则 TOEFL iBT ≥80、IELTS ≥6.5、Duolingo ≥110、PTE ≥53</t>
+        </is>
+      </c>
+      <c r="K220" s="31" t="inlineStr">
+        <is>
+          <t>hkgraduateprograms@unomaha.edu(研究生顾问 Hannah Ries);unohk@unomaha.edu(健康与运动学院)</t>
+        </is>
+      </c>
       <c r="L220" s="22" t="inlineStr">
         <is>
           <t>https://catalog.unomaha.edu/graduate/financing-education/graduate-assistantships/</t>
@@ -13879,15 +14155,31 @@
           <t>校级GA:除活动费外全部学费杂费减免;系级未明文</t>
         </is>
       </c>
-      <c r="F221" s="22" t="n"/>
-      <c r="G221" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H221" s="22" t="n"/>
-      <c r="I221" s="22" t="n"/>
-      <c r="J221" s="22" t="n"/>
+      <c r="F221" s="31" t="inlineStr">
+        <is>
+          <t>建议:申请GA需联系 Lee Weidauer 并提交意向信、简历、3位推荐人;强烈鼓励面试;与导师匹配研究方向有帮助</t>
+        </is>
+      </c>
+      <c r="G221" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。需营养/运动科学/生物/化学/流行病学等相关学士(其他背景可有条件录取);先修:STAT 281、NUTR 315、CHEM 106/108或112/114、BIOL 221、BIOL 325、EXS 350或同等课程;⚠️ GPA≥3.0无条件录取(第三方)</t>
+        </is>
+      </c>
+      <c r="H221" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/4/15(研究生院统一截止,逾期不保证审核);春季 10/15;国际生录取后5/1前交$400押金</t>
+        </is>
+      </c>
+      <c r="I221" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J221" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士学位豁免);否则 IELTS ≥6.5、Duolingo ≥110、TOEFL iBT ≥79</t>
+        </is>
+      </c>
       <c r="K221" s="22" t="n"/>
       <c r="L221" s="22" t="inlineStr">
         <is>
@@ -13921,16 +14213,36 @@
           <t>校级GTA最多100%学费减免(≤12学分/学期);系页无信息</t>
         </is>
       </c>
-      <c r="F222" s="22" t="n"/>
-      <c r="G222" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H222" s="22" t="n"/>
-      <c r="I222" s="22" t="n"/>
-      <c r="J222" s="22" t="n"/>
-      <c r="K222" s="22" t="n"/>
+      <c r="F222" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,所有学期均可入学;可联系研究生协调员 Dr. Michael Rogers</t>
+        </is>
+      </c>
+      <c r="G222" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:区域认证学士,GPA≥2.75(目录按全部课程,系页按最后60学时);先修课 CHEM 110、HPS 313/328/490(运动生理)、人体解剖或同等课程(系页另列CHEM 101、BIO 223);剩余≤9学分可正式录取,1年内补完</t>
+        </is>
+      </c>
+      <c r="H222" s="31" t="inlineStr">
+        <is>
+          <t>项目全年各学期招生无专门截止日;国际生秋季优先 3/1、次截止 4/30(之后算迟交);⚠️ 2027秋具体日期未公布</t>
+        </is>
+      </c>
+      <c r="I222" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未提及,第三方称可接受GRE,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J222" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:美国学位在入学前2年内获得可豁免(研究生院页面),美本应届通常适用;否则 ⚠️ TOEFL ≥79(第三方)</t>
+        </is>
+      </c>
+      <c r="K222" s="31" t="inlineStr">
+        <is>
+          <t>michael.rogers@wichita.edu(Dr. Michael Rogers,运动科学研究生协调员);wsugradschool@wichita.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L222" s="22" t="inlineStr">
         <is>
           <t>https://www.wichita.edu/academics/graduate_school/assistantships.php</t>
@@ -13963,16 +14275,36 @@
           <t>'apply by the Fall Priority date to be considered for fellowships or assistantships';无数量</t>
         </is>
       </c>
-      <c r="F223" s="22" t="n"/>
-      <c r="G223" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H223" s="22" t="n"/>
-      <c r="I223" s="22" t="n"/>
-      <c r="J223" s="22" t="n"/>
-      <c r="K223" s="22" t="n"/>
+      <c r="F223" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,每年仅秋季入学;问题可发 KINgrad@ucf.edu</t>
+        </is>
+      </c>
+      <c r="G223" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(需在秋季优先截止日前申请才考虑fellowship/assistantship)。先修:解剖与生理学共8学分且含实验(成绩C及以上)</t>
+        </is>
+      </c>
+      <c r="H223" s="31" t="inlineStr">
+        <is>
+          <t>秋季优先(奖学金/资助)2027/1/15;⚠️ 最终截止日官网未明,往年约 7/1(按往年,2027待核实)</t>
+        </is>
+      </c>
+      <c r="I223" s="31" t="inlineStr">
+        <is>
+          <t>不需要(⚠️ 旧版目录曾要求,系FAQ现明确不需要)</t>
+        </is>
+      </c>
+      <c r="J223" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士及以上学位豁免);否则 TOEFL iBT ≥80、IELTS ≥6.5(⚠️ 部分来源称项目要求 TOEFL 89/IELTS 7.0)</t>
+        </is>
+      </c>
+      <c r="K223" s="31" t="inlineStr">
+        <is>
+          <t>KINgrad@ucf.edu(研究生项目,主任 Grant E. Norte)</t>
+        </is>
+      </c>
       <c r="L223" s="22" t="inlineStr">
         <is>
           <t>https://www.ucf.edu/degree/kinesiology-ms/</t>
@@ -14005,16 +14337,32 @@
           <t>'funding opportunities with movement sciences teaching assistantships';填General Assistantship Application</t>
         </is>
       </c>
-      <c r="F224" s="22" t="n"/>
-      <c r="G224" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F224" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;如需助教,填 General Assistantship Application 并可联系系研究生主任</t>
+        </is>
+      </c>
+      <c r="G224" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(运动科学方向有TA资助机会)。先修:区域认证学士,GPA≥3.0(或最后60学分3.0等替代条件);未列具体先修课,优先健康/体育/运动科学背景</t>
         </is>
       </c>
       <c r="H224" s="22" t="n"/>
-      <c r="I224" s="22" t="n"/>
-      <c r="J224" s="22" t="n"/>
-      <c r="K224" s="22" t="n"/>
+      <c r="I224" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J224" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士学位豁免);否则 TOEFL ≥79(2026/1/21后新制4.5)、IELTS ≥6.5、Duolingo ≥115</t>
+        </is>
+      </c>
+      <c r="K224" s="31" t="inlineStr">
+        <is>
+          <t>dpaul@uidaho.edu(David Paul,研究生主任);movementsciences@uidaho.edu(运动科学系)</t>
+        </is>
+      </c>
       <c r="L224" s="22" t="inlineStr">
         <is>
           <t>https://www.uidaho.edu/ed/mvsc</t>
@@ -14167,16 +14515,32 @@
           <t>GA仅二年级、名额极少;一年级靠Graduate Tuition Scholarship</t>
         </is>
       </c>
-      <c r="F227" s="22" t="n"/>
-      <c r="G227" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F227" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可联系MPH项目协调员安排咨询</t>
+        </is>
+      </c>
+      <c r="G227" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(一年级主要靠Graduate Tuition Scholarship,GA仅二年级且极少)。认证学士,GPA≥2.7(3.0优先考虑);无具体先修课。需简历、≤1500字目的陈述、成绩单、⚠️ 3封推荐信。不再使用SOPHAS,走校内申请系统</t>
         </is>
       </c>
       <c r="H227" s="22" t="n"/>
-      <c r="I227" s="22" t="n"/>
-      <c r="J227" s="22" t="n"/>
-      <c r="K227" s="22" t="n"/>
+      <c r="I227" s="31" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J227" s="31" t="inlineStr">
+        <is>
+          <t>否(美国区域认证院校学位通常豁免,但项目可另行要求);否则 TOEFL ≥79、IELTS ≥6、Duolingo ≥120</t>
+        </is>
+      </c>
+      <c r="K227" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ sara.paton@wright.edu(MPH项目主任,信息可能过时);wsugrad@wright.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L227" s="22" t="inlineStr">
         <is>
           <t>https://medicine.wright.edu/population-and-public-health-sciences/master-of-public-health</t>
@@ -14209,16 +14573,36 @@
           <t>仅校级GA池:GTA学费减免+stipend、GRA非居民学费减免+stipend</t>
         </is>
       </c>
-      <c r="F228" s="22" t="n"/>
-      <c r="G228" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H228" s="22" t="n"/>
-      <c r="I228" s="22" t="n"/>
-      <c r="J228" s="22" t="n"/>
-      <c r="K228" s="22" t="n"/>
+      <c r="F228" s="31" t="inlineStr">
+        <is>
+          <t>不需要:研究生院统一录取;如需GTA/GRA需自行联系院系/教授</t>
+        </is>
+      </c>
+      <c r="G228" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅校级GA池)。学士学位,最后60学时GPA≥3.0;无具体先修课。需个人陈述、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H228" s="31" t="inlineStr">
+        <is>
+          <t>国际生秋季建议截止 1/8(即2027/1/8);国内无硬性截止,建议秋季 7/1、春季 11/1</t>
+        </is>
+      </c>
+      <c r="I228" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J228" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 是/否视情况:2年内获美国认证大学学位可豁免提交成绩,但入校后需参加英语水平测试;否则 TOEFL iBT ≥79(新制4.5)、IELTS ≥6.5、PTE ≥58(不接受Duolingo)</t>
+        </is>
+      </c>
+      <c r="K228" s="31" t="inlineStr">
+        <is>
+          <t>mphealth@k-state.edu(MPH项目办公室)</t>
+        </is>
+      </c>
       <c r="L228" s="22" t="inlineStr">
         <is>
           <t>https://www.k-state.edu/grad/financial-support/assistantships.html</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -10985,12 +10985,32 @@
           <t>GA:每学期12学分免学费+医保优惠;SNR内部约4个GA/年,截止12/13;外部RA联系导师</t>
         </is>
       </c>
-      <c r="F164" s="21" t="n"/>
-      <c r="G164" s="21" t="n"/>
+      <c r="F164" s="30" t="inlineStr">
+        <is>
+          <t>强烈建议:SNR称加入研究生项目的第一步是联系研究生导师;GA名额少,外部RA需联系导师</t>
+        </is>
+      </c>
+      <c r="G164" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可申GA/导师RA)。先修:自然资源或相关领域学士学位;最低GPA 3.0(4分制),未达标者可能以provisional身份录取</t>
+        </is>
+      </c>
       <c r="H164" s="21" t="n"/>
-      <c r="I164" s="21" t="n"/>
-      <c r="J164" s="21" t="n"/>
-      <c r="K164" s="21" t="n"/>
+      <c r="I164" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ SNR页面列为需提交(5年内有效,建议V153/Q149/AW4.0),页面可能过时,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J164" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:非英语母语国际生需TOEFL iBT≥79或IELTS≥6.5,页面未提美国学位豁免,建议向协调员确认</t>
+        </is>
+      </c>
+      <c r="K164" s="30" t="inlineStr">
+        <is>
+          <t>bmott2@unl.edu(SNR研究生项目招生协调员 Brooke Mott);graduate@unl.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L164" s="21" t="inlineStr">
         <is>
           <t>https://snr.unl.edu/gradstudent/funding.aspx</t>
@@ -11023,15 +11043,31 @@
           <t>导师岗位形式发布,如$22,600/yr+学费支持×2年</t>
         </is>
       </c>
-      <c r="F165" s="21" t="n"/>
-      <c r="G165" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H165" s="21" t="n"/>
-      <c r="I165" s="21" t="n"/>
-      <c r="J165" s="21" t="n"/>
+      <c r="F165" s="30" t="inlineStr">
+        <is>
+          <t>必须:学院要求申请前邮件联系教师并请其担任major professor;RA以导师岗位形式发布</t>
+        </is>
+      </c>
+      <c r="G165" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可申导师RA岗位)。先修:学士学位;教师一般期望GPA≥3.0(可例外);MS需≥30学分(21学分专业课+4-6学分论文)</t>
+        </is>
+      </c>
+      <c r="H165" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 学院无固定截止日,以导师岗位为准;研究生院要求国际生申请及成绩于开学前3个月送达(2027秋季约2027/5月中前),建议尽早</t>
+        </is>
+      </c>
+      <c r="I165" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 学院野生动物页称以GRE评估(期望V/Q约50百分位),第三方亦列必需,可能过时,建议向导师确认</t>
+        </is>
+      </c>
+      <c r="J165" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:TOEFL iBT≥79(2026/1/21后新版≥4.5,各项≥4.0)/IELTS≥6.5;研究生院称美国认证院校学位可被考虑豁免,但逐案审核</t>
+        </is>
+      </c>
       <c r="K165" s="21" t="n"/>
       <c r="L165" s="21" t="inlineStr">
         <is>
@@ -11297,12 +11333,32 @@
           <t>'Not all incoming students will receive financial assistance';通常2年;merit自动考虑</t>
         </is>
       </c>
-      <c r="F170" s="21" t="n"/>
-      <c r="G170" s="21" t="n"/>
-      <c r="H170" s="21" t="n"/>
+      <c r="F170" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;建议参加招生办线上说明会</t>
+        </is>
+      </c>
+      <c r="G170" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(merit资助自动考虑,但不保证)。先修:认可院校学士学位;审核本科成绩、环境相关经历、领导力、推荐信与文书;⚠️ 第三方称需自然/社会科学相关课程、微积分、统计</t>
+        </is>
+      </c>
+      <c r="H170" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/15(现行bulletin;旧版为1/15,逾期视名额审理)</t>
+        </is>
+      </c>
       <c r="I170" s="21" t="n"/>
-      <c r="J170" s="21" t="n"/>
-      <c r="K170" s="21" t="n"/>
+      <c r="J170" s="30" t="inlineStr">
+        <is>
+          <t>否(美国本科学位豁免TOEFL/IELTS/DET;学院不设最低分;入学后非母语者需参加英语测试)</t>
+        </is>
+      </c>
+      <c r="K170" s="30" t="inlineStr">
+        <is>
+          <t>nicholas-admissions@duke.edu(⚠️ bulletin中招生办成绩单递送地址,建议官网确认咨询邮箱)</t>
+        </is>
+      </c>
       <c r="L170" s="21" t="inlineStr">
         <is>
           <t>https://nicholas.duke.edu/admissions/financial-aid</t>
@@ -11335,16 +11391,36 @@
           <t>Block Grant仅第一学期;之后靠GSR(免州内学费+月薪)/GSI</t>
         </is>
       </c>
-      <c r="F171" s="21" t="n"/>
+      <c r="F171" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:按项目整体录取,官网未见套磁要求,文书可写感兴趣的教授</t>
+        </is>
+      </c>
       <c r="G171" s="21" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="H171" s="21" t="n"/>
-      <c r="I171" s="21" t="n"/>
-      <c r="J171" s="21" t="n"/>
-      <c r="K171" s="21" t="n"/>
+      <c r="H171" s="30" t="inlineStr">
+        <is>
+          <t>约2026/12月初(按2025周期为2025/12/1,2027待官网公布;⚠️ 第三方称2026/12/1);3/1前出结果</t>
+        </is>
+      </c>
+      <c r="I171" s="30" t="inlineStr">
+        <is>
+          <t>不接受(2021起硕博均不收GRE,提交也不考虑)</t>
+        </is>
+      </c>
+      <c r="J171" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院规定在美国院校获英语授课学位可豁免,上传成绩单由审核方判定);否则TOEFL≥90,只接受TOEFL/IELTS</t>
+        </is>
+      </c>
+      <c r="K171" s="30" t="inlineStr">
+        <is>
+          <t>erggrad@berkeley.edu(ERG研究生项目/招生);isharay@berkeley.edu(Head Graduate Advisor Isha Ray)</t>
+        </is>
+      </c>
       <c r="L171" s="21" t="inlineStr">
         <is>
           <t>https://erg.berkeley.edu/academics/financing-your-education</t>
@@ -11377,16 +11453,32 @@
           <t>'must contact faculty members…and confirm support, before they submit';non-thesis自费</t>
         </is>
       </c>
-      <c r="F172" s="21" t="n"/>
-      <c r="G172" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H172" s="21" t="n"/>
-      <c r="I172" s="21" t="n"/>
+      <c r="F172" s="30" t="inlineStr">
+        <is>
+          <t>必须:thesis申请者须在提交研究生院申请前联系教师并确认资助</t>
+        </is>
+      </c>
+      <c r="G172" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(thesis需导师确认资助;non-thesis自费)。先修:学士学位,非相关专业亦可但需有大量理科课程与研究能力;thesis共36学分(≥20学分NRM)</t>
+        </is>
+      </c>
+      <c r="H172" s="30" t="inlineStr">
+        <is>
+          <t>按学期滚动:完整申请须在开学前至少10周提交(秋季约2027/6月初);官网具体日期为2022周期,2027待公布,实际以导师资助时间为准</t>
+        </is>
+      </c>
+      <c r="I172" s="30" t="inlineStr">
+        <is>
+          <t>不需要(系FAQ:目前不要求GRE;第三方仍列必需)</t>
+        </is>
+      </c>
       <c r="J172" s="21" t="n"/>
-      <c r="K172" s="21" t="n"/>
+      <c r="K172" s="30" t="inlineStr">
+        <is>
+          <t>rachel.montoya@ttu.edu(研究生协调员 Rachel Montoya);nrm@ttu.edu(系办)</t>
+        </is>
+      </c>
       <c r="L172" s="21" t="inlineStr">
         <is>
           <t>https://www.depts.ttu.edu/nrm/graduate/howtoapply/index.php</t>
@@ -11419,11 +11511,31 @@
           <t>≥25% GSR/TA覆盖州内学费;GGE Fellowship仅第一年覆盖州外学费</t>
         </is>
       </c>
-      <c r="F173" s="21" t="n"/>
-      <c r="G173" s="21" t="n"/>
-      <c r="H173" s="21" t="n"/>
-      <c r="I173" s="21" t="n"/>
-      <c r="J173" s="21" t="n"/>
+      <c r="F173" s="30" t="inlineStr">
+        <is>
+          <t>必须:只有教授同意收入实验室才会被录取;需在申请前(夏/秋)联系确认其招生,申请中填写该导师</t>
+        </is>
+      </c>
+      <c r="G173" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GGE Fellowship仅第一年覆盖州外学费)。先修:入门生物、普通化学、物理、微积分、统计及高年级生态学;最低GPA 3.0,录取者多≥3.25</t>
+        </is>
+      </c>
+      <c r="H173" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/1(普通申请及Prospective Student Fellowship);申请系统2026年9月中下旬开放</t>
+        </is>
+      </c>
+      <c r="I173" s="30" t="inlineStr">
+        <is>
+          <t>不接受(研究生院2027-28表:Ecology GRE not required or accepted)</t>
+        </is>
+      </c>
+      <c r="J173" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院规定美国区域认证院校英语授课学士可豁免;⚠️ GGE页面措辞较旧,建议确认)</t>
+        </is>
+      </c>
       <c r="K173" s="21" t="n"/>
       <c r="L173" s="21" t="inlineStr">
         <is>
@@ -11457,11 +11569,31 @@
           <t>'generally supported through a mix of fellowships, TA, RA, and faculty grants';fellowship仅顶尖者;TA覆盖部分fees+stipend</t>
         </is>
       </c>
-      <c r="F174" s="21" t="n"/>
-      <c r="G174" s="21" t="n"/>
-      <c r="H174" s="21" t="n"/>
-      <c r="I174" s="21" t="n"/>
-      <c r="J174" s="21" t="n"/>
+      <c r="F174" s="30" t="inlineStr">
+        <is>
+          <t>必须:每名学生录取前必须有faculty sponsor;项目强烈建议申请前直接联系潜在导师</t>
+        </is>
+      </c>
+      <c r="G174" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(资助为fellowship/TA/RA/导师经费组合)。先修:环境科学相关或生物/化学/物理学士;各方向要求不同(大气方向建议化学、物理、有机、微积分、统计);缺课需补;⚠️ 最低GPA 3.0-3.25</t>
+        </is>
+      </c>
+      <c r="H174" s="30" t="inlineStr">
+        <is>
+          <t>优先 2025/12/1;一般 2026/1/5(按2026周期,2027待公布;⚠️ 第三方称2027秋季12/1);2027申请系统2026/9/1已开放</t>
+        </is>
+      </c>
+      <c r="I174" s="30" t="inlineStr">
+        <is>
+          <t>可选(Fall 2026起可选)</t>
+        </is>
+      </c>
+      <c r="J174" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院规定美国区域认证院校英语授课学位可豁免);否则TOEFL iBT≥80(新版≥4.0)</t>
+        </is>
+      </c>
       <c r="K174" s="21" t="n"/>
       <c r="L174" s="21" t="inlineStr">
         <is>
@@ -11495,15 +11627,31 @@
           <t>所有录取自动考虑资助;GSI/GSRA 50%=全额学费+医保+津贴;但'MS 全奖不常见';全额/部分学费奖学金给部分 MS</t>
         </is>
       </c>
-      <c r="F175" s="21" t="n"/>
-      <c r="G175" s="21" t="inlineStr">
-        <is>
-          <t>✅ 明文</t>
-        </is>
-      </c>
-      <c r="H175" s="21" t="n"/>
-      <c r="I175" s="21" t="n"/>
-      <c r="J175" s="21" t="n"/>
+      <c r="F175" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,所有录取者自动考虑资助</t>
+        </is>
+      </c>
+      <c r="G175" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 明文:所有录取者自动考虑资助)。先修:3学期微积分(含多元)、1学期线性代数、1学期统计;网课一般不认;准备不足可条件录取;不要求生物</t>
+        </is>
+      </c>
+      <c r="H175" s="30" t="inlineStr">
+        <is>
+          <t>优先 2026/12/1(资助完全考虑);之后滚动录取;Accelerated MS 2027/1/15</t>
+        </is>
+      </c>
+      <c r="I175" s="30" t="inlineStr">
+        <is>
+          <t>不接受(学院不要求也不审阅GRE)</t>
+        </is>
+      </c>
+      <c r="J175" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:需TOEFL(2026/1/21前考试≥100,新版标准见官网);学院豁免列表未完整查到,Rackham规定本科全程于英语授课院校获学位可豁免,建议确认</t>
+        </is>
+      </c>
       <c r="K175" s="21" t="n"/>
       <c r="L175" s="21" t="inlineStr">
         <is>
@@ -11537,16 +11685,36 @@
           <t>'所有学生不论国籍可获资助,但不保证';GRA(津贴+医保)+ Grad School merit fellowship</t>
         </is>
       </c>
-      <c r="F176" s="21" t="n"/>
-      <c r="G176" s="21" t="inlineStr">
-        <is>
-          <t>✅ 明文</t>
-        </is>
-      </c>
-      <c r="H176" s="21" t="n"/>
-      <c r="I176" s="21" t="n"/>
-      <c r="J176" s="21" t="n"/>
-      <c r="K176" s="21" t="n"/>
+      <c r="F176" s="30" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(经研究生院申请,无需面试)</t>
+        </is>
+      </c>
+      <c r="G176" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 明文:所有学生不论国籍均可获资助但不保证)。先修:学士学位,数学至少含多元微积分与线性代数</t>
+        </is>
+      </c>
+      <c r="H176" s="30" t="inlineStr">
+        <is>
+          <t>2026/11/17(2027秋季入学)</t>
+        </is>
+      </c>
+      <c r="I176" s="30" t="inlineStr">
+        <is>
+          <t>不需要(不要求,一般也不建议提交)</t>
+        </is>
+      </c>
+      <c r="J176" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院允许美国认证院校学位申请豁免,需在申请中上传成绩单);否则TOEFL/IELTS(2年内)</t>
+        </is>
+      </c>
+      <c r="K176" s="30" t="inlineStr">
+        <is>
+          <t>mhobgood@bios.unc.edu(非MPH学生学术协调员 Melissa Hobgood);sph-admissions@unc.edu(Gillings招生)</t>
+        </is>
+      </c>
       <c r="L176" s="21" t="inlineStr">
         <is>
           <t>https://sph.unc.edu/bios/bios-faqs/</t>
@@ -11579,16 +11747,36 @@
           <t>RA/TA'支持相当数量新生和在读';50% FTE 含全额学费减免+医保+津贴;'PhD 获 RA 比例高于硕士'</t>
         </is>
       </c>
-      <c r="F177" s="21" t="n"/>
-      <c r="G177" s="21" t="inlineStr">
-        <is>
-          <t>✅ 明文</t>
-        </is>
-      </c>
-      <c r="H177" s="21" t="n"/>
-      <c r="I177" s="21" t="n"/>
-      <c r="J177" s="21" t="n"/>
-      <c r="K177" s="21" t="n"/>
+      <c r="F177" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:官网未见套磁要求,按项目整体录取;RA多给PhD,可主动联系教授询问RA</t>
+        </is>
+      </c>
+      <c r="G177" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(✅ 明文:RA/TA含全额学费减免+医保+津贴,但PhD比例更高)。先修:学士学位;近60学期学分GPA≥3.0;健康/生物/数学/量化社科背景;无明文数学先修,部分课程需BIOST 511及SAS/Stata</t>
+        </is>
+      </c>
+      <c r="H177" s="30" t="inlineStr">
+        <is>
+          <t>2026/12/1(MS与MPH,2027秋季;MPH需同时提交SOPHAS与UW研究生院申请)</t>
+        </is>
+      </c>
+      <c r="I177" s="30" t="inlineStr">
+        <is>
+          <t>不接受(永久取消,提交也不考虑)</t>
+        </is>
+      </c>
+      <c r="J177" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:UW研究生院认可美国认证院校英语授课学位,需满足在校就读条件;2027冬季起政策修订,建议确认);当TA另需口语证明,美国本科学位且在校就读可满足</t>
+        </is>
+      </c>
+      <c r="K177" s="30" t="inlineStr">
+        <is>
+          <t>epi@uw.edu(流行病学系)</t>
+        </is>
+      </c>
       <c r="L177" s="21" t="inlineStr">
         <is>
           <t>https://epi.washington.edu/admissions/funding-tuition/</t>
@@ -14635,16 +14823,36 @@
           <t>'100% of students accepted…eligible for scholarship aid (Access Grant)';有full/half-tuition奖但无比例;无stipend</t>
         </is>
       </c>
-      <c r="F229" s="22" t="n"/>
-      <c r="G229" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H229" s="22" t="n"/>
-      <c r="I229" s="22" t="n"/>
-      <c r="J229" s="22" t="n"/>
-      <c r="K229" s="22" t="n"/>
+      <c r="F229" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(SOPHAS),无需联系导师</t>
+        </is>
+      </c>
+      <c r="G229" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(奖学金如Access Grant面向全部录取者)。先修:认证院校学士学位,无指定先修课;on-campus MPH无工作经验要求(在线MPH建议约2年经验);材料:3封推荐信、CV、SOP</t>
+        </is>
+      </c>
+      <c r="H229" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ on-campus MPH:优先 2027/1/15;国际生最终 2027/4/1(官网列表中另有 2026/10/15 优先日期,国内最终日期显示为 2026/6/15 疑为笔误);截止指SOPHAS提交日,建议尽早</t>
+        </is>
+      </c>
+      <c r="I229" s="31" t="inlineStr">
+        <is>
+          <t>不需要(MPH提交GRE也不予考虑)</t>
+        </is>
+      </c>
+      <c r="J229" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:TOEFL iBT ≥100,IELTS ≥7.0,不接受Duolingo;自动豁免仅限WES认证英语授课学位等情形,美国学位需提交豁免申请表+学校官方证明信,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K229" s="31" t="inlineStr">
+        <is>
+          <t>asksph@bu.edu(SPH招生办)</t>
+        </is>
+      </c>
       <c r="L229" s="22" t="inlineStr">
         <is>
           <t>https://www.bu.edu/sph/admissions/tuition-and-funding/scholarships/</t>
@@ -14677,16 +14885,32 @@
           <t>Master's Tuition Scholarship:第二年75%学费(或25%+50%);need-based MSPH奖≤50%首年;Dean's Fellowship $10k+保证带薪工作</t>
         </is>
       </c>
-      <c r="F230" s="22" t="n"/>
-      <c r="G230" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F230" s="31" t="inlineStr">
+        <is>
+          <t>不需要:招生办审核材料完整后交项目教师评审,无需事先联系教师</t>
+        </is>
+      </c>
+      <c r="G230" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修因项目而异:多数ScM/MHS不要求工作经验;MSPH Health Systems偏好生物/健康科学或管理/社科背景;MPH需2年全职健康相关工作经验(不在本行项目内);需经SOPHAS申请</t>
         </is>
       </c>
       <c r="H230" s="22" t="n"/>
-      <c r="I230" s="22" t="n"/>
-      <c r="J230" s="22" t="n"/>
-      <c r="K230" s="22" t="n"/>
+      <c r="I230" s="31" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J230" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:TOEFL iBT ≥100(2026/1/21后新制≥5.0)/IELTS ≥7.0;国际卫生系FAQ称英语国家大学学位可邮件向项目经理申请豁免,美本大概率可豁免,需确认</t>
+        </is>
+      </c>
+      <c r="K230" s="31" t="inlineStr">
+        <is>
+          <t>jhsph.admiss@jhu.edu(招生服务办公室)</t>
+        </is>
+      </c>
       <c r="L230" s="22" t="inlineStr">
         <is>
           <t>https://publichealth.jhu.edu/offices-and-services/office-of-admissions-services/funding-and-scholarships</t>
@@ -14719,16 +14943,36 @@
           <t>'94% of enrolled students received a loan or scholarship';merit'may not fully cover'</t>
         </is>
       </c>
-      <c r="F231" s="22" t="n"/>
-      <c r="G231" s="22" t="inlineStr">
-        <is>
-          <t>可(不限国籍)</t>
-        </is>
-      </c>
-      <c r="H231" s="22" t="n"/>
-      <c r="I231" s="22" t="n"/>
-      <c r="J231" s="22" t="n"/>
-      <c r="K231" s="22" t="n"/>
+      <c r="F231" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G231" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(不限国籍)。先修:入学前获得学士学位即可,无指定本科先修课;无明确工作经验要求(第三方称需2年,官网未见)</t>
+        </is>
+      </c>
+      <c r="H231" s="31" t="inlineStr">
+        <is>
+          <t>Round 1 2026/12/1;Round 2 2027/2/1;最终 2027/4/15(之后仍滚动审核,早申请更利于奖学金)</t>
+        </is>
+      </c>
+      <c r="I231" s="31" t="inlineStr">
+        <is>
+          <t>不需要(GRE不审阅)</t>
+        </is>
+      </c>
+      <c r="J231" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 大概率否:非母语者需TOEFL ≥100/IELTS ≥7/Duolingo ≥120;官网明文豁免英语授课院校学位持有者,美国学位应同样适用,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K231" s="31" t="inlineStr">
+        <is>
+          <t>Geisel.MPH.MS.Admissions@dartmouth.edu(MPH/MS招生办)</t>
+        </is>
+      </c>
       <c r="L231" s="22" t="inlineStr">
         <is>
           <t>https://healthsciences.dartmouth.edu/education/admissions/tuition-fees</t>
@@ -14761,16 +15005,32 @@
           <t>'a small number of scholarships…25 to 50 percent of tuition'</t>
         </is>
       </c>
-      <c r="F232" s="22" t="n"/>
-      <c r="G232" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H232" s="22" t="n"/>
+      <c r="F232" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取(SOPHAS),无需联系导师</t>
+        </is>
+      </c>
+      <c r="G232" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。⚠️ 先修:官网未列具体本科专业或先修课要求;需提交全部正式成绩单(在读者可交在读成绩)</t>
+        </is>
+      </c>
+      <c r="H232" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 优先(奖学金)12/15;常规 2/15;之后视名额滚动审核至 5/1(按往年日期,2027周期预计 2026/12/15、2027/2/15,待确认)</t>
+        </is>
+      </c>
       <c r="I232" s="22" t="n"/>
-      <c r="J232" s="22" t="n"/>
-      <c r="K232" s="22" t="n"/>
+      <c r="J232" s="31" t="inlineStr">
+        <is>
+          <t>否(MPH招生页:在英语授课院校完成学位者免TOEFL/IELTS);注:研究生院总政策更严,建议确认</t>
+        </is>
+      </c>
+      <c r="K232" s="31" t="inlineStr">
+        <is>
+          <t>mph@vanderbilt.edu(MPH项目办公室)</t>
+        </is>
+      </c>
       <c r="L232" s="22" t="inlineStr">
         <is>
           <t>https://medschool.vanderbilt.edu/mph/admissions/cost/</t>
@@ -14803,16 +15063,36 @@
           <t>仅Global Game Changer Scholarship(需索取申请)</t>
         </is>
       </c>
-      <c r="F233" s="22" t="n"/>
-      <c r="G233" s="22" t="inlineStr">
-        <is>
-          <t>可(优先人群含国际生)</t>
-        </is>
-      </c>
-      <c r="H233" s="22" t="n"/>
-      <c r="I233" s="22" t="n"/>
-      <c r="J233" s="22" t="n"/>
-      <c r="K233" s="22" t="n"/>
+      <c r="F233" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G233" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(优先人群含国际生)。先修:认证院校学士学位,GPA建议≥3.0;官网未列具体先修课;需同时提交SOPHAS与Cornell研究生院Quick Application</t>
+        </is>
+      </c>
+      <c r="H233" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 校目录:秋季标准项目 5/17、加速项目 4/1(未注明年份);第三方列 2027/5/15;Fellowship优先截止 3/23(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I233" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J233" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:官网称国际生一般需提交TOEFL或IELTS(极少例外);TOEFL分项 口语22/阅读20/听力15/写作20,或IELTS ≥7.0;美国学位是否豁免未明确,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K233" s="31" t="inlineStr">
+        <is>
+          <t>cornellmph@cornell.edu(MPH项目)</t>
+        </is>
+      </c>
       <c r="L233" s="22" t="inlineStr">
         <is>
           <t>https://publichealth.cornell.edu/prospectivestudents/funding/</t>
@@ -14845,16 +15125,32 @@
           <t>GA有限、竞争性、年度stipend;'Students are expected to cover all tuition and fees!'</t>
         </is>
       </c>
-      <c r="F234" s="22" t="n"/>
-      <c r="G234" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F234" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GA有限、竞争性,可向项目询问</t>
+        </is>
+      </c>
+      <c r="G234" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(GA有限且竞争激烈,学费通常需自付)。注:USU该方向现为MPH(Health Education &amp; Promotion)。先修:任意认证本科专业;录取GPA≥3.0(按最后60学期学分计);3封推荐信、SOP、申请费$55</t>
         </is>
       </c>
       <c r="H234" s="22" t="n"/>
-      <c r="I234" s="22" t="n"/>
-      <c r="J234" s="22" t="n"/>
-      <c r="K234" s="22" t="n"/>
+      <c r="I234" s="31" t="inlineStr">
+        <is>
+          <t>不需要(不要求GRE/MAT等入学考试)</t>
+        </is>
+      </c>
+      <c r="J234" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:TOEFL iBT ≥79(Duolingo ≥105);豁免按国家名单,美国学位未明列,但成绩单注明英语授课可满足要求,建议向研究生院确认</t>
+        </is>
+      </c>
+      <c r="K234" s="31" t="inlineStr">
+        <is>
+          <t>melissa.johnson@usu.edu(KHS研究生项目协调员);julie.gast@usu.edu(MPH项目主任)</t>
+        </is>
+      </c>
       <c r="L234" s="22" t="inlineStr">
         <is>
           <t>https://cehhs.usu.edu/khs/graduate/student-resources/grad-assistantships</t>
@@ -14887,16 +15183,36 @@
           <t>奖学金$1,000–4,000;≥$1,000竞争性奖学金可享州内学费;GA'typically not offered to incoming master's students'</t>
         </is>
       </c>
-      <c r="F235" s="22" t="n"/>
-      <c r="G235" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H235" s="22" t="n"/>
-      <c r="I235" s="22" t="n"/>
-      <c r="J235" s="22" t="n"/>
-      <c r="K235" s="22" t="n"/>
+      <c r="F235" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G235" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(GA一般不给新入学硕士;≥$1,000竞争性奖学金可享州内学费)。先修:认证院校学士学位;Health Behavior方向本科GPA≥2.75;无先修课要求</t>
+        </is>
+      </c>
+      <c r="H235" s="31" t="inlineStr">
+        <is>
+          <t>2026/9/1 开放;国际生 2027/4/15;国内 2027/6/1;奖学金自 12/1 起滚动发放,早申请优先</t>
+        </is>
+      </c>
+      <c r="I235" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J235" s="31" t="inlineStr">
+        <is>
+          <t>否(TAMU政策:美国认证院校学士即满足英语要求;SPH另注明在美完成全部4年本科可替代认证);否则TOEFL ≥95;担任教学类助教需另获ELP认证</t>
+        </is>
+      </c>
+      <c r="K235" s="31" t="inlineStr">
+        <is>
+          <t>SPH-Gradinfo@tamu.edu(SPH研究生招生)</t>
+        </is>
+      </c>
       <c r="L235" s="22" t="inlineStr">
         <is>
           <t>https://public-health.tamu.edu/degrees/scholarships.html</t>
@@ -14929,15 +15245,31 @@
           <t>校级GA可能含州外学费减免+stipend;系重组中</t>
         </is>
       </c>
-      <c r="F236" s="22" t="n"/>
-      <c r="G236" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H236" s="22" t="n"/>
-      <c r="I236" s="22" t="n"/>
-      <c r="J236" s="22" t="n"/>
+      <c r="F236" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G236" s="31" t="inlineStr">
+        <is>
+          <t>❌ 该MA仅以在线形式开设,F-1国际生通常无法凭纯在线项目维持签证身份;州外申请者还取决于ECU能否获得所在州授权。先修:区域认证学士,GPA建议≥3.0,健康教育/社科/生物背景优先(非硬性),不足者需补修</t>
+        </is>
+      </c>
+      <c r="H236" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季 8/1(另:春季 12/15、夏I 5/1、夏II 6/15);按2024版项目手册,2027待确认</t>
+        </is>
+      </c>
+      <c r="I236" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官方手册未列GRE(应为不需要),第三方Yocket称需要,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J236" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 否(ECU研究生院相关页面:本科来自美国院校可免英语要求);否则TOEFL ≥80/IELTS ≥6.5</t>
+        </is>
+      </c>
       <c r="K236" s="22" t="n"/>
       <c r="L236" s="22" t="inlineStr">
         <is>
@@ -14971,16 +15303,32 @@
           <t>'付费研究职位可能有,视资金'</t>
         </is>
       </c>
-      <c r="F237" s="22" t="n"/>
-      <c r="G237" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ 国际生可录,资助未明</t>
-        </is>
-      </c>
-      <c r="H237" s="22" t="n"/>
-      <c r="I237" s="22" t="n"/>
+      <c r="F237" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 未明确要求:官网未提套磁;因带薪研究职位视资金而定,建议先联系Dr. Egleton询问</t>
+        </is>
+      </c>
+      <c r="G237" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生可录,资助未明)。先修:普通生物、普化、有机化学、物理各两学期(含实验)+生化一学期,C以上(校目录版要求较少);建议总GPA及理科GPA≥3.0,可个案豁免;3封推荐信(理工科教授优先)</t>
+        </is>
+      </c>
+      <c r="H237" s="31" t="inlineStr">
+        <is>
+          <t>国际生 3/15;优先 6/1;最终 6/30(视空位,滚动审核);仅秋季入学(未注明年份,2027周期待确认)</t>
+        </is>
+      </c>
+      <c r="I237" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
       <c r="J237" s="22" t="n"/>
-      <c r="K237" s="22" t="n"/>
+      <c r="K237" s="31" t="inlineStr">
+        <is>
+          <t>carothers@marshall.edu(研究生招生专员Kelly Carothers);brandm@marshall.edu(研究生事务主任)</t>
+        </is>
+      </c>
       <c r="L237" s="22" t="inlineStr">
         <is>
           <t>https://jcesom.marshall.edu/research/office-of-research-and-graduate-education/graduate-education-programs/clinical-translational-science/</t>
@@ -15013,16 +15361,36 @@
           <t>部分merit奖(不限国籍);保证实地研究stipend;可申校内GA</t>
         </is>
       </c>
-      <c r="F238" s="22" t="n"/>
-      <c r="G238" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H238" s="22" t="n"/>
-      <c r="I238" s="22" t="n"/>
-      <c r="J238" s="22" t="n"/>
-      <c r="K238" s="22" t="n"/>
+      <c r="F238" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,无需联系导师</t>
+        </is>
+      </c>
+      <c r="G238" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(部分merit奖不限国籍,可申校内GA)。先修:学士GPA≥3.0;无先修课要求;美国学位无需WES认证</t>
+        </is>
+      </c>
+      <c r="H238" s="31" t="inlineStr">
+        <is>
+          <t>优先 2027/1/15(录取及merit奖学金机会更大,免申请费);最终 2027/6/1</t>
+        </is>
+      </c>
+      <c r="I238" s="31" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="J238" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士免TOEFL/IELTS;否则TOEFL iBT ≥100/IELTS ≥7.0)</t>
+        </is>
+      </c>
+      <c r="K238" s="31" t="inlineStr">
+        <is>
+          <t>globalhealthms@georgetown.edu(项目协调员Kathryn Baartmans);gradmail@georgetown.edu(研究生招生办)</t>
+        </is>
+      </c>
       <c r="L238" s="22" t="inlineStr">
         <is>
           <t>https://globalhealthms.georgetown.edu/admissions/faq/</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -16305,15 +16305,31 @@
           <t>'partial funding from the Nungesser…Fellowship';自动考虑;recruitment scholarship让国际生按州内学费</t>
         </is>
       </c>
-      <c r="F254" s="22" t="n"/>
-      <c r="G254" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H254" s="22" t="n"/>
-      <c r="I254" s="22" t="n"/>
-      <c r="J254" s="22" t="n"/>
+      <c r="F254" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,意向书写读研原因与职业规划即可</t>
+        </is>
+      </c>
+      <c r="G254" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(Nungesser奖学金自动考虑,recruitment scholarship可让国际生按州内学费)。先修:美国认证本科学位,专业不限;最低GPA 3.0(可只看最后60学分);需2封推荐信、意向书、简历</t>
+        </is>
+      </c>
+      <c r="H254" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未列具体日期,材料随到随审(滚动);第三方Peterson's称秋季国际生 3/1、国内 6/15,建议 2027/3/1 前提交</t>
+        </is>
+      </c>
+      <c r="I254" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网项目要求未列GRE,但学校称部分项目可能要求;第三方称需GRE,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J254" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:在美国获认证学士及以上学位的非美国公民可免语言成绩);否则 TOEFL 79 / IELTS 6.5 / Duolingo 100,成绩2年内有效</t>
+        </is>
+      </c>
       <c r="K254" s="22" t="n"/>
       <c r="L254" s="22" t="inlineStr">
         <is>
@@ -16347,16 +16363,28 @@
           <t>仅校级GA池:stipend+非居民费减免,tuition remission视岗位</t>
         </is>
       </c>
-      <c r="F255" s="22" t="n"/>
-      <c r="G255" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="F255" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GA相关可咨询系内 Dr. Bethany Stich / Dr. Monica Farris</t>
+        </is>
+      </c>
+      <c r="G255" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅校级GA池)。先修:美国区域认证学士学位,专业不限;⚠️ 第三方称最低GPA 3.0,需两页目的陈述、简历、写作样本(部分来源称另需3封推荐信);45学分,PAB认证</t>
         </is>
       </c>
       <c r="H255" s="22" t="n"/>
       <c r="I255" s="22" t="n"/>
-      <c r="J255" s="22" t="n"/>
-      <c r="K255" s="22" t="n"/>
+      <c r="J255" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国认证学士/硕士学位可豁免);否则 IELTS 6.5 / PTE 58 / Duolingo 105 / TOEFL 79(旧版)</t>
+        </is>
+      </c>
+      <c r="K255" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网邮箱被隐藏:MURP协调员 Marla Nelson, Ph.D.(请在MURP页面获取邮箱);研究生招生电话 504-280-6595</t>
+        </is>
+      </c>
       <c r="L255" s="22" t="inlineStr">
         <is>
           <t>https://www.lsuneworleans.edu/academics/grad/assistantships</t>
@@ -16389,16 +16417,36 @@
           <t>研究生院:'many of our master's students are appointed to graduate assistantships';GA享tuition &amp; fee awards+stipend+医保;系页被屏蔽</t>
         </is>
       </c>
-      <c r="F256" s="22" t="n"/>
-      <c r="G256" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H256" s="22" t="n"/>
-      <c r="I256" s="22" t="n"/>
-      <c r="J256" s="22" t="n"/>
-      <c r="K256" s="22" t="n"/>
+      <c r="F256" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述可写感兴趣的教授;GA多分配给硕士生</t>
+        </is>
+      </c>
+      <c r="G256" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(多数硕士生获GA:学费减免+stipend+医保;当TA需OECT口语测试)。先修:四年制学士学位,专业不限;最低GPA 3.0(项目可调整);3封推荐信</t>
+        </is>
+      </c>
+      <c r="H256" s="31" t="inlineStr">
+        <is>
+          <t>优先截止 2027/2/1(官网每年固定2/1);之后继续审理直至名额满</t>
+        </is>
+      </c>
+      <c r="I256" s="31" t="inlineStr">
+        <is>
+          <t>不需要(研究生院项目页明确 GRE: No)</t>
+        </is>
+      </c>
+      <c r="J256" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院手册称在英语国家英语授课院校获学位可满足要求,但项目页称无TOEFL/IELTS不审;否则 TOEFL 79 / IELTS 6.5 / PTE 53 / Duolingo 115;入学前需EPT;当TA需OECT口语测试(美国学位不豁免)</t>
+        </is>
+      </c>
+      <c r="K256" s="31" t="inlineStr">
+        <is>
+          <t>merfoley@iastate.edu(MCRP研究生招生协调员 Meredith Foley);crp@iastate.edu(系办)</t>
+        </is>
+      </c>
       <c r="L256" s="22" t="inlineStr">
         <is>
           <t>https://www.grad-college.iastate.edu/resources/finance/assistantships</t>
@@ -16431,16 +16479,36 @@
           <t>'GTA positions are limited and are very competitive';奖学金需FAFSA</t>
         </is>
       </c>
-      <c r="F257" s="22" t="n"/>
-      <c r="G257" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H257" s="22" t="n"/>
-      <c r="I257" s="22" t="n"/>
-      <c r="J257" s="22" t="n"/>
-      <c r="K257" s="22" t="n"/>
+      <c r="F257" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,看GPA、推荐信和个人陈述</t>
+        </is>
+      </c>
+      <c r="G257" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(GTA名额有限且竞争激烈)。先修:学士学位,专业不限;无条件录取需GPA≥3.0、优秀推荐信、写作良好的个人陈述;不满足者可试读录取;规划相关专业+5年经验可走30学分快速轨道</t>
+        </is>
+      </c>
+      <c r="H257" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/6/15;春季 10/15(官网目录常年日期);研究生院建议入学前90天提交,争取GTA宜尽早</t>
+        </is>
+      </c>
+      <c r="I257" s="31" t="inlineStr">
+        <is>
+          <t>必需(仅UTA本校3年内毕业且最后60学时GPA≥3.0可豁免);偏好 V150/Q141/AW4,非硬性门槛</t>
+        </is>
+      </c>
+      <c r="J257" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国区域认证学士/硕士学位无需提交);否则 TOEFL 79(写22/说21/读20/听16)或 IELTS 6.5</t>
+        </is>
+      </c>
+      <c r="K257" s="31" t="inlineStr">
+        <is>
+          <t>cappa.advising@uta.edu(CAPPA学术咨询办公室,推荐信也发此邮箱)</t>
+        </is>
+      </c>
       <c r="L257" s="22" t="inlineStr">
         <is>
           <t>https://www.uta.edu/academics/schools-colleges/cappa/admissions/graduate</t>
@@ -16473,16 +16541,32 @@
           <t>仅校级GA政策;'International students are limited to 50% FTE';系站挂起</t>
         </is>
       </c>
-      <c r="F258" s="22" t="n"/>
-      <c r="G258" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H258" s="22" t="n"/>
+      <c r="F258" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,申请时选方向(社区发展/原住民规划/自然资源环境/物理规划设计);GA多在首轮录取后决定</t>
+        </is>
+      </c>
+      <c r="G258" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生GA限50% FTE)。先修:学士学位,专业不限;本科最后两年GPA≥3.0;需意向书(按写作样本评分)、3封推荐信(至少1封学术)、简历,$70申请费;48学分PAB认证</t>
+        </is>
+      </c>
+      <c r="H258" s="31" t="inlineStr">
+        <is>
+          <t>优先截止:国际生 2026/12/1,美国居民 2027/1/15(17:00 MST);4/1前为第二轮;4/1后视名额;想拿GA须赶优先截止</t>
+        </is>
+      </c>
       <c r="I258" s="22" t="n"/>
-      <c r="J258" s="22" t="n"/>
-      <c r="K258" s="22" t="n"/>
+      <c r="J258" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:UNM国际招生页列明美国区域认证学士学位豁免,申请时自动审核);否则 TOEFL iBT 79</t>
+        </is>
+      </c>
+      <c r="K258" s="31" t="inlineStr">
+        <is>
+          <t>saapadvise@unm.edu(建筑与规划学院研究生顾问 Natalie Rowe);saap@unm.edu(学院办公室)</t>
+        </is>
+      </c>
       <c r="L258" s="22" t="inlineStr">
         <is>
           <t>https://grad.unm.edu/funding/assistantships/assistantships.html</t>
@@ -16557,16 +16641,36 @@
           <t>'limited number of assistantships…competitive';最多4学期</t>
         </is>
       </c>
-      <c r="F260" s="22" t="n"/>
-      <c r="G260" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H260" s="22" t="n"/>
-      <c r="I260" s="22" t="n"/>
-      <c r="J260" s="22" t="n"/>
-      <c r="K260" s="22" t="n"/>
+      <c r="F260" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;可提前联系实验方向协调员 Dr. Cyrille Magne 了解研究与GA</t>
+        </is>
+      </c>
+      <c r="G260" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:学士学位(心理学背景为宜);GPA≥3.0;GRE约291(V+Q);需统计、研究方法、测量等核心领域课程(可入学后补修);不达标可先非学位入学,首学期9学分GPA≥3.25后转正</t>
+        </is>
+      </c>
+      <c r="H260" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/3/1(GA申请材料同日截止);春季 10/1;逾期合格者个案审理</t>
+        </is>
+      </c>
+      <c r="I260" s="31" t="inlineStr">
+        <is>
+          <t>必需(目录要求可接受的GRE成绩,参考 V+Q≈291)</t>
+        </is>
+      </c>
+      <c r="J260" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国认证四年制学士/硕士学位无需语言成绩);否则 TOEFL 71 / IELTS 6</t>
+        </is>
+      </c>
+      <c r="K260" s="31" t="inlineStr">
+        <is>
+          <t>Cyrille.Magne@mtsu.edu(实验方向协调员);⚠️ Ying.Jin@mtsu.edu(定量方向协调员,来自旧目录)</t>
+        </is>
+      </c>
       <c r="L260" s="22" t="inlineStr">
         <is>
           <t>https://psychology.mtsu.edu/finance/</t>
@@ -16599,16 +16703,36 @@
           <t>仅校级GA:州内外学费减免+stipend</t>
         </is>
       </c>
-      <c r="F261" s="22" t="n"/>
-      <c r="G261" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H261" s="22" t="n"/>
-      <c r="I261" s="22" t="n"/>
-      <c r="J261" s="22" t="n"/>
-      <c r="K261" s="22" t="n"/>
+      <c r="F261" s="31" t="inlineStr">
+        <is>
+          <t>建议:研究导向小班(每届限12人),陈述中写明感兴趣的教授,可先联系项目协调员</t>
+        </is>
+      </c>
+      <c r="G261" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(校级GA:州内外学费减免+stipend)。先修:区域认证学士学位,GPA≥3.0(近两届录取均分3.63/3.79);须修过心理学导论、统计、研究方法及另外2门心理课;3封推荐信(至少1封来自教授/科研导师)、个人陈述,建议附写作样本;仅秋季入学</t>
+        </is>
+      </c>
+      <c r="H261" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 来源冲突:研究生院最新截止表 秋季 2027/4/1;项目页写 2/15(旧页曾为优先 2/5)。建议 2027/2/15 前提交以争取GA</t>
+        </is>
+      </c>
+      <c r="I261" s="31" t="inlineStr">
+        <is>
+          <t>可选(自Fall 2026起可选;⚠️ 2027周期待确认)</t>
+        </is>
+      </c>
+      <c r="J261" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国认证院校学位可免);否则 TOEFL 75 / IELTS 6.0,2年内有效</t>
+        </is>
+      </c>
+      <c r="K261" s="31" t="inlineStr">
+        <is>
+          <t>ahackney@georgiasouthern.edu(研究生项目协调员 Dr. Amy Hackney);gradadmissions@georgiasouthern.edu(研究生招生办)</t>
+        </is>
+      </c>
       <c r="L261" s="22" t="inlineStr">
         <is>
           <t>https://www.georgiasouthern.edu/admissions-aid/graduate-students/graduate-assistantships</t>
@@ -16641,15 +16765,31 @@
           <t>'limited number of graduate assistantships which reduce tuition and provide a monthly income'</t>
         </is>
       </c>
-      <c r="F262" s="22" t="n"/>
-      <c r="G262" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H262" s="22" t="n"/>
-      <c r="I262" s="22" t="n"/>
-      <c r="J262" s="22" t="n"/>
+      <c r="F262" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;General Experimental方向需独立研究论文,陈述中可写研究兴趣</t>
+        </is>
+      </c>
+      <c r="G262" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:认证学士学位,本科GPA≥3.0;3封推荐信(至少2封学术);三个方向可选(General Experimental为博士预备、需论文;Clinical/Counseling为60学分LPC方向)</t>
+        </is>
+      </c>
+      <c r="H262" s="31" t="inlineStr">
+        <is>
+          <t>2026/3/1(截止后2周内仍接受补充材料)(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I262" s="31" t="inlineStr">
+        <is>
+          <t>不需要(官网明确不要求任何标准化考试)</t>
+        </is>
+      </c>
+      <c r="J262" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:持美国区域认证学士及以上学位,收到成绩单后豁免);否则 TOEFL 79 / IELTS 6.5</t>
+        </is>
+      </c>
       <c r="K262" s="22" t="n"/>
       <c r="L262" s="22" t="inlineStr">
         <is>
@@ -16683,16 +16823,36 @@
           <t>GA需在读≥1年并修PSY 600后;第一年不可得</t>
         </is>
       </c>
-      <c r="F263" s="22" t="n"/>
-      <c r="G263" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H263" s="22" t="n"/>
-      <c r="I263" s="22" t="n"/>
-      <c r="J263" s="22" t="n"/>
-      <c r="K263" s="22" t="n"/>
+      <c r="F263" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,滚动审理</t>
+        </is>
+      </c>
+      <c r="G263" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(但GA需在读≥1年并修完PSY 600,第一年无GA)。先修:本科GPA≥3.0;须以B及以上修过统计、实验心理/研究方法、变态、学习、社会、发展心理;缺≤2门可临时录取</t>
+        </is>
+      </c>
+      <c r="H263" s="31" t="inlineStr">
+        <is>
+          <t>滚动录取,每学期均可入学,须在入学学期开始前获录取;建议 2027 春季前提交</t>
+        </is>
+      </c>
+      <c r="I263" s="31" t="inlineStr">
+        <is>
+          <t>必需(建议 V≥150、Q≥141、总分≥300;GPA或GRE满足其一可临时录取)</t>
+        </is>
+      </c>
+      <c r="J263" s="31" t="inlineStr">
+        <is>
+          <t>否(可豁免:在美国认证大学全日制学习满1年即可豁免;⚠️ 建议向研究生招生办确认);否则 TOEFL 80(2026/1/21后新版4.5)/ IELTS 6.5 / Duolingo 105</t>
+        </is>
+      </c>
+      <c r="K263" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ linz@marshall.edu(研究生项目负责人 Marianna Linz,来源排版混乱需核实);graduateadmissions@marshall.edu(研究生招生办)</t>
+        </is>
+      </c>
       <c r="L263" s="22" t="inlineStr">
         <is>
           <t>https://www.marshall.edu/psych/awards-and-scholarships/assistantship-opportunities/</t>
@@ -16725,16 +16885,36 @@
           <t>全职/半职GA'through internal offers';校级GA学费全付;无比例</t>
         </is>
       </c>
-      <c r="F264" s="22" t="n"/>
-      <c r="G264" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H264" s="22" t="n"/>
-      <c r="I264" s="22" t="n"/>
-      <c r="J264" s="22" t="n"/>
-      <c r="K264" s="22" t="n"/>
+      <c r="F264" s="31" t="inlineStr">
+        <is>
+          <t>建议:导师制(每名学生有指定导师,相关I/OBM方向按申请志愿分配导师),申请前可联系感兴趣教授并向项目确认分配方式</t>
+        </is>
+      </c>
+      <c r="G264" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(全职/半职GA通过内部分配)。先修:心理学本科专业或辅修优先,至少18学分心理学(含统计);GPA≥3.0;3封推荐信、专业陈述、简历;可选论文或项目(实践)方向</t>
+        </is>
+      </c>
+      <c r="H264" s="31" t="inlineStr">
+        <is>
+          <t>秋季 2027/1/15(项目页常年日期)</t>
+        </is>
+      </c>
+      <c r="I264" s="31" t="inlineStr">
+        <is>
+          <t>不需要(项目不要求研究生入学考试)</t>
+        </is>
+      </c>
+      <c r="J264" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:WMU称在英语国家完成学业可豁免,但官网豁免列表未确认含美国学位;否则 ⚠️ TOEFL 80 / IELTS 6.5,建议邮件国际招生办确认</t>
+        </is>
+      </c>
+      <c r="K264" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ amber.l.hutson@wmich.edu(心理系研究生培养行政助理 Amber Hutson,来自2023手册)</t>
+        </is>
+      </c>
       <c r="L264" s="22" t="inlineStr">
         <is>
           <t>https://wmich.edu/psychology/funding</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -17171,16 +17171,36 @@
           <t>~50% 新生获 merit fellowship(从 25% 学费起);'不提供全奖';GA 为时薪无学费减免</t>
         </is>
       </c>
-      <c r="F269" s="22" t="n"/>
-      <c r="G269" s="22" t="inlineStr">
-        <is>
-          <t>✅ 国际生可获部分</t>
-        </is>
-      </c>
-      <c r="H269" s="22" t="n"/>
-      <c r="I269" s="22" t="n"/>
-      <c r="J269" s="22" t="n"/>
-      <c r="K269" s="22" t="n"/>
+      <c r="F269" s="31" t="inlineStr">
+        <is>
+          <t>不需要:专业型硕士,按项目整体录取;个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G269" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获部分merit fellowship,约50%新生获得,从25%学费起;无全奖)。先修:微积分(M211或同等)+一学期无机化学含实验,成绩C及以上;招生委员会可要求入学前/首学期补修;GPA通常≥3.0</t>
+        </is>
+      </c>
+      <c r="H269" s="31" t="inlineStr">
+        <is>
+          <t>官网列(未标年份):优先 1/15;国际生 3/1;最终 5/1 → 按2027周期推为 2027/1/15、2027/3/1、2027/5/1(2027待官网确认)</t>
+        </is>
+      </c>
+      <c r="I269" s="31" t="inlineStr">
+        <is>
+          <t>可选(O'Neill硕士项目GRE/GMAT可选)</t>
+        </is>
+      </c>
+      <c r="J269" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免;否则TOEFL ≥100,各项建议≥25,IELTS亦可)</t>
+        </is>
+      </c>
+      <c r="K269" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ oneillrc@indiana.edu(O'Neill研究生档案办公室,非确认的招生邮箱);建议通过 oneill.indiana.edu/masters/apply 页面的招生联系方式确认</t>
+        </is>
+      </c>
       <c r="L269" s="22" t="inlineStr">
         <is>
           <t>https://oneill.indiana.edu/masters/cost-financial-aid/international-funding.html</t>
@@ -17213,16 +17233,36 @@
           <t>'several paid teaching assistantships each semester';非居民GA仅免州外差额</t>
         </is>
       </c>
-      <c r="F270" s="22" t="n"/>
-      <c r="G270" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H270" s="22" t="n"/>
-      <c r="I270" s="22" t="n"/>
-      <c r="J270" s="22" t="n"/>
-      <c r="K270" s="22" t="n"/>
+      <c r="F270" s="31" t="inlineStr">
+        <is>
+          <t>必须:研究型项目,需有教师同意担任主导师才录取;官网强烈建议申请前联系导师</t>
+        </is>
+      </c>
+      <c r="G270" s="31" t="inlineStr">
+        <is>
+          <t>可以申请,但资助有限(每学期少量带薪TA;非居民GA仅免州外差额)。先修:学士学位,GPA≥3.0,3封推荐信;未列具体先修课</t>
+        </is>
+      </c>
+      <c r="H270" s="31" t="inlineStr">
+        <is>
+          <t>研究生院:国内优先 2027/1/15,国内最终 2027/7/30;国际生 2027/5/1(项目可能更早或滚动,以导师/项目为准)</t>
+        </is>
+      </c>
+      <c r="I270" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J270" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士学位豁免;否则TOEFL ≥79,IELTS ≥6.5,Duolingo ≥115)</t>
+        </is>
+      </c>
+      <c r="K270" s="31" t="inlineStr">
+        <is>
+          <t>cnr-grad-studies@uidaho.edu(CNR研究生办公室);jayceei@uidaho.edu(研究生项目协调员 JayCee Hollingshead)</t>
+        </is>
+      </c>
       <c r="L270" s="22" t="inlineStr">
         <is>
           <t>https://www.uidaho.edu/cnr/grad-programs/cnr-graduate-funding-opportunities</t>
@@ -17255,16 +17295,36 @@
           <t>仅校级/系级奖学金;GA比例未明</t>
         </is>
       </c>
-      <c r="F271" s="22" t="n"/>
-      <c r="G271" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H271" s="22" t="n"/>
-      <c r="I271" s="22" t="n"/>
-      <c r="J271" s="22" t="n"/>
-      <c r="K271" s="22" t="n"/>
+      <c r="F271" s="31" t="inlineStr">
+        <is>
+          <t>必须:官网称申请前第一步是确定愿意指导的导师</t>
+        </is>
+      </c>
+      <c r="G271" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(仅校级/系级奖学金,GA比例未明;不提供provisional admission)。先修:学士学位,未指定专业或先修课;需个人陈述、学术陈述、简历、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H271" s="31" t="inlineStr">
+        <is>
+          <t>申请窗口 2026/8/1–2027/2/1(仅秋季入学,按cohort录取;早申请更利于资助)</t>
+        </is>
+      </c>
+      <c r="I271" s="31" t="inlineStr">
+        <is>
+          <t>可选(若提交须5年内有效)</t>
+        </is>
+      </c>
+      <c r="J271" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:系国际生页写TOEFL iBT ≥80(阅读/听力/口语≥19,写作≥22),仅列豁免国家;MSU多个系对美国学士自动豁免,需向系确认。当TA另需SPEAK口语测试</t>
+        </is>
+      </c>
+      <c r="K271" s="31" t="inlineStr">
+        <is>
+          <t>owentif2@msu.edu(学术项目协调员 Tiffany Owen);zwicklea@msu.edu(研究生项目主任 Adam Zwickle)</t>
+        </is>
+      </c>
       <c r="L271" s="22" t="inlineStr">
         <is>
           <t>https://www.canr.msu.edu/csus/graduate/</t>
@@ -17297,16 +17357,36 @@
           <t>系GA池偏向PhD;MS靠个别导师RA岗位</t>
         </is>
       </c>
-      <c r="F272" s="22" t="n"/>
-      <c r="G272" s="22" t="inlineStr">
-        <is>
-          <t>可(个别岗位)</t>
-        </is>
-      </c>
-      <c r="H272" s="22" t="n"/>
-      <c r="I272" s="22" t="n"/>
-      <c r="J272" s="22" t="n"/>
-      <c r="K272" s="22" t="n"/>
+      <c r="F272" s="31" t="inlineStr">
+        <is>
+          <t>必须:须事先与导师建立联系才能录取;MS资助主要靠个别导师RA岗位</t>
+        </is>
+      </c>
+      <c r="G272" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可通过个别导师RA岗位获资助;当GTA需TOEFL≥100,美本可豁免)。先修:科学、社科或人文相关本科学位;3封推荐信(可含拟定导师)</t>
+        </is>
+      </c>
+      <c r="H272" s="31" t="inlineStr">
+        <is>
+          <t>资助优先 2027/1/1;最终 2027/4/15(按项目页;研究生院页另列6/24,以项目页为准)</t>
+        </is>
+      </c>
+      <c r="I272" s="31" t="inlineStr">
+        <is>
+          <t>不需要(2018年起取消)</t>
+        </is>
+      </c>
+      <c r="J272" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,提交成绩单即可;否则TOEFL ≥90,GTA资助需≥100)</t>
+        </is>
+      </c>
+      <c r="K272" s="31" t="inlineStr">
+        <is>
+          <t>rsenrgc@uvm.edu(Rubenstein研究生项目协调员 Katie Fraioli);kfraioli@uvm.edu</t>
+        </is>
+      </c>
       <c r="L272" s="22" t="inlineStr">
         <is>
           <t>https://www.uvm.edu/rsenr/graduate-assistantships-and-fellowships</t>
@@ -17339,16 +17419,32 @@
           <t>'A limited number of GRAs and GTAs';含学费+州外减免</t>
         </is>
       </c>
-      <c r="F273" s="22" t="n"/>
-      <c r="G273" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F273" s="31" t="inlineStr">
+        <is>
+          <t>必须:官网建议未联系教授并获鼓励前不要正式申请,录取取决于导师是否愿意指导</t>
+        </is>
+      </c>
+      <c r="G273" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(有限GRA/GTA,含学费+州外减免)。先修:认证院校林学、野生动物、渔业或其他自然资源相关本科;⚠️第三方列GPA≥2.7;野生动物与渔业项目需同时提交系内申请表</t>
         </is>
       </c>
       <c r="H273" s="22" t="n"/>
-      <c r="I273" s="22" t="n"/>
-      <c r="J273" s="22" t="n"/>
-      <c r="K273" s="22" t="n"/>
+      <c r="I273" s="31" t="inlineStr">
+        <is>
+          <t>可选(推荐但非必需;部分导师看重GRE,建议问意向导师)</t>
+        </is>
+      </c>
+      <c r="J273" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院规定以英语授课院校获得的学位可豁免(上传成绩单),美本应适用;否则TOEFL ≥80,IELTS ≥6.5,Duolingo ≥120</t>
+        </is>
+      </c>
+      <c r="K273" s="31" t="inlineStr">
+        <is>
+          <t>hresig@tennessee.edu(研究生项目学术协调员 Heather Resig)</t>
+        </is>
+      </c>
       <c r="L273" s="22" t="inlineStr">
         <is>
           <t>https://naturalresources.tennessee.edu/graduate-student-handbook/financial-support/</t>
@@ -17381,16 +17477,32 @@
           <t>'A limited number of graduate assistantships';无导师同意不录</t>
         </is>
       </c>
-      <c r="F274" s="22" t="n"/>
-      <c r="G274" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="F274" s="31" t="inlineStr">
+        <is>
+          <t>必须:无导师同意不录取;官网建议申请前邮件附CV联系导师,GA须事先与导师商定</t>
+        </is>
+      </c>
+      <c r="G274" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获有限GA,需与导师商定)。先修:UF最低要求大三大四GPA≥3.0;未列具体先修课;另交$30申请费及全部成绩单</t>
         </is>
       </c>
       <c r="H274" s="22" t="n"/>
-      <c r="I274" s="22" t="n"/>
-      <c r="J274" s="22" t="n"/>
-      <c r="K274" s="22" t="n"/>
+      <c r="I274" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(UF多数系已免GRE,FFGS未单独说明)</t>
+        </is>
+      </c>
+      <c r="J274" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:美国学位可豁免,但由系酌情决定(非自动,可能需申请后邮件系里);否则TOEFL ≥80,IELTS ≥6.5(2026春起)</t>
+        </is>
+      </c>
+      <c r="K274" s="31" t="inlineStr">
+        <is>
+          <t>ffgs-academics@ifas.ufl.edu(FFGS研究生项目,Dianne Behringer)</t>
+        </is>
+      </c>
       <c r="L274" s="22" t="inlineStr">
         <is>
           <t>https://ffgs.ifas.ufl.edu/academics/apply/</t>
@@ -17423,16 +17535,32 @@
           <t>'a number of GTA/GRA available';金额未列</t>
         </is>
       </c>
-      <c r="F275" s="22" t="n"/>
-      <c r="G275" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="F275" s="31" t="inlineStr">
+        <is>
+          <t>强烈建议:官网鼓励申请前后联系潜在导师,申请陈述需写明首选导师</t>
+        </is>
+      </c>
+      <c r="G275" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(有若干GTA/GRA,金额未列)。先修:Park Mgmt方向优先生命科学或自然资源本科,但非必须;最后两年GPA≥3.0;3封推荐信+学术目标陈述</t>
         </is>
       </c>
       <c r="H275" s="22" t="n"/>
-      <c r="I275" s="22" t="n"/>
-      <c r="J275" s="22" t="n"/>
-      <c r="K275" s="22" t="n"/>
+      <c r="I275" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J275" s="31" t="inlineStr">
+        <is>
+          <t>否(近2年内获美国学位豁免;否则TOEFL iBT ≥79,各项≥20)</t>
+        </is>
+      </c>
+      <c r="K275" s="31" t="inlineStr">
+        <is>
+          <t>shpark@ksu.edu(研究生项目主任 Sunghun Park);hnrinfo@ksu.edu(系办)</t>
+        </is>
+      </c>
       <c r="L275" s="22" t="inlineStr">
         <is>
           <t>https://hnr.k-state.edu/graduate/admissions.html</t>
@@ -17465,16 +17593,36 @@
           <t>校级GA全部学费杂费减免(除活动费)</t>
         </is>
       </c>
-      <c r="F276" s="22" t="n"/>
-      <c r="G276" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H276" s="22" t="n"/>
-      <c r="I276" s="22" t="n"/>
-      <c r="J276" s="22" t="n"/>
-      <c r="K276" s="22" t="n"/>
+      <c r="F276" s="31" t="inlineStr">
+        <is>
+          <t>必须:需导师同意支持才录取,且导师无经费不收;官网建议申请前联系导师</t>
+        </is>
+      </c>
+      <c r="G276" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(校级GA含全额学费杂费减免,活动费除外;须导师有经费)。先修:学士学位,GPA≥3.0可无条件录取;未列具体先修课;论文型30学分/非论文32学分</t>
+        </is>
+      </c>
+      <c r="H276" s="31" t="inlineStr">
+        <is>
+          <t>系内全年审核,无固定截止;⚠️ 第三方列国际生秋季 4/15,建议尽早联系导师</t>
+        </is>
+      </c>
+      <c r="I276" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J276" s="31" t="inlineStr">
+        <is>
+          <t>否(美国认证院校学士学位豁免;否则TOEFL ≥71,IELTS ≥6.0,Duolingo ≥100)</t>
+        </is>
+      </c>
+      <c r="K276" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ sdsu.nrm@sdstate.edu(系通用邮箱,来自系Facebook页,待核实);系主任 Michele Dudash(电话 605-688-6121)</t>
+        </is>
+      </c>
       <c r="L276" s="22" t="inlineStr">
         <is>
           <t>https://www.sdstate.edu/graduate-school/graduate-assistantships</t>
@@ -17507,16 +17655,36 @@
           <t>'TA/RA may be available through funded research or participating departments'</t>
         </is>
       </c>
-      <c r="F277" s="22" t="n"/>
-      <c r="G277" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H277" s="22" t="n"/>
-      <c r="I277" s="22" t="n"/>
-      <c r="J277" s="22" t="n"/>
-      <c r="K277" s="22" t="n"/>
+      <c r="F277" s="31" t="inlineStr">
+        <is>
+          <t>必须:需ECS教师同意接收进实验室并安排津贴和研究经费才会考虑</t>
+        </is>
+      </c>
+      <c r="G277" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(TA/RA依赖导师经费或参与系)。先修:认证院校学士学位,累计GPA≥3.0;未列具体先修课;个人陈述+3封推荐信</t>
+        </is>
+      </c>
+      <c r="H277" s="31" t="inlineStr">
+        <is>
+          <t>国际生 2027/5/1(秋季);国内生开课前至少1个月;实际取决于导师接收</t>
+        </is>
+      </c>
+      <c r="I277" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(官网未列GRE要求)</t>
+        </is>
+      </c>
+      <c r="J277" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院可豁免英语国家学位,美本通常适用,但需邮件 ndsu.grad.school@ndsu.edu 确认;项目要求TOEFL ≥79,IELTS ≥6.5,Duolingo ≥105</t>
+        </is>
+      </c>
+      <c r="K277" s="31" t="inlineStr">
+        <is>
+          <t>laura.aldrichwolfe@ndsu.edu(ECS项目主任 Laura Aldrich-Wolfe);ndsu.grad.school@ndsu.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L277" s="22" t="inlineStr">
         <is>
           <t>https://www.ndsu.edu/ecs/index.php/future-students</t>
@@ -17549,16 +17717,36 @@
           <t>'limited funding and very few TA or GA';'Most students have funding through their major professor';RA须含学费(工会合同)</t>
         </is>
       </c>
-      <c r="F278" s="22" t="n"/>
-      <c r="G278" s="22" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H278" s="22" t="n"/>
-      <c r="I278" s="22" t="n"/>
-      <c r="J278" s="22" t="n"/>
-      <c r="K278" s="22" t="n"/>
+      <c r="F278" s="31" t="inlineStr">
+        <is>
+          <t>必须:未找到导师不能录取;个人陈述需写明想合作的ESM教师</t>
+        </is>
+      </c>
+      <c r="G278" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(资助有限,TA/GA极少,多数靠导师经费;RA须含学费)。先修:理科本科;一年生物、一年化学、一门物理、微积分、至少一门统计;GPA≥3.0(研究生院表)</t>
+        </is>
+      </c>
+      <c r="H278" s="31" t="inlineStr">
+        <is>
+          <t>2027/1/15(每年仅秋季一轮,9/1开放;研究生院表列1/1,建议按1/1前提交)</t>
+        </is>
+      </c>
+      <c r="I278" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院表列为必需,系页面未提及,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J278" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学士学位可作英语能力证明)</t>
+        </is>
+      </c>
+      <c r="K278" s="31" t="inlineStr">
+        <is>
+          <t>esmoff@pdx.edu(ESM系办,⚠️另一页面写作 esmoffice@pdx.edu);pag3@pdx.edu(办公室协调员 Samantha Paganelli)</t>
+        </is>
+      </c>
       <c r="L278" s="22" t="inlineStr">
         <is>
           <t>https://www.pdx.edu/environmental-science/prospective-graduate-students</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -17779,16 +17779,36 @@
           <t>'General Recruitment Fellowship to 25-40% of incoming MESM';TA竞争性且不覆盖NRST;国际生6学期约$99k</t>
         </is>
       </c>
-      <c r="F279" s="22" t="n"/>
-      <c r="G279" s="22" t="inlineStr">
-        <is>
-          <t>可(need-based仅美籍)</t>
-        </is>
-      </c>
-      <c r="H279" s="22" t="n"/>
-      <c r="I279" s="22" t="n"/>
-      <c r="J279" s="22" t="n"/>
-      <c r="K279" s="22" t="n"/>
+      <c r="F279" s="31" t="inlineStr">
+        <is>
+          <t>不需要:MESM为专业型项目,按项目整体录取(holistic review),无需联系导师</t>
+        </is>
+      </c>
+      <c r="G279" s="31" t="inlineStr">
+        <is>
+          <t>可以申请,但need-based资助仅限美籍;国际生可获General Recruitment Fellowship(竞争性)。先修:2门科学(化学/生物/物理/地球/大气)、2门数学(微积分/统计/计量/线代)、1门社科,成绩≥C;可申请时未修完但入学前须完成并附说明memo;本科GPA≥3.0;录取者平均2.5年工作经验</t>
+        </is>
+      </c>
+      <c r="H279" s="31" t="inlineStr">
+        <is>
+          <t>2026/12/16(2026–27申请周期,仅秋季入学);2027年3月下旬出结果,4/15前确认入学</t>
+        </is>
+      </c>
+      <c r="I279" s="31" t="inlineStr">
+        <is>
+          <t>不需要(2026–27周期免除GRE,每年重新评估)</t>
+        </is>
+      </c>
+      <c r="J279" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:UCSB研究生院对“英语为唯一教学语言”的认证美国院校学位可豁免(需该校在WHED数据库中仅列英语),否则需TOEFL iBT ≥80(2026/1/21后新版≥4.0)/IELTS ≥7.0/DET ≥120,且Bren要求明显高于最低线;入学后仍有Grad ELPE分级测试</t>
+        </is>
+      </c>
+      <c r="K279" s="31" t="inlineStr">
+        <is>
+          <t>admissions@bren.ucsb.edu(Bren招生办)</t>
+        </is>
+      </c>
       <c r="L279" s="22" t="inlineStr">
         <is>
           <t>https://bren.ucsb.edu/masters-programs/master-environmental-science-and-management</t>
@@ -17821,16 +17841,36 @@
           <t>'associate positions are the primary source of aid…apply by Dec.1';无硕士比例</t>
         </is>
       </c>
-      <c r="F280" s="22" t="n"/>
-      <c r="G280" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H280" s="22" t="n"/>
-      <c r="I280" s="22" t="n"/>
-      <c r="J280" s="22" t="n"/>
-      <c r="K280" s="22" t="n"/>
+      <c r="F280" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;资助主要为GRA/GAA associate职位,可录取后主动联系教授争取</t>
+        </is>
+      </c>
+      <c r="G280" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:学士学位,建议GPA≥3.0,需较强数学/理科基础(⚠️ MS Biostat具体先修未在官网查到,同校在线MPH Biostat要求线代、微积分及≥1门概率/统计)</t>
+        </is>
+      </c>
+      <c r="H280" s="31" t="inlineStr">
+        <is>
+          <t>MS Biostatistics / MS Epidemiology:优先 2026/12/1(资助/associate职位考虑须在此前申请);常规 2027/5/15(按2026/2027周期页面);⚠️ CPH FAQ另列11/14为优先及fellowship截止,需确认;经SOPHAS+OSU补充申请,建议提前3–4周提交</t>
+        </is>
+      </c>
+      <c r="I280" s="31" t="inlineStr">
+        <is>
+          <t>可选(CPH所有研究生项目GRE可选)</t>
+        </is>
+      </c>
+      <c r="J280" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:OSU中心政策按国籍或“学位所在国”豁免,部分系页面列美国学士可豁免,但官网清单未确认;否则 TOEFL ≥79(新版≥4.0)/IELTS/Duolingo,成绩2年内有效</t>
+        </is>
+      </c>
+      <c r="K280" s="31" t="inlineStr">
+        <is>
+          <t>cph@osu.edu(公共卫生学院招生与学生服务);gpadmissions@osu.edu(OSU研究生招生办)</t>
+        </is>
+      </c>
       <c r="L280" s="22" t="inlineStr">
         <is>
           <t>https://cph.osu.edu/future-students/financial-aid</t>
@@ -17863,16 +17903,36 @@
           <t>MSPH Biostat资助考虑截止12/1;'International students with &gt;3.0 GPA eligible for scholarships during their second year'</t>
         </is>
       </c>
-      <c r="F281" s="22" t="n"/>
-      <c r="G281" s="22" t="inlineStr">
-        <is>
-          <t>部分(国际生第二年起)</t>
-        </is>
-      </c>
-      <c r="H281" s="22" t="n"/>
-      <c r="I281" s="22" t="n"/>
-      <c r="J281" s="22" t="n"/>
-      <c r="K281" s="22" t="n"/>
+      <c r="F281" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,经SOPHAS/研究生院申请</t>
+        </is>
+      </c>
+      <c r="G281" s="31" t="inlineStr">
+        <is>
+          <t>可以申请,但国际生奖学金仅第二年起(GPA&gt;3.0)。先修:MS Biostat需三学期微积分+线代、GPA≥3.0且微积分/线代≥B;MSPH Biostat需两学期微积分+线代+编程能力;MSPH Applied Epi需GPA≥3.0、2封推荐信</t>
+        </is>
+      </c>
+      <c r="H281" s="31" t="inlineStr">
+        <is>
+          <t>MSPH Biostat资助考虑 12/1;秋季国际生 4/1;国内 MS/MSPH Biostat 5/1、MSPH Applied Epi 7/1(按2026周期,2027待公布);国际生仅秋季入学</t>
+        </is>
+      </c>
+      <c r="I281" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:SOPH申请页称所有硕士项目免GRE(目录/第三方仍有旧要求,建议确认)</t>
+        </is>
+      </c>
+      <c r="J281" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位且GPA≥3.0自动豁免);否则 TOEFL ≥80/IELTS ≥6.5/Duolingo ≥120</t>
+        </is>
+      </c>
+      <c r="K281" s="31" t="inlineStr">
+        <is>
+          <t>soph@uab.edu(公共卫生学院);⚠️ abosque@uab.edu(研究生招生与奖学金经理Amanda Bosque,目录可能过时)</t>
+        </is>
+      </c>
       <c r="L281" s="22" t="inlineStr">
         <is>
           <t>https://www.uab.edu/soph/home/apply/graduate</t>
@@ -17905,16 +17965,36 @@
           <t>GRA $11,000/学年;学费仅有限州外减免</t>
         </is>
       </c>
-      <c r="F282" s="22" t="n"/>
+      <c r="F282" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;资助(GRA)询问研究生项目主任</t>
+        </is>
+      </c>
       <c r="G282" s="22" t="inlineStr">
         <is>
           <t>未说明</t>
         </is>
       </c>
-      <c r="H282" s="22" t="n"/>
-      <c r="I282" s="22" t="n"/>
-      <c r="J282" s="22" t="n"/>
-      <c r="K282" s="22" t="n"/>
+      <c r="H282" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 优先 1/15(资助强烈建议此前提交),开放至 5/15(按Fall 2023周期,2027待公布);研究生院秋季最终截止 8/1;系另列资助申请截止 3/1</t>
+        </is>
+      </c>
+      <c r="I282" s="31" t="inlineStr">
+        <is>
+          <t>不需要(系页面:GRE/MAT 均不要求)</t>
+        </is>
+      </c>
+      <c r="J282" s="31" t="inlineStr">
+        <is>
+          <t>否(研究生院:在美国至少一年大学学习可替代语言成绩)</t>
+        </is>
+      </c>
+      <c r="K282" s="31" t="inlineStr">
+        <is>
+          <t>campbellco16@ecu.edu(研究生项目主任Colin Campbell)</t>
+        </is>
+      </c>
       <c r="L282" s="22" t="inlineStr">
         <is>
           <t>https://sociology.ecu.edu/graduate/</t>
@@ -17947,16 +18027,36 @@
           <t>'competitive funding'、'limited graduate teaching positions';无金额</t>
         </is>
       </c>
-      <c r="F283" s="22" t="n"/>
-      <c r="G283" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
-        </is>
-      </c>
-      <c r="H283" s="22" t="n"/>
-      <c r="I283" s="22" t="n"/>
-      <c r="J283" s="22" t="n"/>
-      <c r="K283" s="22" t="n"/>
+      <c r="F283" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取,个人陈述写明研究兴趣即可</t>
+        </is>
+      </c>
+      <c r="G283" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(资助为竞争性,TA名额有限)。先修:认证院校学士,≥20学期学时社会学课程(应含统计、方法、理论,系评估较灵活);GPA≥3.0;需陈述、写作样本、3封推荐信</t>
+        </is>
+      </c>
+      <c r="H283" s="31" t="inlineStr">
+        <is>
+          <t>2027/3/15(完整材料截止;仅秋季入学)(按现行页面,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I283" s="31" t="inlineStr">
+        <is>
+          <t>可选(推荐但不要求)</t>
+        </is>
+      </c>
+      <c r="J283" s="31" t="inlineStr">
+        <is>
+          <t>否(非英语国家申请人2年内获美国认证院校学位可豁免);否则 TOEFL iBT ≥4(新版)/IELTS ≥6.5(资助资格档,TA另有要求)</t>
+        </is>
+      </c>
+      <c r="K283" s="31" t="inlineStr">
+        <is>
+          <t>socanth@ohio.edu(社会学与人类学系通用邮箱)</t>
+        </is>
+      </c>
       <c r="L283" s="22" t="inlineStr">
         <is>
           <t>https://www.ohio.edu/cas/sociology-anthropology/sociology-graduate</t>
@@ -18047,16 +18147,36 @@
           <t>'small number of graduate assistantships';stipend+州内学费;国际生持GA仍需自付约$17,500/年差额</t>
         </is>
       </c>
-      <c r="F285" s="22" t="n"/>
+      <c r="F285" s="31" t="inlineStr">
+        <is>
+          <t>不需要:按项目整体录取;GA名额少,可向研究生项目主任询问</t>
+        </is>
+      </c>
       <c r="G285" s="22" t="inlineStr">
         <is>
           <t>可(部分)</t>
         </is>
       </c>
-      <c r="H285" s="22" t="n"/>
-      <c r="I285" s="22" t="n"/>
-      <c r="J285" s="22" t="n"/>
-      <c r="K285" s="22" t="n"/>
+      <c r="H285" s="31" t="inlineStr">
+        <is>
+          <t>优先 2027/3/1;最终 2027/8/1(研究生院)/ 8/15(系页面,较旧)(按往年周期,2027待确认)</t>
+        </is>
+      </c>
+      <c r="I285" s="31" t="inlineStr">
+        <is>
+          <t>不需要(项目页注明 GRE Not Required)</t>
+        </is>
+      </c>
+      <c r="J285" s="31" t="inlineStr">
+        <is>
+          <t>否(获美国院校学位或在美完成一年学习即豁免)</t>
+        </is>
+      </c>
+      <c r="K285" s="31" t="inlineStr">
+        <is>
+          <t>lisa.walker@charlotte.edu(社会学研究生项目主任/协调员Lisa Walker);⚠️ jdippong@charlotte.edu(研究生招生页旧列主任Joseph Dippong)</t>
+        </is>
+      </c>
       <c r="L285" s="22" t="inlineStr">
         <is>
           <t>https://sociology.charlotte.edu/graduate/faq-sociology-ma-program/</t>
@@ -18147,16 +18267,36 @@
           <t>系GA'to the most qualified doctoral students';MA仅泛称</t>
         </is>
       </c>
-      <c r="F287" s="22" t="n"/>
+      <c r="F287" s="31" t="inlineStr">
+        <is>
+          <t>不需要:但个人陈述(250–500字)需写明与系研究方向相关的兴趣及想合作的教师</t>
+        </is>
+      </c>
       <c r="G287" s="22" t="inlineStr">
         <is>
           <t>可申请</t>
         </is>
       </c>
-      <c r="H287" s="22" t="n"/>
-      <c r="I287" s="22" t="n"/>
-      <c r="J287" s="22" t="n"/>
-      <c r="K287" s="22" t="n"/>
+      <c r="H287" s="31" t="inlineStr">
+        <is>
+          <t>秋季:国内 2027/7/1;国际生 2027/1/15(按UCF往年周期,以研究生院2027页面为准)</t>
+        </is>
+      </c>
+      <c r="I287" s="31" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="J287" s="31" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免);否则 TOEFL iBT ≥91/IELTS ≥7.0/Duolingo ≥125</t>
+        </is>
+      </c>
+      <c r="K287" s="31" t="inlineStr">
+        <is>
+          <t>socadmissions@ucf.edu(社会学系招生);⚠️ amy.donley@ucf.edu(社会学研究生主任Amy Donley,页面较旧)</t>
+        </is>
+      </c>
       <c r="L287" s="22" t="inlineStr">
         <is>
           <t>https://sciences.ucf.edu/sociology/graduate/f-a-q-graduate/</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -6841,19 +6841,43 @@
           <t>各校 GA 含学费+津贴;Wyoming ~7 GA/yr 全额学费+费用+津贴</t>
         </is>
       </c>
-      <c r="F93" s="21" t="n"/>
+      <c r="F93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: 不需要:按项目整体录取;如选论文型capstone可写感兴趣教授
+Boise State: 不需要:按项目录取,但需与项目主任面试+现场写作测试
+Montana State: 强烈建议:Exercise &amp; Nutrition Sciences MS为导师制,官网建议申请前联系导师,RA/TA由导师决定
+Wyoming: 必须(事实上):官网称未正式联系教授者很难被录取或获GA推荐,需邮件确认导师是否招生</t>
+        </is>
+      </c>
       <c r="G93" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
+      <c r="I93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: ⚠️ 不明确:项目页称GRE/GMAT目前豁免,另一页称需5年内GRE,建议邮件确认
+Boise State: 不需要
+Montana State: 不需要(MSU自2021年10月起所有项目不要求也不考虑GRE)
+Wyoming: 可选(不要求,可提交以增强申请/GA竞争力)</t>
+        </is>
+      </c>
       <c r="J93" s="21" t="n"/>
-      <c r="K93" s="21" t="n"/>
-      <c r="L93" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="K93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: healthsci@csuohio.edu(健康科学与人体运动系)
+Boise State: mhsinfo@boisestate.edu(MHS项目,预约写作测试与面试)
+Montana State: fsnk-grad@montana.edu(FSNK系研究生办公室);⚠️hhdgrad@montana.edu(旧HHD研究生办)
+Wyoming: kelly.simonton@uwyo.edu(研究生项目协调员Dr. Kelly Simonton);kines@uwyo.edu(系办)</t>
+        </is>
+      </c>
+      <c r="L93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: https://health.csuohio.edu/health-sci/master-science-in-health-sciences
+Boise State: https://www.boisestate.edu/graduatecollege/programs2/health-science/
+Montana State: https://www.montana.edu/fsnk/graduate/exerciseandnutrition/index.html
+Wyoming: https://www.uwyo.edu/kandh/academics/graduate/future-grad-students.html</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7209,18 @@
           <t>各校有限 GA(津贴+学费减免);竞争性</t>
         </is>
       </c>
-      <c r="F99" s="21" t="n"/>
+      <c r="F99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: 不需要:按项目整体录取(SOPHAS),GRA由教师课题经费提供可后续联系
+GaSou: 不需要:按项目整体录取(SOPHAS),2/1前申请可获GA优先考虑
+CMU: 不需要:按项目整体录取,录取后向系里申请GA
+ISU: 不需要:按项目整体录取(但项目为纯网课,见先修列)
+USM: 不需要:按项目整体录取
+USC: 不需要:按项目整体录取;GA需向所申项目咨询
+UNMC: 不需要:按项目整体录取(SOPHAS)
+TXST: 不需要:按项目整体录取(但MPH为纯网课,见先修列)</t>
+        </is>
+      </c>
       <c r="G99" s="21" t="inlineStr">
         <is>
           <t>部分明确可(ISU 国际 GA 需英语测试)</t>
@@ -7195,9 +7230,16 @@
       <c r="I99" s="21" t="n"/>
       <c r="J99" s="21" t="n"/>
       <c r="K99" s="21" t="n"/>
-      <c r="L99" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="L99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: https://publichealth.gsu.edu/academics-admissions/georgia-state-mph-program/mph-application-process/
+GaSou: https://www.georgiasouthern.edu/degrees/master-of-public-health
+CMU: https://www.cmich.edu/program/master-of-public-health
+ISU: https://www.isu.edu/mph/
+USM: https://www.usm.edu/graduate-programs/public-health.php
+USC: https://sc.edu/study/colleges_schools/public_health/apply/graduate_applicants/deadlines_and_degrees_offered/
+UNMC: https://www.unmc.edu/publichealth/academics/programs/masters/mph/mph-admissions.html
+TXST: https://www.gradcollege.txst.edu/programs/public-health.html</t>
         </is>
       </c>
     </row>
@@ -12229,9 +12271,16 @@
       <c r="I185" s="21" t="n"/>
       <c r="J185" s="21" t="n"/>
       <c r="K185" s="21" t="n"/>
-      <c r="L185" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="L185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: https://gradcollege.txst.edu/programs/sociology.html
+Mississippi State: https://www.catalog.msstate.edu/graduate/colleges-degree-programs/arts-sciences/sociology
+UGA: https://soci.franklin.uga.edu/how-apply
+Texas Tech: https://www.depts.ttu.edu/sasw/majors/sociology/soc-grad-program.php
+Illinois State: https://illinoisstate.edu/academics/sociology-masters
+U Alabama: ⚠️ 无社会学硕士页;社会学辅修 https://catalog.ua.edu/undergraduate/arts-sciences/gender-race-studies/sociology-minor/ ;相近项目 https://cj.ua.edu/graduate-program/
+South Dakota State: https://catalog.sdstate.edu/preview_program.php?catoid=56&amp;poid=14007
+U Montana: https://www.umt.edu/grad/explore/programs/sociology.php</t>
         </is>
       </c>
     </row>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -8653,19 +8653,60 @@
           <t>OSU GA 全额学费+津贴但比例未公布;USF fellowship 80% 州内学费;MIT DUSP ≥80% 学费+RA/TA</t>
         </is>
       </c>
-      <c r="F123" s="21" t="n"/>
+      <c r="F123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: ⚠️ 不需要:规划硕士按项目整体录取(官网未提导师联系)
+USF: ⚠️ 不需要:申请由招生办转公共事务学院统一审核
+Texas A&amp;M: ⚠️ 不需要:GradCAS 统一申请,按项目录取
+Temple: 不适用:项目暂停招生
+UNC: ⚠️ 不需要:按项目录取,资助随录取评定
+MIT: ⚠️ 不需要:按项目录取,资助随录取发放;部分学生另获教师 RA</t>
+        </is>
+      </c>
       <c r="G123" s="21" t="inlineStr">
         <is>
           <t>MIT 明文不看国籍</t>
         </is>
       </c>
       <c r="H123" s="21" t="n"/>
-      <c r="I123" s="21" t="n"/>
-      <c r="J123" s="21" t="n"/>
-      <c r="K123" s="21" t="n"/>
-      <c r="L123" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="I123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: ⚠️ 不需要(官网仅写 2023–24 周期不需要,当前周期未更新)
+USF: ⚠️ 必需(catalog:建议 V153/Q144);本科高年级 GPA≥3.25 可豁免(catalog 较旧,需确认)
+Texas A&amp;M: 不需要
+Temple: 不需要(可选提交)
+UNC: ⚠️ 不需要(第三方信息)
+MIT: 可选(MCP 不要求)</t>
+        </is>
+      </c>
+      <c r="J123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: ⚠️ 大概率否:仅要求"主要在美国以外受教育"的非母语者提交(TOEFL 100/IELTS 7.5),美本需确认是否算
+USF: 否(美国学士学位豁免)
+Texas A&amp;M: 否(美国认证院校学士即满足英语要求);⚠️ 当 TA 官网写需 TOEFL 口语 23
+Temple: 否(英语授课学士豁免)
+UNC: 否(美国认证大学学位可豁免,需上传成绩单)
+MIT: 否(5年内在美国英语大学读3–4年取得本科自动豁免;DUSP 不接受单独豁免申请)</t>
+        </is>
+      </c>
+      <c r="K123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: KnowltonGrad@osu.edu(Knowlton 研究生学生服务);⚠️ bullock.151@osu.edu(研究生项目协调员 Jon Bullock)
+USF: elinkous@usf.edu(MURP 项目主任 Dr. Evangeline Linkous);cas-spa@usf.edu(公共事务学院)
+Texas A&amp;M: urplgrad@tamu.edu(系研究生联系邮箱);ivis.garcia@tamu.edu(MUP 协调员)
+Temple: tylerart@temple.edu(Tyler 学院研究生招生)
+UNC: dcrp-admissions@unc.edu(DCRP 招生);awhittem@email.unc.edu(硕士项目及招生主任 Dr. Andrew Whittemore)
+MIT: duspapply@mit.edu(DUSP 招生)</t>
+        </is>
+      </c>
+      <c r="L123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: https://knowlton.osu.edu/mcrp-apply
+USF: https://www.usf.edu/arts-sciences/departments/public-affairs/murp/admissions.aspx
+Texas A&amp;M: https://www.arch.tamu.edu/academics/graduate-programs/landscape-architecture-urban-planning-graduate-programs/master-of-urban-planning/
+Temple: https://www.temple.edu/academics/degree-programs/city-regional-planning-ms/tyl-city-regional-planning-ms-admissions
+UNC: https://planning.unc.edu/academics/masters/
+MIT: https://oge.mit.edu/programs/urban-studies-and-planning/</t>
         </is>
       </c>
     </row>
@@ -9821,15 +9862,51 @@
           <t>TA/RA 含津贴+学费减免;竞争性</t>
         </is>
       </c>
-      <c r="F143" s="21" t="n"/>
-      <c r="G143" s="21" t="n"/>
+      <c r="F143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: ⚠️ 建议:官网未说明是否需联系导师;MS 每年秋季仅录 5–10 人,陈述中写匹配教授,可提前邮件联系
+UNCW: 建议:录取后按导师匹配制,面试后教师排序选学生;陈述须写感兴趣的教授/实验室
+ULL: ⚠️ 不需要:系里统一录取(研究生院+心理系双审),官网未要求联系导师
+NAU: 建议:官网建议申请前查看教师研究方向确认匹配,陈述中写意向教授
+Montclair: ⚠️ 不需要:按项目整体录取;论文方向可在陈述中提及意向教授</t>
+        </is>
+      </c>
+      <c r="G143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: 可以申请(终结型 MS,偏心理健康方向;MS 助教资助⚠️未确认)。先修:≥18学分心理/相关课(含普通心理、统计、实验设计与方法);GPA&gt;3.0 录取几率大;2封推荐信+CV+SOP
+UNCW: 可以申请(现为 M.S.;TA 名额有限,RA 依教师经费)。先修:≥21学分心理课平均B以上,须含统计与心理研究方法;3封推荐信(≥1封来自大学教师),陈述500–800词;申请费$75
+ULL: 可以申请(系里每年给新生5–6个GA,多数学生在校内其他部门拿GA)。先修:本科GPA≥3.0;18学分心理课(含普通心理及统计/研究设计)+1门本科统计;不要求心理专业;3封推荐信+CV+陈述;国际生申请费$30
+NAU: 可以申请(多数学生通过GA或学费减免获资助)。先修:GPA≥3.0;≥18学分心理课(含心理学导论、统计、研究方法);3封推荐信+CV+陈述+问答;36学分,论文/非论文可选
+Montclair: 可以申请(⚠️ 资助:校研究生中心统一管理 GA,非项目保证)。先修:心理学学士或≥12学分心理课(须含统计和实验课,导论课不计入);MA Psychological Sciences;申请费$60</t>
+        </is>
+      </c>
       <c r="H143" s="21" t="n"/>
-      <c r="I143" s="21" t="n"/>
+      <c r="I143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: ⚠️ 官网 MS 页面未提及 GRE(研究生院称"如系里要求"),建议邮件确认
+UNCW: 不需要(心理系目前不使用 GRE)
+ULL: ⚠️ 官网未列为要求;系里明确不以 GRE 决定 GA(第三方称需 GRE,可能过时)
+NAU: ⚠️ 不明确:现行页面未列,旧目录曾要求;FAQ称有竞争力申请者 V+Q≥300,建议邮件确认
+Montclair: 必需,但本科总 GPA≥3.3 可豁免</t>
+        </is>
+      </c>
       <c r="J143" s="21" t="n"/>
-      <c r="K143" s="21" t="n"/>
-      <c r="L143" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="K143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: taknaus@uno.edu(Dr. Tracey Knaus,心理学 MS 联系人)
+UNCW: psygradprogram@uncw.edu(研究生项目协调员 Dr. Tom Cariveau);gradschool@uncw.edu(研究生院)
+ULL: amy.brown@louisiana.edu(研究生项目协调员 Amy Brown);gradschool@louisiana.edu(研究生院)
+NAU: PSYInfoCenter@nau.edu(心理系研究生协调员信箱);⚠️ Eric.Cerino@nau.edu(MA 协调员,来源页面归属存疑)
+Montclair: psycgrad@montclair.edu(心理系研究生项目);pardoj@montclair.edu(项目协调员 Dr. Jennifer Pardo)</t>
+        </is>
+      </c>
+      <c r="L143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: https://www.uno.edu/academics/cos/psychology/graduate/application-process
+UNCW: https://www.uncw.edu/academics/majors-programs/cse/psychology-ms/
+ULL: https://psychology.louisiana.edu/programs/masters-program
+NAU: https://nau.edu/psychological-sciences/ma-psychological-sciences/
+Montclair: https://www.montclair.edu/academics/programs/ma-psychological-sciences</t>
         </is>
       </c>
     </row>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -11990,19 +11990,74 @@
           <t>各校部分学费奖学金或有限 GRA;Duke 部分 10-50%</t>
         </is>
       </c>
-      <c r="F179" s="21" t="n"/>
-      <c r="G179" s="21" t="inlineStr">
-        <is>
-          <t>Duke 奖学金可</t>
-        </is>
-      </c>
-      <c r="H179" s="21" t="n"/>
-      <c r="I179" s="21" t="n"/>
-      <c r="J179" s="21" t="n"/>
-      <c r="K179" s="21" t="n"/>
-      <c r="L179" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="F179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: 不需要:MS 按项目整体录取(SOPHAS 申请),个人陈述可写感兴趣的教授
+KUMC: 不需要:按项目整体录取;12/1 前申请可参评资助,GRA 入学后可联系
+UNMC: 不需要:SOPHAS 整体录取,无需提前联系导师
+Louisville: 不需要:按项目整体录取;先修/补课问题可联系项目协调员
+Kentucky: 不需要:SOPHAS 初审后再交 UK 补充申请,整体录取
+Duke: 不需要:按项目整体录取,申请即自动参评奖学金,助研入学后竞争</t>
+        </is>
+      </c>
+      <c r="G179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: 可以申请。先修:2 学期(6 学分)大学微积分(AP 可抵);生物背景不要求但鼓励;需学士学位+3 封推荐信
+KUMC: 可以申请。先修:学士 GPA≥3.0;Calculus I–III 均 B 以上;线代/微分方程/数值分析至少一门;一门编程课;研究经历推荐非必需;入学需背景审查
+UNMC: 可以申请。先修:数学/统计/CS 或相关专业学士,GPA≥3.0;微积分、多元微积分、线代、统计入门均 B 以上;缺先修可有条件录取
+Louisville: 可以申请。先修:生统/统计/数学或相关专业,微积分至多元微积分+统计;GPA≥3.0 无条件录取,低于可有条件录取;缺微积分可夏季补修(需 B- 以上)
+Kentucky: 可以申请。先修:Calculus I、II + 一门入门统计/生统(可在入学前夏季补修);GPA 最低 2.75,3.0 优先;3 封推荐信
+Duke: 可以申请(国际生可获部分奖学金,约 10–50% 学费,申请即参评)。先修:数学至多元微积分,强烈建议线代;生物课程加分非必需</t>
+        </is>
+      </c>
+      <c r="H179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: 滚动录取,优先截止 1/15(国内外同),建议 2027/1/15 前提交
+KUMC: 资助优先 2026/12/1;最终 2027/2/1(⚠️ 项目概览页/手册写 3/1,以招生页为准)
+UNMC: 国际生 2027/2/1;国内 2027/6/1(按官网现行日期)
+Louisville: ⚠️ 秋季 6/30(目录,全体申请人);第三方称国际生 5/1,建议 2027/3 前提交并邮件确认
+Kentucky: 国际生 4/1–4/15;国内 6/1(项目页另写 7/24)(按2026周期,2027待公布)
+Duke: 1/5(推荐信 1/12)(按2026周期;⚠️ 第三方显示 2027/1/5)</t>
+        </is>
+      </c>
+      <c r="I179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: 可选(GRE 数学≥70 百分位可作为准备充分的证明)
+KUMC: ⚠️ 必需(KU 目录列为必交,ETS 代码 6895;第三方称推荐非必需,建议确认)
+UNMC: 可选;GPA&lt;3.0 或先修课有 C 者必需
+Louisville: ⚠️ 不明确:官方目录未提及 GRE,第三方称必需,建议邮件确认
+Kentucky: 不需要
+Duke: 可选,不提交不扣分</t>
+        </is>
+      </c>
+      <c r="J179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: 否(美国认证院校学位豁免);否则 TOEFL ≥80(2026/1/21 后新版≥4.0)/IELTS ≥6.5
+KUMC: ⚠️ 是:母语非英语者需 2 年内 TOEFL/IELTS,未见美国学位豁免条款(第三方称 TOEFL 80/IELTS 6.5),建议确认
+UNMC: ⚠️ 不明确:MS 页未写;研究生院一般要求 TOEFL 80/IELTS 6.5/DET 120,美国学位是否豁免待确认
+Louisville: ⚠️ 否(可凭英语授课院校学位并提供正式证明豁免);否则 TOEFL ≥79/IELTS ≥6.5/DET ≥105
+Kentucky: 否(美国认证大学学位豁免);否则 TOEFL ≥79/IELTS ≥6.5/DET ≥115
+Duke: ⚠️ 可能豁免:研究生院规定在英语国家英语授课院校全日制学习≥2 年可豁免(美本符合),但项目页未写豁免;否则 TOEFL ≥90/IELTS ≥7.0/DET ≥125;入学后非母语者可能需英语测评</t>
+        </is>
+      </c>
+      <c r="K179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: PHadmissions@pitt.edu(公卫学院招生);⚠️ anb61@pitt.edu(Andriy Bandos,目录所列系联系人,职务未核实)
+KUMC: stats_education@kumc.edu(系研究生教育邮箱);jwick@kumc.edu(Jo Wick,Director of Graduate Education)
+UNMC: ⚠️ coph@unmc.edu(公卫学院通用邮箱,来源较旧);项目主任 Chris Wichman 电话 402-559-8407
+Louisville: lisa.bell@louisville.edu(项目协调员);gradadm@louisville.edu(研究生院招生)
+Kentucky: ukcph@uky.edu(公卫学院招生);DGS Dr. Amanda Ellis 电话 859-218-2080
+Duke: biostatsadmissions@dm.duke.edu(Master of Biostatistics 招生)</t>
+        </is>
+      </c>
+      <c r="L179" s="30" t="inlineStr">
+        <is>
+          <t>Pitt: https://www.publichealth.pitt.edu/biostatistics/admissions
+KUMC: https://www.kumc.edu/school-of-medicine/academics/departments/biostatistics-and-data-science/academics/master-of-science-in-biostatistics/admissions.html
+UNMC: https://www.unmc.edu/publichealth/admissions/masterofscience/msbiostatistics.html
+Louisville: https://publichealth.louisville.edu/academics-and-programs/graduate-programs/master-science-biostatistics
+Kentucky: https://cph.uky.edu/programs/master-science-biostatistics/admissions
+Duke: https://biostat.duke.edu/education-and-training/master-biostatistics/master-biostatistics-admissions</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15662,21 @@
           <t>各校'有限'assistantship 或仅部分奖学金;UTK GTA 仅一年后;TAMU'通常不给入学硕士'</t>
         </is>
       </c>
-      <c r="F240" s="22" t="n"/>
+      <c r="F240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: 不需要:按项目整体录取(SOPHAS),个人陈述写感兴趣方向即可
+UT Knoxville: 不需要:按项目整体录取;助教岗位需每年另行申请,可在陈述中提感兴趣的教授
+U Memphis: 不需要:按项目整体录取(SOPHAS),个人陈述写感兴趣方向即可
+UNCG: 不需要:按项目整体录取;GA由研究生项目副主任邀请合格申请者申请
+UW Global Health: 不需要:按项目整体录取;目的陈述需写清研究/实践方向及与项目的契合度
+East Texas A&amp;M: 不需要:按项目整体录取;录取后再申请奖学金/助教
+Mississippi State: ⚠️ 不需要:MPH按项目整体录取(未找到项目页,通识判断)
+UAB: 不需要:按项目整体录取(SOPHAS+UAB研究生院补充申请)
+Michigan State: 不需要:按项目整体录取(SOPHAS,滚动录取)
+Texas A&amp;M: 不需要:按项目整体录取(SOPHAS)
+Brown: 不需要:按项目整体录取(SOPHAS);Health Equity Scholars含有偿RA,无需提前联系导师</t>
+        </is>
+      </c>
       <c r="G240" s="22" t="inlineStr">
         <is>
           <t>UTK/UAB 明文国际生可(有条件)</t>
@@ -15617,9 +15686,19 @@
       <c r="I240" s="22" t="n"/>
       <c r="J240" s="22" t="n"/>
       <c r="K240" s="22" t="n"/>
-      <c r="L240" s="22" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="L240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: https://cph.uky.edu/programs/master-public-health/apply
+UT Knoxville: https://cehhs.utk.edu/publichealth/degree-programs/mph/
+U Memphis: https://www.memphis.edu/publichealth/apply/mph.php
+UNCG: https://phe.uncg.edu/graduate/master-of-public-health/admissions-requirements/
+UW Global Health: https://globalhealth.uw.edu/academic-programs/master-public-health/admissions-eligibility
+East Texas A&amp;M: https://www.etamu.edu/programs/public-health-mph/
+Mississippi State: https://www.bchnhp.msstate.edu/students/public-health-master.php
+UAB: https://www.uab.edu/soph/home/apply/graduate
+Michigan State: https://mph.msu.edu/apply-now/information-for-applicants
+Texas A&amp;M: https://public-health.tamu.edu/degrees/mph/index.html
+Brown: https://sph.brown.edu/admission-aid/application-requirements</t>
         </is>
       </c>
     </row>
@@ -16725,19 +16804,43 @@
           <t>MCH Scholars 津贴 $21,000(USF)等;学费不直接覆盖</t>
         </is>
       </c>
-      <c r="F259" s="22" t="n"/>
+      <c r="F259" s="31" t="inlineStr">
+        <is>
+          <t>USF: 不需要:MPH 按项目整体录取(SOPHAS),个人陈述可写 MCH 兴趣
+UAB: 不需要:MPH 按项目整体录取(SOPHAS+研究生院补充申请)
+SLU: 不需要:滚动整体录取,MCH 为可加修证书
+U Minnesota: 不需要:MPH 按项目整体录取(SOPHAS)</t>
+        </is>
+      </c>
       <c r="G259" s="22" t="inlineStr">
         <is>
           <t>❌ USF/UAB 明文仅美籍/PR(HRSA)</t>
         </is>
       </c>
-      <c r="H259" s="22" t="n"/>
-      <c r="I259" s="22" t="n"/>
+      <c r="H259" s="31" t="inlineStr">
+        <is>
+          <t>USF: 秋季优先截止 2027/5/1
+UAB: 秋季国际生 2027/4/1;国内 2027/7/1
+SLU: 滚动录取;秋季国际生 2027/6/1(春季 12/1),建议早交
+U Minnesota: 优先(奖学金)2026/12/1;最终 2027/5/15</t>
+        </is>
+      </c>
+      <c r="I259" s="31" t="inlineStr">
+        <is>
+          <t>USF: 可选(ETS 代码 4224)
+UAB: 不需要(推荐但非必需,仅部分 DrPH 必需)
+SLU: 不需要
+U Minnesota: 不需要(全院学位均不要求)</t>
+        </is>
+      </c>
       <c r="J259" s="22" t="n"/>
       <c r="K259" s="22" t="n"/>
-      <c r="L259" s="22" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="L259" s="31" t="inlineStr">
+        <is>
+          <t>USF: https://health.usf.edu/publichealth/apply/masters/mph-mch
+UAB: https://www.uab.edu/soph/home/graduate/programs/mph-mch
+SLU: https://www.slu.edu/public-health-social-justice/programs/public-health/public-health-mph.php
+U Minnesota: https://www.sph.umn.edu/academics/graduate/mph/maternal-child-health/</t>
         </is>
       </c>
     </row>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -1340,7 +1340,11 @@
           <t>'近年来能为几乎所有想要 assistantship 的硕士生提供';包=全额学费+月津贴+医保</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要:未查到导师制要求,按项目整体录取;个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
       <c r="G2" s="23" t="inlineStr">
         <is>
           <t>可以申请(⚠️ 官网未明确国际生资助限制)。先修:学士学位,本科最后2年(约60学分)GPA≥3.0。⚠️ 现行目录中 Applied Family Science 可能已并入 HDFS MS(Family and Community Services 等方向),建议确认</t>
@@ -1351,7 +1355,11 @@
           <t>⚠️ 研究生院国际生秋季截止 1/8(即 2027/1/8),项目可设更早截止;同系 Prevention Science 方向优先截止 12/1,建议 2026/12/1 前提交以争取 assistantship(按2026周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n"/>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>⚠️ 不需要(同系 CFT 目录明文不需 GRE;本方向官网未查到)</t>
+        </is>
+      </c>
       <c r="J2" s="24" t="inlineStr">
         <is>
           <t>否(美国学位豁免,研究生院手册明文);⚠️ 当 GTA 可能另需口语英语测试</t>
@@ -1419,7 +1427,11 @@
           <t>⚠️ 不明确:USU 研究生院通常豁免美国学位,建议确认;当 TA 可能需国际助教口语评估</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n"/>
+      <c r="K3" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 研究生项目协调员 RaNae Wamsley(邮箱官网未查到,建议在系网站确认)</t>
+        </is>
+      </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
           <t>https://cehhs.usu.edu/hdfs/graduate/financial-assistance</t>
@@ -1447,9 +1459,9 @@
           <t>MS HDFS</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   </t>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 12/1 前申请可优先考虑 assistantship 与奖学金;ISU 半时 assistantship 通常含学费奖学金+月津贴+医保补贴;具体金额官网未查到,建议邮件确认</t>
         </is>
       </c>
       <c r="F4" s="23" t="inlineStr">
@@ -1539,7 +1551,11 @@
           <t>否(大概率豁免):UMN研究生院规定近2年内在美国完成≥16学期学分(非ESL)即满足英语要求,美本应届/近两年毕业符合;⚠️ 系内未见更严规定,建议确认。需提交时为 TOEFL 79/IELTS 6.5(⚠️第三方)</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n"/>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>geog-dgs@umn.edu(研究生项目主任DGS,来自校目录);⚠️ 研究生项目协调员 Sara Braun 电话 612-625-0864,邮箱未查到</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
           <t>https://cla.umn.edu/geography/graduate/funding</t>
@@ -1659,7 +1675,11 @@
           <t>否(美国学位豁免):在美国认证院校在校完成(非网课)的学士学位可满足KU英语要求;但不适用于GTA,担任GTA须另符合Kansas Board of Regents口语英语要求</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n"/>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>graduateadm@ku.edu(KU研究生招生办,通用);⚠️ 地理系研究生主任 David A. Rahn 邮箱未查到,见 geog.ku.edu/people</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>https://geog.ku.edu/admission</t>
@@ -1759,12 +1779,16 @@
           <t>不需要:按项目录取;GA分配至教师研究项目,需另交GA申请表,陈述可写感兴趣的研究方向/教授</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n"/>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生能否获GA官网未明确)。先修:欢迎各专业背景,无必修先修课;需区域认证学士学位、说明职业目标的个人陈述;推荐信强烈建议(至少1封来自大学教师);⚠️ 最低GPA未查到</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>秋季:国际生 2027/2/15;美国本土 2027/7/1(官网常规日期,逾期顺延下学期);⚠️ GA申请截止未查到,建议2月前一并提交</t>
+        </is>
+      </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
           <t>可选(仅在能证明学术准备时提交)</t>
@@ -1832,7 +1856,11 @@
           <t>可选(GPA 2.5-3.0或非相关专业者可提交加分)</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,需申请):持美国区域认证院校学士可豁免,但须在递交申请约72小时后提交 Other Exemption Form;⚠️ TA口语要求未查到</t>
+        </is>
+      </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
           <t>SGSUP.gradprograms@asu.edu(SGSUP研究生项目办公室);mfquiroz@asu.edu(研究生顾问 Fernanda Quiroz)</t>
@@ -2061,9 +2089,9 @@
           <t>必须:申请前须联系并获得一位教师同意担任导师,否则不予考虑;个人陈述末尾需列潜在导师</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 官网未说明国籍限制;thesis MS保证≥2年assistantship含学费减免)。先修:须获至少一位教师支持;⚠️ 官网未查到具体专业/先修课/最低GPA要求</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -2081,7 +2109,11 @@
           <t>否(美国学位豁免):UGA研究生院规定美国认证院校学位持有者通常无需TOEFL/IELTS(个别系可另要求);担任TA须按UGA TA政策另证英语能力</t>
         </is>
       </c>
-      <c r="K14" s="4" t="n"/>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到研究生协调员邮箱,建议邮件确认(研究生主任 John Wares,见 ecology.uga.edu/directory)</t>
+        </is>
+      </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>https://ecology.uga.edu/academics/graduate-school/how-to-apply/faqs/</t>
@@ -2119,12 +2151,16 @@
           <t>⚠️ 不需要(推断):terminal MA按项目整体录取,官网未见套磁要求;可先邮件 jmthoma4@olemiss.edu 了解方向</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确;联系 jmthoma4@olemiss.edu</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>可以申请(系明文保证为录取学生提供资助)。⚠️ 先修/最低GPA官网未查到具体条款,建议邮件确认;研究生院一般要求本科学位</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>⚠️ 研究生院默认秋季 4/1(春季 10/1),项目可另设截止日;社会学MA具体日期官网未查到,建议邮件确认并尽早(资助考虑)提交</t>
+        </is>
+      </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
           <t>不需要(研究生院页面将 Sociology MA 列为不要求 GRE/GMAT 的项目,页面表述略含糊)</t>
@@ -2595,7 +2631,11 @@
           <t>否(美国学位豁免:研究生院对5年内获美国学位者豁免);但当TA需TOEFL口语≥24(2026/1/21后新版口语≥5.0)或通过校内口语评估(EPI)</t>
         </is>
       </c>
-      <c r="K22" s="12" t="n"/>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到具体邮箱,建议通过 https://www.hk.illinois.edu/admissions/graduate-admissions/ 联系系研究生办公室</t>
+        </is>
+      </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
           <t>https://hk.illinois.edu/admissions/graduate-admissions/hk-graduate-admissions-faqs/</t>
@@ -2822,9 +2862,9 @@
           <t>不需要:MPH按项目整体录取(经SOPHAS申请),个人陈述可写感兴趣的方向/教授</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G26" s="27" t="inlineStr">
+        <is>
+          <t>可以申请(原备注:可)。经SOPHAS申请;⚠️ 官网未查到指定先修课或最低GPA,一般各本科专业均可申请</t>
         </is>
       </c>
       <c r="H26" s="27" t="inlineStr">
@@ -2884,7 +2924,11 @@
           <t>必须:论文方向(含Behavioral Science &amp; Community Health)须匹配教师导师,官网强烈建议申请前联系;未匹配可转非论文方向但仍需选导师</t>
         </is>
       </c>
-      <c r="G27" s="12" t="n"/>
+      <c r="G27" s="27" t="inlineStr">
+        <is>
+          <t>可以申请(TA/RA为主,全额TA含学费减免+津贴)。先修:研究生院最低GPA 3.0(低于不审);⚠️ 未查到指定本科专业/先修课;论文方向强考虑者2–3月面试</t>
+        </is>
+      </c>
       <c r="H27" s="27" t="inlineStr">
         <is>
           <t>2026/12/1(仅秋季入学,不接受春/夏入学)</t>
@@ -2900,7 +2944,11 @@
           <t>否(美国认证院校学士/硕士学位豁免);否则 TOEFL ≥80 / IELTS ≥6.5。⚠️ 当TA可能需ITA口语测试,未核实</t>
         </is>
       </c>
-      <c r="K27" s="12" t="n"/>
+      <c r="K27" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到邮箱,建议通过 health.utah.edu/health-kinesiology/graduate-programs 联系 Graduate Program Manager</t>
+        </is>
+      </c>
       <c r="L27" s="15" t="inlineStr">
         <is>
           <t>https://health.utah.edu/health-kinesiology/graduate-programs</t>
@@ -3000,9 +3048,9 @@
           <t>⚠️ 建议:资助为TA/RA,建议提前联系方向匹配的教师(官网未明确要求)</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>✅ 国际生可持(教学需英语)</t>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获资助;当TA需通过ITA口语面试)。先修:⚠️ 官网未查到指定本科专业/先修课/最低GPA;方向含GIS、遥感、气候、自然资源管理等</t>
         </is>
       </c>
       <c r="H29" s="26" t="inlineStr">
@@ -3062,9 +3110,9 @@
           <t>⚠️ 建议:可先联系研究生主任 Dr. Tom Smucker 了解方向匹配;官网未要求套磁</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>✅ 明文'国内外申请者按 merit 同等考虑'</t>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(明文'国内外申请者按 merit 同等考虑')。先修:⚠️ 未查到指定专业/先修课;部分项目最低GPA 3.0;需1–2页兴趣陈述、简历、3封推荐信</t>
         </is>
       </c>
       <c r="H30" s="26" t="inlineStr">
@@ -3082,7 +3130,11 @@
           <t>⚠️ 不明确:官网要求非英语母语者提交 TOEFL/IELTS,未见美国学位豁免说明(⚠️ 第三方:TOEFL 80 / IELTS 6.5 / Duolingo 115),建议邮件确认</t>
         </is>
       </c>
-      <c r="K30" s="12" t="n"/>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到邮箱,建议联系研究生主任 Dr. Tom Smucker(邮箱需在系网站确认)</t>
+        </is>
+      </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
           <t>https://www.ohio.edu/cas/geography/graduate/financial-aid</t>
@@ -3120,9 +3172,9 @@
           <t>不需要:国内外申请者统一考虑多年资助包;⚠️ 个人陈述写明方向/教授,建议提前联系潜在导师</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(明文国内外申请者均考虑多年保障资助,MS通常2年)。先修:⚠️ 论文型MS未查到指定先修;主攻地图/GIS应申 Cartography &amp; GIS MS-Thesis;需个人陈述+3封推荐信</t>
         </is>
       </c>
       <c r="H31" s="26" t="inlineStr">
@@ -3182,9 +3234,9 @@
           <t>强烈建议:官网称联系潜在导师是关键步骤,录取看 merit 与教师研究匹配</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(原备注:未说明)。先修:⚠️ 未查到指定专业/先修课/最低GPA;需个人陈述(写明意向教师)、个人经历陈述(≤1页)、3封推荐信</t>
         </is>
       </c>
       <c r="H32" s="26" t="inlineStr">
@@ -3197,8 +3249,16 @@
           <t>不需要(研究生院页面;⚠️ Peterson's 仍列GRE,可能过时)</t>
         </is>
       </c>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
+      <c r="J32" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生需 TOEFL/IELTS,未查到美国学位豁免条款,建议向研究生院确认</t>
+        </is>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到邮箱;旧页列招生主任 Clark Gray、研究生协调员 Nell Phillips,系电话 919-962-8902</t>
+        </is>
+      </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
           <t>https://geography.unc.edu/wp-content/uploads/sites/140/2026/05/GEOGGraduateHandbook.pdf</t>
@@ -3251,8 +3311,16 @@
           <t>⚠️ 不需要(官网未列GRE;Peterson's 称需GRE≥297,可能过时)</t>
         </is>
       </c>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:官网写英语非母语者 TOEFL ≥550(纸考)/213(机考),未查到美国学位豁免条款,建议确认</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到邮箱;项目负责人 Paul Loikith(研究生项目主任),邮箱需在系网站确认</t>
+        </is>
+      </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
           <t>https://www.pdx.edu/academics/programs/graduate/geography</t>
@@ -3543,8 +3611,16 @@
           <t>可以申请(thesis轨通常首年获TA,non-thesis无资助)。本科学士学位(区域认证);研究生院常规录取GPA≥3.0(限制性录取2.75);个人陈述300–400字,说明对行为生物学基础的兴趣;⚠️ 官网未列具体先修课</t>
         </is>
       </c>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 项目MA截止日官网未查到;研究生院硕士通用:国内秋季 7/1,国际生秋季 6/1(按2026周期,2027待公布);同系PhD为12/1,资助考虑建议12月前提交</t>
+        </is>
+      </c>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院本身不要求GRE,部分硕士项目要求;MA项目政策未查到,建议邮件确认(GRE 5年有效)</t>
+        </is>
+      </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
           <t>否(美国学位豁免):两年内从美国院校毕业可自动豁免;否则需TOEFL≥79;⚠️ 部分系保留要求EAP考试的权利</t>
@@ -3597,7 +3673,11 @@
           <t>可以申请(多数学生通过RA获资助)。接受多元本科背景,视研究方向可能需补先修课;最后60学分GPA≥3.2;申请费$55</t>
         </is>
       </c>
-      <c r="H39" s="12" t="n"/>
+      <c r="H39" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 第三方(Petersons)显示秋季 6/15、滚动审理;官网未查到明确截止日,资助随导师经费,建议尽早(12月–1月前)联系导师并提交</t>
+        </is>
+      </c>
       <c r="I39" s="26" t="inlineStr">
         <is>
           <t>⚠️ 不明确:官网项目页未提GRE,Petersons称需GRE,建议邮件确认</t>
@@ -3903,7 +3983,11 @@
           <t>可以申请(多数学生由导师课题经费资助,如$21,000/年+学费减免)。Forest Resources:林学/林产品或相关理学士优先但非必须;WFB:野生动物/生态/生物或相关学士;需2封推荐信</t>
         </is>
       </c>
-      <c r="H44" s="12" t="n"/>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>WFB:国内秋季 6/30,国际生建议秋季 4/15(按2024-25手册,2027待公布);⚠️ Forest Resources专门截止未查到,实际取决于导师招生时间,建议尽早</t>
+        </is>
+      </c>
       <c r="I44" s="26" t="inlineStr">
         <is>
           <t>不需要(申请不要求,但个别导师可能要求)</t>
@@ -3962,7 +4046,11 @@
           <t>可以申请(国际生可获YSE奖学金,约80%硕士生获资助,仅抵学费)。无硬性先修课和最低GPA;强烈建议修过生态学/生态系统、自然科学、社会科学、微观经济学和统计学;MEM入学时需具备上述基础(统计可修学院提供的非学分预备课)。</t>
         </is>
       </c>
-      <c r="H45" s="12" t="n"/>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 官网暂未查到2027秋季日期;上一周期为 2025/9/1 开放、2025/12/1 截止(按2026周期,2027待公布,预计约 2026/12/1);仅秋季入学,建议12月中前寄齐所有材料</t>
+        </is>
+      </c>
       <c r="I45" s="26" t="inlineStr">
         <is>
           <t>可选(GRE/GMAT/LSAT 均可选)</t>
@@ -4030,7 +4118,11 @@
           <t>⚠️ 不需要:系页面未列GRE(在线PSM明确不需要),论文型建议邮件确认</t>
         </is>
       </c>
-      <c r="J46" s="12" t="n"/>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ 否(美国学位豁免,来源为系页面及第三方,MSU官网原文未查到);否则 TOEFL iBT ≥80 / IELTS ≥6.5 / Duolingo ≥120;⚠️ 当GTA是否需口语测试未查到</t>
+        </is>
+      </c>
       <c r="K46" s="26" t="inlineStr">
         <is>
           <t>lresinfo@montana.edu(LRES系研究生项目);gradschool@montana.edu(MSU研究生院)</t>
@@ -4197,9 +4289,9 @@
           <t>不需要:按项目整体录取(SOPHAS),GA多在入学后第一年内自行找到</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>可以申请(想要GA的硕士生几乎都能在首年找到,享州内学费率+stipend)。需简历、个人陈述、全部成绩单、≥3封推荐信;⚠️ 先修课官网未查到(见系研究生手册)</t>
         </is>
       </c>
       <c r="H49" s="26" t="inlineStr">
@@ -4217,7 +4309,11 @@
           <t>否(美国学位豁免,⚠️ 依据MPH页面):有美国院校学位可豁免;否则TOEFL≥90/IELTS≥7.0</t>
         </is>
       </c>
-      <c r="K49" s="12" t="n"/>
+      <c r="K49" s="26" t="inlineStr">
+        <is>
+          <t>⚠️ MS项目主任邮箱未查到;torresme@mailbox.sc.edu(MPH项目主任,可代转),建议邮件确认</t>
+        </is>
+      </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
           <t>https://sc.edu/study/colleges_schools/public_health/departments/epi-bios/students/prospective/funding/index.php</t>
@@ -4317,12 +4413,16 @@
           <t>⚠️ 官网未明确要求;建议申请前联系研究方向匹配的教师及 Graduate Chair(GA 多与教师项目相关)</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
-        <is>
-          <t>✅ 国际 TA 需参加 ITA Institute(隐含可持)</t>
-        </is>
-      </c>
-      <c r="H51" s="21" t="n"/>
+      <c r="G51" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获GA,担任TA需参加 ITA Institute)。先修:学士学位,HDFS/相关背景;⚠️ 具体先修课与最低GPA官网未查到。材料:成绩单、简历、职业目标陈述、3封推荐信;论文/非论文可选</t>
+        </is>
+      </c>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 统一截止日未查到;Child Development/ECE 方向:秋季 4/15(春季 10/15);MFT 方向 2026/12/1。建议向 Graduate Chair 确认所选方向</t>
+        </is>
+      </c>
       <c r="I51" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:系官网未提 GRE;Peterson's(第三方,可能过时)列为必需,建议确认</t>
@@ -4395,7 +4495,11 @@
           <t>否(美国学位豁免;UGA 研究生院2025年3月修订后仍保留)。担任TA需另证英语能力</t>
         </is>
       </c>
-      <c r="K52" s="21" t="n"/>
+      <c r="K52" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 项目协调员邮箱官网未查到;tfutris@uga.edu(Ted Futris,HDFS 教师,职务未确认),建议邮件确认</t>
+        </is>
+      </c>
       <c r="L52" s="21" t="inlineStr">
         <is>
           <t>https://www.fcs.uga.edu/hdfs/graduate-financial-aid</t>
@@ -4572,7 +4676,11 @@
           <t>⚠️ 不明确:系FAQ称不设最低GRE,但同页称校内MS申请包含GRE,建议向协调员确认</t>
         </is>
       </c>
-      <c r="J55" s="21" t="n"/>
+      <c r="J55" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免,TTU 研究生院 OP 64.01 明文)。⚠️ TA口语要求未查到</t>
+        </is>
+      </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
           <t>jeremiah.ramirez@ttu.edu(Jeremiah Ramirez,HDFS 研究生项目协调员);Ali.J.Luempert@ttu.edu(研究生项目副主任)</t>
@@ -4610,7 +4718,11 @@
           <t>'系 assistantship 竞争性可申';2-1 优先</t>
         </is>
       </c>
-      <c r="F56" s="21" t="n"/>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到明确要求;建议联系研究方向匹配的教师以争取 assistantship</t>
+        </is>
+      </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
           <t>可以申请(⚠️ 国际生资助资格未明确;2/1优先截止者获 assistantship 考虑)。先修:⚠️ 本科后60学分GPA≥3.0(第三方);材料:3封推荐信、目的陈述、简历</t>
@@ -4621,7 +4733,11 @@
           <t>资助优先 2027/2/1;最终 2027/3/15(按往年周期,2027待公布)</t>
         </is>
       </c>
-      <c r="I56" s="21" t="n"/>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到:第三方列为必需,UF多数院系已免GRE,建议确认</t>
+        </is>
+      </c>
       <c r="J56" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:UF称美国学位可由院系酌情豁免;否则 IELTS ≥6,TOEFL ≥77/80(来源不一),建议向协调员确认</t>
@@ -4937,7 +5053,11 @@
           <t>⚠️ 不明确:HDFS 要求非母语者 TOEFL iBT ≥100 或 IELTS ≥7.0;研究生院仅对英语为主要语言国家的学位授权豁免,须由项目负责人正式申请,美国学位能否豁免需邮件确认</t>
         </is>
       </c>
-      <c r="K61" s="21" t="n"/>
+      <c r="K61" s="30" t="inlineStr">
+        <is>
+          <t>hdfs-dept@udel.edu(HDFS 系办公室;⚠️ 未查到研究生协调员个人邮箱)</t>
+        </is>
+      </c>
       <c r="L61" s="21" t="inlineStr">
         <is>
           <t>https://www.hdfs.udel.edu/graduate-assistantship-opportunities/</t>
@@ -5047,8 +5167,16 @@
           <t>⚠️ 秋季优先 2026/12/1;秋季最终 2026/12/15(系页面较旧,2027待确认)</t>
         </is>
       </c>
-      <c r="I63" s="21" t="n"/>
-      <c r="J63" s="21" t="n"/>
+      <c r="I63" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到该方向的 GRE 要求(仅 MFT 方向写 GRE 优先但不强制),建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J63" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:catalog 要求非母语者 TOEFL iBT ≥79;美国学位能否豁免官网未查到,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K63" s="30" t="inlineStr">
         <is>
           <t>brandt.gardner@okstate.edu(HDFS 项目协调员 Dr. Brandt Gardner,⚠️ 需核实是否仍在任)</t>
@@ -5091,9 +5219,9 @@
           <t>不需要:按项目整体录取(SOPHAS),个人陈述可写感兴趣的HPM教授;MS偏研究,可选择性提前联系项目主任了解匹配度</t>
         </is>
       </c>
-      <c r="G64" s="21" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="G64" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(SPHHS所有研究生项目录取者均有资格获校内assistantship,含stipend+学费及健康费减免)。先修:⚠️ 官网未查到具体先修课/最低GPA,建议邮件确认;仅秋季入学,SOPHAS+UMass补充申请(Slate)两步</t>
         </is>
       </c>
       <c r="H64" s="30" t="inlineStr">
@@ -5153,12 +5281,16 @@
           <t>不需要:MPH按项目整体录取,无需套磁;TA/RA优先给博士生,可在录取后联系系里/教授询问岗位</t>
         </is>
       </c>
-      <c r="G65" s="21" t="inlineStr">
-        <is>
-          <t>可(无全额保证)</t>
-        </is>
-      </c>
-      <c r="H65" s="21" t="n"/>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>可以申请,但资助无全额保证(TA/RA优先博士生,其次硕士)。先修:学士学位;直录通道(仅限UA/ASU/NAU本科)要求GPA≥3.0及代数/预科微积分/微积分B以上,常规申请⚠️ 官网未查到具体先修课/最低GPA。SOPHAS+GradApp($90)两步,HSA方向在GradApp中选择</t>
+        </is>
+      </c>
+      <c r="H65" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到2027周期日期;第三方显示秋季截止 2027/1/15,建议邮件确认</t>
+        </is>
+      </c>
       <c r="I65" s="30" t="inlineStr">
         <is>
           <t>不需要(官网:GRE仅PhD Epidemiology、MS/PhD Biostatistics需要;MPH已取消GRE/MCAT要求)</t>
@@ -5211,19 +5343,31 @@
           <t>不需要:系里整体审核(holistic review)录取;个人陈述可提感兴趣的教授/研究方向</t>
         </is>
       </c>
-      <c r="G66" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未限制</t>
-        </is>
-      </c>
-      <c r="H66" s="21" t="n"/>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(未限制本科专业)。先修:本科最后60学分GPA ≥3.2;需简历/CV+2封推荐信(优先教授推荐);⚠️ 未查到必修先修课</t>
+        </is>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>滚动录取(仅秋/春入学),秋季优先处理日 2027/8/1,入学前≥3个月提交者优先;⚠️ GTA申请时间未查到,国际生建议 2027 年初前提交</t>
+        </is>
+      </c>
       <c r="I66" s="30" t="inlineStr">
         <is>
           <t>⚠️ 官网未提及;第三方(IDP)称最后60学分GPA&lt;3.5时需GRE,建议邮件确认</t>
         </is>
       </c>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免:研究生院规定在美国院校完成学位者免交)。若需:TOEFL ≥79(2026/1/21后新制≥4);⚠️ GTA口语测试要求未查到</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目招生邮箱;系电话 806-742-3371,建议邮件确认</t>
+        </is>
+      </c>
       <c r="L66" s="21" t="inlineStr">
         <is>
           <t>https://www.depts.ttu.edu/ksm/grad/assistantships.php</t>
@@ -5400,7 +5544,11 @@
           <t>不需要(系官网:不再要求 GRE)</t>
         </is>
       </c>
-      <c r="J69" s="21" t="n"/>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院要求 TOEFL ≥90(2026/1/26后新制≥5)/IELTS ≥7/Duolingo ≥110,豁免清单未查到是否含美国学位,可在网申中申请豁免,建议确认</t>
+        </is>
+      </c>
       <c r="K69" s="30" t="inlineStr">
         <is>
           <t>nelspopp@email.unc.edu(EXSS 研究生招生主任 Dr. Nels Popp)</t>
@@ -5474,8 +5622,42 @@
 ETAMU: 可以申请。认证学士学位;正式成绩单;部分方向需2封推荐信;Exercise Science 方向申请费$75(MS Health, Kinesiology &amp; Sports Studies)</t>
         </is>
       </c>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: ⚠️ 官网未列截止日;第三方称滚动录取、开学前6周前提交;GA 通常春季发放,建议 2027/1 前提交
+ISU: 秋季 2027/2/1(国际生同)(按官网现行周期;⚠️ Peterson's 写 1/1)
+App State: 2027/2/1 开始审核(录取+GA优先);最终 2027/4/1(按2026周期,2027待公布)
+ECU: 2027/2/1 开始初审(非硬截止,按方向名额录取),建议 2/1 前提交
+Georgia Southern: Exercise Science:2027/2/1 开始审核;最终 2027/7/1;仅秋季入学,不招春季(按官网现行周期)
+MSU: ⚠️ MS 暂停招生,无截止日;同系 PhD 为 8/1 开放、1/15 截止,MS 重开后可能类似,需确认
+Baylor: 秋季最终 2027/4/1;春季 10/1(按官网现行周期);⚠️第三方称资助优先 2/15
+UMN: 2026/12/1(录取及资助优先,推荐信同日截止);1–2月出结果
+UConn: 建议 2027/2/1 前提交(官网推荐截止,非硬截止)
+UGA: 2027/1/10(论文型及多数方向);Sport Pedagogy 等非论文型 6/1(按官网现行周期)
+PSU: 无固定截止,滚动录取;资助考虑建议 2027/1/15 前提交完整申请
+MTSU: 夏/秋季 2027/3/1;春季 10/1;逾期合格者个案考虑(⚠️国际生页面写秋季 6/1,以系为准)
+SCSU: ⚠️ 官网未查到;Peterson's 称秋季 7/15,建议邮件确认
+ETAMU: 国际生:秋季 2027/5/15;春季 10/15;夏季 3/15(研究生院多数项目为开放录取)</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>OSU: ⚠️ 官网申请材料未列GRE,疑似不需要,建议确认
+ISU: 不需要(Graduate College 项目页明确)
+App State: 必需,但本科GPA≥3.0可申请豁免
+ECU: 不需要
+Georgia Southern: ⚠️ 大概率不需要:Peterson's 称 Exercise Science/Coaching 方向免GRE;官网目录仅明确 Coaching 方向不需要
+MSU: ⚠️ 官网未查到(MS 暂停招生),建议邮件确认
+Baylor: 不需要(官网明确)
+UMN: 不接受(2024-25周期起录取不考虑GRE)
+UConn: ⚠️ 不明确:系申请页把GRE列入材料但未说明是否必需,建议问 kinesiology@uconn.edu
+UGA: 按方向:Sport Pedagogy/APE 不需要;⚠️ Exercise Physiology 页面列 GRE 写作≥4,需确认
+PSU: 可选
+MTSU: 必需:录取者通常 V&gt;150、Q&gt;141、合计&gt;291
+SCSU: ⚠️ 未见GRE要求,大概率不需要,建议确认
+ETAMU: ⚠️ 研究生院称多数项目不再要求GRE;本项目页未说明,大概率不需要</t>
+        </is>
+      </c>
       <c r="J70" s="30" t="inlineStr">
         <is>
           <t>OSU: 否(美国学位豁免:英语国家英语授课学士/研究生学位可豁免);否则 TOEFL≥79/IELTS≥6.5/DET≥115
@@ -5582,7 +5764,11 @@
           <t>⚠️ 不明确:研究生院对特定国家学位豁免,名单未确认含美国;⚠️ 第三方称美国学位可免;否则 TOEFL ≥80/IELTS ≥6.5/Duolingo ≥110</t>
         </is>
       </c>
-      <c r="K71" s="21" t="n"/>
+      <c r="K71" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到邮箱,建议邮件确认;研究生项目主任 John Schuna Jr(见 health.oregonstate.edu/kinesiology/faculty)</t>
+        </is>
+      </c>
       <c r="L71" s="21" t="inlineStr">
         <is>
           <t>https://health.oregonstate.edu/kinesiology/graduate/apply</t>
@@ -5811,8 +5997,16 @@
           <t>可以申请(国际生可申GTA,带stipend+部分学费减免)。先修:Exercise Science方向需≥18学分运动/体育/健身相关课程;3封推荐信(≥1封来自教授);⚠️ 最低GPA各来源不一(2.7/2.75/3.0),未达标可有条件录取</t>
         </is>
       </c>
-      <c r="H75" s="21" t="n"/>
-      <c r="I75" s="21" t="n"/>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到具体截止日(校方称见Graduate Catalog各项目页);GA申请无截止,建议录取后尽快提交,建议2027/3前递交</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到明确要求,疑似不需要,建议邮件确认</t>
+        </is>
+      </c>
       <c r="J75" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免:持美国区域认证大学学位者无需提交英语成绩);否则TOEFL ≥79,IELTS ≥6.0</t>
@@ -5865,8 +6059,16 @@
           <t>可以申请(GA免学费及外州费)。先修:运动科学或相关本科;化学或生物1门+生理学、营养学本科课;最低GPA 2.75(最后60学分);需SOP、简历、3封推荐信。⚠️ 该方向目录标注100%在线,需确认是否有校园版/能否持F-1</t>
         </is>
       </c>
-      <c r="H76" s="21" t="n"/>
-      <c r="I76" s="21" t="n"/>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 未查到项目截止日;研究生院国际生秋季 2027/5/1(春季10/1);一般截止秋季8/10。建议2027/3前提交以争取GA</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目要求(研究生院不设最低GRE,由系决定),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J76" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免:持美国认证大学学位可免);否则TOEFL ≥71,IELTS ≥6.0</t>
@@ -5986,7 +6188,11 @@
           <t>资助/优先 2027/1/15;最终 2027/7/1(视名额)</t>
         </is>
       </c>
-      <c r="I78" s="21" t="n"/>
+      <c r="I78" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到(同系MSAT不需要GRE),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J78" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免,材料齐后招生专员手动豁免);入学后所有国际生需参加UNCG英语测评</t>
@@ -6116,7 +6322,11 @@
           <t>否(美国学位豁免:美国认证大学学位或≥24学分美国学习可免);否则TOEFL ≥79,IELTS ≥6.5;成绩2年有效</t>
         </is>
       </c>
-      <c r="K80" s="21" t="n"/>
+      <c r="K80" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 项目邮箱官网未查到;研究生项目主任 Scott Trappe(HPL电话 765-285-1145);admissions@bsu.edu(招生办)</t>
+        </is>
+      </c>
       <c r="L80" s="21" t="inlineStr">
         <is>
           <t>https://www.bsu.edu/academics/collegesanddepartments/kinesiology/academic-programs/masters-degrees/exercise-physiology</t>
@@ -6355,7 +6565,11 @@
           <t>可选:2026 秋季起所有硕士项目标化成绩均为可选</t>
         </is>
       </c>
-      <c r="J84" s="21" t="n"/>
+      <c r="J84" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:Mailman 对非英语母语者要求 TOEFL/IELTS/Duolingo(Duolingo ≥135),官网称豁免申请仅针对成绩过期者、需申请后邮件 ph-admit@columbia.edu;未查到美国学位自动豁免条款,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K84" s="30" t="inlineStr">
         <is>
           <t>ph-admit@columbia.edu(Mailman 招生办)</t>
@@ -6413,7 +6627,11 @@
           <t>⚠️ 多数项目不需要/可选(第三方 Peterson's 仍列 GRE,官网未核实,建议按具体系确认)</t>
         </is>
       </c>
-      <c r="J85" s="21" t="n"/>
+      <c r="J85" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:Epidemiology 系要求国际生 TOEFL iBT ≥100;是否豁免美国学位未查到官方说明(本批检索额度耗尽,未能核实),建议邮件确认;当 GSI 需另行英语口语评估(⚠️)</t>
+        </is>
+      </c>
       <c r="K85" s="30" t="inlineStr">
         <is>
           <t>⚠️ sph.inquiries@umich.edu(SPH 招生办,未经本次检索核实)</t>
@@ -6518,9 +6736,9 @@
           <t>⚠️ 不需要:硕士按项目整体录取(官网未明确);如争取系GA可提前邮件系里询问</t>
         </is>
       </c>
-      <c r="G87" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未明确</t>
+      <c r="G87" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 国际生GA资格官网未明确)。⚠️ 项目具体先修课/最低GPA官网未查到,建议邮件确认;需满足研究生院统一申请要求</t>
         </is>
       </c>
       <c r="H87" s="30" t="inlineStr">
@@ -6528,8 +6746,16 @@
           <t>⚠️ 研究生院最终截止:秋季 2027/8/1(系里可能更早);第三方(Petersons)显示国际生秋季 4/1;系GA优先 1/15(见E列)</t>
         </is>
       </c>
-      <c r="I87" s="21" t="n"/>
-      <c r="J87" s="21" t="n"/>
+      <c r="I87" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院不要求标化,但项目可自行要求,官网未查到项目GRE政策,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="J87" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:需满足研究生院英语要求(见Graduate Catalog),美国学位是否豁免未查到</t>
+        </is>
+      </c>
       <c r="K87" s="30" t="inlineStr">
         <is>
           <t>⚠️ alsulliv@uark.edu(Amanda Sullivan,公共卫生系研究生协调员,信息可能过时);elindly@uark.edu(MPH协调员)</t>
@@ -6587,7 +6813,11 @@
           <t>可选</t>
         </is>
       </c>
-      <c r="J88" s="21" t="n"/>
+      <c r="J88" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:非英语母语者需TOEFL ≥80/IELTS ≥6.5,美国学位豁免政策官网未查到,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K88" s="30" t="inlineStr">
         <is>
           <t>CEBLAKE@mailbox.sc.edu(HPEB研究生项目主任 Christine Blake);EDENAG@mailbox.sc.edu(MPH项目主任 Edena Guimaraes)</t>
@@ -6625,19 +6855,74 @@
           <t>各校有限 GA(津贴+学费减免/部分)</t>
         </is>
       </c>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="21" t="n"/>
-      <c r="K89" s="21" t="n"/>
-      <c r="L89" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="F89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: 不需要:按项目整体录取;选论文方向可在陈述中写感兴趣教授
+BSU: 不需要:按项目整体录取
+UNCG: 不需要:按项目整体录取(GA按申请材料择优分配)
+UNC: 不需要:按项目整体录取
+TWU: ⚠️ 不需要:按项目整体录取(未查到项目说明)
+ECU: 不需要(但F-1不可就读,见先修)</t>
+        </is>
+      </c>
+      <c r="G89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: 可以申请(GA有限)。区域认证学士;最后60学分GPA≥2.75;简历/CV、500字目的陈述、推荐信(⚠️ Peterson's称3封)。注意该专业另有在线版,须选校园版以符合F-1
+BSU: ⚠️ 可以申请,但官网仅查到100%在线MS Health Science(生统/流病方向),在线项目通常不能办F-1,需确认是否有校园版;研究生院最低GPA 2.75;陈述约1000字、2封推荐信、简历
+UNCG: 可以申请(MPH有少量GA:需全职、GPA≥3.0、无条件录取,未说明国际生是否可获,需确认)。系里无最低GPA;简历、一页职业目标陈述、3封推荐信
+UNC: ⚠️ 可以申请,但catalog标注学制3.5年、晚间/兼职形式,可能不满足F-1全日制要求,需确认;第三方称需2封推荐信
+TWU: ⚠️ 可以申请(官网细节未查到):须满足TWU研究生院一般要求,项目可能另有要求
+ECU: ❌ MA Health Education为纯在线项目,研究生院官网明确F-1学生不可就读。(先修:区域认证学士,GPA建议≥3.0)</t>
+        </is>
+      </c>
+      <c r="H89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: 研究生院秋季优先 2027/2/1(国际生同);⚠️ Peterson's:秋季国内 6/15、国际 2/1,滚动审理(按2026周期,2027待公布)
+BSU: ⚠️ 官网未查到;第三方称秋季 3/1(资助/FAFSA 3/1);研究生院要求开学前至少2周交齐材料
+UNCG: GA最佳考虑 2027/2/1;MPH最佳考虑 2027/3/1;滚动审理(按2026周期,2027待公布;⚠️ Peterson's另列 2/15)
+UNC: ⚠️ 第三方称滚动录取,资助申请 3/1;官网未查到
+TWU: ⚠️ Peterson's:秋季 3/1;官网未查到
+ECU: 秋季 8/1(研究生院通用截止;F-1不可就读)</t>
+        </is>
+      </c>
+      <c r="I89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: ⚠️ 不需要(Peterson's;官网未明示)
+BSU: 不需要(官网在线MS Health Science:多数学生无需GRE)
+UNCG: ⚠️ 不明确:Peterson's列GRE/MAT,系官网MPH材料清单未列GRE,建议确认
+UNC: ⚠️ 必需?(Peterson's列GRE General Test,官网当前政策未查到)
+TWU: ⚠️ 不需要(第三方仅显示运动机能学生物力学方向要求GRE)
+ECU: 不需要(研究生院官网)</t>
+        </is>
+      </c>
+      <c r="J89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: 否(美国学位豁免,官网目录明示)
+BSU: ⚠️ 不明确:官网未查到,建议确认是否豁免美国学位
+UNCG: ⚠️ 不明确:系网页称母语非英语需TOEFL(&gt;550纸考)/IELTS,未提美国学位豁免,需向研究生院确认
+UNC: ⚠️ 不明确:官网未查到
+TWU: ⚠️ 不明确:官网未查到
+ECU: 不适用(F-1不可就读)</t>
+        </is>
+      </c>
+      <c r="K89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: gradcollege@txstate.edu(研究生院)
+BSU: ⚠️ 官网未查到,建议通过 bsu.edu/gradschool 联系研究生院
+UNCG: ⚠️ 未查到邮箱;Public Health Education 系电话 336-334-5532
+UNC: ⚠️ 未查到邮箱;Peterson's列协调员 Dr. Deborah Givray 970-351-2403;catalog列校区主任 Patricia Valverde
+TWU: ⚠️ 官网未查到,建议邮件确认
+ECU: martinry@ecu.edu(项目联系人 Dr. Ryan Martin)</t>
+        </is>
+      </c>
+      <c r="L89" s="30" t="inlineStr">
+        <is>
+          <t>TXST: https://www.gradcollege.txstate.edu/programs/public-health-ed
+BSU: https://www.bsu.edu/academics/collegesanddepartments/online/academic-programs/masters/ms-health-science
+UNCG: https://phe.uncg.edu/graduate/master-of-public-health/admissions-requirements/
+UNC: https://unco.edu/graduate-school/degrees-and-programs/masters-specialist-programs/public-health-community-health-education-emphasis-mph.aspx
+TWU: ⚠️ 官网页未查到;catalog: https://twu-preview.courseleaf.com/graduate/health-sciences/health-promotion-kinesiology/master-public-health-mph/
+ECU: https://gradschool.ecu.edu/?id=324</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6977,11 @@
           <t>否(美国学位豁免:研究生院政策,美国认证院校学位通常无需TOEFL/IELTS;⚠️ 个别项目可能仍要求,建议确认)</t>
         </is>
       </c>
-      <c r="K90" s="21" t="n"/>
+      <c r="K90" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到招生邮箱;MPH招生办电话 706-583-0885,建议通过 publichealth.uga.edu 联系</t>
+        </is>
+      </c>
       <c r="L90" s="21" t="inlineStr">
         <is>
           <t>https://publichealth.uga.edu/mph-faqs/</t>
@@ -6730,9 +7019,9 @@
           <t>不需要:按项目整体录取</t>
         </is>
       </c>
-      <c r="G91" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G91" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可获资助但不保证)。先修:学士学位,⚠️ 具体先修课/GPA官网未查到;需SOPHAS+IU Bloomington研究生补充申请;个人陈述≤600词</t>
         </is>
       </c>
       <c r="H91" s="30" t="inlineStr">
@@ -6740,7 +7029,11 @@
           <t>优先 2027/1/15;最终 2027/4/1(学院通用日期,各项目可能不同);Hoosier Public Health Scholars奖学金预申请 2027/1/15</t>
         </is>
       </c>
-      <c r="I91" s="21" t="n"/>
+      <c r="I91" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:当前政策未查到;旧版bulletin要求GRE,可能已取消,建议确认</t>
+        </is>
+      </c>
       <c r="J91" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免:官网明确持有美国大学学位可免;否则 IELTS ≥6.5/Duolingo ≥105)</t>
@@ -6803,7 +7096,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J92" s="21" t="n"/>
+      <c r="J92" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生需TOEFL iBT ≥80(各项≥18)/IELTS ≥6.5,成绩2年内;豁免名单是否含美国学位未查到,可由项目代为申请例外</t>
+        </is>
+      </c>
       <c r="K92" s="30" t="inlineStr">
         <is>
           <t>amanda.armington@oregonstate.edu(MPH项目经理)</t>
@@ -6849,12 +7146,22 @@
 Wyoming: 必须(事实上):官网称未正式联系教授者很难被录取或获GA推荐,需邮件确认导师是否招生</t>
         </is>
       </c>
-      <c r="G93" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="21" t="n"/>
+      <c r="G93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: 可以申请(GA含学费奖学金/津贴,有限竞争,申请时勾选意向)。先修:需持医疗执照或健康相关学位并计划从事医疗工作;GPA≥2.75(旧目录3.0)
+Boise State: 可以申请(GA由院系竞争分配,MHS专项资助⚠️未查到)。先修:美国区域认证学士,GPA≥3.0;陈述250-500字、简历、2封推荐信,需写作测试+面试
+Montana State: 可以申请(RA/TA视导师经费)。先修:运动学/运动科学/营养/健康/体育/AT等相关本科;GPA≥3.0。注:原HHD系已拆分,对应Exercise &amp; Nutrition Sciences MS(FSNK系)或Community Health MS(HDCH系)
+Wyoming: 可以申请(仅Laramie校区全日制可申GA,需填K&amp;H补充申请表)。先修:GPA≥3.0;3封推荐信(至少1封学术)</t>
+        </is>
+      </c>
+      <c r="H93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: 研究生院秋季 7/1(2027/7/1,按通用截止);项目页称入学前1个月;⚠️GA建议尽早申请
+Boise State: ⚠️ MHS专项截止官网未查到,建议邮件确认(同校MPH:优先1/15、最终5/15可参考)
+Montana State: Exercise Physiology &amp; Nutrition方向 2027/2/15(仅秋季入学);Sport &amp; Coaching方向 5/15(优先);Community Health MS 4/1(按现行周期,2027待公布)
+Wyoming: 校内MS 2027/2/1(同时为GA优先截止;按现行周期,2027待公布);⚠️系主页另称通常1/15,建议按1/15前提交</t>
+        </is>
+      </c>
       <c r="I93" s="30" t="inlineStr">
         <is>
           <t>Cleveland State: ⚠️ 不明确:项目页称GRE/GMAT目前豁免,另一页称需5年内GRE,建议邮件确认
@@ -6863,7 +7170,14 @@
 Wyoming: 可选(不要求,可提交以增强申请/GA竞争力)</t>
         </is>
       </c>
-      <c r="J93" s="21" t="n"/>
+      <c r="J93" s="30" t="inlineStr">
+        <is>
+          <t>Cleveland State: 否(美国学位豁免,学校明文美国大学毕业生免语言成绩)
+Boise State: ⚠️ 不明确:国际生要求TOEFL≥80/IELTS≥6.0,美国学位豁免未查证,建议邮件确认
+Montana State: ⚠️ 不明确:国际生要求TOEFL≥80(新制4.2)/IELTS≥6.5/Duolingo≥120,美国学位豁免未查证
+Wyoming: ⚠️ 不明确:国际生须提交TOEFL/IELTS(⚠️第三方称TOEFL≥76),美国学位豁免未查证</t>
+        </is>
+      </c>
       <c r="K93" s="30" t="inlineStr">
         <is>
           <t>Cleveland State: healthsci@csuohio.edu(健康科学与人体运动系)
@@ -6927,7 +7241,11 @@
           <t>⚠️ 多数项目不需要/可选(第三方 Peterson's 仍列 GRE,官网未核实,建议按具体系确认)</t>
         </is>
       </c>
-      <c r="J94" s="21" t="n"/>
+      <c r="J94" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:Epidemiology 系要求国际生 TOEFL iBT ≥100;是否豁免美国学位未查到官方说明(本批检索额度耗尽,未能核实),建议邮件确认;当 GSI 需另行英语口语评估(⚠️)</t>
+        </is>
+      </c>
       <c r="K94" s="30" t="inlineStr">
         <is>
           <t>⚠️ sph.inquiries@umich.edu(SPH 招生办,未经本次检索核实)</t>
@@ -7156,9 +7474,9 @@
           <t>不需要:GA按SOPHAS申请材料merit授予,无需另申或套磁</t>
         </is>
       </c>
-      <c r="G98" s="21" t="inlineStr">
-        <is>
-          <t>✅ F-1 可;需 OPI 口语</t>
+      <c r="G98" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(F-1可获GA;需OPI口语测试)。先修:学士学位,⚠️ 最低GPA/先修课官网未查到;SOPHAS申请+官方成绩单(另寄一份至SOPHAS)</t>
         </is>
       </c>
       <c r="H98" s="30" t="inlineStr">
@@ -7171,7 +7489,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J98" s="21" t="n"/>
+      <c r="J98" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:TOEFL"如适用"提交至SOPHAS,美国学位豁免未查到;第三方称TOEFL ≥79;当GA需OPI口语</t>
+        </is>
+      </c>
       <c r="K98" s="30" t="inlineStr">
         <is>
           <t>huntjr1@etsu.edu(研究生项目顾问 Jennifer Hunt);publichealth@etsu.edu(公卫学院)</t>
@@ -7221,15 +7543,66 @@
 TXST: 不需要:按项目整体录取(但MPH为纯网课,见先修列)</t>
         </is>
       </c>
-      <c r="G99" s="21" t="inlineStr">
-        <is>
-          <t>部分明确可(ISU 国际 GA 需英语测试)</t>
-        </is>
-      </c>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="21" t="n"/>
-      <c r="J99" s="21" t="n"/>
-      <c r="K99" s="21" t="n"/>
+      <c r="G99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: 可以申请(GRA名额有限,来自教师课题;需GPA≥3.0且有签证工时限制)。无最低GPA,2.75以上优先;SOPHAS+研究生院双申请,3封推荐信
+GaSou: 可以申请(有限GA,仅秋季入学,临时录取者无资格)。先修:学士学位,GPA≥2.75;CV、目的陈述、2-3封推荐信
+CMU: 可以申请(GA竞争约5:1,全/半/四分之一职,含学费减免+津贴)。先修:学士学位,GPA≥3.0;⚠️第三方称需简历、目的陈述、2封推荐信
+ISU: ❌ MPH为全网课项目,官网明确国际生无法据此获得F-1签证;另注:国际GA需英语口语测试。GPA≥3.0(最后60学分),SOPHAS+研究生院双申请
+USM: 可以申请,但仅流行病与生物统计方向为校内授课(⚠️第三方信息,其余方向为网课,F-1需校内);GA每周20小时含津贴+学费减免,有限。GPA≥2.75(最后60学分),3封推荐信
+USC: 可以申请(有限GA:学费特价+津贴,每周10-20小时;⚠️国际生GA资格未明确)。GPA≥3.0;简历、目的陈述、≥3封推荐信(至少1封学术)
+UNMC: 可以申请(⚠️GA信息官网未查到)。学士学位,GPA≥3.0;环境与职业健康方向需生物、化学、大学数学各1学期;3封推荐信
+TXST: ❌ 现MPH(社区健康行为/卫生政策管理)均为加速网课,F-1不可;⚠️可改申MS Public Health Education &amp; Promotion(有论文型,需确认是否校内)。GPA≥2.75</t>
+        </is>
+      </c>
+      <c r="H99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: 秋季优先/奖学金/国际生 2027/2/15;常规 6/15(按现行周期,2027待公布)
+GaSou: GA优先 2027/2/1;国际生最终 5/1;美国申请人 6/1(仅秋季入学;SOPHAS材料需提前4周到齐)
+CMU: ⚠️ 官网未查到;第三方称秋季6/15,建议邮件确认
+ISU: 滚动录取(秋/春/夏)
+USM: ⚠️ 国际生秋季 5/1(研究生院页面,约2年前);网课MPH 8/1,建议邮件确认
+USC: 多数MPH方向秋季 6/15;流行病学MPH 1/15(按2026周期,2027待公布)
+UNMC: 秋季优先 2027/2/15;国际生(校内)4/1;国内 6/1(按现行周期,2027待公布)
+TXST: 网课MPH 8周滚动入学(秋1 8/5…);公共卫生GA优先截止 秋季2/1</t>
+        </is>
+      </c>
+      <c r="I99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: 不需要
+GaSou: 不需要(学院FAQ称不再要求;⚠️第三方称仅流行病学方向需要)
+CMU: ⚠️ 不明确:第三方称可选/可豁免,建议邮件确认
+ISU: ⚠️ 官网未查到,建议邮件确认
+USM: ⚠️ 不明确:网课方向不需要;第三方称校内方向需GRE/GMAT/MAT
+USC: 视方向:环境健康/健康促进可选;流行病学、卫生政策管理不审阅;⚠️General MPH页仍写需GRE/MCAT/PCAT
+UNMC: 可选(GPA&lt;3.0强烈建议提交,代码0695)
+TXST: 不需要</t>
+        </is>
+      </c>
+      <c r="J99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: ⚠️ 不明确:MPH页要求国际申请人提交TOEFL/IELTS,未见美国学位豁免(博士FAQ有认证学位豁免),建议邮件确认
+GaSou: 否(美国学位豁免);否则TOEFL≥80/IELTS≥6(⚠️来源不一)
+CMU: ⚠️ 不明确:FAQ称国际生需提交TOEFL等,第三方称TOEFL≥79,美国学位豁免未查证
+ISU: ⚠️ 官网未查到;国际GA需英语口语测试
+USM: ⚠️ 不明确:国际生TOEFL≥79,美国学位豁免未查证
+USC: ⚠️ 不明确:非英语母语需TOEFL/IELTS(⚠️第三方称TOEFL≥77/IELTS≥6.5),美国学位豁免未查证
+UNMC: 否(美国学位豁免);否则TOEFL≥80(新制4.0)/IELTS≥6.5/Duolingo≥120
+TXST: 否(美国学士豁免);否则TOEFL≥78/IELTS≥6.5</t>
+        </is>
+      </c>
+      <c r="K99" s="30" t="inlineStr">
+        <is>
+          <t>GSU: sphadmissions@gsu.edu(公共卫生学院招生办)
+GaSou: jphcoph@georgiasouthern.edu(公共卫生学院)
+CMU: mph@cmich.edu(MPH项目)
+ISU: ⚠️ gradschool@isu.edu(研究生院,MPH专属邮箱未查到)
+USM: ⚠️ hwanseok.choi@usm.edu(第三方所列项目主任,可能过时)
+USC: sphstsrv@mailbox.sc.edu(研究生学生服务办);edenag@mailbox.sc.edu(MPH研究生主任)
+UNMC: ⚠️ coph@unmc.edu(公共卫生学院,用途未完全确认)
+TXST: sheri.burson@txstate.edu(公共卫生研究生协调员);gradcollege@txstate.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L99" s="30" t="inlineStr">
         <is>
           <t>GSU: https://publichealth.gsu.edu/academics-admissions/georgia-state-mph-program/mph-application-process/
@@ -7274,9 +7647,9 @@
           <t>不需要:按项目整体录取,录取者自动考虑奖学金;RA竞争激烈,可选择性联系研究方向匹配的教授</t>
         </is>
       </c>
-      <c r="G100" s="21" t="inlineStr">
-        <is>
-          <t>⚠️ 未限制</t>
+      <c r="G100" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(录取者自动考虑奖学金,⚠️ 国际生未限制)。先修:美国学士或同等学位,GPA≥3.0优先;⚠️ MS具体先修未查到,PhD页建议统计/微积分(经济方向需微观经济)</t>
         </is>
       </c>
       <c r="H100" s="30" t="inlineStr">
@@ -7413,7 +7786,11 @@
           <t>不需要(可选提交GRE/GMAT;⚠️ 旧FAQ称必需,以项目页为准)</t>
         </is>
       </c>
-      <c r="J102" s="21" t="n"/>
+      <c r="J102" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生需TOEFL ≥80 或 IELTS ≥6.5;2016手册称有美国学习经历可经研究生院同意豁免,现行政策未查到</t>
+        </is>
+      </c>
       <c r="K102" s="30" t="inlineStr">
         <is>
           <t>nnatafgi@mailbox.sc.edu(MHA项目临时主任 Dr. Nabil Natafgi)</t>
@@ -7461,18 +7838,64 @@
 U Michigan HMP: 不需要:按项目整体录取(SOPHAS)</t>
         </is>
       </c>
-      <c r="G103" s="21" t="inlineStr">
-        <is>
-          <t>UNC 明文国际生可但处劣势</t>
-        </is>
-      </c>
-      <c r="H103" s="21" t="n"/>
-      <c r="I103" s="21" t="n"/>
-      <c r="J103" s="21" t="n"/>
-      <c r="K103" s="21" t="n"/>
-      <c r="L103" s="21" t="inlineStr">
-        <is>
-          <t>(见 agent 原始输出)</t>
+      <c r="G103" s="30" t="inlineStr">
+        <is>
+          <t>KUMC: 可以申请。需区域认证学士学位,累计 GPA≥3.0,入学前须修完统计学课程(官网)
+Georgia State: ⚠️ 可以申请;官网先修未查到(第三方称需 TOEFL/IELTS)
+UNC HPM: 可以申请,但国际生明文可申但处劣势(资助竞争不利);12/1 前提交可获研究生院奖学金考虑;⚠️ 先修未查到
+Northwestern HSOR: 可以申请;⚠️ 先修未查到,建议有统计/研究方法背景
+UAB MSHA: 可以申请;12/1 优先截止前申请可获有限学费奖学金考虑;⚠️ 先修未查到
+U Michigan HMP: 可以申请;⚠️ 先修未查到</t>
+        </is>
+      </c>
+      <c r="H103" s="30" t="inlineStr">
+        <is>
+          <t>KUMC: 9/1 开放,仅秋季入学;⚠️ 第三方(Peterson's)称 3/1 截止,可能过时
+Georgia State: ⚠️ 官网未查到,建议邮件确认
+UNC HPM: 按2024周期:优先 12/12、最终 2/13;研究生院奖学金需 12/1 前提交(按2024周期,2027待公布)
+Northwestern HSOR: 按2025周期:季度滚动,秋季 2025/7/8 截止;另一 Feinberg 页面写 12/1(按2025周期,2027待公布)
+UAB MSHA: 优先 2026/12/1(官网每年固定),之后有名额可继续审;12月起审核,1–2月面试
+U Michigan HMP: 按2026周期:优先 12/1;最终 国内 5/15、国际生 1/15(按2026周期,2027待公布)</t>
+        </is>
+      </c>
+      <c r="I103" s="30" t="inlineStr">
+        <is>
+          <t>KUMC: ⚠️ 官网未说明;Peterson's 称需 GRE(可能过时)
+Georgia State: ⚠️ 官网未查到
+UNC HPM: ⚠️ HPM 未见明文;Gillings 其他项目一般不需要
+Northwestern HSOR: 不需要(2025周期官网明文,2027待确认)
+UAB MSHA: ⚠️ 官网未说明;Peterson's 列 GMAT 或 GRE
+U Michigan HMP: 不需要(官网明文:不要求也不审阅 GRE 等标化成绩)</t>
+        </is>
+      </c>
+      <c r="J103" s="30" t="inlineStr">
+        <is>
+          <t>KUMC: ⚠️ 不明确:官网未查到豁免政策
+Georgia State: ⚠️ 不明确:第三方称在英语授课国家取得学位可豁免;参考 TOEFL 90/IELTS 6.5
+UNC HPM: ⚠️ 不明确:UNC 豁免页要求近4年在英语授课学校就读(美本4年通常满足),以研究生院为准
+Northwestern HSOR: 否(官网:英语授课认可院校的学位可满足英语要求)
+UAB MSHA: ⚠️ 不明确:第三方称 TOEFL 80/IELTS 6.5/DET 120
+U Michigan HMP: ⚠️ 不明确:仅母语非英语者需满足语言要求,美国学位豁免条件未查到;Peterson's 称 TOEFL 100</t>
+        </is>
+      </c>
+      <c r="K103" s="30" t="inlineStr">
+        <is>
+          <t>KUMC: KS_HSA@kumc.edu(MHSA 项目联系邮箱)
+Georgia State: ⚠️ 官网未查到,建议邮件确认
+UNC HPM: sph-admissions@unc.edu(Gillings 招生办)
+Northwestern HSOR: ⚠️ 官网未查到,建议邮件确认
+UAB MSHA: ⚠️ 官网未查到,建议邮件确认
+U Michigan HMP: ⚠️ 官网未查到,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="L103" s="30" t="inlineStr">
+        <is>
+          <t>KUMC: https://www.kumc.edu/school-of-medicine/academics/departments/population-health/academics/master-of-health-services-administration/admissions.html
+Georgia State: ⚠️ 未查到官方页面(MSHA 属 Robinson College of Business)
+UNC HPM: https://sph.unc.edu/?p=399150(HPM 硕士 MHA 页面;MSPH 同系)
+Northwestern HSOR: https://feinberg.northwestern.edu/sites/hsor/admissions/index.html
+UAB MSHA: https://www.uab.edu/shp/hsa/graduate/residential-msha/admissions
+U Michigan HMP: https://sph.umich.edu/admissions/programs-degrees/masters/how-to-apply.html</t>
         </is>
       </c>
     </row>
@@ -7874,13 +8297,21 @@
           <t>硕士 assistantship ~$14,500/9 个月+秋春学费减免+医保</t>
         </is>
       </c>
-      <c r="F110" s="21" t="n"/>
+      <c r="F110" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(论文型建议联系方向相符教授)</t>
+        </is>
+      </c>
       <c r="G110" s="30" t="inlineStr">
         <is>
           <t>可以申请。先修:需相关背景课程(具体未列);GPA:M.A.Geo. ≥3.0(或最后60学时≥3.0),M.S. ≥3.2(系FAQ另写MS 3.4/MAGeo 3.2,有冲突);需陈述、CV、3封推荐信</t>
         </is>
       </c>
-      <c r="H110" s="21" t="n"/>
+      <c r="H110" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季 4/15,春季 10/1(仅第三方IDP,官网未查到;资助建议尽早申请)</t>
+        </is>
+      </c>
       <c r="I110" s="30" t="inlineStr">
         <is>
           <t>不需要</t>
@@ -7948,7 +8379,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J111" s="21" t="n"/>
+      <c r="J111" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:非母语者需TOEFL ≥80,IELTS ≥6.5,DET ≥115;未查到美国学位豁免</t>
+        </is>
+      </c>
       <c r="K111" s="30" t="inlineStr">
         <is>
           <t>geog-info@du.edu(地理系);⚠️ Eric.Boschmann@du.edu(研究生项目主任,第三方来源)</t>
@@ -8006,7 +8441,11 @@
           <t>⚠️ 不明确:旧目录要求GRE,新目录未列,建议邮件确认</t>
         </is>
       </c>
-      <c r="J112" s="21" t="n"/>
+      <c r="J112" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K112" s="30" t="inlineStr">
         <is>
           <t>ajoslin@k-state.edu(研究生项目主任 Dr. Audrey Joslin);pmcra@k-state.edu(系办)</t>
@@ -8044,7 +8483,16 @@
           <t>TA/RA/fellowship 通常 2 年(ProFellow 汇总)</t>
         </is>
       </c>
-      <c r="F113" s="21" t="n"/>
+      <c r="F113" s="30" t="inlineStr">
+        <is>
+          <t>IU: ⚠️ 官网未查到,建议先确认教授是否招生再联系
+VT: 必须:无教师愿意指导者不予录取,需申请前邮件联系
+WVU: 必须:申请表须列潜在导师,应提前联系
+OU: 建议:导师可能对先修课有偏好,建议申请前联系
+UW: 强烈建议:录取需多位教师支持,先读相关教授论文
+UIUC: 建议:欢迎但不要求申请前联系tenure-track教师</t>
+        </is>
+      </c>
       <c r="G113" s="30" t="inlineStr">
         <is>
           <t>IU: 可以申请。GPA≥3.0;硕士为MS(GIS方向),未见MA
@@ -8209,7 +8657,11 @@
           <t>⚠️ 不明确:研究生院将GRE列为学术型项目要求,但系新页面称不以GRE/GPA单独录取或拒绝,建议邮件确认</t>
         </is>
       </c>
-      <c r="J115" s="21" t="n"/>
+      <c r="J115" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):美国区域认证学士学位且在提交申请前2年内获得即可;否则TOEFL ≥80,IELTS ≥6.5,Duolingo ≥105。⚠️ 当TA的口语要求未查到</t>
+        </is>
+      </c>
       <c r="K115" s="30" t="inlineStr">
         <is>
           <t>⚠️ pam.mitchell@geog.utah.edu(地理研究生协调员 Pam Mitchell,旧页面);summer.rupper@ess.utah.edu(ESS研究生事务副主任)</t>
@@ -8267,7 +8719,11 @@
           <t>不需要(不要求也不考虑GRE)</t>
         </is>
       </c>
-      <c r="J116" s="21" t="n"/>
+      <c r="J116" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 大概率否:研究生院对有美国学位/在美学习经历者可豁免,具体条件需核实研究生院页面;非豁免需TOEFL/IELTS。当TA需另满足英语口语要求(具体未查到)</t>
+        </is>
+      </c>
       <c r="K116" s="30" t="inlineStr">
         <is>
           <t>mcohn@illinois.edu(研究生项目管理员 Matt Cohn)</t>
@@ -8310,7 +8766,11 @@
           <t>强烈建议:申请信需写明潜在导师,建议申请前联系教师</t>
         </is>
       </c>
-      <c r="G117" s="21" t="n"/>
+      <c r="G117" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GTA/GRA,含stipend与州外学费减免)。无特定先修课;非地理本科需补足人文地理、自然地理、统计和制图基础。材料:3封推荐信、单作者写作样本、申请信、CV。⚠️ 最低GPA官网未查到</t>
+        </is>
+      </c>
       <c r="H117" s="30" t="inlineStr">
         <is>
           <t>资助优先 2027/2/1;最终秋季 2027/7/1(春季11/1、夏季4/1)(按官网常规周期,2027待确认)</t>
@@ -8383,7 +8843,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J118" s="21" t="n"/>
+      <c r="J118" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):在美国认证院校完成学士学位即满足英语要求(⚠️ 文理学院页面写需4年在美学习);否则TOEFL ≥80(新制4.5)。⚠️ 当TA的英语认证要求未查到</t>
+        </is>
+      </c>
       <c r="K118" s="30" t="inlineStr">
         <is>
           <t>omb-grad-advising@tamu.edu(研究生项目协调员 Heather Albrecht);⚠️ filippi@tamu.edu(研究生项目主任 Anthony Filippi,来源有冲突)</t>
@@ -8446,7 +8910,11 @@
           <t>否(美国学位豁免):有美国区域认证学士学位无需提交;否则TOEFL ≥79(新制4),IELTS ≥6.5,DET ≥105</t>
         </is>
       </c>
-      <c r="K119" s="21" t="n"/>
+      <c r="K119" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网邮箱被隐藏未查到:研究生顾问 Dr. Hilary McMillan、项目协调员 Valencia Guest,电话(619) 594-5437,建议从系官网获取邮箱</t>
+        </is>
+      </c>
       <c r="L119" s="21" t="inlineStr">
         <is>
           <t>https://geography.sdsu.edu/masters/support</t>
@@ -8489,7 +8957,11 @@
           <t>可以申请(GA $9,000/年,州外差额仅竞争性减免)。需认证学士学位;非地理本科需在研究生委员会指导下补修自然地理、人文地理、地理技术;优先GPA≥3.0。另需≤2页cover letter。</t>
         </is>
       </c>
-      <c r="H120" s="21" t="n"/>
+      <c r="H120" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到地理MA具体截止;研究生院秋季截止分 2/1(最终)或 7/1(建议3/1前提交)两类,建议邮件确认</t>
+        </is>
+      </c>
       <c r="I120" s="30" t="inlineStr">
         <is>
           <t>⚠️ 不明确:旧目录要求GRE(优先任一部分≥50百分位);当前项目页称GPA≥3.0+两页职业目标陈述可免GRE;研究生院整体不强制</t>
@@ -8542,7 +9014,11 @@
           <t>不需要:两步录取(研究生院+学院),无需提前联系;可向研究生顾问 Dr. Hallett 咨询</t>
         </is>
       </c>
-      <c r="G121" s="21" t="n"/>
+      <c r="G121" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(MS生竞争性助教,2/15前申请才考虑)。需地理主修/辅修,或社科、生物、工程、健康、商科、自然科学等相关专业学士;材料含CV、陈述、推荐人信息、成绩单。⚠️ 最低GPA未查到</t>
+        </is>
+      </c>
       <c r="H121" s="30" t="inlineStr">
         <is>
           <t>滚动录取(每学期可入学);助教资助考虑截止 2027/2/15</t>
@@ -8600,7 +9076,11 @@
           <t>不需要:专业型规划硕士,按项目整体录取</t>
         </is>
       </c>
-      <c r="G122" s="21" t="n"/>
+      <c r="G122" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GTA/GRA,减免部分学费+大部分医保)。⚠️ 官网未查到MCRP专门先修课/最低GPA;需4年制美国学士或同等学历,3封推荐信、CV、成绩单、文书。</t>
+        </is>
+      </c>
       <c r="H122" s="30" t="inlineStr">
         <is>
           <t>奖学金优先 2027/1/15;最终 2027/2/15(按目录常规周期,仅秋季入学;⚠️ 学院博士已提前至12/15,MCRP 2027待公布)</t>
@@ -8663,12 +9143,26 @@
 MIT: ⚠️ 不需要:按项目录取,资助随录取发放;部分学生另获教师 RA</t>
         </is>
       </c>
-      <c r="G123" s="21" t="inlineStr">
-        <is>
-          <t>MIT 明文不看国籍</t>
-        </is>
-      </c>
-      <c r="H123" s="21" t="n"/>
+      <c r="G123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: 可以申请(GA 含全额学费+津贴,比例未公布)。任何专业学士,无先修课,建议具备统计/经济/数学/写作基础;GPA≥3.0
+USF: 可以申请(fellowship 覆盖约 80% 州内学费)。任何专业均可,区域认证学士,GPA≥3.0
+Texas A&amp;M: 可以申请。任何专业学士;成绩单+3封推荐信(学术推荐优先)+SOP+简历
+Temple: ❌ 项目官网及 bulletin 称 2026-27 学年不招生,至另行通知暂停招新;建议邮件确认 2027 是否重开
+UNC: 可以申请。⚠️ 官网未查到具体先修课;至少51学分,通常2年
+MIT: 可以申请(明文不看国籍,资助≥80% 学费+RA/TA;DUSP 旧页面称最低 75% 学费+医保)。⚠️ 官网未查到具体先修课</t>
+        </is>
+      </c>
+      <c r="H123" s="30" t="inlineStr">
+        <is>
+          <t>OSU: ⚠️ 官网未查到明确截止;建议 2026/12/1 前提交以获最多资助机会(第三方称 1/1)
+USF: 秋季优先 2027/2/15;最终 2027/6/1(按官网常规日期;⚠️国际生截止可能更早)
+Texas A&amp;M: 首轮及资助考虑 2027/1/15(GradCAS);⚠️ 第三方称最终 3/15
+Temple: 暂停招生;以往秋季截止 1/6
+UNC: 2026/1/13(按2026周期,2027待公布);⚠️ 第三方称资助截止 12/10
+MIT: 2026/12/15(OGE 列表,⚠️ 2027 周期以官网为准)</t>
+        </is>
+      </c>
       <c r="I123" s="30" t="inlineStr">
         <is>
           <t>OSU: ⚠️ 不需要(官网仅写 2023–24 周期不需要,当前周期未更新)
@@ -8741,7 +9235,11 @@
           <t>不需要:按项目整体录取;GA需在申请时勾选意向</t>
         </is>
       </c>
-      <c r="G124" s="21" t="n"/>
+      <c r="G124" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA含9学分州内率学费+$4,200/学期,需GPA≥3.0)。本科GPA≥3.0(学位已授予的成绩单);需GRE(见I列)。⚠️ 专门先修课未查到</t>
+        </is>
+      </c>
       <c r="H124" s="30" t="inlineStr">
         <is>
           <t>⚠️ 国际生秋季约 2027/7/20(国际招生指南,约2年前);第三方Peterson's:秋季国内7/1、国际5/15;⚠️ 资助截止(第三方)3/1,建议尽早</t>
@@ -8876,7 +9374,11 @@
           <t>⚠️ 官网未提及GRE要求(手册录取标准未列考试),大概率不需要,建议确认</t>
         </is>
       </c>
-      <c r="J126" s="21" t="n"/>
+      <c r="J126" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:学位项目最低 TOEFL 79 / IELTS 6.5 / Duolingo 110 / PTE 53,成绩2年有效;未查到美国学位豁免条款,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K126" s="30" t="inlineStr">
         <is>
           <t>planning@bsu.edu(城市规划系);admissions@bsu.edu(学校招生办)</t>
@@ -9001,7 +9503,11 @@
           <t>否(美国学位豁免,有条件):美国区域认证学士学位须在提交申请并缴费前2年内获得;否则 TOEFL ≥80/IELTS ≥6.5/Duolingo ≥110</t>
         </is>
       </c>
-      <c r="K128" s="21" t="n"/>
+      <c r="K128" s="30" t="inlineStr">
+        <is>
+          <t>plan@arch.utah.edu(城市与都市规划系办公室);iao@utah.edu(国际招生办);研究生项目联系人 Alex Francis-Riggan 801-587-7553(邮箱未查到)</t>
+        </is>
+      </c>
       <c r="L128" s="21" t="inlineStr">
         <is>
           <t>https://plan.cap.utah.edu/financial-aid/</t>
@@ -9039,7 +9545,11 @@
           <t>不需要:按项目整体录取,奖学金/assistantship由学院综合评审分配</t>
         </is>
       </c>
-      <c r="G129" s="21" t="n"/>
+      <c r="G129" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(merit aid含assistantship/fellowship/学费减免,1/15前申请者竞争,仅覆盖部分申请者)。⚠️ 本科专业/最低GPA官网未查到</t>
+        </is>
+      </c>
       <c r="H129" s="30" t="inlineStr">
         <is>
           <t>资助优先 2027/1/15(按2026周期,2027待公布);⚠️ 最终(2026周期program explorer):国际生 4/1、美国申请者 7/1;春季 11/1</t>
@@ -9055,7 +9565,11 @@
           <t>⚠️ 不明确:Bloustein项目列表写 Non-U.S. applicants 需 TOEFL/IELTS/Duolingo,未写美国学位豁免;研究生院部分项目对≥3年英语授课本科豁免,建议邮件确认</t>
         </is>
       </c>
-      <c r="K129" s="21" t="n"/>
+      <c r="K129" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ greg.marrero@ejb.rutgers.edu(研究生学生服务高级顾问,来自新生指引页);招生专用邮箱官网未查到,建议参加MCRP信息会或邮件确认</t>
+        </is>
+      </c>
       <c r="L129" s="21" t="inlineStr">
         <is>
           <t>https://bloustein.rutgers.edu/students/ejb-student-funding/</t>
@@ -9113,7 +9627,11 @@
           <t>否(美国学位豁免):已获英语授课认可院校学位者豁免;否则 TOEFL iBT ≥90(各部分≥20)/IELTS ≥6.5。⚠️ 豁免措辞为'已获得'学位,在读者建议确认</t>
         </is>
       </c>
-      <c r="K130" s="21" t="n"/>
+      <c r="K130" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议邮件确认(经 spia.vt.edu MURP 页面联系)</t>
+        </is>
+      </c>
       <c r="L130" s="21" t="inlineStr">
         <is>
           <t>https://spia.vt.edu/academics/graduate/murp/MURP_FAQs.html</t>
@@ -9337,9 +9855,9 @@
           <t>不需要:按项目整体录取,委员会审核时分配奖学金</t>
         </is>
       </c>
-      <c r="G134" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G134" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(美国及非美国公民均可获merit奖学金)。先修:无指定本科专业;⚠️ 官网未查到最低GPA</t>
         </is>
       </c>
       <c r="H134" s="30" t="inlineStr">
@@ -9414,7 +9932,11 @@
           <t>可选(提交则综合考虑,也接受GMAT)</t>
         </is>
       </c>
-      <c r="J135" s="21" t="n"/>
+      <c r="J135" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:项目页指向研究生院英语要求,未查到MCRP具体分数及美国学位豁免条款,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K135" s="30" t="inlineStr">
         <is>
           <t>choquett@uoregon.edu(研究生协调员Bob Choquette);abrown33@uoregon.edu(MCRP主任Anne Brown)</t>
@@ -9457,7 +9979,11 @@
           <t>不需要:按项目整体录取;可预约与MURP主任一对一交流</t>
         </is>
       </c>
-      <c r="G136" s="21" t="n"/>
+      <c r="G136" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(优先轮申请者自动考虑Portland Planning Diversity Award及学院内部资助)。先修:需相当于美国四年制学士学位;⚠️ 官网未查到最低GPA</t>
+        </is>
+      </c>
       <c r="H136" s="30" t="inlineStr">
         <is>
           <t>优先 2026/1/9;第二轮 3/27;第三轮 5/29(补充材料各轮后一周)(按2026周期,2027待公布)</t>
@@ -9515,9 +10041,9 @@
           <t>不需要:按项目整体录取</t>
         </is>
       </c>
-      <c r="G137" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G137" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(研究生院明文国际生可获系管奖学金与assistantship)。先修:本科学位、成绩单、3封推荐信、目标陈述;⚠️ 官网未查到最低GPA</t>
         </is>
       </c>
       <c r="H137" s="30" t="inlineStr">
@@ -9577,7 +10103,11 @@
           <t>不需要:按项目整体录取,滚动审理</t>
         </is>
       </c>
-      <c r="G138" s="21" t="n"/>
+      <c r="G138" s="30" t="inlineStr">
+        <is>
+          <t>可以申请,但两年RA限BIPOC/Hispanic且GPA≥3.5。先修:研究生院最低要求本科高年级GPA≥3.0;⚠️ 未查到指定先修课</t>
+        </is>
+      </c>
       <c r="H138" s="30" t="inlineStr">
         <is>
           <t>系资助 2027/2/15;国际生秋季 2027/1/15(⚠️ 页面正文另写6/1,冲突);美国申请者 7/1;滚动录取</t>
@@ -9588,7 +10118,11 @@
           <t>不需要(MSP暂免GRE)</t>
         </is>
       </c>
-      <c r="J138" s="21" t="n"/>
+      <c r="J138" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生需 TOEFL iBT ≥80 / PTE ≥55,未查到美国学位豁免条款,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K138" s="30" t="inlineStr">
         <is>
           <t>durp@coss.fsu.edu(DURP招生协调员)</t>
@@ -9631,7 +10165,11 @@
           <t>不需要:SOPHAS统一申请,按项目整体录取</t>
         </is>
       </c>
-      <c r="G139" s="21" t="n"/>
+      <c r="G139" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(Harris MCH Scholars学费减免+月津贴,每年3名)。先修:⚠️ 官网未查到具体先修课及最低GPA;仅秋季入学</t>
+        </is>
+      </c>
       <c r="H139" s="30" t="inlineStr">
         <is>
           <t>⚠️ 官网冲突:MCH页写国际生 2026/12/15、国内 2027/2/1;SPH总页写资助优先 12/1、国际生 2/1、最终 4/15;建议12/1前提交</t>
@@ -9709,7 +10247,11 @@
           <t>否(美国学位豁免):Bloomberg 对持有/攻读美国认证大学学士者免语言成绩;否则 TOEFL ≥100/IELTS ≥7/Duolingo ≥130</t>
         </is>
       </c>
-      <c r="K140" s="21" t="n"/>
+      <c r="K140" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(联系PFRH系 Education Office 或 Bloomberg 招生办)</t>
+        </is>
+      </c>
       <c r="L140" s="21" t="inlineStr">
         <is>
           <t>https://publichealth.jhu.edu/academics/academic-program-finder/masters-degrees/msph-in-population-family-and-reproductive-health/msph-frequently-asked-questions</t>
@@ -9767,7 +10309,11 @@
           <t>⚠️ 不明确:目录称有美国以外学习经历者可能需提交,美本可能免交但未明文豁免;门槛 TOEFL 79/IELTS 6.5/PTE 53</t>
         </is>
       </c>
-      <c r="K141" s="21" t="n"/>
+      <c r="K141" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议邮件确认(临床方向研究生主任为 Dr. Tayla Lee)</t>
+        </is>
+      </c>
       <c r="L141" s="21" t="inlineStr">
         <is>
           <t>https://www.bsu.edu/academics/collegesanddepartments/cpspc/admissions-and-financial-aid/graduate-assistantships</t>
@@ -9880,7 +10426,15 @@
 Montclair: 可以申请(⚠️ 资助:校研究生中心统一管理 GA,非项目保证)。先修:心理学学士或≥12学分心理课(须含统计和实验课,导论课不计入);MA Psychological Sciences;申请费$60</t>
         </is>
       </c>
-      <c r="H143" s="21" t="n"/>
+      <c r="H143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: 奖学金优先 2027/3/1;秋季截止 2027/3/15(之后视名额考虑)(按官网常规日期,⚠️2027周期待确认)
+UNCW: ⚠️ 官网有 priority date 但未查到具体日期;面试在1月下旬–3月,建议 2026/12–2027/1 前提交(第三方称2/15或3/15,不可靠)
+ULL: 仅秋季入学;2027/3/1(研究生院 Fall priority 同为3/1)
+NAU: 仅秋季入学;优先 2027/2/1;最终 2027/4/1
+Montclair: 仅秋季入学;优先 2027/4/1(5/15前出结果),之后滚动录取至满额</t>
+        </is>
+      </c>
       <c r="I143" s="30" t="inlineStr">
         <is>
           <t>UNO: ⚠️ 官网 MS 页面未提及 GRE(研究生院称"如系里要求"),建议邮件确认
@@ -9890,7 +10444,15 @@
 Montclair: 必需,但本科总 GPA≥3.3 可豁免</t>
         </is>
       </c>
-      <c r="J143" s="21" t="n"/>
+      <c r="J143" s="30" t="inlineStr">
+        <is>
+          <t>UNO: 否(美国认证院校学士豁免)
+UNCW: ⚠️ 不明确:研究生院页面未查到美国学位豁免条款(第三方称 TOEFL 79/IELTS 6.5),建议问 gradschool@uncw.edu
+ULL: 否(美国认证院校且以英语授课的学位豁免;研究生院保留要求证明的权利)
+NAU: 否(持美国学士及以上学位可豁免 TOEFL/IELTS)
+Montclair: 否(在美国区域认证院校全日制就读≥1学年即豁免)</t>
+        </is>
+      </c>
       <c r="K143" s="30" t="inlineStr">
         <is>
           <t>UNO: taknaus@uno.edu(Dr. Tracey Knaus,心理学 MS 联系人)
@@ -9961,7 +10523,11 @@
           <t>⚠️ 不明确:目录称有美国以外学习经历者可能需提交,美本可能免交但未明文豁免;门槛 TOEFL 79/IELTS 6.5/PTE 53</t>
         </is>
       </c>
-      <c r="K144" s="21" t="n"/>
+      <c r="K144" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议邮件确认(临床方向研究生主任为 Dr. Tayla Lee)</t>
+        </is>
+      </c>
       <c r="L144" s="21" t="inlineStr">
         <is>
           <t>https://www.bsu.edu/academics/collegesanddepartments/psychological-science/admissions-financial-aid/graduate-assistantships</t>
@@ -10014,7 +10580,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J145" s="21" t="n"/>
+      <c r="J145" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:未查到美国学位豁免条款;要求 TOEFL ≥79/Duolingo ≥110(⚠️IELTS 6.5 来自第三方)</t>
+        </is>
+      </c>
       <c r="K145" s="30" t="inlineStr">
         <is>
           <t>paul.fuglestad@unf.edu(项目主任 Dr. Paul Fuglestad);psychgrad@unf.edu(心理系研究生咨询,可能为旧地址)</t>
@@ -10077,7 +10647,11 @@
           <t>否(美国学位豁免):国际招生FAQ称毕业于美国大学可免语言证明(系可能另要求英语测试);否则 TOEFL 78/IELTS 6.0</t>
         </is>
       </c>
-      <c r="K146" s="21" t="n"/>
+      <c r="K146" s="30" t="inlineStr">
+        <is>
+          <t>psychology@csuohio.edu(心理系通用邮箱;MA项目主任邮箱未查到)</t>
+        </is>
+      </c>
       <c r="L146" s="21" t="inlineStr">
         <is>
           <t>https://artsandsciences.csuohio.edu/psychology/psychological-science</t>
@@ -10130,7 +10704,11 @@
           <t>不需要(系FAQ明确不要求;旧手册写可选)</t>
         </is>
       </c>
-      <c r="J147" s="21" t="n"/>
+      <c r="J147" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:UCCS研究生院按项目设英语要求,商学院明文美国学位豁免,心理系未查到明文;数学系标准为TOEFL 80/IELTS 6.5可参考,建议邮件确认</t>
+        </is>
+      </c>
       <c r="K147" s="30" t="inlineStr">
         <is>
           <t>alac@uccs.edu(Andrew Lac,Psychological Science培养主任);intladms@uccs.edu(国际生招生)</t>
@@ -10313,7 +10891,11 @@
           <t>⚠️ 不明确:研究生院按国家列豁免清单,美国学位未明文列出,可向国际招生申请豁免;⚠️第三方 TOEFL 75/IELTS 6.0</t>
         </is>
       </c>
-      <c r="K150" s="21" t="n"/>
+      <c r="K150" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 项目协调员邮箱未查到;international.admissions@emich.edu(国际招生,语言豁免咨询);心理系电话 734.487.1155</t>
+        </is>
+      </c>
       <c r="L150" s="21" t="inlineStr">
         <is>
           <t>https://www.emich.edu/psychology/documents/experimental-student-handbook.pdf</t>
@@ -10366,8 +10948,16 @@
           <t>⚠️ 不明确:学校称多数项目不要求GRE,第三方称需要/可豁免,建议确认</t>
         </is>
       </c>
-      <c r="J151" s="21" t="n"/>
-      <c r="K151" s="21" t="n"/>
+      <c r="J151" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:豁免条件未查到;TOEFL iBT 83(2026/1/21后新版 4.5)/IELTS 6.5/Duolingo 105/PTE 53</t>
+        </is>
+      </c>
+      <c r="K151" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(研究生院或心理系)</t>
+        </is>
+      </c>
       <c r="L151" s="21" t="inlineStr">
         <is>
           <t>https://www.montclair.edu/psychology/graduate-programs/ma-in-psychological-sciences/financial-support-general/</t>
@@ -10420,8 +11010,16 @@
           <t>可选(用于资助评估,建议提交)</t>
         </is>
       </c>
-      <c r="J152" s="21" t="n"/>
-      <c r="K152" s="21" t="n"/>
+      <c r="J152" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:非英语母语需证明,未查到美国学位豁免;⚠️第三方 TOEFL ≥80(单项≥17)/IELTS 6.5</t>
+        </is>
+      </c>
+      <c r="K152" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 邮箱未查到;GPES 办公室协调员 Cariann Linehan,315-470-6528(邮箱见 GPES How to Apply 页)</t>
+        </is>
+      </c>
       <c r="L152" s="21" t="inlineStr">
         <is>
           <t>https://www.esf.edu/graduate/funding/esf-graduate-funding-sources.php</t>
@@ -10655,7 +11253,11 @@
           <t>⚠️ 资助优先 2026/11/30;最终 2027/4/30(官网未注明年份,按往年周期)</t>
         </is>
       </c>
-      <c r="I156" s="21" t="n"/>
+      <c r="I156" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到;第三方称需GRE(5年内有效,低GPA条件录取需提交),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J156" s="30" t="inlineStr">
         <is>
           <t>否(美国学士学位在研究生院豁免国家列表内);当GTA需口语认证(⚠️美国学士24个月内毕业或可豁免)</t>
@@ -10889,15 +11491,31 @@
           <t>强烈建议:官网鼓励申请前联系相关教授,申请表需填写研究方向匹配的教授</t>
         </is>
       </c>
-      <c r="G160" s="21" t="n"/>
-      <c r="H160" s="21" t="n"/>
-      <c r="I160" s="21" t="n"/>
+      <c r="G160" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(校级GA享州外学费减免)。⚠️ 具体先修/最低GPA官网未查到;录取综合看个人素质(领导力、协作、专业性)与学术成绩</t>
+        </is>
+      </c>
+      <c r="H160" s="30" t="inlineStr">
+        <is>
+          <t>资助优先 2027/1/15(秋)、2026/10/15(春);⚠️ 最终截止官网未查到</t>
+        </is>
+      </c>
+      <c r="I160" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到(研究生院不要求,由系自定),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J160" s="30" t="inlineStr">
         <is>
           <t>否(英语授课认证大学学士学位豁免,研究生院审核成绩单后标注);否则TOEFL iBT≥90</t>
         </is>
       </c>
-      <c r="K160" s="21" t="n"/>
+      <c r="K160" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 研究生协调员邮箱未查到;jfknight@vt.edu(系主任);教授邮箱见 frec.vt.edu/people/Faculty.html</t>
+        </is>
+      </c>
       <c r="L160" s="21" t="inlineStr">
         <is>
           <t>https://frec.vt.edu/students/graduate.html</t>
@@ -10955,7 +11573,11 @@
           <t>否(美国学位按GCAC-305豁免;⚠️系里列TOEFL为评估项,建议确认);否则TOEFL新制4.5(口语3.5)/旧制80(口语19)、IELTS 6.5</t>
         </is>
       </c>
-      <c r="K161" s="21" t="n"/>
+      <c r="K161" s="30" t="inlineStr">
+        <is>
+          <t>nmh5631@psu.edu(研究生项目协调员 Nicole Houck);研究生主任 Patrick Drohan(⚠️邮箱未查到)</t>
+        </is>
+      </c>
       <c r="L161" s="21" t="inlineStr">
         <is>
           <t>https://ecosystems.psu.edu/graduate/funding</t>
@@ -10993,7 +11615,11 @@
           <t>必须:录取完全由教师决定,'No student is admitted without a designated faculty major advisor'</t>
         </is>
       </c>
-      <c r="G162" s="21" t="n"/>
+      <c r="G162" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(资助为导师外部经费RA或TA)。需先满足研究生院要求;⚠️ 具体先修/最低GPA官网未查到</t>
+        </is>
+      </c>
       <c r="H162" s="30" t="inlineStr">
         <is>
           <t>⚠️ 秋季 2027/2/1(按2025周期,2027待公布);春季 10/1(第三方)</t>
@@ -11056,7 +11682,11 @@
           <t>可以申请(仅最强申请人可能获学费减免+stipend;RA/TA由导师视经费任命)。先修:大学代数、生物、普通化学,均需B及以上;推荐GPA≥3.0;需CV、1–2页目标陈述、3封推荐信</t>
         </is>
       </c>
-      <c r="H163" s="21" t="n"/>
+      <c r="H163" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(仅秋季入学;官网建议尽早提交)</t>
+        </is>
+      </c>
       <c r="I163" s="30" t="inlineStr">
         <is>
           <t>不需要</t>
@@ -11114,7 +11744,11 @@
           <t>可以申请(国际生可申GA/导师RA)。先修:自然资源或相关领域学士学位;最低GPA 3.0(4分制),未达标者可能以provisional身份录取</t>
         </is>
       </c>
-      <c r="H164" s="21" t="n"/>
+      <c r="H164" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目截止日;SNR内部GA截止12/13;研究生院建议滚动项目秋季入学于3/1前提交,材料至少提前1个月交齐,建议邮件确认</t>
+        </is>
+      </c>
       <c r="I164" s="30" t="inlineStr">
         <is>
           <t>⚠️ SNR页面列为需提交(5年内有效,建议V153/Q149/AW4.0),页面可能过时,建议邮件确认</t>
@@ -11187,7 +11821,11 @@
           <t>⚠️ 不明确:TOEFL iBT≥79(2026/1/21后新版≥4.5,各项≥4.0)/IELTS≥6.5;研究生院称美国认证院校学位可被考虑豁免,但逐案审核</t>
         </is>
       </c>
-      <c r="K165" s="21" t="n"/>
+      <c r="K165" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目招生邮箱,建议直接邮件目标导师(见 cfwe.auburn.edu/faculty-directory)</t>
+        </is>
+      </c>
       <c r="L165" s="21" t="inlineStr">
         <is>
           <t>https://cfwe.auburn.edu/research-assistantships-and-positions/</t>
@@ -11245,7 +11883,11 @@
           <t>否(美国学位豁免):UGA研究生院规定美国认证大学学位一般免交TOEFL/IELTS(个别项目可另要求);如需:TOEFL 80(各项≥20)/IELTS 6.5;当TA另有英语要求</t>
         </is>
       </c>
-      <c r="K166" s="21" t="n"/>
+      <c r="K166" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议通过Warnell Graduate Office确认;资助咨询例:bolding@uga.edu;jlconrad@uga.edu(森林经营方向教师)</t>
+        </is>
+      </c>
       <c r="L166" s="21" t="inlineStr">
         <is>
           <t>https://warnell.uga.edu/life-graduate-student</t>
@@ -11355,7 +11997,11 @@
           <t>奖学金提名 2026/12/31(需完成申请);国际生最终 2027/2/1;国内 2027/5/1</t>
         </is>
       </c>
-      <c r="I168" s="21" t="n"/>
+      <c r="I168" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到GRE要求,建议邮件确认</t>
+        </is>
+      </c>
       <c r="J168" s="30" t="inlineStr">
         <is>
           <t>否(美国学位豁免):TAMU规定持美国认证院校学士学位免交成绩(项目可另设更高要求);当TA需通过ELPE口语(≥80)或申请替代认证</t>
@@ -11403,7 +12049,11 @@
           <t>不需要:按项目整体录取;GSRA多入学后申请,可在申请材料中提及感兴趣教授</t>
         </is>
       </c>
-      <c r="G169" s="21" t="n"/>
+      <c r="G169" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GSI/GSRA竞争性,多入学后申请)。先修:跨学科项目,不限本科专业;⚠️ 具体先修课/GPA官网未查到</t>
+        </is>
+      </c>
       <c r="H169" s="30" t="inlineStr">
         <is>
           <t>资助优先 2026/12/15;资助最终 2027/1/14;最终:国际生 2027/4/1,国内 2027/4/30</t>
@@ -11414,7 +12064,11 @@
           <t>不接受(已不再要求也不接受GRE)</t>
         </is>
       </c>
-      <c r="J169" s="21" t="n"/>
+      <c r="J169" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:SEAS页面未查到,Rackham一般对英语授课学位豁免,建议确认;当GSI需英语口语评估</t>
+        </is>
+      </c>
       <c r="K169" s="30" t="inlineStr">
         <is>
           <t>⚠️ seas-admissions@umich.edu(SEAS招生,据记忆需核实);电话 (734) 764-6453</t>
@@ -11467,7 +12121,11 @@
           <t>2026/12/15(现行bulletin;旧版为1/15,逾期视名额审理)</t>
         </is>
       </c>
-      <c r="I170" s="21" t="n"/>
+      <c r="I170" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到明确政策(bulletin称以学院官网为准,第三方列为必需),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J170" s="30" t="inlineStr">
         <is>
           <t>否(美国本科学位豁免TOEFL/IELTS/DET;学院不设最低分;入学后非母语者需参加英语测试)</t>
@@ -11515,9 +12173,9 @@
           <t>⚠️ 不需要:按项目整体录取,官网未见套磁要求,文书可写感兴趣的教授</t>
         </is>
       </c>
-      <c r="G171" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G171" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(Block Grant仅第一学期,之后靠GSR/GSI)。⚠️ 未查到具体先修课及GPA要求,建议邮件确认;仅秋季入学</t>
         </is>
       </c>
       <c r="H171" s="30" t="inlineStr">
@@ -11592,7 +12250,11 @@
           <t>不需要(系FAQ:目前不要求GRE;第三方仍列必需)</t>
         </is>
       </c>
-      <c r="J172" s="21" t="n"/>
+      <c r="J172" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:非英语母语需TOEFL(研究生院要求,iBT约79-80);未查到美国学位豁免,建议问协调员</t>
+        </is>
+      </c>
       <c r="K172" s="30" t="inlineStr">
         <is>
           <t>rachel.montoya@ttu.edu(研究生协调员 Rachel Montoya);nrm@ttu.edu(系办)</t>
@@ -11655,7 +12317,11 @@
           <t>否(美国学位豁免:研究生院规定美国区域认证院校英语授课学士可豁免;⚠️ GGE页面措辞较旧,建议确认)</t>
         </is>
       </c>
-      <c r="K173" s="21" t="n"/>
+      <c r="K173" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目协调员邮箱,建议通过 ecology.ucdavis.edu 联系 Graduate Program Coordinator</t>
+        </is>
+      </c>
       <c r="L173" s="21" t="inlineStr">
         <is>
           <t>https://ecology.ucdavis.edu/funding</t>
@@ -11713,7 +12379,11 @@
           <t>否(美国学位豁免:研究生院规定美国区域认证院校英语授课学位可豁免);否则TOEFL iBT≥80(新版≥4.0)</t>
         </is>
       </c>
-      <c r="K174" s="21" t="n"/>
+      <c r="K174" s="30" t="inlineStr">
+        <is>
+          <t>grdadmis@ucr.edu(研究生院招生办);⚠️ 项目Student Services Advisor邮箱官网未查到</t>
+        </is>
+      </c>
       <c r="L174" s="21" t="inlineStr">
         <is>
           <t>https://envisci.ucr.edu/graduate/prospective-students/faq</t>
@@ -11771,7 +12441,11 @@
           <t>⚠️ 不明确:需TOEFL(2026/1/21前考试≥100,新版标准见官网);学院豁免列表未完整查到,Rackham规定本科全程于英语授课院校获学位可豁免,建议确认</t>
         </is>
       </c>
-      <c r="K175" s="21" t="n"/>
+      <c r="K175" s="30" t="inlineStr">
+        <is>
+          <t>sph-inquiries@umich.edu(公共卫生学院招生团队);⚠️ 生统MS专用邮箱未查到,电话734-615-9812</t>
+        </is>
+      </c>
       <c r="L175" s="21" t="inlineStr">
         <is>
           <t>https://sph.umich.edu/biostat/programs/faq.html</t>
@@ -12174,7 +12848,11 @@
           <t>否(在美国全日制学习≥4学期且平均B以上可豁免,美本符合);否则TOEFL≥98(新制5.0),IELTS≥7.0,Duolingo≥125</t>
         </is>
       </c>
-      <c r="K181" s="21" t="n"/>
+      <c r="K181" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 官网邮箱在搜索结果中被隐藏未查到;Biostat电话 518-442-2450,Epi语言豁免联系人 Chloe Glenn,建议到 albany.edu/cihs 项目页获取邮箱</t>
+        </is>
+      </c>
       <c r="L181" s="21" t="inlineStr">
         <is>
           <t>https://www.albany.edu/cihs/graduate-admissions#tab-costs-aid</t>
@@ -12393,16 +13071,78 @@
           <t>各校 GA/TA(津贴+学费减免或外州豁免);ISU 历史上接近 A</t>
         </is>
       </c>
-      <c r="F185" s="21" t="n"/>
-      <c r="G185" s="21" t="inlineStr">
-        <is>
-          <t>部分明确可</t>
-        </is>
-      </c>
-      <c r="H185" s="21" t="n"/>
-      <c r="I185" s="21" t="n"/>
-      <c r="J185" s="21" t="n"/>
-      <c r="K185" s="21" t="n"/>
+      <c r="F185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: 不需要:按项目整体录取,个人陈述可写感兴趣的教授
+Mississippi State: 不需要:按项目整体录取,个人陈述可写感兴趣的教授
+UGA: 不需要:按项目整体录取,个人陈述可写感兴趣的教授
+Texas Tech: 不需要:按项目整体录取;想拿TA需联系社会学研究生项目主任申请
+Illinois State: 不需要:按项目整体录取,个人陈述可写感兴趣的教授
+U Alabama: ❌ 不适用:⚠️ Tuscaloosa 校区未查到社会学硕士项目
+South Dakota State: 不需要:按项目整体录取,但个人陈述须说明目标与教师研究专长的契合
+U Montana: 不需要:按项目整体录取,个人陈述可写感兴趣的教授</t>
+        </is>
+      </c>
+      <c r="G185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: 可以申请。MA 36学分含论文;非社会学背景可能需补修 leveling 课程;⚠️ GPA 3.0(最后60学时,来自Peterson's)
+Mississippi State: 可以申请(系有TA/RA)。先修:最后两年 GPA 3.0,英文学术写作样本、3封推荐信、个人陈述
+UGA: 可以申请。MA 定位为读PhD的预备;需CV、个人陈述、写作样本
+Texas Tech: 可以申请(早申请可获TA考虑,TA名额有限、多在秋季发放)。先修:GPA ≥3.0;个人陈述、2封推荐信、CV、10-15页写作样本
+Illinois State: 可以申请(GA需无条件录取+全日制)。先修:最后60学时 GPA 3.0;简历、2页个人陈述、≥5页写作样本、3位推荐人
+U Alabama: ❌ ⚠️ 经两次搜索,UA Tuscaloosa 未查到社会学硕士:社会学仅为本科辅修(隶属 Gender and Race Studies 系);相近项目为 Criminology &amp; Criminal Justice MS/PhD;社会学 MA/PhD 在 UAB(伯明翰,另一所大学)。建议改投或删除
+South Dakota State: 可以申请(⚠️ Peterson's 列有TA/RA/GA)。项目名为 Social Science M.S.(心理/社会学/农村研究学院);GPA ≥3.0 可无条件录取;2封推荐信、写作样本、个人陈述
+U Montana: 可以申请(少量TA,含学费减免)。⚠️ 旧页面要求最后两年 GPA 3.3</t>
+        </is>
+      </c>
+      <c r="H185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: 秋季优先 2027/2/1(国内/国际相同,按官网现行页面)
+Mississippi State: ⚠️ 资助考虑 2/15(系材料);⚠️ 最终 4/15(国际生 5/1)(Peterson's)
+UGA: 12/15(系 How to Apply 页面;⚠️ Peterson's 另列 2/1、国际 1/1,以系页面为准)
+Texas Tech: 秋季 2027/3/1(春季 11/1);想拿TA建议尽早
+Illinois State: 秋季 2027/2/1;⚠️ 资助申请 4/1(Peterson's)
+U Alabama: ❌ 不适用(未查到该项目)
+South Dakota State: 研究生院秋季截止 4/15(之后可能不经系正式审核);⚠️ Peterson's 列 3/1;想拿助教建议 3/1 前提交
+U Montana: 资助考虑 2027/2/15;秋季优先 5/1(之后视名额)</t>
+        </is>
+      </c>
+      <c r="I185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: 不需要
+Mississippi State: 不需要(研究生院2021年起取消;部分系可能为助教资格要求,建议确认)
+UGA: ⚠️ 可选/不需要(Fall 2022起不要求,现行政策未确认)
+Texas Tech: 可选(不要求,提交则参考 V/Q)
+Illinois State: 可选(不要求,低GPA可提交)
+U Alabama: ❌ 不适用(未查到该项目;UA 研究生院规定 GRE 由各项目自定)
+South Dakota State: 必需(2025-26 研究生目录 Social Science M.S. 列 GRE required;⚠️ 建议邮件确认是否仍执行)
+U Montana: ⚠️ 不需要(研究生项目页未列;旧页面曾要求)</t>
+        </is>
+      </c>
+      <c r="J185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: 否(美国学位豁免);否则 TOEFL 78 / IELTS 6.5
+Mississippi State: 否(美国学位豁免:研究生院国际生页注明持美国学士及以上学位者无需提交英语成绩);⚠️ TA 口语要求未查到
+UGA: 否(美国学位豁免,2025年3月新政);但毕业超2年且期间在非英语国家生活/工作需重新提交;部分系可另行要求;TA 另有英语能力要求
+Texas Tech: 否(美国区域认证大学毕业豁免,或在美连续就读满2年);否则 TOEFL iBT 79 / IELTS 6.5
+Illinois State: ⚠️ 不明确:国际生须提交两年内成绩(TOEFL iBT 81 / IELTS 6.5)除非符合豁免;豁免指南列美国学士,但该文件偏本科路径项目,建议邮件 InternationalAdmissions@IllinoisState.edu 确认
+U Alabama: ❌ 不适用(未查到该项目)
+South Dakota State: 否(美国区域认证学士豁免,研究生招生页);否则 TOEFL 90 / IELTS 6.5 / Duolingo 115
+U Montana: 否(美国学位豁免,研究生院 Policy A8.300)</t>
+        </is>
+      </c>
+      <c r="K185" s="30" t="inlineStr">
+        <is>
+          <t>Texas State: dd34@txstate.edu(研究生项目主任 Dr. David Dietrich);sociology@txstate.edu(系办)
+Mississippi State: sociology@soc.msstate.edu(系/研究生协调)
+UGA: socigrad@uga.edu(社会学研究生项目)
+Texas Tech: sociology@ttu.edu(系办,研究生项目主任 Dr. Brandon Wagner,个人邮箱未查到);graduate.admissions@ttu.edu(研究生院招生)
+Illinois State: wavogo@ilstu.edu(研究生协调员 Dr. Winfred Avogo);⚠️ mcwille@IllinoisState.edu(2025年新闻署名协调员 Dr. Marion Willetts,现任者待确认)
+U Alabama: ❌ 不适用(未查到该项目)
+South Dakota State: ⚠️ sdsu.sopsrs@sdstate.edu(心理/社会学/农村研究学院通用邮箱,来自学院社交页);代理研究生协调员 Paul Markel 电话 605-688-4322(邮箱未查到)
+U Montana: mark.heirigs@mso.umt.edu(研究生项目协调员 Mark Heirigs)</t>
+        </is>
+      </c>
       <c r="L185" s="30" t="inlineStr">
         <is>
           <t>Texas State: https://gradcollege.txst.edu/programs/sociology.html
@@ -12524,7 +13264,11 @@
           <t>不需要(系申请页明确不再要求GRE)</t>
         </is>
       </c>
-      <c r="J187" s="21" t="n"/>
+      <c r="J187" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院对在英语为主要语言国家的认证院校获学士学位者自动豁免;否则 TOEFL ≥79 / IELTS ≥6.5 / DET ≥115 / PTE ≥53。⚠️ 任TA是否需口语测试未查到</t>
+        </is>
+      </c>
       <c r="K187" s="30" t="inlineStr">
         <is>
           <t>jonathan.s.coley@okstate.edu(研究生项目主任 Jonathan Coley);grad-i@okstate.edu(研究生院国际招生)</t>
@@ -12567,18 +13311,26 @@
           <t>不需要:按项目整体录取,所有申请者自动参与资助评审;目标陈述中写研究兴趣及与教师的匹配即可</t>
         </is>
       </c>
-      <c r="G188" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="H188" s="21" t="n"/>
+      <c r="G188" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(所有申请者自动考虑GA资助)。先修:入学前须获学士学位;材料为1-2页目标陈述(学术/研究兴趣、职业目标)+3封教授推荐信;⚠️ 最低GPA与先修课官网未查到。论文型MA,30学分</t>
+        </is>
+      </c>
+      <c r="H188" s="30" t="inlineStr">
+        <is>
+          <t>秋季优先 2026/12/1(此前提交获最优先考虑,含资助);⚠️ 最终截止未查到,建议12/1前提交</t>
+        </is>
+      </c>
       <c r="I188" s="30" t="inlineStr">
         <is>
           <t>不需要(自2026秋季入学起取消GRE;旧版2025-26目录仍写需要)</t>
         </is>
       </c>
-      <c r="J188" s="21" t="n"/>
+      <c r="J188" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):入学时已在美国大学完成≥2年学习即免考(可能需书面向国际招生办申请豁免);否则 TOEFL ≥94 / IELTS ≥7.0 / PTE ≥65 / DET ≥120,未达分者不予考虑。⚠️ 任TA是否需口语测试未查到</t>
+        </is>
+      </c>
       <c r="K188" s="30" t="inlineStr">
         <is>
           <t>sroxburg@kent.edu(研究生项目协调员 Susan Roxburgh);soc_crim@kent.edu(系办公室)</t>
@@ -12621,9 +13373,9 @@
           <t>不需要:按项目整体录取;个人陈述说明攻读社会学的原因与兴趣方向即可</t>
         </is>
       </c>
-      <c r="G189" s="21" t="inlineStr">
-        <is>
-          <t>可</t>
+      <c r="G189" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(GA含学费杂费减免,明确包括州外/国际学费)。先修:须修过本科社会学研究方法、理论、统计课(或证明等同);材料:1-2页个人陈述+3封推荐信;⚠️ 最低GPA未查到</t>
         </is>
       </c>
       <c r="H189" s="30" t="inlineStr">
@@ -12636,7 +13388,11 @@
           <t>不需要(系官网明确不要求GRE;Peterson's称需要,已过时)</t>
         </is>
       </c>
-      <c r="J189" s="21" t="n"/>
+      <c r="J189" s="30" t="inlineStr">
+        <is>
+          <t>否(美国学位豁免):研究生院接受认证美国院校学士/硕士学位作为英语能力证明(需正式成绩单);否则 TOEFL ≥80 / IELTS ≥6.5 / DET ≥110 / PTE ≥59。⚠️ 任TA是否需口语测试未查到</t>
+        </is>
+      </c>
       <c r="K189" s="30" t="inlineStr">
         <is>
           <t>socgradcoord@memphis.edu(研究生项目邮箱);tmccuddy@memphis.edu(研究生主任 Timothy McCuddy)</t>
@@ -12803,7 +13559,11 @@
           <t>不需要:按项目整体录取,2/1前申请自动考虑GA</t>
         </is>
       </c>
-      <c r="G192" s="21" t="n"/>
+      <c r="G192" s="30" t="inlineStr">
+        <is>
+          <t>可以申请(⚠️ 未查到国际生资助限制)。先修:本科社科≥24学分,其中社会学≥15学分,含理论和研究方法(不足可入学后补);社会学课程GPA≥3.0;传记陈述、写作样本、3封推荐信;仅秋季入学</t>
+        </is>
+      </c>
       <c r="H192" s="30" t="inlineStr">
         <is>
           <t>GA资助 2027/2/1;其他申请至 2027/6/30(按系网页,2027待确认)</t>
@@ -12814,7 +13574,11 @@
           <t>不需要(系页面;⚠️旧目录列GRE,建议确认)</t>
         </is>
       </c>
-      <c r="J192" s="21" t="n"/>
+      <c r="J192" s="30" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生英语要求仅列WMU学位为替代,未查到美国学位豁免;TOEFL iBT≥80</t>
+        </is>
+      </c>
       <c r="K192" s="30" t="inlineStr">
         <is>
           <t>⚠️ 研究生主任 Patrick Cundiff(邮箱未显示,电话 269-387-5293);系办公室 269-387-5270,建议邮件确认</t>
@@ -13120,7 +13884,11 @@
           <t>⚠️ 不需要(系页称不要求GRE,未完全确认为HDFS页)</t>
         </is>
       </c>
-      <c r="J197" s="22" t="n"/>
+      <c r="J197" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院有英语豁免机制但未查到美国学位豁免细则;第三方:TOEFL ≥79,IELTS ≥6.5,Duolingo ≥110</t>
+        </is>
+      </c>
       <c r="K197" s="31" t="inlineStr">
         <is>
           <t>dcasper@ches.ua.edu(Deborah Casper,研究生项目协调员)</t>
@@ -13307,7 +14075,11 @@
           <t>否(美国认证大学学士学位豁免);否则 TOEFL ≥71,IELTS ≥6.0,Duolingo ≥100</t>
         </is>
       </c>
-      <c r="K200" s="22" t="n"/>
+      <c r="K200" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 项目联系人 Amber Letcher 邮箱未查到(电话 605-688-4941);gradschl@sdstate.edu(研究生院)</t>
+        </is>
+      </c>
       <c r="L200" s="22" t="inlineStr">
         <is>
           <t>https://www.sdstate.edu/programs/graduate/human-sciences-ms-human-development-family-science-specialization</t>
@@ -13350,7 +14122,11 @@
           <t>可以申请。先修:儿童发展、家庭研究、心理、社会学、教育或相关本科;GPA ≥2.7;本科至少各修1门儿童发展和家庭研究课程(否则可能需补修);需3封推荐信、目的陈述</t>
         </is>
       </c>
-      <c r="H201" s="22" t="n"/>
+      <c r="H201" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认</t>
+        </is>
+      </c>
       <c r="I201" s="31" t="inlineStr">
         <is>
           <t>⚠️ 项目页未提及GRE,大概率不需要,建议邮件确认</t>
@@ -13666,8 +14442,16 @@
           <t>不需要(系招生页明确不要求GRE)</t>
         </is>
       </c>
-      <c r="J206" s="22" t="n"/>
-      <c r="K206" s="22" t="n"/>
+      <c r="J206" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 很可能否:UK部分院系页写明美国认证学士学位可豁免TOEFL,但研究生院统一政策页未查到原文;如需提交:TOEFL iBT ≥79,IELTS ≥6.5,建议邮件确认</t>
+        </is>
+      </c>
+      <c r="K206" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱;项目主任 Alexander T. Vazsonyi, Ph.D.(Director),建议通过系网站 fam.mgcafe.uky.edu 联系方式确认</t>
+        </is>
+      </c>
       <c r="L206" s="22" t="inlineStr">
         <is>
           <t>https://fam.mgcafe.uky.edu/content/funding</t>
@@ -13787,7 +14571,11 @@
           <t>⚠️ 很可能否:ODU英语要求页列'在英语为官方语言国家的认证院校获学士/硕士学位'可满足要求(未点名美国,措辞有版本差异);否则 TOEFL iBT ≥79(2026/1/21后新制≥4.5),IELTS ≥6.5,Duolingo ≥120</t>
         </is>
       </c>
-      <c r="K208" s="22" t="n"/>
+      <c r="K208" s="31" t="inlineStr">
+        <is>
+          <t>jsph@odu.edu(Joint School of Public Health 总邮箱,757-683-4259);⚠️ MHA项目主任邮箱官网未查到</t>
+        </is>
+      </c>
       <c r="L208" s="22" t="inlineStr">
         <is>
           <t>https://catalog.odu.edu/graduate/financialawardsforgraduatestudents/</t>
@@ -14135,15 +14923,31 @@
           <t>不需要:按项目整体录取;可预约招生咨询(advising appointment)</t>
         </is>
       </c>
-      <c r="G214" s="22" t="n"/>
+      <c r="G214" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(fee-based项目,院方不保证资助,≤6个Master's Fellowship)。先修:区域认证学士学位(GPA要求未查全);无指定先修课;最具竞争力者有≥1年医疗相关工作经验;需研究生院申请+MHA补充申请。</t>
+        </is>
+      </c>
       <c r="H214" s="31" t="inlineStr">
         <is>
           <t>优先 2026/12/1;常规截止 2027/1/15(2026/9/1开放,滚动审理)</t>
         </is>
       </c>
-      <c r="I214" s="22" t="n"/>
-      <c r="J214" s="22" t="n"/>
-      <c r="K214" s="22" t="n"/>
+      <c r="I214" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 可能不需要:官网未查到全日制MHA的GRE政策;Executive MHA已取消GRE要求,第三方列为No GRE</t>
+        </is>
+      </c>
+      <c r="J214" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:本次搜索未查到MHA页对美国学位的豁免说明,建议向uwgrad@uw.edu确认</t>
+        </is>
+      </c>
+      <c r="K214" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到MHA项目邮箱(页面指向招生专员);uwgrad@uw.edu(UW研究生院,英语要求问题)</t>
+        </is>
+      </c>
       <c r="L214" s="22" t="inlineStr">
         <is>
           <t>https://sph.washington.edu/students/sph-scholarships-and-funding</t>
@@ -14258,7 +15062,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J216" s="22" t="n"/>
+      <c r="J216" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:UNT官网未查到美国学位豁免条款;第三方称TOEFL ≥79/IELTS ≥6.0,建议向GradAdmission@unt.edu确认</t>
+        </is>
+      </c>
       <c r="K216" s="31" t="inlineStr">
         <is>
           <t>Sabrina.Queen@unt.edu(KHPR研究生协调员);khpr@unt.edu(系办公室)</t>
@@ -14306,7 +15114,11 @@
           <t>可以申请(F/J签证学生明文可任GA)。先修:区域认证学士学位;本科运动科学课程≥6学分(2025秋起,不足需补修leveling课);GPA≥2.75(总GPA或最后60学时)。需简历、约500字个人陈述、3封推荐信</t>
         </is>
       </c>
-      <c r="H217" s="22" t="n"/>
+      <c r="H217" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网设优先截止日,之后按名额滚动审核至招满(2027秋具体日期官网未查到,建议尽早提交);第三方 Peterson's:国际生 2/1、国内 5/15(可能过时)</t>
+        </is>
+      </c>
       <c r="I217" s="31" t="inlineStr">
         <is>
           <t>不需要</t>
@@ -14317,7 +15129,11 @@
           <t>否(美国区域认证大学学士学位豁免);否则 TOEFL iBT ≥78,PTE ≥52,Duolingo ≥110</t>
         </is>
       </c>
-      <c r="K217" s="22" t="n"/>
+      <c r="K217" s="31" t="inlineStr">
+        <is>
+          <t>gradcollege@txstate.edu(研究生院招生);⚠️ tingliu@txstate.edu(Peterson's 所列研究生导师,可能过时;官网现列 Dr. Joni Mettler,邮箱未查到)</t>
+        </is>
+      </c>
       <c r="L217" s="22" t="inlineStr">
         <is>
           <t>https://www.gradcollege.txst.edu/programs/exercise-science.html</t>
@@ -14365,13 +15181,21 @@
           <t>Exercise Physiology 优先及部门助教截止 1/1(生物力学 2/1);国际生需在 12/31 前完成研究生院申请;之后有名额可补录(⚠️ 按往年系页面,2027待核实)</t>
         </is>
       </c>
-      <c r="I218" s="22" t="n"/>
+      <c r="I218" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(第三方称不需要)</t>
+        </is>
+      </c>
       <c r="J218" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:研究生院政策对“学位授予院校以英语为主要教学语言”者豁免,美本应可适用但未明文写美国学位;否则 TOEFL iBT ≥80(各项约20)、IELTS ≥6.5、Duolingo ≥120</t>
         </is>
       </c>
-      <c r="K218" s="22" t="n"/>
+      <c r="K218" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议通过系网站 cehhs.utk.edu/krss 或 UTK Graduate Admissions 联系确认</t>
+        </is>
+      </c>
       <c r="L218" s="22" t="inlineStr">
         <is>
           <t>https://cehhs.utk.edu/krss/graduate/kinesiology-masters-degree-programs/</t>
@@ -14476,7 +15300,11 @@
           <t>可以申请。GPA≥3.0无条件录取(2.70–2.99可临时录取);⚠️ 未列具体先修课。需2封推荐信、≤300字目标陈述、成绩单。论文(30+6学分)或非论文36学分+综合考试</t>
         </is>
       </c>
-      <c r="H220" s="22" t="n"/>
+      <c r="H220" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 第三方 Peterson's:秋季 7/1(国内与国际生相同),春季 11/1;官网未查到项目专门截止日,建议邮件确认</t>
+        </is>
+      </c>
       <c r="I220" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:Peterson's 列为需要GRE(可能过时),其他来源称无要求,建议邮件确认</t>
@@ -14549,7 +15377,11 @@
           <t>否(美国认证院校学士学位豁免);否则 IELTS ≥6.5、Duolingo ≥110、TOEFL iBT ≥79</t>
         </is>
       </c>
-      <c r="K221" s="22" t="n"/>
+      <c r="K221" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目协调员邮箱(运动科学研究生协调员 Allison Barry,电话 605-688-4829;GA联系 Lee Weidauer,605-688-4630),建议通过 sdstate.edu 目录查询</t>
+        </is>
+      </c>
       <c r="L221" s="22" t="inlineStr">
         <is>
           <t>https://www.sdstate.edu/graduate-school/graduate-assistantships</t>
@@ -14716,7 +15548,11 @@
           <t>可以申请(运动科学方向有TA资助机会)。先修:区域认证学士,GPA≥3.0(或最后60学分3.0等替代条件);未列具体先修课,优先健康/体育/运动科学背景</t>
         </is>
       </c>
-      <c r="H224" s="22" t="n"/>
+      <c r="H224" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 第三方(Peterson's):秋季国内 7/30、国际生 5/15;春季国内 12/1、国际生 10/15;官网未查到项目专门日期,建议确认</t>
+        </is>
+      </c>
       <c r="I224" s="31" t="inlineStr">
         <is>
           <t>不需要</t>
@@ -14769,9 +15605,9 @@
           <t>不需要:MPH经SOPHAS按项目整体录取;GA多由教师科研经费资助,无正式申请流程,录取后可主动联系有经费的教师</t>
         </is>
       </c>
-      <c r="G225" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="G225" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(国际生可申请GA,但学院GA名额有限,多来自教师科研项目或其他院系)。先修:学士学位;经SOPHAS申请,需目的陈述、简历/CV、3位推荐人、成绩单;官网未查到具体先修课及最低GPA要求</t>
         </is>
       </c>
       <c r="H225" s="31" t="inlineStr">
@@ -14846,7 +15682,11 @@
           <t>不需要(学院明确MPH/MS不要求GRE,仅PhD需要)</t>
         </is>
       </c>
-      <c r="J226" s="22" t="n"/>
+      <c r="J226" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:学院页提供英语要求豁免申请表,但未查到明文豁免美国学位;如不豁免需TOEFL ≥79,IELTS ≥6.5,PTE ≥58 或 DET ≥110</t>
+        </is>
+      </c>
       <c r="K226" s="31" t="inlineStr">
         <is>
           <t>publichealth@kent.edu(公共卫生学院总邮箱);⚠️ kbaker80@kent.edu(研究生项目助理协调员,目录信息待核实)</t>
@@ -14894,7 +15734,11 @@
           <t>可以申请(一年级主要靠Graduate Tuition Scholarship,GA仅二年级且极少)。认证学士,GPA≥2.7(3.0优先考虑);无具体先修课。需简历、≤1500字目的陈述、成绩单、⚠️ 3封推荐信。不再使用SOPHAS,走校内申请系统</t>
         </is>
       </c>
-      <c r="H227" s="22" t="n"/>
+      <c r="H227" s="31" t="inlineStr">
+        <is>
+          <t>奖学金考虑截止 2/1;之后滚动审核;⚠️ 最终截止日官网未查到,学校国际生秋季建议截止 6/30</t>
+        </is>
+      </c>
       <c r="I227" s="31" t="inlineStr">
         <is>
           <t>可选</t>
@@ -15076,7 +15920,11 @@
           <t>可以申请。先修因项目而异:多数ScM/MHS不要求工作经验;MSPH Health Systems偏好生物/健康科学或管理/社科背景;MPH需2年全职健康相关工作经验(不在本行项目内);需经SOPHAS申请</t>
         </is>
       </c>
-      <c r="H230" s="22" t="n"/>
+      <c r="H230" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 各系截止不同,2027-28官方表未查到;2026周期参考:ScM Biostat 2025/12/1、MSPH IH 1/15、MHS PFRH/MSPH HBS 2026/3/1;MSPH need-based奖学金需 3/1 前交齐+CSS Profile(按2026周期,2027待公布)</t>
+        </is>
+      </c>
       <c r="I230" s="31" t="inlineStr">
         <is>
           <t>可选</t>
@@ -15201,7 +16049,11 @@
           <t>⚠️ 优先(奖学金)12/15;常规 2/15;之后视名额滚动审核至 5/1(按往年日期,2027周期预计 2026/12/15、2027/2/15,待确认)</t>
         </is>
       </c>
-      <c r="I232" s="22" t="n"/>
+      <c r="I232" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到MPH明确政策(范德堡研究生院整体不要求GRE),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J232" s="31" t="inlineStr">
         <is>
           <t>否(MPH招生页:在英语授课院校完成学位者免TOEFL/IELTS);注:研究生院总政策更严,建议确认</t>
@@ -15316,7 +16168,11 @@
           <t>可以申请(GA有限且竞争激烈,学费通常需自付)。注:USU该方向现为MPH(Health Education &amp; Promotion)。先修:任意认证本科专业;录取GPA≥3.0(按最后60学期学分计);3封推荐信、SOP、申请费$55</t>
         </is>
       </c>
-      <c r="H234" s="22" t="n"/>
+      <c r="H234" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 学院研究生页:MA/MEd/MS 秋季 4/1(同页另有 All Programs 7/1,存在冲突);MPH专项截止官网未查到,建议邮件确认</t>
+        </is>
+      </c>
       <c r="I234" s="31" t="inlineStr">
         <is>
           <t>不需要(不要求GRE/MAT等入学考试)</t>
@@ -15451,7 +16307,11 @@
           <t>⚠️ 否(ECU研究生院相关页面:本科来自美国院校可免英语要求);否则TOEFL ≥80/IELTS ≥6.5</t>
         </is>
       </c>
-      <c r="K236" s="22" t="n"/>
+      <c r="K236" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ wallenm@ecu.edu(系主任Michele Wallen,曾任项目协调员;现任协调员未查到)</t>
+        </is>
+      </c>
       <c r="L236" s="22" t="inlineStr">
         <is>
           <t>https://gradschool.ecu.edu/assistantships/</t>
@@ -15504,7 +16364,11 @@
           <t>不需要</t>
         </is>
       </c>
-      <c r="J237" s="22" t="n"/>
+      <c r="J237" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:国际生需提交英语能力证明,具体分数及美国学位豁免官网未查到(第三方称TOEFL ≥61),建议邮件确认</t>
+        </is>
+      </c>
       <c r="K237" s="31" t="inlineStr">
         <is>
           <t>carothers@marshall.edu(研究生招生专员Kelly Carothers);brandm@marshall.edu(研究生事务主任)</t>
@@ -15629,7 +16493,11 @@
           <t>否(规定:英语授课学习满4年可免;美本四年应可豁免,⚠️未写明最低分)</t>
         </is>
       </c>
-      <c r="K239" s="22" t="n"/>
+      <c r="K239" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(可通过 globalhealth.nd.edu 或 Notre Dame Graduate School 询问)</t>
+        </is>
+      </c>
       <c r="L239" s="22" t="inlineStr">
         <is>
           <t>https://globalhealth.nd.edu/education-training/masters/admissions/tuition-and-fees/</t>
@@ -15677,15 +16545,81 @@
 Brown: 不需要:按项目整体录取(SOPHAS);Health Equity Scholars含有偿RA,无需提前联系导师</t>
         </is>
       </c>
-      <c r="G240" s="22" t="inlineStr">
-        <is>
-          <t>UTK/UAB 明文国际生可(有条件)</t>
-        </is>
-      </c>
-      <c r="H240" s="22" t="n"/>
-      <c r="I240" s="22" t="n"/>
-      <c r="J240" s="22" t="n"/>
-      <c r="K240" s="22" t="n"/>
+      <c r="G240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: 可以申请。任何本科专业均可,无指定先修课;本科GPA≥2.75(建议3.0)。SOPHAS申请(含写作样本、3封推荐信),录取后另交UK研究生院补充申请。资助有限
+UT Knoxville: 可以申请(原备注:明文国际生可,有条件;MPH助教名额少、优先博士生,需每年申请,国际生获GTA须通过OPIC口语测试)。本科GPA≥3.0,优先有1年健康相关工作经验;研究生院申请+MPH补充申请
+U Memphis: 可以申请。本科GPA≥3.0或专业GPA≥3.5;3封推荐信、简历;国际申请者目的陈述750-1000词;未列指定先修课
+UNCG: 可以申请。无GPA最低线,综合评估(GPA、相关工作/志愿经历、推荐信);GA名额有限,需申请时勾选意向并于2/1前交齐材料
+UW Global Health: 可以申请。各专业背景均可,需有全球卫生相关工作/志愿经历;须满足UW研究生院最低要求;国际生需证明第一年资金;仅秋季入学
+East Texas A&amp;M: 可以申请,但⚠️ 项目页称全在线/混合授课(另有Dallas校区面授),F-1需确认面授选项。本科GPA≥3.0,任何专业均可;42学分
+Mississippi State: ⚠️ 可以申请(推测)。研究生院通用要求:目的陈述、3封推荐信、成绩单;⚠️第三方称GPA≥2.7;MPH仅校园授课。项目页未查到,建议邮件确认
+UAB: 可以申请(原备注:明文国际生可,有条件)。本科GPA偏好≥3.0(较低者可凭其他条件);国际生仅秋季入学;SOPHAS+UAB研究生院补充申请
+Michigan State: 可以申请。⚠️ 先修课/最低GPA官网未查到;SOPHAS+MSU补充申请,滚动录取
+Texas A&amp;M: 可以申请,但原备注:通常不给入学硕士资助。需美国学士或同等学位;流行病学GPA≥3.0、健康行为≥2.75;3封推荐信(建议1学术+1专业)、目的陈述、简历
+Brown: 可以申请。未列专业/先修限制;⚠️ 无国际生专项奖学金,主要资助为Health Equity Scholars(最高全额学费+有偿RA,竞争性),国际生多需自筹或外部资助</t>
+        </is>
+      </c>
+      <c r="H240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: 校园MPH最终 2026/4/1(国际生同)(按2026周期,2027待公布);⚠️第三方列 2027/4/1 或 4/15
+UT Knoxville: 国内秋季 4/1(严格执行);国际生按研究生院国际截止表(⚠️ 具体日期官网未查到,建议3月前提交);GA通知约4月底
+U Memphis: 国际生秋季 5/15;国内秋季 7/15
+UNCG: 滚动录取;GA/奖学金优先 2027/2/1;最佳考虑 2027/3/1
+UW Global Health: 2026/12/7(部分页面写12/1,建议12/1前提交);仅秋季入学,2月中旬发结果
+East Texas A&amp;M: 国际生秋季 5/15(春季 10/15);国内未列截止
+Mississippi State: 国内2027秋季申请窗口 2026/8/2–2027/8/1;⚠️ 国际生截止官网未查到,建议邮件确认
+UAB: 国际生秋季 4/1;国内 7/1(按学院通用日程,各方向可能不同)
+Michigan State: 滚动录取;MSU补充申请秋季 6/1,SOPHAS须提前10天;国际生建议提前4个月提交(约2/1前)
+Texas A&amp;M: 国际生 4/15;国内 6/1(按2026周期,2027待公布);⚠️第三方列 2027/4/15
+Brown: 优先 2026/12/1;最终 2027/1/15</t>
+        </is>
+      </c>
+      <c r="I240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: 可选(test-optional)
+UT Knoxville: 不需要(系FAQ明确;旧版目录写必需,已过时)
+U Memphis: 不需要
+UNCG: ⚠️ 官网未查到,建议邮件确认(第三方旧信息称录取者常≥300)
+UW Global Health: 不需要(GRE不予考虑)
+East Texas A&amp;M: ⚠️ 不需要(项目页未列GRE要求)
+Mississippi State: ⚠️ 官网未查到,建议邮件确认
+UAB: 不需要(GPA&lt;3.0且相关经验&lt;5年者强烈建议提交)
+Michigan State: 不需要(No GRE)
+Texas A&amp;M: 不需要(GRE Verbal≥153可作英语证明)
+Brown: 不需要(仅生物统计PhD需要)</t>
+        </is>
+      </c>
+      <c r="J240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: ⚠️ 不明确:非母语者需TOEFL≥79/IELTS≥6.5/DET≥115;2022版清单称美国学位可豁免,现页面未见,建议确认
+UT Knoxville: 否(美国学位豁免:研究生院规定以英语授课院校学位可豁免,需上传已授位成绩单);否则TOEFL≥80/IELTS≥6.5/DET≥120;当GTA需通过OPIC口语测试
+U Memphis: ⚠️ 不明确:非母语者需TOEFL/IELTS/DET(SOPHAS代码6980),未见美国学位豁免说明;⚠️第三方最低TOEFL 80/IELTS 6.5
+UNCG: ⚠️ 不明确:非母语者需TOEFL或IELTS,未见美国学位豁免说明;⚠️第三方TOEFL≥79/IELTS≥6.5
+UW Global Health: 否(美国学位豁免:UW研究生院对美国区域认证学士及以上豁免);否则TOEFL≥80(新制≥4.0)/IELTS≥6.5/DET≥110
+East Texas A&amp;M: 否(美国学位豁免:持美国区域认证学士及以上可豁免);否则TOEFL≥79/IELTS≥6.0/PTE≥53/DET≥105
+Mississippi State: ⚠️ 不明确:官网未查到;⚠️第三方TOEFL≥79/IELTS≥6.5
+UAB: ⚠️ 不明确:国际申请者需TOEFL≥80/IELTS≥6.5/DET≥120,未见美国学位豁免说明,建议邮件确认
+Michigan State: ⚠️ 不明确:国际申请者需提交英语成绩,未见最低分及美国学位豁免说明
+Texas A&amp;M: ⚠️ 不明确:国际生需TOEFL≥95/IELTS≥7.0(或GRE Verbal≥153);学院页仅列英语国家公民豁免,美国学位是否豁免需确认
+Brown: 否(美国学位豁免:在英语为唯一授课语言院校获学位者免考);否则TOEFL≥90(旧制)/新制5.5,IELTS≥7.0</t>
+        </is>
+      </c>
+      <c r="K240" s="31" t="inlineStr">
+        <is>
+          <t>U Kentucky: ukcph@uky.edu(公共卫生学院招生)
+UT Knoxville: publichealth@utk.edu(公共卫生系)
+U Memphis: sphadmissions@memphis.edu(招生协调员 Briana McNeil)
+UNCG: jjmilroy@uncg.edu(研究生项目主任 Jeffrey Milroy)
+UW Global Health: ghprog@uw.edu(全球卫生系MPH项目)
+East Texas A&amp;M: ⚠️ 项目主任 Elizabeth Wachira(邮箱未查到),系电话 903.886.5549;⚠️ graduate.school@etamu.edu(研究生院,第三方来源)
+Mississippi State: ⚠️ gradapps@grad.msstate.edu(研究生院;MPH协调员邮箱未查到)
+UAB: soph@uab.edu(公共卫生学院)
+Michigan State: CHM.MPH_GenInfo@msu.edu(MPH招生咨询);chm.mph_admissions@msu.edu(申请状态,旧页面)
+Texas A&amp;M: sph-gradinfo@tamu.edu(公共卫生学院研究生招生)
+Brown: sph-admissions@brown.edu(公共卫生学院招生)</t>
+        </is>
+      </c>
       <c r="L240" s="31" t="inlineStr">
         <is>
           <t>U Kentucky: https://cph.uky.edu/programs/master-public-health/apply
@@ -15738,7 +16672,11 @@
           <t>可以申请(资金有限,有经费时才资助)。先修:官网未列具体课程;需2分钟视频、≤2页目的陈述、3封推荐信直接寄系;不接受有条件录取</t>
         </is>
       </c>
-      <c r="H241" s="22" t="n"/>
+      <c r="H241" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到具体截止日;申请系统每年8/1开放(2027秋季已开放),建议12月前提交并邮件确认</t>
+        </is>
+      </c>
       <c r="I241" s="31" t="inlineStr">
         <is>
           <t>不需要</t>
@@ -16106,14 +17044,26 @@
           <t>可以申请(校级TA/RA/fellowship明确对国际生开放)。先修:区域认证学士学位;GPA ≥3.0正式录取,2.5–2.9可条件录取;需叙述性个人陈述+3封推荐信</t>
         </is>
       </c>
-      <c r="H247" s="22" t="n"/>
+      <c r="H247" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 秋季:国际生 4/1;本国生 5/1或7/1(第三方来源不一致);奖学金/资助 5/1(第三方);官网截止日未查到</t>
+        </is>
+      </c>
       <c r="I247" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不明确:Peterson's列GRE为部分申请者需提交,另有第三方称不需要,建议邮件确认</t>
         </is>
       </c>
-      <c r="J247" s="22" t="n"/>
-      <c r="K247" s="22" t="n"/>
+      <c r="J247" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:第三方列 TOEFL iBT ≥70(PBT 550)/IELTS ≥6/Duolingo ≥115;是否豁免美国学位官网未查到</t>
+        </is>
+      </c>
+      <c r="K247" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到(搜索配额用尽),建议邮件确认(可通过 School of Graduate Studies 联系)</t>
+        </is>
+      </c>
       <c r="L247" s="22" t="inlineStr">
         <is>
           <t>https://www.morgan.edu/grad-city-and-regional-planning</t>
@@ -16233,7 +17183,11 @@
           <t>否(UB研究生院对在美国获得学位且未中断学业者通常自动豁免;⚠️MUP页未明写,建议确认);否则 ⚠️TOEFL ≥79,IELTS ≥6.5</t>
         </is>
       </c>
-      <c r="K249" s="22" t="n"/>
+      <c r="K249" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议通过 archplan.buffalo.edu MUP招生页联系或邮件确认</t>
+        </is>
+      </c>
       <c r="L249" s="22" t="inlineStr">
         <is>
           <t>https://archplan.buffalo.edu/academics/related/fellowshipsscholarships.html</t>
@@ -16286,7 +17240,11 @@
           <t>不需要(系FAQ);但 MRP/MPPA 双学位需GRE</t>
         </is>
       </c>
-      <c r="J250" s="22" t="n"/>
+      <c r="J250" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院有豁免条件但未查到美国本科学位是否适用(部分系明确美国学位可免);要求 TOEFL ≥80(2026/1后新制≥4),IELTS ≥6.5,Duolingo ≥115</t>
+        </is>
+      </c>
       <c r="K250" s="31" t="inlineStr">
         <is>
           <t>teisenman@umass.edu(MRP项目主任 Theodore Eisenman,⚠️由目录"[at]"格式推断);系电话 413-545-2255</t>
@@ -16535,7 +17493,11 @@
           <t>否(美国学位豁免:在美国获认证学士及以上学位的非美国公民可免语言成绩);否则 TOEFL 79 / IELTS 6.5 / Duolingo 100,成绩2年内有效</t>
         </is>
       </c>
-      <c r="K254" s="22" t="n"/>
+      <c r="K254" s="31" t="inlineStr">
+        <is>
+          <t>urbanplanning@utsa.edu(城市规划项目邮箱);⚠️ 研究生顾问 Sarah Serpas(邮箱官网未查到)</t>
+        </is>
+      </c>
       <c r="L254" s="22" t="inlineStr">
         <is>
           <t>https://future.utsa.edu/programs/master/urban-regional-planning/</t>
@@ -16578,8 +17540,16 @@
           <t>可以申请(仅校级GA池)。先修:美国区域认证学士学位,专业不限;⚠️ 第三方称最低GPA 3.0,需两页目的陈述、简历、写作样本(部分来源称另需3封推荐信);45学分,PAB认证</t>
         </is>
       </c>
-      <c r="H255" s="22" t="n"/>
-      <c r="I255" s="22" t="n"/>
+      <c r="H255" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到:第三方Peterson's称秋季国际生 6/1、国内 7/1(滚动审理);Mastersportal称2027秋季 3/15;建议 2027/3/15 前提交以争取GA</t>
+        </is>
+      </c>
+      <c r="I255" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到;第三方冲突(Peterson's/Mastersportal称必需,Yocket称可选),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J255" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免:持美国认证学士/硕士学位可豁免);否则 IELTS 6.5 / PTE 58 / Duolingo 105 / TOEFL 79(旧版)</t>
@@ -16761,7 +17731,11 @@
           <t>优先截止:国际生 2026/12/1,美国居民 2027/1/15(17:00 MST);4/1前为第二轮;4/1后视名额;想拿GA须赶优先截止</t>
         </is>
       </c>
-      <c r="I258" s="22" t="n"/>
+      <c r="I258" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到MCRP的GRE要求(同学院建筑项目不要求),建议邮件确认</t>
+        </is>
+      </c>
       <c r="J258" s="31" t="inlineStr">
         <is>
           <t>否(美国学位豁免:UNM国际招生页列明美国区域认证学士学位豁免,申请时自动审核);否则 TOEFL iBT 79</t>
@@ -16812,9 +17786,12 @@
 U Minnesota: 不需要:MPH 按项目整体录取(SOPHAS)</t>
         </is>
       </c>
-      <c r="G259" s="22" t="inlineStr">
-        <is>
-          <t>❌ USF/UAB 明文仅美籍/PR(HRSA)</t>
+      <c r="G259" s="31" t="inlineStr">
+        <is>
+          <t>USF: 可以申请,但❌ MCH Scholars(HRSA/Title V 资助)明文仅限美籍/PR。先修:无指定先修课;须满足大学及英语要求
+UAB: 可以申请,但❌ HRSA MCH 学员资助限美籍/国民/PR/合格外籍。先修:满足 MPH 通用要求,无专门先修;国际生需等同美国 4 年学士
+SLU: 可以申请(⚠️ 国际生资助未查到)。MCH 现为 12 学分证书,可叠加在 MPH 上;学士 GPA 3.0 优先,整体审核,3 封推荐信+CV+目标陈述
+U Minnesota: 可以申请(12/1 前申请可参评学院奖学金,国际新生资助有限)。先修:GPA 约 3.0 优先;相关工作/志愿经历优先非必需</t>
         </is>
       </c>
       <c r="H259" s="31" t="inlineStr">
@@ -16833,8 +17810,22 @@
 U Minnesota: 不需要(全院学位均不要求)</t>
         </is>
       </c>
-      <c r="J259" s="22" t="n"/>
-      <c r="K259" s="22" t="n"/>
+      <c r="J259" s="31" t="inlineStr">
+        <is>
+          <t>USF: ⚠️ 不明确:需满足 USF 英语要求(TOEFL ≥79/IELTS ≥6.5),美国学位是否豁免未查到,建议确认
+UAB: 否(美国学士及以上学位且 GPA≥3.0 可豁免);否则 TOEFL ≥80/IELTS ≥6.5/DET ≥120
+SLU: ⚠️ 不明确:第三方称 TOEFL ≥80/IELTS ≥6.5,美国学位豁免未查证
+U Minnesota: ⚠️ 大概率否:入学前 24 个月内在美国认证英语授课院校修满 16 学期学分可豁免(需 WES ICAP 验证);否则 TOEFL ≥100(新版≥5)/IELTS ≥7.0</t>
+        </is>
+      </c>
+      <c r="K259" s="31" t="inlineStr">
+        <is>
+          <t>USF: ⚠️ 官网未查到,建议邮件确认(公卫学院研究生招生)
+UAB: ⚠️ mslay@uab.edu(Martha Wingate,MCH 项目联系人,来源可能过时);maltima@uab.edu(MCH DrPH 项目协调员)
+SLU: cphsjgrad@slu.edu(公卫学院研究生招生)
+U Minnesota: sph-admissions@umn.edu(SPH 招生);zbonilla@umn.edu(MCH 项目主任 Zobeida Bonilla)</t>
+        </is>
+      </c>
       <c r="L259" s="31" t="inlineStr">
         <is>
           <t>USF: https://health.usf.edu/publichealth/apply/masters/mph-mch
@@ -17019,7 +18010,11 @@
           <t>否(美国学位豁免:持美国区域认证学士及以上学位,收到成绩单后豁免);否则 TOEFL 79 / IELTS 6.5</t>
         </is>
       </c>
-      <c r="K262" s="22" t="n"/>
+      <c r="K262" s="31" t="inlineStr">
+        <is>
+          <t>graduateadmissions@augusta.edu(研究生院招生办;项目主任邮箱官网未查到)</t>
+        </is>
+      </c>
       <c r="L262" s="22" t="inlineStr">
         <is>
           <t>https://www.augusta.edu/pamplin/psychology/graduate.php</t>
@@ -17186,7 +18181,11 @@
           <t>可以申请(GTA名额有限,州外学费减免仅第一年且只降到州内)。先修:期望心理学专业且心理学GPA≥3.0;非心理专业需≥21学分心理学课(含研究方法与统计,研究方法须为心理学课);总GPA≥3.0;3封推荐信(至少1封来自教授)、陈述、CV;只能申请一个方向</t>
         </is>
       </c>
-      <c r="H265" s="22" t="n"/>
+      <c r="H265" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到具体日期:每年仅秋季入学,官网强调优先截止日,入围者1月下旬面试(优先截止应在12月–1月初);第三方(Peterson's)列 3/15,建议12月前提交并邮件确认</t>
+        </is>
+      </c>
       <c r="I265" s="31" t="inlineStr">
         <is>
           <t>不需要(官网FAQ:目前不考虑GRE)</t>
@@ -17197,7 +18196,11 @@
           <t>否(美国学位豁免:UNCW研究生院认可美国认证院校学士学位免语言成绩;否则 TOEFL ≥79)</t>
         </is>
       </c>
-      <c r="K265" s="22" t="n"/>
+      <c r="K265" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到,建议邮件确认(项目页 Prospective Students &gt; Admission Timeline 有联系方式)</t>
+        </is>
+      </c>
       <c r="L265" s="22" t="inlineStr">
         <is>
           <t>https://uncw.edu/academics/majors-programs/cse/psychology-ms/details/prospective-students/financial-support</t>
@@ -17250,7 +18253,11 @@
           <t>⚠️ 可能不需要:HFES目录称 Fall 2023 起免GRE,官网目录未见GRE要求,建议确认</t>
         </is>
       </c>
-      <c r="J266" s="22" t="n"/>
+      <c r="J266" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:USD国际研究生页要求 TOEFL ≥79 / IELTS ≥6.0 / Duolingo ≥110;豁免名单列英语国家学位及母语者,未查到美国学位豁免明文,建议确认</t>
+        </is>
+      </c>
       <c r="K266" s="31" t="inlineStr">
         <is>
           <t>⚠️ Michael.Granaas@usd.edu(HFES目录所列项目联系人,可能过时);心理系电话 605-658-6140</t>
@@ -17360,14 +18367,26 @@
           <t>可以申请(仅校级GA,每周≤20小时)。先修(2025–26目录):本科最后60学分GPA≥3.0;统计和/或研究方法本科课成绩B以上;3封推荐信;500词目标陈述;CV。论文型项目,共36学分,为读博做准备</t>
         </is>
       </c>
-      <c r="H268" s="22" t="n"/>
+      <c r="H268" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到具体日期(见 utrgv.edu/gradapply);第三方(Peterson's,旧UTPA)列秋季 3/31;国际生成绩单材料要求更早。建议 2027/3 前提交并确认</t>
+        </is>
+      </c>
       <c r="I268" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要:2025–26目录未列GRE(旧目录曾要求 V153/Q144),建议确认</t>
         </is>
       </c>
-      <c r="J268" s="22" t="n"/>
-      <c r="K268" s="22" t="n"/>
+      <c r="J268" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:研究生院要求 IELTS ≥6.5 等;未查到美国学位豁免条款,建议确认</t>
+        </is>
+      </c>
+      <c r="K268" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到项目邮箱,建议通过心理科学系页面或 utrgv.edu/gradapply 联系研究生院确认</t>
+        </is>
+      </c>
       <c r="L268" s="22" t="inlineStr">
         <is>
           <t>https://www.utrgv.edu/admissions/graduate/funding/index.htm</t>
@@ -17658,7 +18677,11 @@
           <t>可以申请(有限GRA/GTA,含学费+州外减免)。先修:认证院校林学、野生动物、渔业或其他自然资源相关本科;⚠️第三方列GPA≥2.7;野生动物与渔业项目需同时提交系内申请表</t>
         </is>
       </c>
-      <c r="H273" s="22" t="n"/>
+      <c r="H273" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到;第三方(Peterson's)列秋季 2/1(野生动物与渔业为优先日),建议邮件确认</t>
+        </is>
+      </c>
       <c r="I273" s="31" t="inlineStr">
         <is>
           <t>可选(推荐但非必需;部分导师看重GRE,建议问意向导师)</t>
@@ -17716,7 +18739,11 @@
           <t>可以申请(国际生可获有限GA,需与导师商定)。先修:UF最低要求大三大四GPA≥3.0;未列具体先修课;另交$30申请费及全部成绩单</t>
         </is>
       </c>
-      <c r="H274" s="22" t="n"/>
+      <c r="H274" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 系官网未查到;UF截止日由各系自定(其他学院页面列秋季优先约1/5),建议邮件确认</t>
+        </is>
+      </c>
       <c r="I274" s="31" t="inlineStr">
         <is>
           <t>⚠️ 不需要(UF多数系已免GRE,FFGS未单独说明)</t>
@@ -17774,7 +18801,11 @@
           <t>可以申请(有若干GTA/GRA,金额未列)。先修:Park Mgmt方向优先生命科学或自然资源本科,但非必须;最后两年GPA≥3.0;3封推荐信+学术目标陈述</t>
         </is>
       </c>
-      <c r="H275" s="22" t="n"/>
+      <c r="H275" s="31" t="inlineStr">
+        <is>
+          <t>滚动录取(全年受理,秋/春/夏均可入学);⚠️ 具体日期未查到,建议尽早(如2027年初前)提交以争取GTA/GRA</t>
+        </is>
+      </c>
       <c r="I275" s="31" t="inlineStr">
         <is>
           <t>不需要</t>
@@ -18199,9 +19230,9 @@
           <t>不需要:按项目整体录取;资助(GRA)询问研究生项目主任</t>
         </is>
       </c>
-      <c r="G282" s="22" t="inlineStr">
-        <is>
-          <t>未说明</t>
+      <c r="G282" s="31" t="inlineStr">
+        <is>
+          <t>可以申请。先修:学士学位,本科总GPA≥2.7(研究生院基本要求);需个人陈述及推荐信;⚠️ 未查到指定先修课</t>
         </is>
       </c>
       <c r="H282" s="31" t="inlineStr">
@@ -18338,7 +19369,11 @@
           <t>不需要(系官网:GRE不要求)</t>
         </is>
       </c>
-      <c r="J284" s="22" t="n"/>
+      <c r="J284" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 不明确:Toulouse Graduate School 对美国学位豁免的规定未查到,建议邮件 graduateschool@unt.edu 确认</t>
+        </is>
+      </c>
       <c r="K284" s="31" t="inlineStr">
         <is>
           <t>William.Scarborough@unt.edu(研究生项目主任);sociology@unt.edu(系办公室)</t>
@@ -18381,9 +19416,9 @@
           <t>不需要:按项目整体录取;GA名额少,可向研究生项目主任询问</t>
         </is>
       </c>
-      <c r="G285" s="22" t="inlineStr">
-        <is>
-          <t>可(部分)</t>
+      <c r="G285" s="31" t="inlineStr">
+        <is>
+          <t>可以申请,但GA名额很少,国际生持GA仍需自付约$17,500/年州外学费差额。先修:⚠️ 官网未查到具体先修课/最低GPA,建议邮件确认</t>
         </is>
       </c>
       <c r="H285" s="31" t="inlineStr">
@@ -18463,7 +19498,11 @@
           <t>⚠️ 不明确:原要求非母语国际生 TOEFL 550(纸考)等,未写美国学位豁免;项目已停招</t>
         </is>
       </c>
-      <c r="K286" s="22" t="n"/>
+      <c r="K286" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 官网未查到;项目已停招,建议向ODU研究生招生办确认</t>
+        </is>
+      </c>
       <c r="L286" s="22" t="inlineStr">
         <is>
           <t>https://www.odu.edu/sociology/academics/graduate/assistantship</t>
@@ -18501,9 +19540,9 @@
           <t>不需要:但个人陈述(250–500字)需写明与系研究方向相关的兴趣及想合作的教师</t>
         </is>
       </c>
-      <c r="G287" s="22" t="inlineStr">
-        <is>
-          <t>可申请</t>
+      <c r="G287" s="31" t="inlineStr">
+        <is>
+          <t>可以申请(系GA主要给博士生,MA资助有限)。先修:学士学位;需3封推荐信(≥2封学术)、个人陈述、简历;⚠️ 未查到指定先修课/最低GPA</t>
         </is>
       </c>
       <c r="H287" s="31" t="inlineStr">
@@ -18568,7 +19607,11 @@
           <t>可以申请(有国际生专项奖 International Chancellor's Scholarship)。⚠️ 先修(按2023-2025目录):社会科学或相关专业本科,GPA≥3.3(录取者通常≥3.5);统计和研究方法课程成绩优秀;材料:成绩单、CV、3封推荐信</t>
         </is>
       </c>
-      <c r="H288" s="22" t="n"/>
+      <c r="H288" s="31" t="inlineStr">
+        <is>
+          <t>⚠️ 资助申请者及国际生 2027/3/1(按2023-2025目录,2027待公布);不申请资助的国内生截止日未查到</t>
+        </is>
+      </c>
       <c r="I288" s="31" t="inlineStr">
         <is>
           <t>⚠️ 目录未提GRE,可能不需要,建议确认</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J85" s="30" t="inlineStr">
         <is>
-          <t>⚠️ 不明确:Epidemiology 系要求国际生 TOEFL iBT ≥100;是否豁免美国学位未查到官方说明(本批检索额度耗尽,未能核实),建议邮件确认;当 GSI 需另行英语口语评估(⚠️)</t>
+          <t>⚠️ 很可能否:SPH 招生页列出“本科在纯英语授课院校完成”即可豁免英语成绩,Biostat FAQ 也明确美国学位可豁免;不豁免时 Epidemiology 要求 TOEFL iBT ≥100 / IELTS ≥7.0,建议邮件确认;当 GSI 需另行英语口语评估</t>
         </is>
       </c>
       <c r="K85" s="30" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="J94" s="30" t="inlineStr">
         <is>
-          <t>⚠️ 不明确:Epidemiology 系要求国际生 TOEFL iBT ≥100;是否豁免美国学位未查到官方说明(本批检索额度耗尽,未能核实),建议邮件确认;当 GSI 需另行英语口语评估(⚠️)</t>
+          <t>⚠️ 很可能否:SPH 招生页列出“本科在纯英语授课院校完成”即可豁免英语成绩,Biostat FAQ 也明确美国学位可豁免;不豁免时 Epidemiology 要求 TOEFL iBT ≥100 / IELTS ≥7.0,建议邮件确认;当 GSI 需另行英语口语评估</t>
         </is>
       </c>
       <c r="K94" s="30" t="inlineStr">
@@ -10833,7 +10833,11 @@
           <t>否(美国区域认证学士学位豁免);否则 TOEFL iBT ≥78(2026/1/21前考试的标准,新分制下要求待确认)</t>
         </is>
       </c>
-      <c r="K149" s="21" t="n"/>
+      <c r="K149" s="30" t="inlineStr">
+        <is>
+          <t>psychology-masters@txstate.edu(MAPR 项目邮箱);warnell@txstate.edu(Dr. Kate Warnell,研究生项目主任)</t>
+        </is>
+      </c>
       <c r="L149" s="21" t="inlineStr">
         <is>
           <t>https://www.psych.txst.edu/graduate/funding-assistantships.html</t>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -1372,7 +1372,8 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>https://www.hhs.k-state.edu/fshs/academics/afs/funding.html</t>
+          <t>https://catalog.k-state.edu/preview_program.php?catoid=63&amp;poid=24105
+(原 Applied Family Science 页面已下线;该方向现归入 Human Development and Family Science 硕士,最接近的在校方向是 Prevention Science,可选论文轨,协调员 Alisha Hardman)</t>
         </is>
       </c>
     </row>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -3232,17 +3232,17 @@
       </c>
       <c r="F32" s="26" t="inlineStr">
         <is>
-          <t>强烈建议:官网称联系潜在导师是关键步骤,录取看 merit 与教师研究匹配</t>
+          <t>必须(实质上):系里只录取有具体教师愿意支持并担任第一年导师的申请者。官网强烈建议申请前先给研究方向相近的教师或研究生项目主任发邮件,附简历并问是否招新生</t>
         </is>
       </c>
       <c r="G32" s="26" t="inlineStr">
         <is>
-          <t>可以申请(原备注:未说明)。先修:⚠️ 未查到指定专业/先修课/最低GPA;需个人陈述(写明意向教师)、个人经历陈述(≤1页)、3封推荐信</t>
+          <t>可以申请,但⚠️ 系里以 PhD 为主,只读 MA 的申请者官网要求先与潜在导师商量再递交。先修:⚠️ 未查到指定专业/先修课/最低GPA;需目的陈述(写明意向教师及为何选 UNC)、个人经历陈述、3封推荐信</t>
         </is>
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
-          <t>研究生院资助/fellowship 2026/12/12;系资助 2027/1/10(按往年周期,2027待公布)</t>
+          <t>2027 秋季入学截止 2026/12/15(系官网);研究生院 fellowship 考虑也以此为准,建议提前</t>
         </is>
       </c>
       <c r="I32" s="26" t="inlineStr">
@@ -3252,17 +3252,18 @@
       </c>
       <c r="J32" s="26" t="inlineStr">
         <is>
-          <t>⚠️ 不明确:国际生需 TOEFL/IELTS,未查到美国学位豁免条款,建议向研究生院确认</t>
+          <t>否(美国学位豁免:研究生院规定持有或即将获得美国认证大学学位者免交 TOEFL/IELTS/Duolingo,需在申请中上传显示学位的非正式成绩单或注册处证明;若最终未获学位则须补交成绩)</t>
         </is>
       </c>
       <c r="K32" s="26" t="inlineStr">
         <is>
-          <t>⚠️ 官网未查到邮箱;旧页列招生主任 Clark Gray、研究生协调员 Nell Phillips,系电话 919-962-8902</t>
+          <t>diegori@unc.edu(研究生项目主任 Dr. Diego Riveros-Iregui);nphillip@email.unc.edu(研究生协调员 Nell Phillips,⚠️ 来自旧页面);系电话 919-962-8902</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>https://geography.unc.edu/wp-content/uploads/sites/140/2026/05/GEOGGraduateHandbook.pdf</t>
+          <t>https://geography.unc.edu/graduate-program/prospective-students/
+申请步骤页:https://geography.unc.edu/graduate-program/prospective-students/applications/</t>
         </is>
       </c>
     </row>

--- a/全奖硕士-已补全.xlsx
+++ b/全奖硕士-已补全.xlsx
@@ -3242,7 +3242,7 @@
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
-          <t>2027 秋季入学截止 2026/12/15(系官网);研究生院 fellowship 考虑也以此为准,建议提前</t>
+          <t>2027 秋季入学所有申请截止 2026/12/15(系官网)</t>
         </is>
       </c>
       <c r="I32" s="26" t="inlineStr">
